--- a/data/processed/dfpc_scores.xlsx
+++ b/data/processed/dfpc_scores.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -457,19 +457,19 @@
         <v>45628</v>
       </c>
       <c r="B2" t="n">
-        <v>1.613687831267181</v>
+        <v>1.958356685614624</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.4730591842856539</v>
+        <v>-0.6689449354761765</v>
       </c>
       <c r="D2" t="n">
-        <v>1.111406334240445</v>
+        <v>1.006959639280406</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1774213621170749</v>
+        <v>0.01123499808397659</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.08466631070893006</v>
+        <v>-0.2053069453823281</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         <v>45629</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5271068296924618</v>
+        <v>0.8035913285283833</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.17513052759208</v>
+        <v>-0.09198990831421196</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.02796755729781751</v>
+        <v>-0.03270931208632955</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0391029531144883</v>
+        <v>-0.128448781212516</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1447315014323429</v>
+        <v>0.1352359785177278</v>
       </c>
     </row>
     <row r="4">
@@ -497,19 +497,19 @@
         <v>45630</v>
       </c>
       <c r="B4" t="n">
-        <v>0.04428297140294399</v>
+        <v>0.4005464238988992</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06110822454274494</v>
+        <v>-0.0523761107395658</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8564229696970553</v>
+        <v>0.8802810563987422</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0691507143656092</v>
+        <v>-0.02676555487567922</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2028721794202351</v>
+        <v>0.07022039993110878</v>
       </c>
     </row>
     <row r="5">
@@ -517,19 +517,19 @@
         <v>45631</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.03758188041515609</v>
+        <v>-1.185181118257078</v>
       </c>
       <c r="C5" t="n">
-        <v>0.007789655256860969</v>
+        <v>0.1112881157872983</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1435180488456593</v>
+        <v>0.3738941526119327</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0896647341453904</v>
+        <v>-0.02587282171305294</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2130186663812746</v>
+        <v>0.1373243010906286</v>
       </c>
     </row>
     <row r="6">
@@ -537,19 +537,19 @@
         <v>45632</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.8409997867836151</v>
+        <v>-0.7367513148878663</v>
       </c>
       <c r="C6" t="n">
-        <v>1.685592975399623</v>
+        <v>1.488960176622684</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6698942922988489</v>
+        <v>0.782736864164267</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3580974655460269</v>
+        <v>0.4208334796782311</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.05548196847810721</v>
+        <v>-0.1548115321238455</v>
       </c>
     </row>
     <row r="7">
@@ -557,19 +557,19 @@
         <v>45635</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4274248179176283</v>
+        <v>0.7004580098479121</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.6507947534724765</v>
+        <v>-0.5818957181964696</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1947578772969109</v>
+        <v>0.07036429723015329</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.01732946068739183</v>
+        <v>-0.06651923923788226</v>
       </c>
       <c r="F7" t="n">
-        <v>0.217328850037266</v>
+        <v>0.2850768284013562</v>
       </c>
     </row>
     <row r="8">
@@ -577,19 +577,19 @@
         <v>45636</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.7978486420026019</v>
+        <v>-0.8067881154811281</v>
       </c>
       <c r="C8" t="n">
-        <v>0.07561918125180424</v>
+        <v>0.1381494191311005</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.03480533842809821</v>
+        <v>0.1089413939190721</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1465261691107559</v>
+        <v>-0.1120316999714104</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4446342917894389</v>
+        <v>0.2291370868375747</v>
       </c>
     </row>
     <row r="9">
@@ -597,19 +597,19 @@
         <v>45637</v>
       </c>
       <c r="B9" t="n">
-        <v>3.699080450707724</v>
+        <v>3.788000104728074</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2218336547049312</v>
+        <v>0.335829170076147</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5075831110005263</v>
+        <v>-0.4308967432513633</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1188510608303104</v>
+        <v>-0.1291341945833661</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.03246961548190708</v>
+        <v>-0.102367302656118</v>
       </c>
     </row>
     <row r="10">
@@ -617,19 +617,19 @@
         <v>45638</v>
       </c>
       <c r="B10" t="n">
-        <v>1.784869061849733</v>
+        <v>1.137669721888422</v>
       </c>
       <c r="C10" t="n">
-        <v>0.07758933117256522</v>
+        <v>-0.01109755690841314</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1434054439011343</v>
+        <v>0.2852799455624641</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1189954856168463</v>
+        <v>-0.05007235377494133</v>
       </c>
       <c r="F10" t="n">
-        <v>0.08159422852220033</v>
+        <v>-0.06749023128299085</v>
       </c>
     </row>
     <row r="11">
@@ -637,19 +637,19 @@
         <v>45639</v>
       </c>
       <c r="B11" t="n">
-        <v>-1.027456541710886</v>
+        <v>-0.8384009375313284</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3965845076344635</v>
+        <v>0.2415267141705298</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5943103705964267</v>
+        <v>0.486955526695538</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01132301992512856</v>
+        <v>0.2306997534525279</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3505135582379553</v>
+        <v>-0.3969261870541537</v>
       </c>
     </row>
     <row r="12">
@@ -657,19 +657,19 @@
         <v>45642</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.9282122710975756</v>
+        <v>-0.9591562543131644</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.646727754759054</v>
+        <v>-0.714000195623278</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01127826998326493</v>
+        <v>-0.07914537389139445</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3985202156549233</v>
+        <v>0.4013220824162444</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.276914798862734</v>
+        <v>0.2443052795916671</v>
       </c>
     </row>
     <row r="13">
@@ -677,19 +677,19 @@
         <v>45643</v>
       </c>
       <c r="B13" t="n">
-        <v>3.662327034577545</v>
+        <v>3.675703199664823</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3172250151896419</v>
+        <v>0.3104541366706348</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1808020093458691</v>
+        <v>0.1711690314571827</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2513380494569467</v>
+        <v>0.1926426073886052</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1105142849259434</v>
+        <v>0.09574193345509699</v>
       </c>
     </row>
     <row r="14">
@@ -697,19 +697,19 @@
         <v>45644</v>
       </c>
       <c r="B14" t="n">
-        <v>2.640742663378034</v>
+        <v>2.704141645799291</v>
       </c>
       <c r="C14" t="n">
-        <v>0.256209019118615</v>
+        <v>0.1855313454160554</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6890225507275356</v>
+        <v>0.7132068534684286</v>
       </c>
       <c r="E14" t="n">
-        <v>0.02984105402600238</v>
+        <v>0.2022939462518787</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0888450951931167</v>
+        <v>-0.2613992954016857</v>
       </c>
     </row>
     <row r="15">
@@ -717,19 +717,19 @@
         <v>45645</v>
       </c>
       <c r="B15" t="n">
-        <v>1.565914257590683</v>
+        <v>1.59293920888317</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.06077876475939808</v>
+        <v>-0.1530137021280542</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.06550601818894593</v>
+        <v>-0.1185930502136967</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1071635715337101</v>
+        <v>0.006957790608417502</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3151855411009079</v>
+        <v>-0.2604227902345344</v>
       </c>
     </row>
     <row r="16">
@@ -737,19 +737,19 @@
         <v>45646</v>
       </c>
       <c r="B16" t="n">
-        <v>1.529240262949892</v>
+        <v>1.66705829757284</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.1481920807207452</v>
+        <v>0.02497439237810851</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1525179088492162</v>
+        <v>-0.2707210967981196</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3547534948196447</v>
+        <v>0.09929325894470289</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2781213863244231</v>
+        <v>0.4395977683441961</v>
       </c>
     </row>
     <row r="17">
@@ -757,19 +757,19 @@
         <v>45649</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.8099444363144483</v>
+        <v>-0.5153538982007982</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4434561224769156</v>
+        <v>0.2965005737925094</v>
       </c>
       <c r="D17" t="n">
-        <v>0.228886318329164</v>
+        <v>0.1904147230348672</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1063223811576944</v>
+        <v>0.1765872085248101</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3578979192738039</v>
+        <v>-0.3379270810317909</v>
       </c>
     </row>
     <row r="18">
@@ -777,19 +777,19 @@
         <v>45652</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1789258045171365</v>
+        <v>0.156434201446434</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.4972200226316241</v>
+        <v>-0.4034782489333208</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2986654059522212</v>
+        <v>-0.3519760131175526</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5771561511773207</v>
+        <v>0.2509260690656418</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2481116402758166</v>
+        <v>0.7318422309410031</v>
       </c>
     </row>
     <row r="19">
@@ -797,19 +797,19 @@
         <v>45653</v>
       </c>
       <c r="B19" t="n">
-        <v>1.46753174708185</v>
+        <v>1.682689372286276</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.3634269245779157</v>
+        <v>-0.5151577669984192</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8938292275857578</v>
+        <v>0.6900609995663041</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4180369327823611</v>
+        <v>-0.1551177501678043</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.08108311686865438</v>
+        <v>-0.2582173660091493</v>
       </c>
     </row>
     <row r="20">
@@ -817,19 +817,19 @@
         <v>45656</v>
       </c>
       <c r="B20" t="n">
-        <v>0.2222787592545719</v>
+        <v>0.3182446870078257</v>
       </c>
       <c r="C20" t="n">
-        <v>0.938886481030095</v>
+        <v>0.8292107051129336</v>
       </c>
       <c r="D20" t="n">
-        <v>1.199346115258627</v>
+        <v>1.433302194547047</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.07282102803989214</v>
+        <v>0.214368525983533</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2867302769179642</v>
+        <v>-0.04750742793115519</v>
       </c>
     </row>
     <row r="21">
@@ -837,19 +837,19 @@
         <v>45659</v>
       </c>
       <c r="B21" t="n">
-        <v>2.056669425533372</v>
+        <v>2.261644982756497</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2282804351765048</v>
+        <v>0.1991517827327137</v>
       </c>
       <c r="D21" t="n">
-        <v>0.423411106551786</v>
+        <v>0.3558970884774415</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1161458733834819</v>
+        <v>-0.05783571107804835</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1531611059925279</v>
+        <v>-0.04393406063755148</v>
       </c>
     </row>
     <row r="22">
@@ -857,19 +857,19 @@
         <v>45660</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.4404429691094407</v>
+        <v>-0.2762625561798449</v>
       </c>
       <c r="C22" t="n">
-        <v>0.587813465515917</v>
+        <v>0.4268023586161522</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2001716121189364</v>
+        <v>0.1955815054311736</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3665379167647986</v>
+        <v>-0.09889526531096696</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6334084756961653</v>
+        <v>-0.8080297839771152</v>
       </c>
     </row>
     <row r="23">
@@ -877,19 +877,19 @@
         <v>45663</v>
       </c>
       <c r="B23" t="n">
-        <v>1.823079525277135</v>
+        <v>1.998867383387668</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1274654831101562</v>
+        <v>0.2386121481594057</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.08757463923357652</v>
+        <v>-0.08419368982315777</v>
       </c>
       <c r="E23" t="n">
-        <v>0.010622827908664</v>
+        <v>-0.1713520924007513</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3772989409715121</v>
+        <v>0.3151460420465029</v>
       </c>
     </row>
     <row r="24">
@@ -897,19 +897,19 @@
         <v>45664</v>
       </c>
       <c r="B24" t="n">
-        <v>0.5023988750768033</v>
+        <v>-0.1843844519801889</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.4729464645228242</v>
+        <v>-0.4008004537803188</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3053519868010541</v>
+        <v>-0.5271452365263206</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1821780634321712</v>
+        <v>-0.07512813831310658</v>
       </c>
       <c r="F24" t="n">
-        <v>0.304302295964389</v>
+        <v>0.4449981544749843</v>
       </c>
     </row>
     <row r="25">
@@ -917,19 +917,19 @@
         <v>45665</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.5654001446893514</v>
+        <v>-0.5386955220853565</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8771742066445336</v>
+        <v>0.8393177501635954</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1265858414881879</v>
+        <v>-0.004685384267538889</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.09353118810504013</v>
+        <v>0.2874323643573888</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.05289162689583182</v>
+        <v>0.03984215008774414</v>
       </c>
     </row>
     <row r="26">
@@ -937,19 +937,19 @@
         <v>45666</v>
       </c>
       <c r="B26" t="n">
-        <v>-2.110806339187596</v>
+        <v>-2.094832664640359</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6511708010088694</v>
+        <v>0.6216954833915764</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2447957264081468</v>
+        <v>0.4316465769552436</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1223723916523971</v>
+        <v>0.2851559284108562</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1457474871964745</v>
+        <v>-0.3033815971780771</v>
       </c>
     </row>
     <row r="27">
@@ -957,19 +957,19 @@
         <v>45667</v>
       </c>
       <c r="B27" t="n">
-        <v>0.974696272625203</v>
+        <v>1.099618410702528</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2299810877071768</v>
+        <v>0.3328237261707437</v>
       </c>
       <c r="D27" t="n">
-        <v>0.01041914211658901</v>
+        <v>0.04469840606976523</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.02403048451276136</v>
+        <v>-0.08759520528617559</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1560391425457582</v>
+        <v>0.07632967382268641</v>
       </c>
     </row>
     <row r="28">
@@ -977,19 +977,19 @@
         <v>45670</v>
       </c>
       <c r="B28" t="n">
-        <v>-0.4806877830775614</v>
+        <v>-0.4668832185390526</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.2690408684966532</v>
+        <v>-0.1437222650634651</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3700654003027928</v>
+        <v>-0.3092702438841473</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1937574634899666</v>
+        <v>0.04868333812434932</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1940552803379935</v>
+        <v>0.2676903208365754</v>
       </c>
     </row>
     <row r="29">
@@ -997,19 +997,19 @@
         <v>45671</v>
       </c>
       <c r="B29" t="n">
-        <v>2.330862353717554</v>
+        <v>2.441780347415474</v>
       </c>
       <c r="C29" t="n">
-        <v>0.04190684545682413</v>
+        <v>0.1308041538098364</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1589325035453818</v>
+        <v>0.1399371003986459</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2093091228589389</v>
+        <v>0.1289771144100338</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1029421315231183</v>
+        <v>0.1492721429071309</v>
       </c>
     </row>
     <row r="30">
@@ -1017,19 +1017,19 @@
         <v>45672</v>
       </c>
       <c r="B30" t="n">
-        <v>1.022710644096035</v>
+        <v>1.096850836250794</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3024688453323484</v>
+        <v>-0.2926413858833911</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.02557385776633505</v>
+        <v>0.004682396671152667</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2097794877027389</v>
+        <v>-0.1241872797183776</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1121744625526598</v>
+        <v>0.04564222656996915</v>
       </c>
     </row>
     <row r="31">
@@ -1037,19 +1037,19 @@
         <v>45673</v>
       </c>
       <c r="B31" t="n">
-        <v>-1.033548093829617</v>
+        <v>-0.7624912783059458</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3275784005819796</v>
+        <v>-0.3876117793426322</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3677122794870989</v>
+        <v>0.2013013269929982</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3716773597609535</v>
+        <v>0.3477423835680314</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1018168431838672</v>
+        <v>0.2186282358818374</v>
       </c>
     </row>
     <row r="32">
@@ -1057,19 +1057,19 @@
         <v>45674</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.5996953775269364</v>
+        <v>-0.793183072740931</v>
       </c>
       <c r="C32" t="n">
-        <v>-1.275864163868282</v>
+        <v>-1.468270835351477</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.05939225259145334</v>
+        <v>-0.1357366466195688</v>
       </c>
       <c r="E32" t="n">
-        <v>0.3148737718732633</v>
+        <v>-0.3373681328239043</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1304194730360853</v>
+        <v>-0.05860028280423625</v>
       </c>
     </row>
     <row r="33">
@@ -1077,19 +1077,19 @@
         <v>45677</v>
       </c>
       <c r="B33" t="n">
-        <v>0.2651862311076715</v>
+        <v>0.3239106212613694</v>
       </c>
       <c r="C33" t="n">
-        <v>-1.170053197720166</v>
+        <v>-1.092476013371869</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0327656187489001</v>
+        <v>-0.05576755761455892</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.04082949535615685</v>
+        <v>-0.03905580626631065</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4374380684288902</v>
+        <v>0.5073672760076651</v>
       </c>
     </row>
     <row r="34">
@@ -1097,19 +1097,19 @@
         <v>45678</v>
       </c>
       <c r="B34" t="n">
-        <v>-0.4178787047141035</v>
+        <v>-0.3751591033773422</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.9902151400120872</v>
+        <v>-1.19670746964222</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3075125134969647</v>
+        <v>0.09010683617692811</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.0227255169497516</v>
+        <v>0.164579128166342</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.3584314889646426</v>
+        <v>-0.04953820455415278</v>
       </c>
     </row>
     <row r="35">
@@ -1117,19 +1117,19 @@
         <v>45679</v>
       </c>
       <c r="B35" t="n">
-        <v>-0.848497174390012</v>
+        <v>-0.9040013262353958</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.8123648161068726</v>
+        <v>-0.9408635321422816</v>
       </c>
       <c r="D35" t="n">
-        <v>0.07720414441521622</v>
+        <v>0.1146856323649111</v>
       </c>
       <c r="E35" t="n">
-        <v>0.4453920785004141</v>
+        <v>-0.2697592992399717</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.08693713547930144</v>
+        <v>-0.1660266788875626</v>
       </c>
     </row>
     <row r="36">
@@ -1137,19 +1137,19 @@
         <v>45680</v>
       </c>
       <c r="B36" t="n">
-        <v>0.9709757386337249</v>
+        <v>1.177878025268143</v>
       </c>
       <c r="C36" t="n">
-        <v>0.03540241435137687</v>
+        <v>0.01972172497577101</v>
       </c>
       <c r="D36" t="n">
-        <v>0.00101450350732879</v>
+        <v>-0.1153735483662444</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2715850582150471</v>
+        <v>-0.03124523694789088</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.2133575314991744</v>
+        <v>-0.3342373044516582</v>
       </c>
     </row>
     <row r="37">
@@ -1157,19 +1157,19 @@
         <v>45681</v>
       </c>
       <c r="B37" t="n">
-        <v>-1.365143259973252</v>
+        <v>-0.9901445505520226</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.7512597487037835</v>
+        <v>-0.8445011652166076</v>
       </c>
       <c r="D37" t="n">
-        <v>0.7394533825299967</v>
+        <v>0.5892347830926653</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.1070226078587547</v>
+        <v>0.1342749222797341</v>
       </c>
       <c r="F37" t="n">
-        <v>0.167094789137248</v>
+        <v>0.2275908449324106</v>
       </c>
     </row>
     <row r="38">
@@ -1177,19 +1177,19 @@
         <v>45684</v>
       </c>
       <c r="B38" t="n">
-        <v>0.3796215237573906</v>
+        <v>0.6161812467856032</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.6709858023740779</v>
+        <v>-0.5800853525735681</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1093436529490234</v>
+        <v>-0.003293513501177614</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1827757321511743</v>
+        <v>-0.2767377707936176</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5412119739599579</v>
+        <v>0.428760669756848</v>
       </c>
     </row>
     <row r="39">
@@ -1197,19 +1197,19 @@
         <v>45685</v>
       </c>
       <c r="B39" t="n">
-        <v>-2.023884387554368</v>
+        <v>-1.973658903773158</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.389052367781051</v>
+        <v>-0.1773051736865769</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1898109694886304</v>
+        <v>-0.1235017956398193</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.6033137640756498</v>
+        <v>0.1609096189855631</v>
       </c>
       <c r="F39" t="n">
-        <v>0.3326350049814422</v>
+        <v>0.5459869896282039</v>
       </c>
     </row>
     <row r="40">
@@ -1217,19 +1217,19 @@
         <v>45686</v>
       </c>
       <c r="B40" t="n">
-        <v>-0.3622979311858018</v>
+        <v>-0.219236536537644</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.8128070360453798</v>
+        <v>-0.8043656124368419</v>
       </c>
       <c r="D40" t="n">
-        <v>0.7650953030554675</v>
+        <v>0.6199378385152159</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1824556616663318</v>
+        <v>-0.1385585971787631</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.05827239212044277</v>
+        <v>-0.1125956238170956</v>
       </c>
     </row>
     <row r="41">
@@ -1237,19 +1237,19 @@
         <v>45687</v>
       </c>
       <c r="B41" t="n">
-        <v>1.189460780721978</v>
+        <v>1.380674352874246</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4699188774234648</v>
+        <v>-0.3395752222774661</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1726364104018462</v>
+        <v>-0.2932612836154425</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.01503780178395862</v>
+        <v>-0.1505052252813207</v>
       </c>
       <c r="F41" t="n">
-        <v>0.325111537319772</v>
+        <v>0.3953753939262285</v>
       </c>
     </row>
     <row r="42">
@@ -1257,19 +1257,19 @@
         <v>45688</v>
       </c>
       <c r="B42" t="n">
-        <v>0.2731829424725422</v>
+        <v>0.2457567418654774</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.8272383320536589</v>
+        <v>-0.9681618830746284</v>
       </c>
       <c r="D42" t="n">
-        <v>0.3394291244162509</v>
+        <v>0.2810145858875045</v>
       </c>
       <c r="E42" t="n">
-        <v>0.009302801112335968</v>
+        <v>0.09911780837291971</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.05548783957783161</v>
+        <v>0.03780681551086673</v>
       </c>
     </row>
     <row r="43">
@@ -1277,19 +1277,19 @@
         <v>45691</v>
       </c>
       <c r="B43" t="n">
-        <v>1.41847493903362</v>
+        <v>1.234321184111209</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.7681396269566458</v>
+        <v>-0.932350814316129</v>
       </c>
       <c r="D43" t="n">
-        <v>0.5038727573057525</v>
+        <v>0.5236622535093466</v>
       </c>
       <c r="E43" t="n">
-        <v>0.02791364378855362</v>
+        <v>-0.1554685834693134</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5188023086103642</v>
+        <v>0.5545216699871582</v>
       </c>
     </row>
     <row r="44">
@@ -1297,19 +1297,19 @@
         <v>45692</v>
       </c>
       <c r="B44" t="n">
-        <v>0.03763722461229424</v>
+        <v>0.08703772671582018</v>
       </c>
       <c r="C44" t="n">
-        <v>0.7761362686702862</v>
+        <v>0.6864522481046156</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2531026787446667</v>
+        <v>-0.228490799756413</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.01973481484772539</v>
+        <v>0.1701207551950865</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.4031555730186626</v>
+        <v>-0.3357214092774188</v>
       </c>
     </row>
     <row r="45">
@@ -1317,19 +1317,19 @@
         <v>45693</v>
       </c>
       <c r="B45" t="n">
-        <v>0.5561182945723192</v>
+        <v>0.626505287212203</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.08732266551837782</v>
+        <v>-0.1300894526480614</v>
       </c>
       <c r="D45" t="n">
-        <v>0.2274679534364036</v>
+        <v>0.2332768487408687</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3488967726738739</v>
+        <v>-0.07138708409127403</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.1820662023300573</v>
+        <v>-0.4340115118825238</v>
       </c>
     </row>
     <row r="46">
@@ -1337,19 +1337,19 @@
         <v>45694</v>
       </c>
       <c r="B46" t="n">
-        <v>0.0868089965723947</v>
+        <v>0.2565099394655986</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2195289781620527</v>
+        <v>0.04629233544494468</v>
       </c>
       <c r="D46" t="n">
-        <v>0.6261143798607866</v>
+        <v>0.4802802925234269</v>
       </c>
       <c r="E46" t="n">
-        <v>0.065094898628678</v>
+        <v>0.1798187038556461</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.2546523962930025</v>
+        <v>-0.3404379390472033</v>
       </c>
     </row>
     <row r="47">
@@ -1357,19 +1357,19 @@
         <v>45695</v>
       </c>
       <c r="B47" t="n">
-        <v>0.1908991099184156</v>
+        <v>0.4105717541311224</v>
       </c>
       <c r="C47" t="n">
-        <v>0.8020898920035189</v>
+        <v>0.5544537865571664</v>
       </c>
       <c r="D47" t="n">
-        <v>1.533740369755475</v>
+        <v>1.557164652935914</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1724207442729757</v>
+        <v>0.1251109461978779</v>
       </c>
       <c r="F47" t="n">
-        <v>0.06796076354772933</v>
+        <v>-0.2290777167327447</v>
       </c>
     </row>
     <row r="48">
@@ -1377,19 +1377,19 @@
         <v>45698</v>
       </c>
       <c r="B48" t="n">
-        <v>-0.1120483640229453</v>
+        <v>-0.2709270234183199</v>
       </c>
       <c r="C48" t="n">
-        <v>0.3507321426489823</v>
+        <v>0.4965292296736621</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.267038209972239</v>
+        <v>-0.08380083601196978</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2466915388820827</v>
+        <v>-0.2638072126876518</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4077260327464735</v>
+        <v>0.1630085750053369</v>
       </c>
     </row>
     <row r="49">
@@ -1397,19 +1397,19 @@
         <v>45699</v>
       </c>
       <c r="B49" t="n">
-        <v>-1.543193214179255</v>
+        <v>-1.45553332804174</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.1072687745679183</v>
+        <v>0.1640584697108377</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.9247661861299936</v>
+        <v>-0.90859255568885</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.1423663385977505</v>
+        <v>-0.1538333786218876</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.1833196532558594</v>
+        <v>-0.08535839515852879</v>
       </c>
     </row>
     <row r="50">
@@ -1417,19 +1417,19 @@
         <v>45700</v>
       </c>
       <c r="B50" t="n">
-        <v>2.410344064596988</v>
+        <v>2.487833854228257</v>
       </c>
       <c r="C50" t="n">
-        <v>0.2464076507207569</v>
+        <v>0.1606678831994951</v>
       </c>
       <c r="D50" t="n">
-        <v>0.2156585873811207</v>
+        <v>0.252307129748061</v>
       </c>
       <c r="E50" t="n">
-        <v>0.008301444065063701</v>
+        <v>0.05440609957181837</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.07996035394586586</v>
+        <v>-0.05798187461778595</v>
       </c>
     </row>
     <row r="51">
@@ -1437,19 +1437,19 @@
         <v>45701</v>
       </c>
       <c r="B51" t="n">
-        <v>-0.7013484091044193</v>
+        <v>-0.8012367081973729</v>
       </c>
       <c r="C51" t="n">
-        <v>0.6435202043821668</v>
+        <v>0.5411414231860535</v>
       </c>
       <c r="D51" t="n">
-        <v>0.3794311351369819</v>
+        <v>0.6393748432773743</v>
       </c>
       <c r="E51" t="n">
-        <v>0.5621206093494296</v>
+        <v>-0.374309509627364</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1807204094472975</v>
+        <v>-0.2985528902523466</v>
       </c>
     </row>
     <row r="52">
@@ -1457,19 +1457,19 @@
         <v>45702</v>
       </c>
       <c r="B52" t="n">
-        <v>1.206720733183609</v>
+        <v>-0.2223330697682003</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.6604063714435439</v>
+        <v>-0.603912870695649</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5431765400526618</v>
+        <v>-0.9581580908395108</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.09030670084331667</v>
+        <v>-0.1264663042834583</v>
       </c>
       <c r="F52" t="n">
-        <v>0.3884387678625538</v>
+        <v>0.6333970145403257</v>
       </c>
     </row>
     <row r="53">
@@ -1477,19 +1477,19 @@
         <v>45705</v>
       </c>
       <c r="B53" t="n">
-        <v>-2.958101616599864</v>
+        <v>-3.053993742490919</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.8221700860537835</v>
+        <v>-0.9384266504241714</v>
       </c>
       <c r="D53" t="n">
-        <v>0.349005982899526</v>
+        <v>0.4105857187286178</v>
       </c>
       <c r="E53" t="n">
-        <v>0.02973152771640182</v>
+        <v>-0.02243396243704745</v>
       </c>
       <c r="F53" t="n">
-        <v>0.2239286756246033</v>
+        <v>0.2480859591404626</v>
       </c>
     </row>
     <row r="54">
@@ -1497,19 +1497,19 @@
         <v>45706</v>
       </c>
       <c r="B54" t="n">
-        <v>-1.714368813651206</v>
+        <v>-1.695711314712448</v>
       </c>
       <c r="C54" t="n">
-        <v>0.2176843912731621</v>
+        <v>0.1901539097066554</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4831071993808315</v>
+        <v>-0.4712351606973265</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.4440912531072476</v>
+        <v>0.3246369582601036</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.1692809829563701</v>
+        <v>0.2377446414727068</v>
       </c>
     </row>
     <row r="55">
@@ -1517,19 +1517,19 @@
         <v>45707</v>
       </c>
       <c r="B55" t="n">
-        <v>-0.7768172829445072</v>
+        <v>-1.181068691323866</v>
       </c>
       <c r="C55" t="n">
-        <v>0.7116336515743882</v>
+        <v>0.7761760628090801</v>
       </c>
       <c r="D55" t="n">
-        <v>0.2138968126445069</v>
+        <v>0.3757994885164608</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.2123838920984743</v>
+        <v>0.1601890567091248</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.08366832425253701</v>
+        <v>-0.08734243360796645</v>
       </c>
     </row>
     <row r="56">
@@ -1537,19 +1537,19 @@
         <v>45708</v>
       </c>
       <c r="B56" t="n">
-        <v>-1.451570901956513</v>
+        <v>-1.465211028781511</v>
       </c>
       <c r="C56" t="n">
-        <v>0.8644403012441297</v>
+        <v>0.8919005227855122</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.1084498720954689</v>
+        <v>0.07258369036235013</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.03056799460524871</v>
+        <v>0.1807776970096865</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.01599826793529654</v>
+        <v>-0.2435591635041794</v>
       </c>
     </row>
     <row r="57">
@@ -1557,19 +1557,19 @@
         <v>45709</v>
       </c>
       <c r="B57" t="n">
-        <v>0.4500187885981949</v>
+        <v>0.5207416725656645</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.7719714863169339</v>
+        <v>-0.7338483161626335</v>
       </c>
       <c r="D57" t="n">
-        <v>0.1303326095823054</v>
+        <v>0.05209693122459891</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.3506912703957607</v>
+        <v>0.1879302589431966</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.1188615872457829</v>
+        <v>0.08997898218667133</v>
       </c>
     </row>
     <row r="58">
@@ -1577,19 +1577,19 @@
         <v>45712</v>
       </c>
       <c r="B58" t="n">
-        <v>0.02482228005195652</v>
+        <v>-0.08904866894223885</v>
       </c>
       <c r="C58" t="n">
-        <v>0.3364248304878221</v>
+        <v>0.3541758329583452</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.08360279031267023</v>
+        <v>-0.001387548070331124</v>
       </c>
       <c r="E58" t="n">
-        <v>0.04794001703973083</v>
+        <v>0.02870494200055775</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0007589008536963899</v>
+        <v>-0.0975444354250258</v>
       </c>
     </row>
     <row r="59">
@@ -1597,19 +1597,19 @@
         <v>45713</v>
       </c>
       <c r="B59" t="n">
-        <v>0.7980855644340246</v>
+        <v>0.7958353257038218</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.5948391779309865</v>
+        <v>-0.7753319757982796</v>
       </c>
       <c r="D59" t="n">
-        <v>0.8527980102058939</v>
+        <v>0.8990868960933744</v>
       </c>
       <c r="E59" t="n">
-        <v>0.3461685798472336</v>
+        <v>-0.1852460197236498</v>
       </c>
       <c r="F59" t="n">
-        <v>0.3689815331392654</v>
+        <v>0.1563179303809563</v>
       </c>
     </row>
     <row r="60">
@@ -1617,19 +1617,19 @@
         <v>45714</v>
       </c>
       <c r="B60" t="n">
-        <v>-0.8639056937883777</v>
+        <v>-0.7997912754948946</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.264956899795411</v>
+        <v>-0.3393935668487038</v>
       </c>
       <c r="D60" t="n">
-        <v>0.8021000259634097</v>
+        <v>0.9573966583451784</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.09396760003595474</v>
+        <v>0.07808686212548221</v>
       </c>
       <c r="F60" t="n">
-        <v>0.2223182196643304</v>
+        <v>0.1309449550736399</v>
       </c>
     </row>
     <row r="61">
@@ -1637,19 +1637,19 @@
         <v>45715</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.129777067836122</v>
+        <v>-0.03928566665788821</v>
       </c>
       <c r="C61" t="n">
-        <v>0.2226255219136448</v>
+        <v>0.07129318849963866</v>
       </c>
       <c r="D61" t="n">
-        <v>0.3521700000880345</v>
+        <v>0.3334926994386951</v>
       </c>
       <c r="E61" t="n">
-        <v>0.1047405297045517</v>
+        <v>-0.08767025392142619</v>
       </c>
       <c r="F61" t="n">
-        <v>0.1708437409396325</v>
+        <v>0.05813753738296432</v>
       </c>
     </row>
     <row r="62">
@@ -1657,19 +1657,19 @@
         <v>45716</v>
       </c>
       <c r="B62" t="n">
-        <v>1.391330241515865</v>
+        <v>1.039540877753068</v>
       </c>
       <c r="C62" t="n">
-        <v>0.4667500221405939</v>
+        <v>0.6095138740790741</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.1051065805970607</v>
+        <v>-0.1089155626557533</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.1711778058749465</v>
+        <v>0.2181587983623835</v>
       </c>
       <c r="F62" t="n">
-        <v>0.08758742635528823</v>
+        <v>0.09469704612002972</v>
       </c>
     </row>
     <row r="63">
@@ -1677,19 +1677,19 @@
         <v>45722</v>
       </c>
       <c r="B63" t="n">
-        <v>3.736641930666056</v>
+        <v>3.816640168256153</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.1120364317743542</v>
+        <v>-0.02420954658539128</v>
       </c>
       <c r="D63" t="n">
-        <v>0.08161770934355293</v>
+        <v>0.04181813253365636</v>
       </c>
       <c r="E63" t="n">
-        <v>0.2685241747355695</v>
+        <v>-0.2249701721448458</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1544109777920823</v>
+        <v>-0.06954103224616413</v>
       </c>
     </row>
     <row r="64">
@@ -1697,19 +1697,19 @@
         <v>45723</v>
       </c>
       <c r="B64" t="n">
-        <v>2.402142742439446</v>
+        <v>2.532537241487398</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.1992659748314631</v>
+        <v>-0.2463068307082065</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.01643012392808476</v>
+        <v>-0.1235792562861355</v>
       </c>
       <c r="E64" t="n">
-        <v>0.2053523929238346</v>
+        <v>-0.2008779997834255</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.07131709334861079</v>
+        <v>-0.1700397887561399</v>
       </c>
     </row>
     <row r="65">
@@ -1717,19 +1717,19 @@
         <v>45726</v>
       </c>
       <c r="B65" t="n">
-        <v>1.576591245900596</v>
+        <v>1.49819538328567</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.4251572611014243</v>
+        <v>-0.4200743303023082</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.04225322395003923</v>
+        <v>-0.05999411099551075</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.126212949763987</v>
+        <v>-0.1124937013907254</v>
       </c>
       <c r="F65" t="n">
-        <v>0.3072532831842157</v>
+        <v>0.377124753873094</v>
       </c>
     </row>
     <row r="66">
@@ -1737,19 +1737,19 @@
         <v>45727</v>
       </c>
       <c r="B66" t="n">
-        <v>-0.2285764368729927</v>
+        <v>-0.2472968045204452</v>
       </c>
       <c r="C66" t="n">
-        <v>0.03787582929156399</v>
+        <v>0.01927167576000488</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.1748134216268654</v>
+        <v>-0.08138455702706546</v>
       </c>
       <c r="E66" t="n">
-        <v>0.1468393628584785</v>
+        <v>0.05655420616640441</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.1718330799908199</v>
+        <v>-0.2231980935915365</v>
       </c>
     </row>
     <row r="67">
@@ -1757,19 +1757,19 @@
         <v>45728</v>
       </c>
       <c r="B67" t="n">
-        <v>1.423962613584485</v>
+        <v>1.61870195056887</v>
       </c>
       <c r="C67" t="n">
-        <v>0.2248355565559479</v>
+        <v>0.1579961187745502</v>
       </c>
       <c r="D67" t="n">
-        <v>0.821702982716582</v>
+        <v>0.7184100987357888</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.1754657847508464</v>
+        <v>0.1970298472129438</v>
       </c>
       <c r="F67" t="n">
-        <v>0.1701861901632656</v>
+        <v>0.1620755771493016</v>
       </c>
     </row>
     <row r="68">
@@ -1777,19 +1777,19 @@
         <v>45729</v>
       </c>
       <c r="B68" t="n">
-        <v>-1.187798254403916</v>
+        <v>-0.8810794286732705</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.5548785950744656</v>
+        <v>-0.4837583414309807</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.4444653973745486</v>
+        <v>-0.5328646396464823</v>
       </c>
       <c r="E68" t="n">
-        <v>0.04060643581764937</v>
+        <v>-0.2199428302531757</v>
       </c>
       <c r="F68" t="n">
-        <v>0.2617509822119719</v>
+        <v>0.3144634557002974</v>
       </c>
     </row>
     <row r="69">
@@ -1797,19 +1797,19 @@
         <v>45730</v>
       </c>
       <c r="B69" t="n">
-        <v>0.344385419288116</v>
+        <v>-0.05873225778701514</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.4821810853157747</v>
+        <v>-0.3960501013435009</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.09926272890178112</v>
+        <v>-0.09624787915035565</v>
       </c>
       <c r="E69" t="n">
-        <v>0.04866516398344952</v>
+        <v>-0.2946016045693314</v>
       </c>
       <c r="F69" t="n">
-        <v>0.4416030780415557</v>
+        <v>0.4592313161177262</v>
       </c>
     </row>
     <row r="70">
@@ -1817,19 +1817,19 @@
         <v>45733</v>
       </c>
       <c r="B70" t="n">
-        <v>-1.100731220825514</v>
+        <v>-0.787083313936452</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.2854488178056604</v>
+        <v>-0.2411337554871508</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.4348823391946023</v>
+        <v>-0.5111374906773151</v>
       </c>
       <c r="E70" t="n">
-        <v>0.008058027918496191</v>
+        <v>-0.04007497037881436</v>
       </c>
       <c r="F70" t="n">
-        <v>0.2483169526356206</v>
+        <v>0.2952682304376695</v>
       </c>
     </row>
     <row r="71">
@@ -1837,19 +1837,19 @@
         <v>45734</v>
       </c>
       <c r="B71" t="n">
-        <v>1.499445667223588</v>
+        <v>1.596923143312957</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.2533585818561557</v>
+        <v>-0.03183938720809467</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.2539679955576986</v>
+        <v>-0.3192274453214608</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.2372682428687131</v>
+        <v>-0.01206515987725312</v>
       </c>
       <c r="F71" t="n">
-        <v>0.3222273956903033</v>
+        <v>0.3658799935905577</v>
       </c>
     </row>
     <row r="72">
@@ -1857,19 +1857,19 @@
         <v>45735</v>
       </c>
       <c r="B72" t="n">
-        <v>0.3575207430487455</v>
+        <v>0.6504982808875597</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.09837026021765455</v>
+        <v>0.05436820541509618</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.2444637041499125</v>
+        <v>-0.266536372983686</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.4161154632195713</v>
+        <v>0.1683763181887765</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2443319210007829</v>
+        <v>0.4723098779075295</v>
       </c>
     </row>
     <row r="73">
@@ -1877,19 +1877,19 @@
         <v>45736</v>
       </c>
       <c r="B73" t="n">
-        <v>-1.653993331654043</v>
+        <v>-1.631081880835517</v>
       </c>
       <c r="C73" t="n">
-        <v>1.06938028660744</v>
+        <v>0.9050441523305534</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.05428183791383345</v>
+        <v>0.0545239520290548</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.180018697213918</v>
+        <v>0.134231295021914</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.5141479394576101</v>
+        <v>-0.4940012634603214</v>
       </c>
     </row>
     <row r="74">
@@ -1897,19 +1897,19 @@
         <v>45737</v>
       </c>
       <c r="B74" t="n">
-        <v>-2.080035665791949</v>
+        <v>-1.81867231372127</v>
       </c>
       <c r="C74" t="n">
-        <v>0.8886604522526613</v>
+        <v>0.8403690059200026</v>
       </c>
       <c r="D74" t="n">
-        <v>0.1871007406455996</v>
+        <v>0.2060969098237351</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.1748817698732156</v>
+        <v>0.2222904630980441</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.411757942578147</v>
+        <v>-0.4646596171814876</v>
       </c>
     </row>
     <row r="75">
@@ -1917,19 +1917,19 @@
         <v>45740</v>
       </c>
       <c r="B75" t="n">
-        <v>-0.8685470818236685</v>
+        <v>-0.6799517345240296</v>
       </c>
       <c r="C75" t="n">
-        <v>0.2159654605181774</v>
+        <v>0.2555048933528325</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.5101187295244133</v>
+        <v>-0.6119844056481196</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.03216396809888613</v>
+        <v>0.09550913220116877</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.5121303342817018</v>
+        <v>-0.378205019802497</v>
       </c>
     </row>
     <row r="76">
@@ -1937,19 +1937,19 @@
         <v>45741</v>
       </c>
       <c r="B76" t="n">
-        <v>0.1426195386344738</v>
+        <v>0.0669311402207463</v>
       </c>
       <c r="C76" t="n">
-        <v>0.4489026956677897</v>
+        <v>0.5319514947239291</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.5768673758521947</v>
+        <v>-0.5476329653076928</v>
       </c>
       <c r="E76" t="n">
-        <v>0.02185246238522445</v>
+        <v>0.06648576181263154</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.1801343934150854</v>
+        <v>-0.2794050887598595</v>
       </c>
     </row>
     <row r="77">
@@ -1957,19 +1957,19 @@
         <v>45742</v>
       </c>
       <c r="B77" t="n">
-        <v>0.03338696399915936</v>
+        <v>0.06384092164896329</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.2011941580032571</v>
+        <v>-0.1417466552307262</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.4419392739352834</v>
+        <v>-0.4360994110091364</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.1148525113661707</v>
+        <v>0.03750464627452673</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.3777049971786263</v>
+        <v>-0.3123174805452509</v>
       </c>
     </row>
     <row r="78">
@@ -1977,19 +1977,19 @@
         <v>45743</v>
       </c>
       <c r="B78" t="n">
-        <v>0.5912744951209893</v>
+        <v>0.7053232652110411</v>
       </c>
       <c r="C78" t="n">
-        <v>0.2719380056547955</v>
+        <v>0.3976163081946904</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.4758931688370032</v>
+        <v>-0.4890500398053919</v>
       </c>
       <c r="E78" t="n">
-        <v>0.1187323985665955</v>
+        <v>-0.06165993716872711</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.1972264097441855</v>
+        <v>-0.2577325663014059</v>
       </c>
     </row>
     <row r="79">
@@ -1997,19 +1997,19 @@
         <v>45744</v>
       </c>
       <c r="B79" t="n">
-        <v>0.7987082136834632</v>
+        <v>0.8499358884300527</v>
       </c>
       <c r="C79" t="n">
-        <v>0.5386509537744284</v>
+        <v>0.4891358553266447</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.2901226812504696</v>
+        <v>-0.2923391153320671</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.1682528949274013</v>
+        <v>0.1960971453345188</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.4192023783859433</v>
+        <v>-0.2328532213921351</v>
       </c>
     </row>
     <row r="80">
@@ -2017,19 +2017,19 @@
         <v>45747</v>
       </c>
       <c r="B80" t="n">
-        <v>1.124535164901487</v>
+        <v>-0.08608079109392669</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.1605526522352494</v>
+        <v>-0.326628249280985</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.1890985754990098</v>
+        <v>-0.1518528912230419</v>
       </c>
       <c r="E80" t="n">
-        <v>0.2130057335868355</v>
+        <v>-0.3343177815744171</v>
       </c>
       <c r="F80" t="n">
-        <v>0.02711239185349803</v>
+        <v>-0.1668145836413026</v>
       </c>
     </row>
     <row r="81">
@@ -2037,19 +2037,19 @@
         <v>45748</v>
       </c>
       <c r="B81" t="n">
-        <v>0.203578559911526</v>
+        <v>0.1948852577856293</v>
       </c>
       <c r="C81" t="n">
-        <v>0.2487658655454164</v>
+        <v>0.3098753562324631</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.3434842203093447</v>
+        <v>-0.1712330458427886</v>
       </c>
       <c r="E81" t="n">
-        <v>0.1549891036238406</v>
+        <v>-0.2962669299533111</v>
       </c>
       <c r="F81" t="n">
-        <v>0.2512345294245061</v>
+        <v>0.2497433080553304</v>
       </c>
     </row>
     <row r="82">
@@ -2057,19 +2057,19 @@
         <v>45749</v>
       </c>
       <c r="B82" t="n">
-        <v>-1.508931131686946</v>
+        <v>-1.208909763768373</v>
       </c>
       <c r="C82" t="n">
-        <v>0.02675126996995656</v>
+        <v>0.04344288250661628</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.245433734270431</v>
+        <v>-0.2350024207893406</v>
       </c>
       <c r="E82" t="n">
-        <v>0.4224019754961846</v>
+        <v>-0.2443716273038776</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.2985853469167083</v>
+        <v>-0.4149459553692483</v>
       </c>
     </row>
     <row r="83">
@@ -2077,19 +2077,19 @@
         <v>45750</v>
       </c>
       <c r="B83" t="n">
-        <v>3.57005357613766</v>
+        <v>3.693390709958256</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.01210570776200441</v>
+        <v>0.003949174645286668</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.1088804427029745</v>
+        <v>-0.1520959576617896</v>
       </c>
       <c r="E83" t="n">
-        <v>0.2318669924074123</v>
+        <v>-0.2439378313088915</v>
       </c>
       <c r="F83" t="n">
-        <v>0.1276035358512901</v>
+        <v>-0.005295632624586411</v>
       </c>
     </row>
     <row r="84">
@@ -2097,19 +2097,19 @@
         <v>45751</v>
       </c>
       <c r="B84" t="n">
-        <v>5.641501139382115</v>
+        <v>5.702981487508214</v>
       </c>
       <c r="C84" t="n">
-        <v>0.4575591255458931</v>
+        <v>0.5117638172255188</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.5076390992783496</v>
+        <v>-0.4772245719451786</v>
       </c>
       <c r="E84" t="n">
-        <v>0.09860937981446107</v>
+        <v>-0.1321021560108453</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.007166019726050532</v>
+        <v>-0.03835140741635321</v>
       </c>
     </row>
     <row r="85">
@@ -2117,19 +2117,19 @@
         <v>45754</v>
       </c>
       <c r="B85" t="n">
-        <v>7.710731148134574</v>
+        <v>7.753915357006658</v>
       </c>
       <c r="C85" t="n">
-        <v>0.05867047196418951</v>
+        <v>0.3247610368883143</v>
       </c>
       <c r="D85" t="n">
-        <v>-1.275579521034901</v>
+        <v>-1.240731046454655</v>
       </c>
       <c r="E85" t="n">
-        <v>0.01212393885249955</v>
+        <v>-0.3176340715241578</v>
       </c>
       <c r="F85" t="n">
-        <v>0.179490878521751</v>
+        <v>0.2277610279184989</v>
       </c>
     </row>
     <row r="86">
@@ -2137,19 +2137,19 @@
         <v>45755</v>
       </c>
       <c r="B86" t="n">
-        <v>6.270172524579979</v>
+        <v>6.265965083866666</v>
       </c>
       <c r="C86" t="n">
-        <v>0.1412833347772509</v>
+        <v>0.3149779631234399</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.7192182915391516</v>
+        <v>-0.7383799153710857</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.2695124727417512</v>
+        <v>0.1436833517941641</v>
       </c>
       <c r="F86" t="n">
-        <v>-0.1289950531726791</v>
+        <v>0.01411667928060609</v>
       </c>
     </row>
     <row r="87">
@@ -2157,19 +2157,19 @@
         <v>45756</v>
       </c>
       <c r="B87" t="n">
-        <v>7.796568656703426</v>
+        <v>7.751523347998763</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.1479525638022933</v>
+        <v>0.1203560214151638</v>
       </c>
       <c r="D87" t="n">
-        <v>-1.379254798223869</v>
+        <v>-1.325091802246758</v>
       </c>
       <c r="E87" t="n">
-        <v>0.08194051580832995</v>
+        <v>-0.3918969350463771</v>
       </c>
       <c r="F87" t="n">
-        <v>0.1971736944572605</v>
+        <v>0.2860272790423098</v>
       </c>
     </row>
     <row r="88">
@@ -2177,19 +2177,19 @@
         <v>45757</v>
       </c>
       <c r="B88" t="n">
-        <v>6.73475857237201</v>
+        <v>6.768797941785852</v>
       </c>
       <c r="C88" t="n">
-        <v>0.04886078641485181</v>
+        <v>0.05093337523159731</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.103404741480122</v>
+        <v>-0.167783181800939</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.07437902458860017</v>
+        <v>0.1045026771482899</v>
       </c>
       <c r="F88" t="n">
-        <v>-0.1164045715379075</v>
+        <v>-0.02286389112905507</v>
       </c>
     </row>
     <row r="89">
@@ -2197,19 +2197,19 @@
         <v>45758</v>
       </c>
       <c r="B89" t="n">
-        <v>4.761701575380055</v>
+        <v>4.787869232808615</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.1464976210964269</v>
+        <v>-0.1328250783199198</v>
       </c>
       <c r="D89" t="n">
-        <v>0.09778781198280324</v>
+        <v>0.124461606999987</v>
       </c>
       <c r="E89" t="n">
-        <v>0.1463603762939166</v>
+        <v>-0.1106930539151926</v>
       </c>
       <c r="F89" t="n">
-        <v>0.2821583154998727</v>
+        <v>0.1423654349857649</v>
       </c>
     </row>
     <row r="90">
@@ -2217,19 +2217,19 @@
         <v>45761</v>
       </c>
       <c r="B90" t="n">
-        <v>3.27317894783138</v>
+        <v>3.348587841389024</v>
       </c>
       <c r="C90" t="n">
-        <v>0.01971073526977643</v>
+        <v>-0.02407856597157555</v>
       </c>
       <c r="D90" t="n">
-        <v>0.2772257330085618</v>
+        <v>0.2818490848042678</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.001943869831587131</v>
+        <v>-0.002749526845766026</v>
       </c>
       <c r="F90" t="n">
-        <v>0.2289256818999459</v>
+        <v>0.2445209576116457</v>
       </c>
     </row>
     <row r="91">
@@ -2237,19 +2237,19 @@
         <v>45762</v>
       </c>
       <c r="B91" t="n">
-        <v>2.203053265862212</v>
+        <v>2.258048136063703</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.2166677946287023</v>
+        <v>-0.3270316417921605</v>
       </c>
       <c r="D91" t="n">
-        <v>0.1712439232387868</v>
+        <v>0.128747937938428</v>
       </c>
       <c r="E91" t="n">
-        <v>0.02021105307421394</v>
+        <v>0.02938954157090642</v>
       </c>
       <c r="F91" t="n">
-        <v>-0.2790443914204319</v>
+        <v>-0.140012071151506</v>
       </c>
     </row>
     <row r="92">
@@ -2257,19 +2257,19 @@
         <v>45763</v>
       </c>
       <c r="B92" t="n">
-        <v>3.645041938116941</v>
+        <v>3.706421676882869</v>
       </c>
       <c r="C92" t="n">
-        <v>0.1373234295557263</v>
+        <v>0.173949345500166</v>
       </c>
       <c r="D92" t="n">
-        <v>0.1133024606694746</v>
+        <v>0.10929764079564</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.3651895424055802</v>
+        <v>0.1553426839100053</v>
       </c>
       <c r="F92" t="n">
-        <v>0.397844815399325</v>
+        <v>0.5424884532289153</v>
       </c>
     </row>
     <row r="93">
@@ -2277,19 +2277,19 @@
         <v>45764</v>
       </c>
       <c r="B93" t="n">
-        <v>1.909541862000241</v>
+        <v>2.056155193253538</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.7335891488093069</v>
+        <v>-0.7791678735761374</v>
       </c>
       <c r="D93" t="n">
-        <v>0.2261287466094264</v>
+        <v>-0.08416302985684371</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.2662427573588249</v>
+        <v>0.2217515026660151</v>
       </c>
       <c r="F93" t="n">
-        <v>-0.2049773706416013</v>
+        <v>0.008029248892161212</v>
       </c>
     </row>
     <row r="94">
@@ -2297,19 +2297,19 @@
         <v>45769</v>
       </c>
       <c r="B94" t="n">
-        <v>1.717103587056221</v>
+        <v>1.935424835246344</v>
       </c>
       <c r="C94" t="n">
-        <v>-1.110135561270754</v>
+        <v>-1.086842508910671</v>
       </c>
       <c r="D94" t="n">
-        <v>0.4025547037427066</v>
+        <v>0.1754115214330866</v>
       </c>
       <c r="E94" t="n">
-        <v>0.08803268588806108</v>
+        <v>-0.1252585099458357</v>
       </c>
       <c r="F94" t="n">
-        <v>0.152954269932183</v>
+        <v>0.1862575482500856</v>
       </c>
     </row>
     <row r="95">
@@ -2317,19 +2317,19 @@
         <v>45770</v>
       </c>
       <c r="B95" t="n">
-        <v>3.08413239381842</v>
+        <v>3.165598371313482</v>
       </c>
       <c r="C95" t="n">
-        <v>0.06950355418290344</v>
+        <v>0.1417926778139887</v>
       </c>
       <c r="D95" t="n">
-        <v>0.2120655885436744</v>
+        <v>0.2572320718718302</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.1812457363617723</v>
+        <v>0.08418488578724542</v>
       </c>
       <c r="F95" t="n">
-        <v>0.4601580090504422</v>
+        <v>0.3986850573970315</v>
       </c>
     </row>
     <row r="96">
@@ -2337,19 +2337,19 @@
         <v>45771</v>
       </c>
       <c r="B96" t="n">
-        <v>1.104478561237022</v>
+        <v>1.408051793945887</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.5947749301570903</v>
+        <v>-0.5323738244680053</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.1465546549245519</v>
+        <v>-0.1956837549557082</v>
       </c>
       <c r="E96" t="n">
-        <v>0.1161604388511006</v>
+        <v>-0.2789257190805907</v>
       </c>
       <c r="F96" t="n">
-        <v>0.3270669192646947</v>
+        <v>0.2966567068431503</v>
       </c>
     </row>
     <row r="97">
@@ -2357,19 +2357,19 @@
         <v>45772</v>
       </c>
       <c r="B97" t="n">
-        <v>0.07248380793038976</v>
+        <v>0.1096992999385887</v>
       </c>
       <c r="C97" t="n">
-        <v>0.5430570443747755</v>
+        <v>0.408407825888404</v>
       </c>
       <c r="D97" t="n">
-        <v>0.273142934443917</v>
+        <v>0.3320391569195111</v>
       </c>
       <c r="E97" t="n">
-        <v>-0.1318481517034079</v>
+        <v>0.2590390169914137</v>
       </c>
       <c r="F97" t="n">
-        <v>-0.112344429217759</v>
+        <v>-0.008101934926892086</v>
       </c>
     </row>
     <row r="98">
@@ -2377,19 +2377,19 @@
         <v>45775</v>
       </c>
       <c r="B98" t="n">
-        <v>0.1251595548116533</v>
+        <v>0.4041349803111598</v>
       </c>
       <c r="C98" t="n">
-        <v>0.1344098814018759</v>
+        <v>0.05603244245034587</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.02543433495270975</v>
+        <v>-0.134026423969089</v>
       </c>
       <c r="E98" t="n">
-        <v>0.1452178023698504</v>
+        <v>0.06205156201747591</v>
       </c>
       <c r="F98" t="n">
-        <v>-0.1363921705639441</v>
+        <v>-0.1623412900067152</v>
       </c>
     </row>
     <row r="99">
@@ -2397,19 +2397,19 @@
         <v>45776</v>
       </c>
       <c r="B99" t="n">
-        <v>-0.2457782562249187</v>
+        <v>0.08853671575095484</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.9338939360845583</v>
+        <v>-0.925493911181246</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.05977244378811034</v>
+        <v>-0.2168332910128939</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.1112357948035307</v>
+        <v>0.01304402766044672</v>
       </c>
       <c r="F99" t="n">
-        <v>-0.01647646394001932</v>
+        <v>0.1646049199490361</v>
       </c>
     </row>
     <row r="100">
@@ -2417,19 +2417,19 @@
         <v>45777</v>
       </c>
       <c r="B100" t="n">
-        <v>1.23714727339626</v>
+        <v>1.24095465732718</v>
       </c>
       <c r="C100" t="n">
-        <v>-0.3117124837947193</v>
+        <v>-0.4509550112883535</v>
       </c>
       <c r="D100" t="n">
-        <v>0.2370996695500277</v>
+        <v>0.2072519201087671</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.04865938971292542</v>
+        <v>0.00880895550770853</v>
       </c>
       <c r="F100" t="n">
-        <v>-0.299037805070865</v>
+        <v>-0.1775427699593791</v>
       </c>
     </row>
     <row r="101">
@@ -2437,19 +2437,19 @@
         <v>45779</v>
       </c>
       <c r="B101" t="n">
-        <v>0.8471850849473423</v>
+        <v>0.8840852384289154</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.1735292423203469</v>
+        <v>-0.2372663702033896</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.1098114059340576</v>
+        <v>-0.09860876857865999</v>
       </c>
       <c r="E101" t="n">
-        <v>0.01293351556105826</v>
+        <v>0.01023521665831415</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.04604488291728495</v>
+        <v>0.09134476924464585</v>
       </c>
     </row>
     <row r="102">
@@ -2457,19 +2457,19 @@
         <v>45782</v>
       </c>
       <c r="B102" t="n">
-        <v>-0.1737163605379807</v>
+        <v>-0.0203373876813996</v>
       </c>
       <c r="C102" t="n">
-        <v>0.2852843042981889</v>
+        <v>0.2875698067303353</v>
       </c>
       <c r="D102" t="n">
-        <v>0.002762880061719797</v>
+        <v>0.01168282453687748</v>
       </c>
       <c r="E102" t="n">
-        <v>0.6719263246539836</v>
+        <v>-0.4181597133826435</v>
       </c>
       <c r="F102" t="n">
-        <v>-0.1084669299806417</v>
+        <v>-0.4570696755193601</v>
       </c>
     </row>
     <row r="103">
@@ -2477,19 +2477,19 @@
         <v>45783</v>
       </c>
       <c r="B103" t="n">
-        <v>-0.1731786493236099</v>
+        <v>-0.1560317876560216</v>
       </c>
       <c r="C103" t="n">
-        <v>0.6586884074870092</v>
+        <v>0.5471830091883391</v>
       </c>
       <c r="D103" t="n">
-        <v>0.4935090299366238</v>
+        <v>0.7556067858988629</v>
       </c>
       <c r="E103" t="n">
-        <v>0.5192766382604718</v>
+        <v>-0.1943857369066581</v>
       </c>
       <c r="F103" t="n">
-        <v>0.06903710588433358</v>
+        <v>-0.4187111170219868</v>
       </c>
     </row>
     <row r="104">
@@ -2497,19 +2497,19 @@
         <v>45784</v>
       </c>
       <c r="B104" t="n">
-        <v>-0.1519338232439785</v>
+        <v>-0.3891159099161144</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.1781396962558881</v>
+        <v>-0.2742630589643018</v>
       </c>
       <c r="D104" t="n">
-        <v>0.2913597915566076</v>
+        <v>0.2827888459923859</v>
       </c>
       <c r="E104" t="n">
-        <v>-0.1268004214562085</v>
+        <v>0.2612079155143409</v>
       </c>
       <c r="F104" t="n">
-        <v>-0.09601925818068548</v>
+        <v>0.08499933500885881</v>
       </c>
     </row>
     <row r="105">
@@ -2517,19 +2517,19 @@
         <v>45785</v>
       </c>
       <c r="B105" t="n">
-        <v>2.958671736350566</v>
+        <v>3.013564685026451</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.2562272602203304</v>
+        <v>-0.1292374065566477</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.313074706490417</v>
+        <v>-0.2916218560529432</v>
       </c>
       <c r="E105" t="n">
-        <v>0.05437765343477011</v>
+        <v>-0.1796464871260008</v>
       </c>
       <c r="F105" t="n">
-        <v>0.3915130456067097</v>
+        <v>0.3395749674023548</v>
       </c>
     </row>
     <row r="106">
@@ -2537,19 +2537,19 @@
         <v>45786</v>
       </c>
       <c r="B106" t="n">
-        <v>-2.191170702427797</v>
+        <v>-1.971213302964143</v>
       </c>
       <c r="C106" t="n">
-        <v>0.6274417868751944</v>
+        <v>0.7146851402453325</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.2419279161832781</v>
+        <v>-0.1514059190852687</v>
       </c>
       <c r="E106" t="n">
-        <v>-0.1967411875265735</v>
+        <v>-0.1636362732268403</v>
       </c>
       <c r="F106" t="n">
-        <v>0.1487956365997822</v>
+        <v>0.04943020485638612</v>
       </c>
     </row>
     <row r="107">
@@ -2557,19 +2557,19 @@
         <v>45789</v>
       </c>
       <c r="B107" t="n">
-        <v>0.3239233832655868</v>
+        <v>0.5015690680789299</v>
       </c>
       <c r="C107" t="n">
-        <v>0.4948991129677507</v>
+        <v>0.5320853785794339</v>
       </c>
       <c r="D107" t="n">
-        <v>0.1678628386679179</v>
+        <v>0.1541483844590449</v>
       </c>
       <c r="E107" t="n">
-        <v>-0.08675396082990694</v>
+        <v>0.086465089204648</v>
       </c>
       <c r="F107" t="n">
-        <v>0.001662758237260165</v>
+        <v>-0.0258383660637745</v>
       </c>
     </row>
     <row r="108">
@@ -2577,19 +2577,19 @@
         <v>45790</v>
       </c>
       <c r="B108" t="n">
-        <v>0.01955652410434921</v>
+        <v>0.07389101107395445</v>
       </c>
       <c r="C108" t="n">
-        <v>-1.595568576411235</v>
+        <v>-1.318598160159417</v>
       </c>
       <c r="D108" t="n">
-        <v>-0.4911850954046826</v>
+        <v>-0.5785546520750821</v>
       </c>
       <c r="E108" t="n">
-        <v>-0.3565576183596471</v>
+        <v>-0.2674316504433466</v>
       </c>
       <c r="F108" t="n">
-        <v>0.789537721137207</v>
+        <v>1.042503365705866</v>
       </c>
     </row>
     <row r="109">
@@ -2597,19 +2597,19 @@
         <v>45791</v>
       </c>
       <c r="B109" t="n">
-        <v>-0.3103366332392516</v>
+        <v>-0.008297976823126203</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.2705856462493023</v>
+        <v>-0.2069236147526669</v>
       </c>
       <c r="D109" t="n">
-        <v>0.442486076957751</v>
+        <v>0.3827476787158569</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.2542700984520431</v>
+        <v>0.1024629084368905</v>
       </c>
       <c r="F109" t="n">
-        <v>0.250135746610318</v>
+        <v>0.3532458699043903</v>
       </c>
     </row>
     <row r="110">
@@ -2617,19 +2617,19 @@
         <v>45792</v>
       </c>
       <c r="B110" t="n">
-        <v>1.178536163607194</v>
+        <v>1.316696407679176</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.2300443370561644</v>
+        <v>-0.4201489646309194</v>
       </c>
       <c r="D110" t="n">
-        <v>0.6286607654745621</v>
+        <v>0.4248016854917327</v>
       </c>
       <c r="E110" t="n">
-        <v>0.09095451122894943</v>
+        <v>0.02823652106545886</v>
       </c>
       <c r="F110" t="n">
-        <v>-0.2043821804001595</v>
+        <v>-0.2945338831753359</v>
       </c>
     </row>
     <row r="111">
@@ -2637,19 +2637,19 @@
         <v>45793</v>
       </c>
       <c r="B111" t="n">
-        <v>1.606362693276351</v>
+        <v>1.738279018224222</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.2472542040735659</v>
+        <v>-0.3682445425725385</v>
       </c>
       <c r="D111" t="n">
-        <v>0.5117291041610948</v>
+        <v>0.3892156853674106</v>
       </c>
       <c r="E111" t="n">
-        <v>-0.06563850727616127</v>
+        <v>-0.01283483203981412</v>
       </c>
       <c r="F111" t="n">
-        <v>0.09001455689204135</v>
+        <v>0.0973918545723463</v>
       </c>
     </row>
     <row r="112">
@@ -2657,19 +2657,19 @@
         <v>45796</v>
       </c>
       <c r="B112" t="n">
-        <v>-1.017059094363302</v>
+        <v>-0.9280643500510728</v>
       </c>
       <c r="C112" t="n">
-        <v>0.02503599860878913</v>
+        <v>-0.1928636081022567</v>
       </c>
       <c r="D112" t="n">
-        <v>0.7269094819635813</v>
+        <v>0.6434071900598011</v>
       </c>
       <c r="E112" t="n">
-        <v>0.04651858836745599</v>
+        <v>0.1367271298073006</v>
       </c>
       <c r="F112" t="n">
-        <v>0.1519176566157429</v>
+        <v>0.1336374372636855</v>
       </c>
     </row>
     <row r="113">
@@ -2677,19 +2677,19 @@
         <v>45797</v>
       </c>
       <c r="B113" t="n">
-        <v>-0.2428922155314969</v>
+        <v>0.1072439837823551</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.1332064440577992</v>
+        <v>-0.307020765269013</v>
       </c>
       <c r="D113" t="n">
-        <v>0.837543814567858</v>
+        <v>0.7285497795297496</v>
       </c>
       <c r="E113" t="n">
-        <v>0.4522648088711342</v>
+        <v>-0.03853700781425165</v>
       </c>
       <c r="F113" t="n">
-        <v>-0.2637375574404661</v>
+        <v>-0.4968798776834986</v>
       </c>
     </row>
     <row r="114">
@@ -2697,19 +2697,19 @@
         <v>45798</v>
       </c>
       <c r="B114" t="n">
-        <v>0.8839201786926906</v>
+        <v>0.9071003069725188</v>
       </c>
       <c r="C114" t="n">
-        <v>0.4564387995404507</v>
+        <v>0.1833768176910077</v>
       </c>
       <c r="D114" t="n">
-        <v>0.8074643861784031</v>
+        <v>0.8019861536271823</v>
       </c>
       <c r="E114" t="n">
-        <v>-0.05984202251365844</v>
+        <v>0.4335315168453663</v>
       </c>
       <c r="F114" t="n">
-        <v>-0.6318536005170158</v>
+        <v>-0.5830934643463884</v>
       </c>
     </row>
     <row r="115">
@@ -2717,19 +2717,19 @@
         <v>45799</v>
       </c>
       <c r="B115" t="n">
-        <v>1.615372418590785</v>
+        <v>1.916677550313644</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.2861396247881339</v>
+        <v>-0.3185562984268398</v>
       </c>
       <c r="D115" t="n">
-        <v>0.06834777361792972</v>
+        <v>0.00396613628368927</v>
       </c>
       <c r="E115" t="n">
-        <v>0.1697390119215578</v>
+        <v>-0.03801480768567853</v>
       </c>
       <c r="F115" t="n">
-        <v>-0.1906235129440246</v>
+        <v>-0.1695834056330006</v>
       </c>
     </row>
     <row r="116">
@@ -2737,19 +2737,19 @@
         <v>45800</v>
       </c>
       <c r="B116" t="n">
-        <v>4.07400313754316</v>
+        <v>3.887093952814809</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.06553273342153423</v>
+        <v>0.01524259716836188</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.1857451729396021</v>
+        <v>-0.2130680263718615</v>
       </c>
       <c r="E116" t="n">
-        <v>-0.05885769222150532</v>
+        <v>0.004570201476872793</v>
       </c>
       <c r="F116" t="n">
-        <v>0.07189986792679247</v>
+        <v>0.06144580464187879</v>
       </c>
     </row>
     <row r="117">
@@ -2757,19 +2757,19 @@
         <v>45803</v>
       </c>
       <c r="B117" t="n">
-        <v>-0.6323156433709225</v>
+        <v>-0.8032080059701712</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.09125363107905761</v>
+        <v>0.01080191160752289</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.9183364989628688</v>
+        <v>-1.036996785165446</v>
       </c>
       <c r="E117" t="n">
-        <v>-0.09623732075914604</v>
+        <v>0.07482714977117165</v>
       </c>
       <c r="F117" t="n">
-        <v>-0.2672979237866984</v>
+        <v>-0.1432118154709662</v>
       </c>
     </row>
     <row r="118">
@@ -2777,19 +2777,19 @@
         <v>45804</v>
       </c>
       <c r="B118" t="n">
-        <v>1.056846319874042</v>
+        <v>1.127845258014332</v>
       </c>
       <c r="C118" t="n">
-        <v>0.09164005303710837</v>
+        <v>0.1421125071723678</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.08079502214006894</v>
+        <v>0.02590653049291389</v>
       </c>
       <c r="E118" t="n">
-        <v>0.1606560047343647</v>
+        <v>-0.1642006267478471</v>
       </c>
       <c r="F118" t="n">
-        <v>0.3109533589529396</v>
+        <v>0.1385020559246322</v>
       </c>
     </row>
     <row r="119">
@@ -2797,19 +2797,19 @@
         <v>45805</v>
       </c>
       <c r="B119" t="n">
-        <v>-1.318524716431638</v>
+        <v>-1.056710583165386</v>
       </c>
       <c r="C119" t="n">
-        <v>0.2961179171340304</v>
+        <v>0.293256050138712</v>
       </c>
       <c r="D119" t="n">
-        <v>0.3151826237499117</v>
+        <v>0.28929654554793</v>
       </c>
       <c r="E119" t="n">
-        <v>-0.2617864839070285</v>
+        <v>0.1997970142023723</v>
       </c>
       <c r="F119" t="n">
-        <v>0.07241557607203637</v>
+        <v>0.1231321063360832</v>
       </c>
     </row>
     <row r="120">
@@ -2817,19 +2817,19 @@
         <v>45806</v>
       </c>
       <c r="B120" t="n">
-        <v>0.2762108486950883</v>
+        <v>0.3984681766586362</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.2027043296517819</v>
+        <v>-0.3063044967219933</v>
       </c>
       <c r="D120" t="n">
-        <v>0.371019360911111</v>
+        <v>0.2225707851127043</v>
       </c>
       <c r="E120" t="n">
-        <v>-0.4461655851770389</v>
+        <v>0.2678420102473527</v>
       </c>
       <c r="F120" t="n">
-        <v>0.06592186446112661</v>
+        <v>0.2755204428323254</v>
       </c>
     </row>
     <row r="121">
@@ -2837,19 +2837,19 @@
         <v>45807</v>
       </c>
       <c r="B121" t="n">
-        <v>0.6939570744797072</v>
+        <v>1.020603031682482</v>
       </c>
       <c r="C121" t="n">
-        <v>0.5262128460003266</v>
+        <v>0.3049915895328164</v>
       </c>
       <c r="D121" t="n">
-        <v>1.050619538320577</v>
+        <v>1.047173499114912</v>
       </c>
       <c r="E121" t="n">
-        <v>0.327829022656382</v>
+        <v>0.1815101198116993</v>
       </c>
       <c r="F121" t="n">
-        <v>-0.4842722744843322</v>
+        <v>-0.673509480919488</v>
       </c>
     </row>
     <row r="122">
@@ -2857,19 +2857,19 @@
         <v>45810</v>
       </c>
       <c r="B122" t="n">
-        <v>1.812368331051782</v>
+        <v>2.060282096564862</v>
       </c>
       <c r="C122" t="n">
-        <v>0.2717485077150298</v>
+        <v>0.2904877838487179</v>
       </c>
       <c r="D122" t="n">
-        <v>0.03744349994096172</v>
+        <v>0.01455658560075994</v>
       </c>
       <c r="E122" t="n">
-        <v>-0.0751128927651669</v>
+        <v>0.1087338854226945</v>
       </c>
       <c r="F122" t="n">
-        <v>-0.1351188636098515</v>
+        <v>-0.09327084524445294</v>
       </c>
     </row>
     <row r="123">
@@ -2877,19 +2877,19 @@
         <v>45811</v>
       </c>
       <c r="B123" t="n">
-        <v>0.3541143545754797</v>
+        <v>0.4265241047329653</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.8688790546380531</v>
+        <v>-0.5901907178819892</v>
       </c>
       <c r="D123" t="n">
-        <v>-0.853002073509072</v>
+        <v>-0.9233731809052454</v>
       </c>
       <c r="E123" t="n">
-        <v>-0.2348686152584986</v>
+        <v>-0.1292500351156522</v>
       </c>
       <c r="F123" t="n">
-        <v>-0.02257186675989767</v>
+        <v>0.2273127318232681</v>
       </c>
     </row>
     <row r="124">
@@ -2897,19 +2897,19 @@
         <v>45812</v>
       </c>
       <c r="B124" t="n">
-        <v>1.537897524251779</v>
+        <v>1.351208824589682</v>
       </c>
       <c r="C124" t="n">
-        <v>0.1724251309873618</v>
+        <v>0.1151920519217169</v>
       </c>
       <c r="D124" t="n">
-        <v>0.2795472317355158</v>
+        <v>0.3150490267449748</v>
       </c>
       <c r="E124" t="n">
-        <v>0.09761288377958385</v>
+        <v>0.08564036779418796</v>
       </c>
       <c r="F124" t="n">
-        <v>-0.004155073218042094</v>
+        <v>-0.1027485284029205</v>
       </c>
     </row>
     <row r="125">
@@ -2917,19 +2917,19 @@
         <v>45813</v>
       </c>
       <c r="B125" t="n">
-        <v>-0.1240259503135203</v>
+        <v>-0.06564633766064319</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.2652249277154412</v>
+        <v>-0.2587143226877545</v>
       </c>
       <c r="D125" t="n">
-        <v>0.2968648050124298</v>
+        <v>0.2897005291850875</v>
       </c>
       <c r="E125" t="n">
-        <v>-0.1192609401320413</v>
+        <v>0.03985367487677609</v>
       </c>
       <c r="F125" t="n">
-        <v>-0.1009178297570981</v>
+        <v>-0.1791922054158217</v>
       </c>
     </row>
     <row r="126">
@@ -2937,19 +2937,19 @@
         <v>45814</v>
       </c>
       <c r="B126" t="n">
-        <v>0.8818835537403935</v>
+        <v>0.9250171838060341</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.07806491148286743</v>
+        <v>-0.105015428346702</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.04382855750847736</v>
+        <v>0.03358068895481222</v>
       </c>
       <c r="E126" t="n">
-        <v>0.3317556028803945</v>
+        <v>-0.187052709805567</v>
       </c>
       <c r="F126" t="n">
-        <v>-0.1555316387841304</v>
+        <v>-0.3673134263738089</v>
       </c>
     </row>
     <row r="127">
@@ -2957,19 +2957,19 @@
         <v>45817</v>
       </c>
       <c r="B127" t="n">
-        <v>1.774169613959883</v>
+        <v>1.810480555167409</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.2091482180741502</v>
+        <v>-0.2519749375216077</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.2967579833962934</v>
+        <v>-0.3200852039738067</v>
       </c>
       <c r="E127" t="n">
-        <v>0.08111611099472389</v>
+        <v>-0.0909313335605003</v>
       </c>
       <c r="F127" t="n">
-        <v>-0.2200010826556039</v>
+        <v>-0.1070498007112713</v>
       </c>
     </row>
     <row r="128">
@@ -2977,19 +2977,19 @@
         <v>45818</v>
       </c>
       <c r="B128" t="n">
-        <v>1.210112611755453</v>
+        <v>0.6142460798612109</v>
       </c>
       <c r="C128" t="n">
-        <v>0.01096622098944481</v>
+        <v>0.1104594446870641</v>
       </c>
       <c r="D128" t="n">
-        <v>0.01997858425715991</v>
+        <v>-0.04699175002903352</v>
       </c>
       <c r="E128" t="n">
-        <v>-0.1523465961415227</v>
+        <v>0.1291819401263677</v>
       </c>
       <c r="F128" t="n">
-        <v>0.06662451506190877</v>
+        <v>0.2286556698730859</v>
       </c>
     </row>
     <row r="129">
@@ -2997,19 +2997,19 @@
         <v>45819</v>
       </c>
       <c r="B129" t="n">
-        <v>2.124329258959744</v>
+        <v>2.188850997656571</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.05488654805814874</v>
+        <v>-0.1824673668986856</v>
       </c>
       <c r="D129" t="n">
-        <v>0.2200442579822381</v>
+        <v>0.1920272056242741</v>
       </c>
       <c r="E129" t="n">
-        <v>-0.0900693369763719</v>
+        <v>-0.02194747402352316</v>
       </c>
       <c r="F129" t="n">
-        <v>-0.07561150605206762</v>
+        <v>0.01654969148092733</v>
       </c>
     </row>
     <row r="130">
@@ -3017,19 +3017,19 @@
         <v>45820</v>
       </c>
       <c r="B130" t="n">
-        <v>0.4743468871438837</v>
+        <v>0.05774616172889706</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.1182612590337367</v>
+        <v>-0.3785933084729058</v>
       </c>
       <c r="D130" t="n">
-        <v>0.4229152632838534</v>
+        <v>0.4451519407565243</v>
       </c>
       <c r="E130" t="n">
-        <v>0.01654086098377225</v>
+        <v>0.07416375307884644</v>
       </c>
       <c r="F130" t="n">
-        <v>-0.2346682019562782</v>
+        <v>-0.4463771424884124</v>
       </c>
     </row>
     <row r="131">
@@ -3037,19 +3037,19 @@
         <v>45821</v>
       </c>
       <c r="B131" t="n">
-        <v>0.05163565540899334</v>
+        <v>0.1855870291819618</v>
       </c>
       <c r="C131" t="n">
-        <v>0.896477665731084</v>
+        <v>0.7971786121239632</v>
       </c>
       <c r="D131" t="n">
-        <v>-0.0523567352293965</v>
+        <v>-0.06483842131992285</v>
       </c>
       <c r="E131" t="n">
-        <v>-0.2303650450378352</v>
+        <v>0.2106183035736895</v>
       </c>
       <c r="F131" t="n">
-        <v>-0.2277035983893027</v>
+        <v>-0.2612175830769494</v>
       </c>
     </row>
     <row r="132">
@@ -3057,19 +3057,19 @@
         <v>45824</v>
       </c>
       <c r="B132" t="n">
-        <v>-0.3661841636087395</v>
+        <v>-0.7670117672826676</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.4639785039605297</v>
+        <v>-0.3135798106331384</v>
       </c>
       <c r="D132" t="n">
-        <v>-0.1717163573356004</v>
+        <v>-0.1166056183355359</v>
       </c>
       <c r="E132" t="n">
-        <v>-0.00354629737990475</v>
+        <v>-0.2642373707167957</v>
       </c>
       <c r="F132" t="n">
-        <v>0.645605973853423</v>
+        <v>0.7597572019067659</v>
       </c>
     </row>
     <row r="133">
@@ -3077,19 +3077,19 @@
         <v>45825</v>
       </c>
       <c r="B133" t="n">
-        <v>-0.8944943990886739</v>
+        <v>-0.5518536558181613</v>
       </c>
       <c r="C133" t="n">
-        <v>0.131533929687188</v>
+        <v>0.09011441465814791</v>
       </c>
       <c r="D133" t="n">
-        <v>0.3790919702624576</v>
+        <v>0.3206110837735383</v>
       </c>
       <c r="E133" t="n">
-        <v>-0.2783973417630982</v>
+        <v>0.3708831566480574</v>
       </c>
       <c r="F133" t="n">
-        <v>-0.2367652996751208</v>
+        <v>-0.08723733941149706</v>
       </c>
     </row>
     <row r="134">
@@ -3097,19 +3097,19 @@
         <v>45826</v>
       </c>
       <c r="B134" t="n">
-        <v>0.3825291199799357</v>
+        <v>0.6959480671956993</v>
       </c>
       <c r="C134" t="n">
-        <v>0.4952001836071865</v>
+        <v>0.4776400927899166</v>
       </c>
       <c r="D134" t="n">
-        <v>0.7792668491211625</v>
+        <v>0.8110389313818103</v>
       </c>
       <c r="E134" t="n">
-        <v>-0.1277449440084331</v>
+        <v>0.1676056173026281</v>
       </c>
       <c r="F134" t="n">
-        <v>0.3021268343452939</v>
+        <v>0.2233126095894057</v>
       </c>
     </row>
     <row r="135">
@@ -3117,19 +3117,19 @@
         <v>45828</v>
       </c>
       <c r="B135" t="n">
-        <v>0.4670170846782086</v>
+        <v>0.6821237773134434</v>
       </c>
       <c r="C135" t="n">
-        <v>0.3359962321491648</v>
+        <v>0.3130324351331663</v>
       </c>
       <c r="D135" t="n">
-        <v>0.4247002276276124</v>
+        <v>0.4011448339066626</v>
       </c>
       <c r="E135" t="n">
-        <v>-0.1309569461849256</v>
+        <v>0.03333485098567735</v>
       </c>
       <c r="F135" t="n">
-        <v>0.1508083496896118</v>
+        <v>0.1179527386444464</v>
       </c>
     </row>
     <row r="136">
@@ -3137,19 +3137,19 @@
         <v>45831</v>
       </c>
       <c r="B136" t="n">
-        <v>-1.939865444761705</v>
+        <v>-1.75183496811186</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.4959015452586766</v>
+        <v>-0.6523263916946785</v>
       </c>
       <c r="D136" t="n">
-        <v>0.3855420571376568</v>
+        <v>0.180084050071551</v>
       </c>
       <c r="E136" t="n">
-        <v>0.5583480215926396</v>
+        <v>-0.2541074724926205</v>
       </c>
       <c r="F136" t="n">
-        <v>-0.2215261591341738</v>
+        <v>-0.4449934716158108</v>
       </c>
     </row>
     <row r="137">
@@ -3157,19 +3157,19 @@
         <v>45832</v>
       </c>
       <c r="B137" t="n">
-        <v>0.6679352874270222</v>
+        <v>0.5287489457337694</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.4568833655703037</v>
+        <v>-0.5130986830935899</v>
       </c>
       <c r="D137" t="n">
-        <v>-0.02059159566207345</v>
+        <v>-0.01932808158900891</v>
       </c>
       <c r="E137" t="n">
-        <v>0.1923127272051888</v>
+        <v>-0.07629082460400356</v>
       </c>
       <c r="F137" t="n">
-        <v>0.01216766998128965</v>
+        <v>0.03712228007487375</v>
       </c>
     </row>
     <row r="138">
@@ -3177,19 +3177,19 @@
         <v>45833</v>
       </c>
       <c r="B138" t="n">
-        <v>-0.3939794153871298</v>
+        <v>-0.578741404116373</v>
       </c>
       <c r="C138" t="n">
-        <v>0.1537613792835454</v>
+        <v>0.07663375497394848</v>
       </c>
       <c r="D138" t="n">
-        <v>0.0733404202578786</v>
+        <v>0.09529614510578165</v>
       </c>
       <c r="E138" t="n">
-        <v>-0.0561129169808889</v>
+        <v>0.07880467102553351</v>
       </c>
       <c r="F138" t="n">
-        <v>-0.1430333903242689</v>
+        <v>-0.1460717113280547</v>
       </c>
     </row>
     <row r="139">
@@ -3197,19 +3197,19 @@
         <v>45834</v>
       </c>
       <c r="B139" t="n">
-        <v>-1.269570939410041</v>
+        <v>-1.482752251204714</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.53148479763316</v>
+        <v>-0.5635775415258678</v>
       </c>
       <c r="D139" t="n">
-        <v>0.07069380819923597</v>
+        <v>0.04556415556606256</v>
       </c>
       <c r="E139" t="n">
-        <v>0.04730290659916107</v>
+        <v>-0.009007322045448385</v>
       </c>
       <c r="F139" t="n">
-        <v>0.2724735477765973</v>
+        <v>0.2952423430886569</v>
       </c>
     </row>
     <row r="140">
@@ -3217,19 +3217,19 @@
         <v>45835</v>
       </c>
       <c r="B140" t="n">
-        <v>-0.3058391074740196</v>
+        <v>-0.9286727634885656</v>
       </c>
       <c r="C140" t="n">
-        <v>0.0839827503158759</v>
+        <v>0.06671486958975253</v>
       </c>
       <c r="D140" t="n">
-        <v>0.0126658760342087</v>
+        <v>-0.03119566156949398</v>
       </c>
       <c r="E140" t="n">
-        <v>-0.03609844978097213</v>
+        <v>0.02428828422217795</v>
       </c>
       <c r="F140" t="n">
-        <v>-0.06277431228967001</v>
+        <v>-0.1708871916664469</v>
       </c>
     </row>
     <row r="141">
@@ -3237,19 +3237,19 @@
         <v>45838</v>
       </c>
       <c r="B141" t="n">
-        <v>0.4956141687047604</v>
+        <v>0.356977993512092</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.2726852613233282</v>
+        <v>-0.3993225953078244</v>
       </c>
       <c r="D141" t="n">
-        <v>0.1950571899617595</v>
+        <v>0.2474867106305875</v>
       </c>
       <c r="E141" t="n">
-        <v>0.3402476080594717</v>
+        <v>-0.1904627789449156</v>
       </c>
       <c r="F141" t="n">
-        <v>0.1050881396687349</v>
+        <v>-0.08147279459292193</v>
       </c>
     </row>
     <row r="142">
@@ -3257,19 +3257,19 @@
         <v>45839</v>
       </c>
       <c r="B142" t="n">
-        <v>-0.7058099964421292</v>
+        <v>-0.5422137501246564</v>
       </c>
       <c r="C142" t="n">
-        <v>-0.5084673838901778</v>
+        <v>-0.5805699251868496</v>
       </c>
       <c r="D142" t="n">
-        <v>0.7251317007744628</v>
+        <v>0.494796930781588</v>
       </c>
       <c r="E142" t="n">
-        <v>0.3165894685388111</v>
+        <v>0.03716766961517703</v>
       </c>
       <c r="F142" t="n">
-        <v>-0.1700632304256213</v>
+        <v>-0.3044152975188026</v>
       </c>
     </row>
     <row r="143">
@@ -3277,19 +3277,19 @@
         <v>45840</v>
       </c>
       <c r="B143" t="n">
-        <v>-1.218222812820884</v>
+        <v>-0.9921191424971042</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.06336272755491483</v>
+        <v>-0.1500151354290998</v>
       </c>
       <c r="D143" t="n">
-        <v>0.01804195524022818</v>
+        <v>-0.122172483876116</v>
       </c>
       <c r="E143" t="n">
-        <v>0.1969748668574533</v>
+        <v>-0.0105378136103658</v>
       </c>
       <c r="F143" t="n">
-        <v>-0.5857138178155005</v>
+        <v>-0.5439621439741255</v>
       </c>
     </row>
     <row r="144">
@@ -3297,19 +3297,19 @@
         <v>45841</v>
       </c>
       <c r="B144" t="n">
-        <v>-0.6162161652333744</v>
+        <v>-0.6899044744917117</v>
       </c>
       <c r="C144" t="n">
-        <v>0.05501039907461988</v>
+        <v>0.08685629050185206</v>
       </c>
       <c r="D144" t="n">
-        <v>-0.2118081359590403</v>
+        <v>-0.1377959817618133</v>
       </c>
       <c r="E144" t="n">
-        <v>0.1776343303501899</v>
+        <v>-0.1060392992694068</v>
       </c>
       <c r="F144" t="n">
-        <v>0.02121675588881957</v>
+        <v>-0.03330886276768537</v>
       </c>
     </row>
     <row r="145">
@@ -3317,19 +3317,19 @@
         <v>45842</v>
       </c>
       <c r="B145" t="n">
-        <v>-4.688926182866251</v>
+        <v>-5.383356781794961</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.3267434933387994</v>
+        <v>-0.3698027855289011</v>
       </c>
       <c r="D145" t="n">
-        <v>-0.94230793751269</v>
+        <v>-1.141495853908466</v>
       </c>
       <c r="E145" t="n">
-        <v>-0.1739625836086082</v>
+        <v>0.04709050361254246</v>
       </c>
       <c r="F145" t="n">
-        <v>-0.3055675405793286</v>
+        <v>-0.1048962059393918</v>
       </c>
     </row>
     <row r="146">
@@ -3337,19 +3337,19 @@
         <v>45845</v>
       </c>
       <c r="B146" t="n">
-        <v>-2.378238186022263</v>
+        <v>-2.331313689098647</v>
       </c>
       <c r="C146" t="n">
-        <v>1.596516581736386</v>
+        <v>1.379179398046614</v>
       </c>
       <c r="D146" t="n">
-        <v>0.7212974258388082</v>
+        <v>0.985741006052307</v>
       </c>
       <c r="E146" t="n">
-        <v>-0.3550866396539619</v>
+        <v>0.4676385241376236</v>
       </c>
       <c r="F146" t="n">
-        <v>-0.1630976970585554</v>
+        <v>-0.1417625540022639</v>
       </c>
     </row>
     <row r="147">
@@ -3357,19 +3357,19 @@
         <v>45846</v>
       </c>
       <c r="B147" t="n">
-        <v>-0.2386630935225999</v>
+        <v>0.08217780576241616</v>
       </c>
       <c r="C147" t="n">
-        <v>0.2585369257546405</v>
+        <v>0.1326460480796834</v>
       </c>
       <c r="D147" t="n">
-        <v>0.2848960377012189</v>
+        <v>0.2491529003874813</v>
       </c>
       <c r="E147" t="n">
-        <v>0.236037143456701</v>
+        <v>-0.05725846539112552</v>
       </c>
       <c r="F147" t="n">
-        <v>-0.01907888075597797</v>
+        <v>-0.2104213380657888</v>
       </c>
     </row>
     <row r="148">
@@ -3377,19 +3377,19 @@
         <v>45847</v>
       </c>
       <c r="B148" t="n">
-        <v>-1.409391476877698</v>
+        <v>-1.097743090680726</v>
       </c>
       <c r="C148" t="n">
-        <v>0.6727092822578813</v>
+        <v>0.6282202896485646</v>
       </c>
       <c r="D148" t="n">
-        <v>-0.1181836265551903</v>
+        <v>-0.02165401317636109</v>
       </c>
       <c r="E148" t="n">
-        <v>-0.3062199332137513</v>
+        <v>0.1425299523020429</v>
       </c>
       <c r="F148" t="n">
-        <v>-0.04684885638647156</v>
+        <v>0.04504981436002569</v>
       </c>
     </row>
     <row r="149">
@@ -3397,19 +3397,19 @@
         <v>45848</v>
       </c>
       <c r="B149" t="n">
-        <v>1.905553390026181</v>
+        <v>2.021277832496201</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.26070039591309</v>
+        <v>-0.2967734829111403</v>
       </c>
       <c r="D149" t="n">
-        <v>-0.01290551710142331</v>
+        <v>-0.1086941598508166</v>
       </c>
       <c r="E149" t="n">
-        <v>0.0265082516944769</v>
+        <v>-0.1013893585993429</v>
       </c>
       <c r="F149" t="n">
-        <v>0.0808134492374987</v>
+        <v>0.1128076966523472</v>
       </c>
     </row>
     <row r="150">
@@ -3417,19 +3417,19 @@
         <v>45849</v>
       </c>
       <c r="B150" t="n">
-        <v>-1.628515592777665</v>
+        <v>-1.77784335172491</v>
       </c>
       <c r="C150" t="n">
-        <v>0.5296267890210389</v>
+        <v>0.5957180249721582</v>
       </c>
       <c r="D150" t="n">
-        <v>-0.09343589884452008</v>
+        <v>0.05128836867760716</v>
       </c>
       <c r="E150" t="n">
-        <v>-0.3327306818405725</v>
+        <v>0.1431399263583774</v>
       </c>
       <c r="F150" t="n">
-        <v>0.1091189360141989</v>
+        <v>0.2735665555613528</v>
       </c>
     </row>
     <row r="151">
@@ -3437,19 +3437,19 @@
         <v>45852</v>
       </c>
       <c r="B151" t="n">
-        <v>-1.740325909194199</v>
+        <v>-1.530540132762689</v>
       </c>
       <c r="C151" t="n">
-        <v>0.8045502988523805</v>
+        <v>0.6764141835726156</v>
       </c>
       <c r="D151" t="n">
-        <v>-0.03482913716743896</v>
+        <v>-0.0323050760080438</v>
       </c>
       <c r="E151" t="n">
-        <v>0.4490678156098218</v>
+        <v>-0.02445075408311607</v>
       </c>
       <c r="F151" t="n">
-        <v>-0.725565940552177</v>
+        <v>-0.9398811822125357</v>
       </c>
     </row>
     <row r="152">
@@ -3457,19 +3457,19 @@
         <v>45853</v>
       </c>
       <c r="B152" t="n">
-        <v>0.5160093291435328</v>
+        <v>0.6163581579278929</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.3784923782274135</v>
+        <v>-0.3106720279439172</v>
       </c>
       <c r="D152" t="n">
-        <v>0.0978222966111356</v>
+        <v>0.03812632761331951</v>
       </c>
       <c r="E152" t="n">
-        <v>-0.03243314082125377</v>
+        <v>-0.01039602823012773</v>
       </c>
       <c r="F152" t="n">
-        <v>-0.1791532699873996</v>
+        <v>-0.1559870957657522</v>
       </c>
     </row>
     <row r="153">
@@ -3477,19 +3477,19 @@
         <v>45854</v>
       </c>
       <c r="B153" t="n">
-        <v>0.6546288789443933</v>
+        <v>0.8121955277251708</v>
       </c>
       <c r="C153" t="n">
-        <v>-0.1942035332467529</v>
+        <v>-0.1067170556818969</v>
       </c>
       <c r="D153" t="n">
-        <v>0.0240038714952509</v>
+        <v>-0.008164920303130475</v>
       </c>
       <c r="E153" t="n">
-        <v>0.05853797962760328</v>
+        <v>-0.1402546908436291</v>
       </c>
       <c r="F153" t="n">
-        <v>0.1701597031346058</v>
+        <v>0.1596740898281709</v>
       </c>
     </row>
     <row r="154">
@@ -3497,19 +3497,19 @@
         <v>45855</v>
       </c>
       <c r="B154" t="n">
-        <v>0.6185220604516759</v>
+        <v>0.9546081723701939</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.3892795485658977</v>
+        <v>-0.472491040072152</v>
       </c>
       <c r="D154" t="n">
-        <v>0.4739656189979754</v>
+        <v>0.3828854776149173</v>
       </c>
       <c r="E154" t="n">
-        <v>-0.07284280199033785</v>
+        <v>0.1302712174817462</v>
       </c>
       <c r="F154" t="n">
-        <v>0.01837404034239477</v>
+        <v>0.06924003643309248</v>
       </c>
     </row>
     <row r="155">
@@ -3517,19 +3517,19 @@
         <v>45856</v>
       </c>
       <c r="B155" t="n">
-        <v>0.5382015097176039</v>
+        <v>0.04871055084569401</v>
       </c>
       <c r="C155" t="n">
-        <v>0.3147671339845501</v>
+        <v>0.2319555343713409</v>
       </c>
       <c r="D155" t="n">
-        <v>-0.035564842042038</v>
+        <v>-0.02459451467472942</v>
       </c>
       <c r="E155" t="n">
-        <v>0.1536051290998768</v>
+        <v>0.06279312660890565</v>
       </c>
       <c r="F155" t="n">
-        <v>-0.3187424624874165</v>
+        <v>-0.4497245447540031</v>
       </c>
     </row>
     <row r="156">
@@ -3537,19 +3537,19 @@
         <v>45859</v>
       </c>
       <c r="B156" t="n">
-        <v>-0.5215468485570189</v>
+        <v>-0.1793600665264673</v>
       </c>
       <c r="C156" t="n">
-        <v>-0.6823115667277895</v>
+        <v>-0.6741629991067661</v>
       </c>
       <c r="D156" t="n">
-        <v>0.2375167864520892</v>
+        <v>0.2014047224234199</v>
       </c>
       <c r="E156" t="n">
-        <v>0.05629602925201579</v>
+        <v>-0.2171985581379304</v>
       </c>
       <c r="F156" t="n">
-        <v>0.263513459061099</v>
+        <v>0.2944233103610238</v>
       </c>
     </row>
     <row r="157">
@@ -3557,19 +3557,19 @@
         <v>45860</v>
       </c>
       <c r="B157" t="n">
-        <v>0.5260310851926858</v>
+        <v>0.5652785873178593</v>
       </c>
       <c r="C157" t="n">
-        <v>0.05412354809005687</v>
+        <v>-0.06708349864849505</v>
       </c>
       <c r="D157" t="n">
-        <v>0.6853167287788507</v>
+        <v>0.815219800634382</v>
       </c>
       <c r="E157" t="n">
-        <v>0.2734182933740543</v>
+        <v>-0.1179056001712282</v>
       </c>
       <c r="F157" t="n">
-        <v>0.2028079656122697</v>
+        <v>-0.1302525278636478</v>
       </c>
     </row>
     <row r="158">
@@ -3577,19 +3577,19 @@
         <v>45861</v>
       </c>
       <c r="B158" t="n">
-        <v>-0.3334148394586032</v>
+        <v>-0.1609898281457661</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.3126110323115778</v>
+        <v>-0.2885639153564538</v>
       </c>
       <c r="D158" t="n">
-        <v>-0.1435327866924201</v>
+        <v>-0.1967671885638723</v>
       </c>
       <c r="E158" t="n">
-        <v>0.4346547569827675</v>
+        <v>-0.4709582195253678</v>
       </c>
       <c r="F158" t="n">
-        <v>0.2242397857365747</v>
+        <v>-0.007534496021101289</v>
       </c>
     </row>
     <row r="159">
@@ -3597,19 +3597,19 @@
         <v>45862</v>
       </c>
       <c r="B159" t="n">
-        <v>-1.090702647688722</v>
+        <v>-2.23961823995939</v>
       </c>
       <c r="C159" t="n">
-        <v>0.3477007019758638</v>
+        <v>0.3942587506343892</v>
       </c>
       <c r="D159" t="n">
-        <v>0.06772280254032124</v>
+        <v>0.2407390054239654</v>
       </c>
       <c r="E159" t="n">
-        <v>0.132571029389677</v>
+        <v>-0.1787067646082179</v>
       </c>
       <c r="F159" t="n">
-        <v>-0.1879916082348948</v>
+        <v>-0.2024943805862063</v>
       </c>
     </row>
     <row r="160">
@@ -3617,19 +3617,19 @@
         <v>45863</v>
       </c>
       <c r="B160" t="n">
-        <v>-1.674062744617989</v>
+        <v>-1.71252394199846</v>
       </c>
       <c r="C160" t="n">
-        <v>1.099343773362554</v>
+        <v>1.121732466841923</v>
       </c>
       <c r="D160" t="n">
-        <v>0.1748613485540944</v>
+        <v>0.5000634779344549</v>
       </c>
       <c r="E160" t="n">
-        <v>-0.001880297360827932</v>
+        <v>0.09615853140190787</v>
       </c>
       <c r="F160" t="n">
-        <v>0.1573214297856244</v>
+        <v>-0.154583182905777</v>
       </c>
     </row>
     <row r="161">
@@ -3637,19 +3637,19 @@
         <v>45866</v>
       </c>
       <c r="B161" t="n">
-        <v>-1.563294049756774</v>
+        <v>-1.743668184313267</v>
       </c>
       <c r="C161" t="n">
-        <v>0.9316574793424085</v>
+        <v>0.9667881736975407</v>
       </c>
       <c r="D161" t="n">
-        <v>-0.4594130052550911</v>
+        <v>-0.3456819214460952</v>
       </c>
       <c r="E161" t="n">
-        <v>-0.1124114510969129</v>
+        <v>0.4353150290063004</v>
       </c>
       <c r="F161" t="n">
-        <v>-0.467762303296245</v>
+        <v>-0.499414832881959</v>
       </c>
     </row>
     <row r="162">
@@ -3657,19 +3657,19 @@
         <v>45867</v>
       </c>
       <c r="B162" t="n">
-        <v>-2.317974433091288</v>
+        <v>-2.289528194505851</v>
       </c>
       <c r="C162" t="n">
-        <v>0.02210392193773465</v>
+        <v>0.08265218415785788</v>
       </c>
       <c r="D162" t="n">
-        <v>-0.1464372612785004</v>
+        <v>0.06477308937633257</v>
       </c>
       <c r="E162" t="n">
-        <v>0.01792926109034012</v>
+        <v>-0.2124418999007593</v>
       </c>
       <c r="F162" t="n">
-        <v>0.1030281509250547</v>
+        <v>-0.08302637297719713</v>
       </c>
     </row>
     <row r="163">
@@ -3677,19 +3677,19 @@
         <v>45868</v>
       </c>
       <c r="B163" t="n">
-        <v>4.283091862629187</v>
+        <v>4.33258917584777</v>
       </c>
       <c r="C163" t="n">
-        <v>0.2571927351845562</v>
+        <v>0.3033506527743213</v>
       </c>
       <c r="D163" t="n">
-        <v>-0.2229236969654688</v>
+        <v>-0.1534456968852648</v>
       </c>
       <c r="E163" t="n">
-        <v>0.07613604732909129</v>
+        <v>-0.1324909053913303</v>
       </c>
       <c r="F163" t="n">
-        <v>0.1185122230184905</v>
+        <v>0.09458077303924065</v>
       </c>
     </row>
     <row r="164">
@@ -3697,19 +3697,19 @@
         <v>45869</v>
       </c>
       <c r="B164" t="n">
-        <v>1.739164926571992</v>
+        <v>1.587447915689395</v>
       </c>
       <c r="C164" t="n">
-        <v>-0.01041030414625894</v>
+        <v>0.05775922448645279</v>
       </c>
       <c r="D164" t="n">
-        <v>0.2155778427341783</v>
+        <v>0.2523131537965338</v>
       </c>
       <c r="E164" t="n">
-        <v>-0.2963747141730548</v>
+        <v>0.1504185756217038</v>
       </c>
       <c r="F164" t="n">
-        <v>0.3809620786678346</v>
+        <v>0.4947737752838731</v>
       </c>
     </row>
     <row r="165">
@@ -3717,19 +3717,19 @@
         <v>45873</v>
       </c>
       <c r="B165" t="n">
-        <v>1.630317542369364</v>
+        <v>1.71261746008725</v>
       </c>
       <c r="C165" t="n">
-        <v>0.0831225077464831</v>
+        <v>0.1219606905435736</v>
       </c>
       <c r="D165" t="n">
-        <v>-0.2126289991011129</v>
+        <v>-0.1956179990675279</v>
       </c>
       <c r="E165" t="n">
-        <v>0.06033557244531518</v>
+        <v>0.1031044709185413</v>
       </c>
       <c r="F165" t="n">
-        <v>-0.2626796158130145</v>
+        <v>-0.2666383983178233</v>
       </c>
     </row>
     <row r="166">
@@ -3737,19 +3737,19 @@
         <v>45874</v>
       </c>
       <c r="B166" t="n">
-        <v>1.387184876346875</v>
+        <v>1.56405891376041</v>
       </c>
       <c r="C166" t="n">
-        <v>-0.09216849768051504</v>
+        <v>-0.09828154719920479</v>
       </c>
       <c r="D166" t="n">
-        <v>0.5896789781820229</v>
+        <v>0.4934352041103157</v>
       </c>
       <c r="E166" t="n">
-        <v>-0.01209420091725312</v>
+        <v>0.02652299380207305</v>
       </c>
       <c r="F166" t="n">
-        <v>0.1214325493361596</v>
+        <v>0.09474868772262866</v>
       </c>
     </row>
     <row r="167">
@@ -3757,19 +3757,19 @@
         <v>45875</v>
       </c>
       <c r="B167" t="n">
-        <v>1.118697654448651</v>
+        <v>1.1790986490365</v>
       </c>
       <c r="C167" t="n">
-        <v>-0.3131020141866237</v>
+        <v>-0.3393494532773552</v>
       </c>
       <c r="D167" t="n">
-        <v>0.1179624514305321</v>
+        <v>0.1674759002399645</v>
       </c>
       <c r="E167" t="n">
-        <v>0.3520748450632434</v>
+        <v>-0.2676010107037695</v>
       </c>
       <c r="F167" t="n">
-        <v>0.1140648263510552</v>
+        <v>-0.1283771141308196</v>
       </c>
     </row>
     <row r="168">
@@ -3777,19 +3777,19 @@
         <v>45876</v>
       </c>
       <c r="B168" t="n">
-        <v>0.3547817027602465</v>
+        <v>0.4650838734870963</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.06857897028183241</v>
+        <v>0.03534483074378098</v>
       </c>
       <c r="D168" t="n">
-        <v>0.262170011426523</v>
+        <v>0.2917411784168142</v>
       </c>
       <c r="E168" t="n">
-        <v>-0.04463894374159753</v>
+        <v>-0.07339231797057236</v>
       </c>
       <c r="F168" t="n">
-        <v>0.4758721502244802</v>
+        <v>0.3075396359024621</v>
       </c>
     </row>
     <row r="169">
@@ -3797,19 +3797,19 @@
         <v>45877</v>
       </c>
       <c r="B169" t="n">
-        <v>-0.7815089196843964</v>
+        <v>-0.4321887759356882</v>
       </c>
       <c r="C169" t="n">
-        <v>0.0007343837460194792</v>
+        <v>-0.1152714758364387</v>
       </c>
       <c r="D169" t="n">
-        <v>0.8449474183585362</v>
+        <v>0.7820448814212309</v>
       </c>
       <c r="E169" t="n">
-        <v>-0.1175439107102023</v>
+        <v>0.3178692463030215</v>
       </c>
       <c r="F169" t="n">
-        <v>-0.1175647570952574</v>
+        <v>-0.0522123780162807</v>
       </c>
     </row>
     <row r="170">
@@ -3817,19 +3817,19 @@
         <v>45880</v>
       </c>
       <c r="B170" t="n">
-        <v>-0.8669328952143129</v>
+        <v>-0.6662016139019559</v>
       </c>
       <c r="C170" t="n">
-        <v>-0.3266826728434739</v>
+        <v>-0.3075566918521289</v>
       </c>
       <c r="D170" t="n">
-        <v>0.03006835142495688</v>
+        <v>-0.08179658459641398</v>
       </c>
       <c r="E170" t="n">
-        <v>-0.05011196334104587</v>
+        <v>-0.1061681870989471</v>
       </c>
       <c r="F170" t="n">
-        <v>0.08584475609975964</v>
+        <v>0.06664944110616036</v>
       </c>
     </row>
     <row r="171">
@@ -3837,19 +3837,19 @@
         <v>45881</v>
       </c>
       <c r="B171" t="n">
-        <v>0.7914386315771271</v>
+        <v>0.8752292354531845</v>
       </c>
       <c r="C171" t="n">
-        <v>-0.4946664402011874</v>
+        <v>-0.4496838241183196</v>
       </c>
       <c r="D171" t="n">
-        <v>-0.01660569075934273</v>
+        <v>0.01662717371105953</v>
       </c>
       <c r="E171" t="n">
-        <v>0.04560021681326818</v>
+        <v>-0.1569941634810992</v>
       </c>
       <c r="F171" t="n">
-        <v>0.2966705023249976</v>
+        <v>0.2734763504076931</v>
       </c>
     </row>
     <row r="172">
@@ -3857,19 +3857,19 @@
         <v>45882</v>
       </c>
       <c r="B172" t="n">
-        <v>-1.131750840523617</v>
+        <v>-0.9900588193843824</v>
       </c>
       <c r="C172" t="n">
-        <v>0.2357306713078537</v>
+        <v>0.05719294041323708</v>
       </c>
       <c r="D172" t="n">
-        <v>0.6164479746010931</v>
+        <v>0.6049089084212573</v>
       </c>
       <c r="E172" t="n">
-        <v>0.0529970484674427</v>
+        <v>0.0004615137340601511</v>
       </c>
       <c r="F172" t="n">
-        <v>0.0936368788861965</v>
+        <v>-0.03214103672580931</v>
       </c>
     </row>
     <row r="173">
@@ -3877,19 +3877,19 @@
         <v>45883</v>
       </c>
       <c r="B173" t="n">
-        <v>0.6795007242073848</v>
+        <v>0.9885302089767862</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.07340339969023124</v>
+        <v>-0.01698855892138255</v>
       </c>
       <c r="D173" t="n">
-        <v>0.1006040441364853</v>
+        <v>0.1158254650960429</v>
       </c>
       <c r="E173" t="n">
-        <v>-0.2837362732916661</v>
+        <v>0.04101626700581701</v>
       </c>
       <c r="F173" t="n">
-        <v>0.2853252894497569</v>
+        <v>0.3743054085466838</v>
       </c>
     </row>
     <row r="174">
@@ -3897,19 +3897,19 @@
         <v>45884</v>
       </c>
       <c r="B174" t="n">
-        <v>-0.2323457869265317</v>
+        <v>-0.1856748413800654</v>
       </c>
       <c r="C174" t="n">
-        <v>0.09941384720022309</v>
+        <v>-0.1265526578866625</v>
       </c>
       <c r="D174" t="n">
-        <v>0.6043302022042595</v>
+        <v>0.6277004473260143</v>
       </c>
       <c r="E174" t="n">
-        <v>0.008310663455207612</v>
+        <v>0.1443015395418269</v>
       </c>
       <c r="F174" t="n">
-        <v>-0.3723116130804279</v>
+        <v>-0.256539391628523</v>
       </c>
     </row>
     <row r="175">
@@ -3917,19 +3917,19 @@
         <v>45887</v>
       </c>
       <c r="B175" t="n">
-        <v>-2.35133246313159</v>
+        <v>-2.515909679089398</v>
       </c>
       <c r="C175" t="n">
-        <v>0.3832595839146286</v>
+        <v>0.4131988655750557</v>
       </c>
       <c r="D175" t="n">
-        <v>-0.238843163263489</v>
+        <v>-0.01724933452738471</v>
       </c>
       <c r="E175" t="n">
-        <v>0.3110234321760584</v>
+        <v>-0.1276210294472931</v>
       </c>
       <c r="F175" t="n">
-        <v>0.02519672881527719</v>
+        <v>-0.2042750656928097</v>
       </c>
     </row>
     <row r="176">
@@ -3937,19 +3937,19 @@
         <v>45888</v>
       </c>
       <c r="B176" t="n">
-        <v>1.647884931996751</v>
+        <v>1.746608532097565</v>
       </c>
       <c r="C176" t="n">
-        <v>0.2319375759928687</v>
+        <v>0.1439386956909497</v>
       </c>
       <c r="D176" t="n">
-        <v>0.2868326192540006</v>
+        <v>0.3642593746333693</v>
       </c>
       <c r="E176" t="n">
-        <v>0.07330236699199855</v>
+        <v>-0.01057387383083037</v>
       </c>
       <c r="F176" t="n">
-        <v>-0.06837671415059318</v>
+        <v>-0.05656822830588751</v>
       </c>
     </row>
     <row r="177">
@@ -3957,19 +3957,19 @@
         <v>45889</v>
       </c>
       <c r="B177" t="n">
-        <v>-2.527981168448433</v>
+        <v>-2.173270023250737</v>
       </c>
       <c r="C177" t="n">
-        <v>0.09039726041426466</v>
+        <v>0.09063074003577337</v>
       </c>
       <c r="D177" t="n">
-        <v>-0.1911149029445579</v>
+        <v>-0.06985118351099713</v>
       </c>
       <c r="E177" t="n">
-        <v>-0.001086237689928449</v>
+        <v>-0.1448449512359731</v>
       </c>
       <c r="F177" t="n">
-        <v>0.107608939320306</v>
+        <v>0.09229100857680744</v>
       </c>
     </row>
     <row r="178">
@@ -3977,19 +3977,19 @@
         <v>45890</v>
       </c>
       <c r="B178" t="n">
-        <v>-0.4986939026258466</v>
+        <v>-0.5686049288831715</v>
       </c>
       <c r="C178" t="n">
-        <v>0.563767581154748</v>
+        <v>0.5969734116357678</v>
       </c>
       <c r="D178" t="n">
-        <v>-0.6861281161214631</v>
+        <v>-0.5431273580610697</v>
       </c>
       <c r="E178" t="n">
-        <v>0.3546797719860487</v>
+        <v>-0.1825804955802858</v>
       </c>
       <c r="F178" t="n">
-        <v>-0.3995723864666161</v>
+        <v>-0.4063736675587061</v>
       </c>
     </row>
     <row r="179">
@@ -3997,19 +3997,19 @@
         <v>45891</v>
       </c>
       <c r="B179" t="n">
-        <v>1.058461213126426</v>
+        <v>1.26041985431246</v>
       </c>
       <c r="C179" t="n">
-        <v>-0.8086998525309893</v>
+        <v>-0.6805622631417789</v>
       </c>
       <c r="D179" t="n">
-        <v>-0.1311631396046783</v>
+        <v>-0.2925830398026744</v>
       </c>
       <c r="E179" t="n">
-        <v>0.03641186403422663</v>
+        <v>-0.2372996859704661</v>
       </c>
       <c r="F179" t="n">
-        <v>0.3746812682873379</v>
+        <v>0.4235821019329965</v>
       </c>
     </row>
     <row r="180">
@@ -4017,19 +4017,19 @@
         <v>45894</v>
       </c>
       <c r="B180" t="n">
-        <v>-1.682037426906356</v>
+        <v>-2.971456720512025</v>
       </c>
       <c r="C180" t="n">
-        <v>-0.08665256349177931</v>
+        <v>-0.07483199008661788</v>
       </c>
       <c r="D180" t="n">
-        <v>0.03568099870299135</v>
+        <v>-0.02811164229173082</v>
       </c>
       <c r="E180" t="n">
-        <v>-0.1015483211139487</v>
+        <v>0.1904950793765071</v>
       </c>
       <c r="F180" t="n">
-        <v>-0.0220803730939299</v>
+        <v>0.3392699937876536</v>
       </c>
     </row>
     <row r="181">
@@ -4037,19 +4037,19 @@
         <v>45895</v>
       </c>
       <c r="B181" t="n">
-        <v>-3.008739645419993</v>
+        <v>-3.214915752024393</v>
       </c>
       <c r="C181" t="n">
-        <v>0.6824118579383296</v>
+        <v>0.6376214808308933</v>
       </c>
       <c r="D181" t="n">
-        <v>-0.1843099673143992</v>
+        <v>-0.005421957607603201</v>
       </c>
       <c r="E181" t="n">
-        <v>0.04871423506733835</v>
+        <v>0.1328918671862318</v>
       </c>
       <c r="F181" t="n">
-        <v>-0.5004394252787903</v>
+        <v>-0.4626275686991094</v>
       </c>
     </row>
     <row r="182">
@@ -4057,19 +4057,19 @@
         <v>45896</v>
       </c>
       <c r="B182" t="n">
-        <v>-1.207211128816852</v>
+        <v>-1.073321623254885</v>
       </c>
       <c r="C182" t="n">
-        <v>-0.1926559928314056</v>
+        <v>-0.1867055887256232</v>
       </c>
       <c r="D182" t="n">
-        <v>0.6686053451244881</v>
+        <v>0.6381386949667326</v>
       </c>
       <c r="E182" t="n">
-        <v>-0.2130444920957141</v>
+        <v>0.1906645969083219</v>
       </c>
       <c r="F182" t="n">
-        <v>0.0683642873253489</v>
+        <v>0.05011135034631709</v>
       </c>
     </row>
     <row r="183">
@@ -4077,19 +4077,19 @@
         <v>45897</v>
       </c>
       <c r="B183" t="n">
-        <v>-0.5044925796695813</v>
+        <v>-0.5493903085023391</v>
       </c>
       <c r="C183" t="n">
-        <v>-0.4342957884680645</v>
+        <v>-0.1973030503914248</v>
       </c>
       <c r="D183" t="n">
-        <v>-0.8396969324957196</v>
+        <v>-0.802853598538661</v>
       </c>
       <c r="E183" t="n">
-        <v>-0.002405943751360129</v>
+        <v>-0.2319769917136636</v>
       </c>
       <c r="F183" t="n">
-        <v>0.5110802650853548</v>
+        <v>0.5735021968183937</v>
       </c>
     </row>
     <row r="184">
@@ -4097,19 +4097,19 @@
         <v>45898</v>
       </c>
       <c r="B184" t="n">
-        <v>-3.350180140175599</v>
+        <v>-3.447728371325899</v>
       </c>
       <c r="C184" t="n">
-        <v>-0.09127776090489484</v>
+        <v>-0.1249348604057633</v>
       </c>
       <c r="D184" t="n">
-        <v>-0.9501463377054773</v>
+        <v>-0.8220282686591344</v>
       </c>
       <c r="E184" t="n">
-        <v>0.5002532846057205</v>
+        <v>-0.4824438509701528</v>
       </c>
       <c r="F184" t="n">
-        <v>-0.3154651283710799</v>
+        <v>-0.3051969213827814</v>
       </c>
     </row>
     <row r="185">
@@ -4117,19 +4117,19 @@
         <v>45901</v>
       </c>
       <c r="B185" t="n">
-        <v>-3.801252932946241</v>
+        <v>-3.696311447055777</v>
       </c>
       <c r="C185" t="n">
-        <v>0.9152692716052901</v>
+        <v>0.7997184175582387</v>
       </c>
       <c r="D185" t="n">
-        <v>-0.4534329070871683</v>
+        <v>-0.4223731825128053</v>
       </c>
       <c r="E185" t="n">
-        <v>0.08598193760650484</v>
+        <v>-0.03085671852544194</v>
       </c>
       <c r="F185" t="n">
-        <v>-0.2940470326973836</v>
+        <v>-0.4545229430335914</v>
       </c>
     </row>
     <row r="186">
@@ -4137,19 +4137,19 @@
         <v>45902</v>
       </c>
       <c r="B186" t="n">
-        <v>0.5809379905640469</v>
+        <v>0.4279641229209725</v>
       </c>
       <c r="C186" t="n">
-        <v>0.5136271759968873</v>
+        <v>0.5438766057952711</v>
       </c>
       <c r="D186" t="n">
-        <v>-0.5799226660002871</v>
+        <v>-0.4766303779314582</v>
       </c>
       <c r="E186" t="n">
-        <v>0.372219595898001</v>
+        <v>-0.2718359151241675</v>
       </c>
       <c r="F186" t="n">
-        <v>-0.2266241777070829</v>
+        <v>-0.4210637927331002</v>
       </c>
     </row>
     <row r="187">
@@ -4157,19 +4157,19 @@
         <v>45903</v>
       </c>
       <c r="B187" t="n">
-        <v>-3.266789632874578</v>
+        <v>-3.025827823056569</v>
       </c>
       <c r="C187" t="n">
-        <v>0.7991658332989512</v>
+        <v>0.9119874725410645</v>
       </c>
       <c r="D187" t="n">
-        <v>-0.590429125660438</v>
+        <v>-0.5846030018330165</v>
       </c>
       <c r="E187" t="n">
-        <v>-0.3721814587168852</v>
+        <v>0.2255919621076009</v>
       </c>
       <c r="F187" t="n">
-        <v>-0.01488162540441191</v>
+        <v>0.07585203858489704</v>
       </c>
     </row>
     <row r="188">
@@ -4177,19 +4177,19 @@
         <v>45904</v>
       </c>
       <c r="B188" t="n">
-        <v>-2.411127985051158</v>
+        <v>-2.251808256564417</v>
       </c>
       <c r="C188" t="n">
-        <v>-0.2684203376872084</v>
+        <v>-0.1018787345931577</v>
       </c>
       <c r="D188" t="n">
-        <v>0.5522900519047089</v>
+        <v>0.53164910430426</v>
       </c>
       <c r="E188" t="n">
-        <v>-0.5382293793856293</v>
+        <v>0.1691674238908579</v>
       </c>
       <c r="F188" t="n">
-        <v>0.8090829581348861</v>
+        <v>0.943267109543519</v>
       </c>
     </row>
     <row r="189">
@@ -4197,19 +4197,19 @@
         <v>45905</v>
       </c>
       <c r="B189" t="n">
-        <v>1.439731910215679</v>
+        <v>1.71065797356899</v>
       </c>
       <c r="C189" t="n">
-        <v>0.1209197401472314</v>
+        <v>0.1716599073080129</v>
       </c>
       <c r="D189" t="n">
-        <v>-0.289112770524212</v>
+        <v>-0.2699252523701314</v>
       </c>
       <c r="E189" t="n">
-        <v>0.04559431138944634</v>
+        <v>-0.06367367809087664</v>
       </c>
       <c r="F189" t="n">
-        <v>-0.06369772009458896</v>
+        <v>-0.03404434386023652</v>
       </c>
     </row>
     <row r="190">
@@ -4217,19 +4217,19 @@
         <v>45908</v>
       </c>
       <c r="B190" t="n">
-        <v>-2.189245086943819</v>
+        <v>-2.183515219080632</v>
       </c>
       <c r="C190" t="n">
-        <v>0.236535265520085</v>
+        <v>0.2753278427955329</v>
       </c>
       <c r="D190" t="n">
-        <v>-0.2429035953273306</v>
+        <v>0.028319225735875</v>
       </c>
       <c r="E190" t="n">
-        <v>0.4918775572378078</v>
+        <v>-0.3624575154164416</v>
       </c>
       <c r="F190" t="n">
-        <v>-0.2143252035259673</v>
+        <v>-0.5293811293568045</v>
       </c>
     </row>
     <row r="191">
@@ -4237,19 +4237,19 @@
         <v>45909</v>
       </c>
       <c r="B191" t="n">
-        <v>-4.379537646291303</v>
+        <v>-4.738346932046585</v>
       </c>
       <c r="C191" t="n">
-        <v>0.3044800675154382</v>
+        <v>0.46182030076367</v>
       </c>
       <c r="D191" t="n">
-        <v>-0.1945928157719593</v>
+        <v>-0.01208367846394163</v>
       </c>
       <c r="E191" t="n">
-        <v>-0.2489675964283116</v>
+        <v>0.3134914071573399</v>
       </c>
       <c r="F191" t="n">
-        <v>0.4242112321829522</v>
+        <v>0.6097326363988773</v>
       </c>
     </row>
     <row r="192">
@@ -4257,19 +4257,19 @@
         <v>45910</v>
       </c>
       <c r="B192" t="n">
-        <v>-1.011158303282583</v>
+        <v>-0.6844969033321631</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.5198002900403268</v>
+        <v>-0.5108450344921718</v>
       </c>
       <c r="D192" t="n">
-        <v>-0.2395344039712168</v>
+        <v>-0.2898485528593697</v>
       </c>
       <c r="E192" t="n">
-        <v>0.3107873249112711</v>
+        <v>-0.2145156877181637</v>
       </c>
       <c r="F192" t="n">
-        <v>-0.3858937416772719</v>
+        <v>-0.3766831840312727</v>
       </c>
     </row>
     <row r="193">
@@ -4277,19 +4277,19 @@
         <v>45911</v>
       </c>
       <c r="B193" t="n">
-        <v>-1.065850163513712</v>
+        <v>-1.0614145930621</v>
       </c>
       <c r="C193" t="n">
-        <v>0.4649600826736562</v>
+        <v>0.5640512334147697</v>
       </c>
       <c r="D193" t="n">
-        <v>-0.7730716246219936</v>
+        <v>-0.6602176252470702</v>
       </c>
       <c r="E193" t="n">
-        <v>0.03932611954586625</v>
+        <v>0.05765733982952869</v>
       </c>
       <c r="F193" t="n">
-        <v>-0.3716788208553344</v>
+        <v>-0.4195849647850753</v>
       </c>
     </row>
     <row r="194">
@@ -4297,19 +4297,19 @@
         <v>45912</v>
       </c>
       <c r="B194" t="n">
-        <v>-0.4693189029119413</v>
+        <v>-0.6054606104436144</v>
       </c>
       <c r="C194" t="n">
-        <v>0.0510385243632602</v>
+        <v>0.1992003431438102</v>
       </c>
       <c r="D194" t="n">
-        <v>-0.4441618239283193</v>
+        <v>-0.4120210650162763</v>
       </c>
       <c r="E194" t="n">
-        <v>-0.4897481833519063</v>
+        <v>0.1472614235755429</v>
       </c>
       <c r="F194" t="n">
-        <v>0.1924775255530404</v>
+        <v>0.5591514020174149</v>
       </c>
     </row>
     <row r="195">
@@ -4317,19 +4317,19 @@
         <v>45915</v>
       </c>
       <c r="B195" t="n">
-        <v>-0.2301916175806246</v>
+        <v>-0.6212781170781537</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.3804490953697666</v>
+        <v>-0.345938588708828</v>
       </c>
       <c r="D195" t="n">
-        <v>-0.5371715837353426</v>
+        <v>-0.7264964081493506</v>
       </c>
       <c r="E195" t="n">
-        <v>0.007411596225689907</v>
+        <v>0.01907507569327464</v>
       </c>
       <c r="F195" t="n">
-        <v>-0.02593429803961631</v>
+        <v>0.07347776442610952</v>
       </c>
     </row>
     <row r="196">
@@ -4337,19 +4337,19 @@
         <v>45916</v>
       </c>
       <c r="B196" t="n">
-        <v>-1.138597830382591</v>
+        <v>-1.674177874516192</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.5528512537328421</v>
+        <v>-0.4813151094507968</v>
       </c>
       <c r="D196" t="n">
-        <v>-0.7477093536693982</v>
+        <v>-0.9042958633597689</v>
       </c>
       <c r="E196" t="n">
-        <v>0.1150586047559922</v>
+        <v>-0.2787622194297795</v>
       </c>
       <c r="F196" t="n">
-        <v>0.1237740291613196</v>
+        <v>0.2009310007815496</v>
       </c>
     </row>
     <row r="197">
@@ -4357,19 +4357,19 @@
         <v>45917</v>
       </c>
       <c r="B197" t="n">
-        <v>2.359724957306279</v>
+        <v>2.450071817647831</v>
       </c>
       <c r="C197" t="n">
-        <v>0.2985688822063693</v>
+        <v>0.1744938894654877</v>
       </c>
       <c r="D197" t="n">
-        <v>0.168379788690981</v>
+        <v>0.07211988855978167</v>
       </c>
       <c r="E197" t="n">
-        <v>0.1537024014596682</v>
+        <v>-0.01777010428674108</v>
       </c>
       <c r="F197" t="n">
-        <v>-0.05780566771374374</v>
+        <v>-0.183545655520967</v>
       </c>
     </row>
     <row r="198">
@@ -4377,19 +4377,19 @@
         <v>45918</v>
       </c>
       <c r="B198" t="n">
-        <v>-2.593471127668847</v>
+        <v>-2.534533387660709</v>
       </c>
       <c r="C198" t="n">
-        <v>-0.1312425927095015</v>
+        <v>-0.07186330726736932</v>
       </c>
       <c r="D198" t="n">
-        <v>0.09715246788236938</v>
+        <v>0.2265203077204896</v>
       </c>
       <c r="E198" t="n">
-        <v>0.2034965545123459</v>
+        <v>-0.2519690580868696</v>
       </c>
       <c r="F198" t="n">
-        <v>-0.03759964068096666</v>
+        <v>-0.2677606931247703</v>
       </c>
     </row>
     <row r="199">
@@ -4397,19 +4397,19 @@
         <v>45919</v>
       </c>
       <c r="B199" t="n">
-        <v>-2.482669618067271</v>
+        <v>-2.949629524719738</v>
       </c>
       <c r="C199" t="n">
-        <v>0.6557261679613087</v>
+        <v>0.6383834168925928</v>
       </c>
       <c r="D199" t="n">
-        <v>-0.06316539372079646</v>
+        <v>-0.0733800798835028</v>
       </c>
       <c r="E199" t="n">
-        <v>-0.08291602545592741</v>
+        <v>0.5517816730008793</v>
       </c>
       <c r="F199" t="n">
-        <v>-0.4258871105895552</v>
+        <v>-0.6297682262293608</v>
       </c>
     </row>
     <row r="200">
@@ -4417,19 +4417,19 @@
         <v>45922</v>
       </c>
       <c r="B200" t="n">
-        <v>-1.161287785220416</v>
+        <v>-0.9075042323142011</v>
       </c>
       <c r="C200" t="n">
-        <v>0.203354661863107</v>
+        <v>0.20493378396812</v>
       </c>
       <c r="D200" t="n">
-        <v>-0.1862441800216134</v>
+        <v>-0.1593835568505169</v>
       </c>
       <c r="E200" t="n">
-        <v>0.2461214588861522</v>
+        <v>-0.2010842064134737</v>
       </c>
       <c r="F200" t="n">
-        <v>-0.3047213493419363</v>
+        <v>-0.3922396535515209</v>
       </c>
     </row>
     <row r="201">
@@ -4437,19 +4437,19 @@
         <v>45923</v>
       </c>
       <c r="B201" t="n">
-        <v>0.2781084221784078</v>
+        <v>0.5834739280411964</v>
       </c>
       <c r="C201" t="n">
-        <v>0.5926561367470305</v>
+        <v>0.6725128556593227</v>
       </c>
       <c r="D201" t="n">
-        <v>-0.2763465942163574</v>
+        <v>-0.1508503277304674</v>
       </c>
       <c r="E201" t="n">
-        <v>-0.07774304871905079</v>
+        <v>-0.08877371303164337</v>
       </c>
       <c r="F201" t="n">
-        <v>0.3748159282483431</v>
+        <v>0.2773475728303846</v>
       </c>
     </row>
     <row r="202">
@@ -4457,19 +4457,19 @@
         <v>45924</v>
       </c>
       <c r="B202" t="n">
-        <v>-6.718982000779867</v>
+        <v>-6.297547292174846</v>
       </c>
       <c r="C202" t="n">
-        <v>0.07857321117319134</v>
+        <v>0.07654619785901995</v>
       </c>
       <c r="D202" t="n">
-        <v>-0.0009953013182679271</v>
+        <v>0.1968038318187791</v>
       </c>
       <c r="E202" t="n">
-        <v>-0.05608552531390481</v>
+        <v>-0.306511615401991</v>
       </c>
       <c r="F202" t="n">
-        <v>0.1494392670007627</v>
+        <v>0.08684558713585702</v>
       </c>
     </row>
     <row r="203">
@@ -4477,19 +4477,19 @@
         <v>45925</v>
       </c>
       <c r="B203" t="n">
-        <v>-0.4960273827004853</v>
+        <v>-0.3219742040988771</v>
       </c>
       <c r="C203" t="n">
-        <v>-0.2978366509255956</v>
+        <v>-0.2991417920062846</v>
       </c>
       <c r="D203" t="n">
-        <v>0.07520816131618967</v>
+        <v>-0.09760953002855424</v>
       </c>
       <c r="E203" t="n">
-        <v>0.04039668389236433</v>
+        <v>0.1147336769416405</v>
       </c>
       <c r="F203" t="n">
-        <v>-0.4101573573827872</v>
+        <v>-0.270931664553843</v>
       </c>
     </row>
     <row r="204">
@@ -4497,19 +4497,19 @@
         <v>45926</v>
       </c>
       <c r="B204" t="n">
-        <v>-2.366011275800803</v>
+        <v>-2.531299790123219</v>
       </c>
       <c r="C204" t="n">
-        <v>0.09299030133309981</v>
+        <v>0.05707728885874807</v>
       </c>
       <c r="D204" t="n">
-        <v>-0.7276668426106394</v>
+        <v>-0.6135393705350093</v>
       </c>
       <c r="E204" t="n">
-        <v>0.5188804015485012</v>
+        <v>-0.368703444975158</v>
       </c>
       <c r="F204" t="n">
-        <v>-0.5443147545225226</v>
+        <v>-0.75340512381326</v>
       </c>
     </row>
     <row r="205">
@@ -4517,19 +4517,19 @@
         <v>45929</v>
       </c>
       <c r="B205" t="n">
-        <v>0.5461289896099907</v>
+        <v>0.3954251139512736</v>
       </c>
       <c r="C205" t="n">
-        <v>-0.08226139304614494</v>
+        <v>-0.1187514398925325</v>
       </c>
       <c r="D205" t="n">
-        <v>0.1671397270130713</v>
+        <v>0.1924030087222057</v>
       </c>
       <c r="E205" t="n">
-        <v>0.04185822723044311</v>
+        <v>0.01679551785581305</v>
       </c>
       <c r="F205" t="n">
-        <v>0.06627867495827781</v>
+        <v>0.04552430716538522</v>
       </c>
     </row>
     <row r="206">
@@ -4537,19 +4537,19 @@
         <v>45930</v>
       </c>
       <c r="B206" t="n">
-        <v>-2.706987751370695</v>
+        <v>-2.914273539202701</v>
       </c>
       <c r="C206" t="n">
-        <v>0.7893285300125881</v>
+        <v>0.7793047837173476</v>
       </c>
       <c r="D206" t="n">
-        <v>-0.06657178573136102</v>
+        <v>0.1840670040276237</v>
       </c>
       <c r="E206" t="n">
-        <v>0.3415500346481359</v>
+        <v>0.03419175143287147</v>
       </c>
       <c r="F206" t="n">
-        <v>-0.2448286194373608</v>
+        <v>-0.4593075942286253</v>
       </c>
     </row>
     <row r="207">
@@ -4557,19 +4557,19 @@
         <v>45931</v>
       </c>
       <c r="B207" t="n">
-        <v>-1.750596996870724</v>
+        <v>-1.710866044102786</v>
       </c>
       <c r="C207" t="n">
-        <v>0.7238231659102312</v>
+        <v>0.8048101324421881</v>
       </c>
       <c r="D207" t="n">
-        <v>-0.1214666935141644</v>
+        <v>0.08430742790676878</v>
       </c>
       <c r="E207" t="n">
-        <v>-0.148974986215503</v>
+        <v>0.2528496456893921</v>
       </c>
       <c r="F207" t="n">
-        <v>-0.1417256630251092</v>
+        <v>-0.2265328271002217</v>
       </c>
     </row>
     <row r="208">
@@ -4577,19 +4577,19 @@
         <v>45932</v>
       </c>
       <c r="B208" t="n">
-        <v>-2.412545775795364</v>
+        <v>-2.087351741023841</v>
       </c>
       <c r="C208" t="n">
-        <v>0.4677163973034241</v>
+        <v>0.4117245872168268</v>
       </c>
       <c r="D208" t="n">
-        <v>-0.4765638726337664</v>
+        <v>-0.4601653888210097</v>
       </c>
       <c r="E208" t="n">
-        <v>-0.05530062403992575</v>
+        <v>0.2007858759286318</v>
       </c>
       <c r="F208" t="n">
-        <v>-0.5209679012040482</v>
+        <v>-0.4162185617986158</v>
       </c>
     </row>
     <row r="209">
@@ -4597,19 +4597,19 @@
         <v>45933</v>
       </c>
       <c r="B209" t="n">
-        <v>-1.412365924042992</v>
+        <v>-1.050806023613709</v>
       </c>
       <c r="C209" t="n">
-        <v>-0.5197556943792404</v>
+        <v>-0.6944794015519338</v>
       </c>
       <c r="D209" t="n">
-        <v>1.485756921697837</v>
+        <v>1.332202865265116</v>
       </c>
       <c r="E209" t="n">
-        <v>0.5248622732643334</v>
+        <v>-0.01810077841738867</v>
       </c>
       <c r="F209" t="n">
-        <v>0.1460374892030008</v>
+        <v>-0.1080473034317879</v>
       </c>
     </row>
     <row r="210">
@@ -4617,19 +4617,19 @@
         <v>45936</v>
       </c>
       <c r="B210" t="n">
-        <v>-1.895223958620017</v>
+        <v>-1.634711930726086</v>
       </c>
       <c r="C210" t="n">
-        <v>0.590498585026654</v>
+        <v>0.5003743255233143</v>
       </c>
       <c r="D210" t="n">
-        <v>-0.0001887068445572737</v>
+        <v>-0.03752690994080857</v>
       </c>
       <c r="E210" t="n">
-        <v>0.06073707015700236</v>
+        <v>0.09092697572985849</v>
       </c>
       <c r="F210" t="n">
-        <v>-0.3653741722549591</v>
+        <v>-0.3880119341915245</v>
       </c>
     </row>
     <row r="211">
@@ -4637,19 +4637,19 @@
         <v>45937</v>
       </c>
       <c r="B211" t="n">
-        <v>-1.955094982518056</v>
+        <v>-2.070941604286682</v>
       </c>
       <c r="C211" t="n">
-        <v>0.6930389963009452</v>
+        <v>0.5955772477519699</v>
       </c>
       <c r="D211" t="n">
-        <v>0.3005962126258779</v>
+        <v>0.442765473086649</v>
       </c>
       <c r="E211" t="n">
-        <v>-0.2024511382045283</v>
+        <v>0.2892434049225592</v>
       </c>
       <c r="F211" t="n">
-        <v>-0.2152539226325276</v>
+        <v>-0.1773214722526585</v>
       </c>
     </row>
     <row r="212">
@@ -4657,19 +4657,19 @@
         <v>45938</v>
       </c>
       <c r="B212" t="n">
-        <v>-2.136498221871474</v>
+        <v>-2.276599590014448</v>
       </c>
       <c r="C212" t="n">
-        <v>-0.05366363765841803</v>
+        <v>-0.02805101317237917</v>
       </c>
       <c r="D212" t="n">
-        <v>-0.3226010741748288</v>
+        <v>-0.1753647346749362</v>
       </c>
       <c r="E212" t="n">
-        <v>0.1870439912982777</v>
+        <v>-0.06206199310980945</v>
       </c>
       <c r="F212" t="n">
-        <v>0.04807034775816752</v>
+        <v>-0.01042003981142936</v>
       </c>
     </row>
     <row r="213">
@@ -4677,19 +4677,19 @@
         <v>45939</v>
       </c>
       <c r="B213" t="n">
-        <v>0.3416496186404294</v>
+        <v>0.04782401717377755</v>
       </c>
       <c r="C213" t="n">
-        <v>0.2227525845414177</v>
+        <v>0.3708938601915637</v>
       </c>
       <c r="D213" t="n">
-        <v>-0.5297063197579398</v>
+        <v>-0.6628708403063059</v>
       </c>
       <c r="E213" t="n">
-        <v>-0.2614572553634051</v>
+        <v>0.3298649499554607</v>
       </c>
       <c r="F213" t="n">
-        <v>-0.1814354912834145</v>
+        <v>0.0363684095173953</v>
       </c>
     </row>
     <row r="214">
@@ -4697,19 +4697,19 @@
         <v>45940</v>
       </c>
       <c r="B214" t="n">
-        <v>1.999833816506988</v>
+        <v>2.140759533504715</v>
       </c>
       <c r="C214" t="n">
-        <v>0.3139019579379016</v>
+        <v>0.3535613438490656</v>
       </c>
       <c r="D214" t="n">
-        <v>-0.241480870137419</v>
+        <v>-0.2662612286945185</v>
       </c>
       <c r="E214" t="n">
-        <v>0.1797772880894721</v>
+        <v>-0.1079205046580203</v>
       </c>
       <c r="F214" t="n">
-        <v>-0.1893309522871882</v>
+        <v>-0.2604246228217327</v>
       </c>
     </row>
     <row r="215">
@@ -4717,19 +4717,19 @@
         <v>45943</v>
       </c>
       <c r="B215" t="n">
-        <v>-1.814578037781311</v>
+        <v>-2.07575330060977</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.2518771666545036</v>
+        <v>-0.1193486407831044</v>
       </c>
       <c r="D215" t="n">
-        <v>-0.7211268321354911</v>
+        <v>-0.8143705462199066</v>
       </c>
       <c r="E215" t="n">
-        <v>-0.264553732322209</v>
+        <v>0.2000024689615586</v>
       </c>
       <c r="F215" t="n">
-        <v>-0.02357884999819682</v>
+        <v>0.2652804216779672</v>
       </c>
     </row>
     <row r="216">
@@ -4737,19 +4737,19 @@
         <v>45944</v>
       </c>
       <c r="B216" t="n">
-        <v>0.7755312678923771</v>
+        <v>0.6999949440902908</v>
       </c>
       <c r="C216" t="n">
-        <v>0.375113484741969</v>
+        <v>0.289440760183724</v>
       </c>
       <c r="D216" t="n">
-        <v>-0.2060226577362691</v>
+        <v>-0.2677225467186031</v>
       </c>
       <c r="E216" t="n">
-        <v>-0.0736165370920847</v>
+        <v>0.2005451734604392</v>
       </c>
       <c r="F216" t="n">
-        <v>-0.544023721192868</v>
+        <v>-0.5009062927605143</v>
       </c>
     </row>
     <row r="217">
@@ -4757,19 +4757,19 @@
         <v>45945</v>
       </c>
       <c r="B217" t="n">
-        <v>1.659732898739317</v>
+        <v>1.900657639780356</v>
       </c>
       <c r="C217" t="n">
-        <v>0.1691524146325666</v>
+        <v>0.2841504920338793</v>
       </c>
       <c r="D217" t="n">
-        <v>-0.1795649630778335</v>
+        <v>-0.206738949388639</v>
       </c>
       <c r="E217" t="n">
-        <v>-0.01373163207614101</v>
+        <v>-0.05467556320872742</v>
       </c>
       <c r="F217" t="n">
-        <v>0.2669595051378916</v>
+        <v>0.2028123489324695</v>
       </c>
     </row>
     <row r="218">
@@ -4777,19 +4777,19 @@
         <v>45946</v>
       </c>
       <c r="B218" t="n">
-        <v>1.80748491760828</v>
+        <v>1.777282034853192</v>
       </c>
       <c r="C218" t="n">
-        <v>0.4681377383890503</v>
+        <v>0.4924072863301048</v>
       </c>
       <c r="D218" t="n">
-        <v>0.3709193290439436</v>
+        <v>0.5552176521996843</v>
       </c>
       <c r="E218" t="n">
-        <v>-0.01047494844536205</v>
+        <v>0.02892784830660235</v>
       </c>
       <c r="F218" t="n">
-        <v>0.3643464111457198</v>
+        <v>0.2755507272272639</v>
       </c>
     </row>
     <row r="219">
@@ -4797,19 +4797,19 @@
         <v>45947</v>
       </c>
       <c r="B219" t="n">
-        <v>0.2252265663232402</v>
+        <v>0.01502874014037494</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.1042128568379891</v>
+        <v>-0.1231398720647346</v>
       </c>
       <c r="D219" t="n">
-        <v>-0.3975274908975026</v>
+        <v>-0.4579677606310396</v>
       </c>
       <c r="E219" t="n">
-        <v>0.2077632692464185</v>
+        <v>-0.154034466263422</v>
       </c>
       <c r="F219" t="n">
-        <v>-0.02276742150335982</v>
+        <v>-0.1732760094654512</v>
       </c>
     </row>
     <row r="220">
@@ -4817,19 +4817,19 @@
         <v>45950</v>
       </c>
       <c r="B220" t="n">
-        <v>-0.7032193433210732</v>
+        <v>-0.9209903079025001</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.3932096239977147</v>
+        <v>-0.217280357783749</v>
       </c>
       <c r="D220" t="n">
-        <v>-0.6773249421283696</v>
+        <v>-0.6822315089488671</v>
       </c>
       <c r="E220" t="n">
-        <v>0.0783462269666827</v>
+        <v>-0.3036406143846917</v>
       </c>
       <c r="F220" t="n">
-        <v>0.4239976754934354</v>
+        <v>0.4351841492290774</v>
       </c>
     </row>
     <row r="221">
@@ -4837,19 +4837,19 @@
         <v>45951</v>
       </c>
       <c r="B221" t="n">
-        <v>-0.6859657232548871</v>
+        <v>-0.753507707855174</v>
       </c>
       <c r="C221" t="n">
-        <v>0.2795263418205317</v>
+        <v>0.2082379997478805</v>
       </c>
       <c r="D221" t="n">
-        <v>0.004445392009113358</v>
+        <v>0.1271849495841383</v>
       </c>
       <c r="E221" t="n">
-        <v>0.1253815702516233</v>
+        <v>-0.2421375183874123</v>
       </c>
       <c r="F221" t="n">
-        <v>-0.08048727119822663</v>
+        <v>-0.1910980288954792</v>
       </c>
     </row>
     <row r="222">
@@ -4857,19 +4857,19 @@
         <v>45952</v>
       </c>
       <c r="B222" t="n">
-        <v>0.7427022172371578</v>
+        <v>0.5999867806664464</v>
       </c>
       <c r="C222" t="n">
-        <v>-0.1015363202741453</v>
+        <v>-0.03383811595418932</v>
       </c>
       <c r="D222" t="n">
-        <v>-0.460516952575199</v>
+        <v>-0.5525021746451969</v>
       </c>
       <c r="E222" t="n">
-        <v>-0.1078779889222102</v>
+        <v>0.1069155653413755</v>
       </c>
       <c r="F222" t="n">
-        <v>-0.1333544103364162</v>
+        <v>-0.03670418027655429</v>
       </c>
     </row>
     <row r="223">
@@ -4877,19 +4877,19 @@
         <v>45953</v>
       </c>
       <c r="B223" t="n">
-        <v>-1.123745927009509</v>
+        <v>-1.247159067284244</v>
       </c>
       <c r="C223" t="n">
-        <v>-0.419683867789147</v>
+        <v>-0.4118843609216323</v>
       </c>
       <c r="D223" t="n">
-        <v>-0.4785721625701737</v>
+        <v>-0.4689820310660755</v>
       </c>
       <c r="E223" t="n">
-        <v>0.08148546008335265</v>
+        <v>-0.1064853097547468</v>
       </c>
       <c r="F223" t="n">
-        <v>-0.1719440452062657</v>
+        <v>-0.05864807697352938</v>
       </c>
     </row>
     <row r="224">
@@ -4897,19 +4897,19 @@
         <v>45954</v>
       </c>
       <c r="B224" t="n">
-        <v>-1.734691111640118</v>
+        <v>-2.369563193156486</v>
       </c>
       <c r="C224" t="n">
-        <v>0.3326346632054263</v>
+        <v>0.6285745161634658</v>
       </c>
       <c r="D224" t="n">
-        <v>-0.9225127002643941</v>
+        <v>-0.8975372878901345</v>
       </c>
       <c r="E224" t="n">
-        <v>0.06295058008139354</v>
+        <v>-0.1950498335455451</v>
       </c>
       <c r="F224" t="n">
-        <v>0.04905024597859924</v>
+        <v>0.02717408432268138</v>
       </c>
     </row>
     <row r="225">
@@ -4917,19 +4917,19 @@
         <v>45957</v>
       </c>
       <c r="B225" t="n">
-        <v>0.2483858160882486</v>
+        <v>0.3522100428762269</v>
       </c>
       <c r="C225" t="n">
-        <v>-0.0526217079404934</v>
+        <v>0.11334603139515</v>
       </c>
       <c r="D225" t="n">
-        <v>-0.5175120703824637</v>
+        <v>-0.450858292433906</v>
       </c>
       <c r="E225" t="n">
-        <v>0.03657990518269618</v>
+        <v>-0.1458518720940135</v>
       </c>
       <c r="F225" t="n">
-        <v>-0.02921008980087463</v>
+        <v>-0.05906199926993408</v>
       </c>
     </row>
     <row r="226">
@@ -4937,19 +4937,19 @@
         <v>45958</v>
       </c>
       <c r="B226" t="n">
-        <v>-2.605389750275462</v>
+        <v>-2.581426835899712</v>
       </c>
       <c r="C226" t="n">
-        <v>0.375715720728335</v>
+        <v>0.2355156345853537</v>
       </c>
       <c r="D226" t="n">
-        <v>0.2693277298473514</v>
+        <v>0.2711056378061173</v>
       </c>
       <c r="E226" t="n">
-        <v>-0.7169424094609133</v>
+        <v>0.5148558796473041</v>
       </c>
       <c r="F226" t="n">
-        <v>-0.08049873429235754</v>
+        <v>0.3283523326520931</v>
       </c>
     </row>
     <row r="227">
@@ -4957,19 +4957,19 @@
         <v>45959</v>
       </c>
       <c r="B227" t="n">
-        <v>-1.351007503075399</v>
+        <v>-1.721717037881546</v>
       </c>
       <c r="C227" t="n">
-        <v>-0.1516084439548502</v>
+        <v>-0.05239842319374719</v>
       </c>
       <c r="D227" t="n">
-        <v>-0.09628055643712444</v>
+        <v>0.02157434110725502</v>
       </c>
       <c r="E227" t="n">
-        <v>-0.04042318118974241</v>
+        <v>-0.115256529837628</v>
       </c>
       <c r="F227" t="n">
-        <v>0.4107862108675544</v>
+        <v>0.4456412773654366</v>
       </c>
     </row>
     <row r="228">
@@ -4977,19 +4977,19 @@
         <v>45960</v>
       </c>
       <c r="B228" t="n">
-        <v>-2.867636724758109</v>
+        <v>-4.5351475842247</v>
       </c>
       <c r="C228" t="n">
-        <v>-0.5521545687794525</v>
+        <v>-0.6542742382147089</v>
       </c>
       <c r="D228" t="n">
-        <v>-0.5739743691472644</v>
+        <v>-0.7025418266907723</v>
       </c>
       <c r="E228" t="n">
-        <v>0.1642905875290659</v>
+        <v>-0.4117127880093595</v>
       </c>
       <c r="F228" t="n">
-        <v>0.2463320700571958</v>
+        <v>0.3857522554032749</v>
       </c>
     </row>
     <row r="229">
@@ -4997,19 +4997,19 @@
         <v>45961</v>
       </c>
       <c r="B229" t="n">
-        <v>-2.461017374153725</v>
+        <v>-2.98838231108765</v>
       </c>
       <c r="C229" t="n">
-        <v>-0.1318871593390658</v>
+        <v>0.007867535281111683</v>
       </c>
       <c r="D229" t="n">
-        <v>-0.2913029338875017</v>
+        <v>-0.2505931382713364</v>
       </c>
       <c r="E229" t="n">
-        <v>-0.09864194313859838</v>
+        <v>-0.1671644121241369</v>
       </c>
       <c r="F229" t="n">
-        <v>0.2978541163599939</v>
+        <v>0.4559605553662908</v>
       </c>
     </row>
     <row r="230">
@@ -5017,19 +5017,19 @@
         <v>45964</v>
       </c>
       <c r="B230" t="n">
-        <v>-2.163277661460814</v>
+        <v>-2.346188083418166</v>
       </c>
       <c r="C230" t="n">
-        <v>0.2959674467072943</v>
+        <v>0.5303244064263714</v>
       </c>
       <c r="D230" t="n">
-        <v>-1.073317453753716</v>
+        <v>-0.8382614384765779</v>
       </c>
       <c r="E230" t="n">
-        <v>0.4807080803567942</v>
+        <v>-0.6209909191247116</v>
       </c>
       <c r="F230" t="n">
-        <v>0.3302541046787249</v>
+        <v>0.06807167575128041</v>
       </c>
     </row>
     <row r="231">
@@ -5037,19 +5037,19 @@
         <v>45965</v>
       </c>
       <c r="B231" t="n">
-        <v>-4.063572970185783</v>
+        <v>-3.681116842820394</v>
       </c>
       <c r="C231" t="n">
-        <v>-1.024214771574694</v>
+        <v>-1.053588390626492</v>
       </c>
       <c r="D231" t="n">
-        <v>0.03287558056962486</v>
+        <v>-0.2072013626670121</v>
       </c>
       <c r="E231" t="n">
-        <v>-0.0377630827088167</v>
+        <v>0.1925423340263723</v>
       </c>
       <c r="F231" t="n">
-        <v>-0.5819504096796723</v>
+        <v>-0.3216169020475645</v>
       </c>
     </row>
     <row r="232">
@@ -5057,19 +5057,19 @@
         <v>45966</v>
       </c>
       <c r="B232" t="n">
-        <v>-0.4619080432157475</v>
+        <v>-0.3306020568159274</v>
       </c>
       <c r="C232" t="n">
-        <v>-1.075061142540739</v>
+        <v>-0.8647230298141353</v>
       </c>
       <c r="D232" t="n">
-        <v>-0.1938657523113383</v>
+        <v>-0.402269204245686</v>
       </c>
       <c r="E232" t="n">
-        <v>-0.4151156148367868</v>
+        <v>-0.03708175764971409</v>
       </c>
       <c r="F232" t="n">
-        <v>0.1097873557580634</v>
+        <v>0.3841948959702755</v>
       </c>
     </row>
     <row r="233">
@@ -5077,19 +5077,19 @@
         <v>45967</v>
       </c>
       <c r="B233" t="n">
-        <v>-1.987687389365859</v>
+        <v>-1.907894865084573</v>
       </c>
       <c r="C233" t="n">
-        <v>-0.6448419195305595</v>
+        <v>-0.6350256956975322</v>
       </c>
       <c r="D233" t="n">
-        <v>0.4212674626114608</v>
+        <v>0.4716969819967471</v>
       </c>
       <c r="E233" t="n">
-        <v>-0.04580180512051207</v>
+        <v>0.01929573277221168</v>
       </c>
       <c r="F233" t="n">
-        <v>-0.03899224889169126</v>
+        <v>-0.02410535648741577</v>
       </c>
     </row>
     <row r="234">
@@ -5097,19 +5097,19 @@
         <v>45968</v>
       </c>
       <c r="B234" t="n">
-        <v>-0.8500024208963556</v>
+        <v>-0.8868557723981649</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.092736505379614</v>
+        <v>-0.0707176482711272</v>
       </c>
       <c r="D234" t="n">
-        <v>-0.163129030421321</v>
+        <v>-0.1005260553386499</v>
       </c>
       <c r="E234" t="n">
-        <v>-0.4042689617048225</v>
+        <v>0.1067960628495768</v>
       </c>
       <c r="F234" t="n">
-        <v>0.08767248558385615</v>
+        <v>0.4310432372021495</v>
       </c>
     </row>
     <row r="235">
@@ -5117,19 +5117,19 @@
         <v>45971</v>
       </c>
       <c r="B235" t="n">
-        <v>-0.9169739162448421</v>
+        <v>-0.9922395903927509</v>
       </c>
       <c r="C235" t="n">
-        <v>-0.3110547352459443</v>
+        <v>-0.2593682558416231</v>
       </c>
       <c r="D235" t="n">
-        <v>0.009492956777070344</v>
+        <v>0.08641819727612608</v>
       </c>
       <c r="E235" t="n">
-        <v>0.07172674283598401</v>
+        <v>-0.1123971362413664</v>
       </c>
       <c r="F235" t="n">
-        <v>0.4719403485851246</v>
+        <v>0.441821091575237</v>
       </c>
     </row>
     <row r="236">
@@ -5137,19 +5137,19 @@
         <v>45972</v>
       </c>
       <c r="B236" t="n">
-        <v>0.5213577903698156</v>
+        <v>0.6309887456354399</v>
       </c>
       <c r="C236" t="n">
-        <v>-0.594737915637191</v>
+        <v>-0.3508214148417312</v>
       </c>
       <c r="D236" t="n">
-        <v>-0.5819176737550382</v>
+        <v>-0.6419936740784231</v>
       </c>
       <c r="E236" t="n">
-        <v>-0.2352039049526912</v>
+        <v>-0.07561681866849959</v>
       </c>
       <c r="F236" t="n">
-        <v>0.06411488543998796</v>
+        <v>0.2463592964157716</v>
       </c>
     </row>
     <row r="237">
@@ -5157,19 +5157,19 @@
         <v>45973</v>
       </c>
       <c r="B237" t="n">
-        <v>-1.513057953905361</v>
+        <v>-1.406785027630518</v>
       </c>
       <c r="C237" t="n">
-        <v>-0.640898334054285</v>
+        <v>-0.716042194201753</v>
       </c>
       <c r="D237" t="n">
-        <v>-0.07599259286089498</v>
+        <v>-0.3358224416269123</v>
       </c>
       <c r="E237" t="n">
-        <v>-0.8478246431927087</v>
+        <v>0.5812642899588444</v>
       </c>
       <c r="F237" t="n">
-        <v>-0.3474877645718579</v>
+        <v>0.2382675572139614</v>
       </c>
     </row>
     <row r="238">
@@ -5177,19 +5177,19 @@
         <v>45974</v>
       </c>
       <c r="B238" t="n">
-        <v>1.50849161871358</v>
+        <v>1.461067756312908</v>
       </c>
       <c r="C238" t="n">
-        <v>-0.05913350397812587</v>
+        <v>-0.1317788087952286</v>
       </c>
       <c r="D238" t="n">
-        <v>0.2559590260666745</v>
+        <v>0.3286586838721245</v>
       </c>
       <c r="E238" t="n">
-        <v>0.2512002574532429</v>
+        <v>-0.07005557918587826</v>
       </c>
       <c r="F238" t="n">
-        <v>0.09158393899309553</v>
+        <v>-0.06021151587895799</v>
       </c>
     </row>
     <row r="239">
@@ -5197,19 +5197,19 @@
         <v>45975</v>
       </c>
       <c r="B239" t="n">
-        <v>1.160234157024224</v>
+        <v>1.291498772492993</v>
       </c>
       <c r="C239" t="n">
-        <v>0.3187587551552722</v>
+        <v>0.3000024686587256</v>
       </c>
       <c r="D239" t="n">
-        <v>0.1248634111192175</v>
+        <v>-0.005640940691179841</v>
       </c>
       <c r="E239" t="n">
-        <v>-0.4616351083120558</v>
+        <v>0.240161703155844</v>
       </c>
       <c r="F239" t="n">
-        <v>0.1409081193589268</v>
+        <v>0.1852486169155247</v>
       </c>
     </row>
     <row r="240">
@@ -5217,19 +5217,19 @@
         <v>45978</v>
       </c>
       <c r="B240" t="n">
-        <v>-0.5170579908156058</v>
+        <v>-0.5350855210267859</v>
       </c>
       <c r="C240" t="n">
-        <v>0.008090645319333378</v>
+        <v>0.04470379942360492</v>
       </c>
       <c r="D240" t="n">
-        <v>-0.1141558013798336</v>
+        <v>-0.06458603061867177</v>
       </c>
       <c r="E240" t="n">
-        <v>-0.5024137578647068</v>
+        <v>0.2656404460514068</v>
       </c>
       <c r="F240" t="n">
-        <v>0.01100774446672115</v>
+        <v>0.4748363795519729</v>
       </c>
     </row>
     <row r="241">
@@ -5237,19 +5237,19 @@
         <v>45979</v>
       </c>
       <c r="B241" t="n">
-        <v>-1.204068089923125</v>
+        <v>-1.573354455210081</v>
       </c>
       <c r="C241" t="n">
-        <v>0.5536231916776545</v>
+        <v>0.6155164040204982</v>
       </c>
       <c r="D241" t="n">
-        <v>-0.138318424491477</v>
+        <v>-0.117105341354985</v>
       </c>
       <c r="E241" t="n">
-        <v>-0.2882379163780229</v>
+        <v>0.2241485225671854</v>
       </c>
       <c r="F241" t="n">
-        <v>-0.1055597657493151</v>
+        <v>-0.04561072558823893</v>
       </c>
     </row>
     <row r="242">
@@ -5257,19 +5257,19 @@
         <v>45980</v>
       </c>
       <c r="B242" t="n">
-        <v>-2.199128390807661</v>
+        <v>-3.389281172677512</v>
       </c>
       <c r="C242" t="n">
-        <v>-0.3506346758516473</v>
+        <v>-0.6026096952669554</v>
       </c>
       <c r="D242" t="n">
-        <v>0.1841808264405837</v>
+        <v>0.151710245781621</v>
       </c>
       <c r="E242" t="n">
-        <v>0.0006508741893439807</v>
+        <v>0.2898268509809501</v>
       </c>
       <c r="F242" t="n">
-        <v>0.03917720857089307</v>
+        <v>0.002907219296607888</v>
       </c>
     </row>
     <row r="243">
@@ -5277,19 +5277,19 @@
         <v>45982</v>
       </c>
       <c r="B243" t="n">
-        <v>1.007193971546554</v>
+        <v>1.104153806226211</v>
       </c>
       <c r="C243" t="n">
-        <v>0.6464302091964627</v>
+        <v>0.6902115607498003</v>
       </c>
       <c r="D243" t="n">
-        <v>-0.3962690450858155</v>
+        <v>-0.3995500200893105</v>
       </c>
       <c r="E243" t="n">
-        <v>-0.3444186031185773</v>
+        <v>0.09215615882528277</v>
       </c>
       <c r="F243" t="n">
-        <v>0.1783206571254796</v>
+        <v>0.2163506069957939</v>
       </c>
     </row>
     <row r="244">
@@ -5297,19 +5297,19 @@
         <v>45985</v>
       </c>
       <c r="B244" t="n">
-        <v>-2.779407681797659</v>
+        <v>-2.451338484446031</v>
       </c>
       <c r="C244" t="n">
-        <v>-0.7051112040017445</v>
+        <v>-0.5458182328748997</v>
       </c>
       <c r="D244" t="n">
-        <v>-0.6159191457308213</v>
+        <v>-0.6583871119247247</v>
       </c>
       <c r="E244" t="n">
-        <v>0.07710044660206503</v>
+        <v>-0.2149174571543608</v>
       </c>
       <c r="F244" t="n">
-        <v>0.07975554185005929</v>
+        <v>0.1993139595370421</v>
       </c>
     </row>
     <row r="245">
@@ -5317,19 +5317,19 @@
         <v>45986</v>
       </c>
       <c r="B245" t="n">
-        <v>0.369535112539098</v>
+        <v>0.3633446751339967</v>
       </c>
       <c r="C245" t="n">
-        <v>0.3829753787047045</v>
+        <v>0.5276568956947721</v>
       </c>
       <c r="D245" t="n">
-        <v>-0.7536059999612306</v>
+        <v>-0.6730103361471836</v>
       </c>
       <c r="E245" t="n">
-        <v>-0.1501824913657651</v>
+        <v>0.1896887073147089</v>
       </c>
       <c r="F245" t="n">
-        <v>-0.1330291327233526</v>
+        <v>-0.07247485886560848</v>
       </c>
     </row>
     <row r="246">
@@ -5337,19 +5337,19 @@
         <v>45987</v>
       </c>
       <c r="B246" t="n">
-        <v>-1.073171113050207</v>
+        <v>-1.505049851505921</v>
       </c>
       <c r="C246" t="n">
-        <v>-1.09993741992831e-05</v>
+        <v>0.104440809205417</v>
       </c>
       <c r="D246" t="n">
-        <v>0.05767120074520166</v>
+        <v>0.1309322153630848</v>
       </c>
       <c r="E246" t="n">
-        <v>0.04227660509226615</v>
+        <v>0.0126962716479941</v>
       </c>
       <c r="F246" t="n">
-        <v>0.3031860327981601</v>
+        <v>0.3260271217603985</v>
       </c>
     </row>
     <row r="247">
@@ -5357,19 +5357,19 @@
         <v>45988</v>
       </c>
       <c r="B247" t="n">
-        <v>-7.352686636334032</v>
+        <v>-7.009968677461611</v>
       </c>
       <c r="C247" t="n">
-        <v>0.99316370505194</v>
+        <v>1.002045400820988</v>
       </c>
       <c r="D247" t="n">
-        <v>-0.6008317848867748</v>
+        <v>-0.5282074044982406</v>
       </c>
       <c r="E247" t="n">
-        <v>0.219706422715139</v>
+        <v>0.1119974667015727</v>
       </c>
       <c r="F247" t="n">
-        <v>-0.9637105704479624</v>
+        <v>-0.922618170580602</v>
       </c>
     </row>
     <row r="248">
@@ -5377,19 +5377,19 @@
         <v>45989</v>
       </c>
       <c r="B248" t="n">
-        <v>-1.535547840835224</v>
+        <v>-1.217288329701981</v>
       </c>
       <c r="C248" t="n">
-        <v>-0.6260172707910265</v>
+        <v>-0.5200956935277581</v>
       </c>
       <c r="D248" t="n">
-        <v>-0.4137071627609543</v>
+        <v>-0.476826653837937</v>
       </c>
       <c r="E248" t="n">
-        <v>0.06572290704525373</v>
+        <v>-0.1777278570892195</v>
       </c>
       <c r="F248" t="n">
-        <v>-0.2508591233475534</v>
+        <v>-0.09928029126672749</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/dfpc_scores.xlsx
+++ b/data/processed/dfpc_scores.xlsx
@@ -457,19 +457,19 @@
         <v>45628</v>
       </c>
       <c r="B2" t="n">
-        <v>1.958356685614624</v>
+        <v>-2.006633394345457</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.6689449354761765</v>
+        <v>1.319768808748043</v>
       </c>
       <c r="D2" t="n">
-        <v>1.006959639280406</v>
+        <v>1.63174846114812</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01123499808397659</v>
+        <v>0.8296891249952568</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2053069453823281</v>
+        <v>0.3800487511232226</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         <v>45629</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8035913285283833</v>
+        <v>-1.69863111722018</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.09198990831421196</v>
+        <v>-1.07435551177384</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.03270931208632955</v>
+        <v>-0.5118241701369847</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.128448781212516</v>
+        <v>-0.1077806476544865</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1352359785177278</v>
+        <v>-0.01748693235170382</v>
       </c>
     </row>
     <row r="4">
@@ -497,19 +497,19 @@
         <v>45630</v>
       </c>
       <c r="B4" t="n">
-        <v>0.4005464238988992</v>
+        <v>0.7504726312310206</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.0523761107395658</v>
+        <v>1.119734527944098</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8802810563987422</v>
+        <v>1.756729225505997</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.02676555487567922</v>
+        <v>0.9594177843132897</v>
       </c>
       <c r="F4" t="n">
-        <v>0.07022039993110878</v>
+        <v>0.9944956400580924</v>
       </c>
     </row>
     <row r="5">
@@ -517,19 +517,19 @@
         <v>45631</v>
       </c>
       <c r="B5" t="n">
-        <v>-1.185181118257078</v>
+        <v>2.214950382811713</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1112881157872983</v>
+        <v>-1.562204059392919</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3738941526119327</v>
+        <v>-0.3498244816622934</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.02587282171305294</v>
+        <v>1.684743888129653</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1373243010906286</v>
+        <v>1.417104832657332</v>
       </c>
     </row>
     <row r="6">
@@ -537,19 +537,19 @@
         <v>45632</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.7367513148878663</v>
+        <v>1.975190185627391</v>
       </c>
       <c r="C6" t="n">
-        <v>1.488960176622684</v>
+        <v>3.265003752210386</v>
       </c>
       <c r="D6" t="n">
-        <v>0.782736864164267</v>
+        <v>-0.4163850425206512</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4208334796782311</v>
+        <v>0.9558658611202699</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1548115321238455</v>
+        <v>1.112752067004814</v>
       </c>
     </row>
     <row r="7">
@@ -557,19 +557,19 @@
         <v>45635</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7004580098479121</v>
+        <v>-1.115379130520231</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.5818957181964696</v>
+        <v>-2.390002870876613</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07036429723015329</v>
+        <v>0.5133536711508996</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.06651923923788226</v>
+        <v>0.8536670594661619</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2850768284013562</v>
+        <v>0.7530329409741205</v>
       </c>
     </row>
     <row r="8">
@@ -577,19 +577,19 @@
         <v>45636</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.8067881154811281</v>
+        <v>1.806403463695434</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1381494191311005</v>
+        <v>-0.5884674942580979</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1089413939190721</v>
+        <v>0.4499057612054456</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1120316999714104</v>
+        <v>-0.2479402471180217</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2291370868375747</v>
+        <v>1.074700623442185</v>
       </c>
     </row>
     <row r="9">
@@ -597,19 +597,19 @@
         <v>45637</v>
       </c>
       <c r="B9" t="n">
-        <v>3.788000104728074</v>
+        <v>-10.17432154652104</v>
       </c>
       <c r="C9" t="n">
-        <v>0.335829170076147</v>
+        <v>-2.976519948813888</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4308967432513633</v>
+        <v>-2.85797959081672</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1291341945833661</v>
+        <v>0.779641503884048</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.102367302656118</v>
+        <v>-0.3114310886992422</v>
       </c>
     </row>
     <row r="10">
@@ -617,19 +617,19 @@
         <v>45638</v>
       </c>
       <c r="B10" t="n">
-        <v>1.137669721888422</v>
+        <v>-2.531870838538045</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.01109755690841314</v>
+        <v>-0.01201296255972557</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2852799455624641</v>
+        <v>-1.791381590677452</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.05007235377494133</v>
+        <v>-1.406065963692346</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.06749023128299085</v>
+        <v>-0.1366775689240997</v>
       </c>
     </row>
     <row r="11">
@@ -637,19 +637,19 @@
         <v>45639</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.8384009375313284</v>
+        <v>2.258735389985342</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2415267141705298</v>
+        <v>2.9718521323506</v>
       </c>
       <c r="D11" t="n">
-        <v>0.486955526695538</v>
+        <v>0.7287797097844092</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2306997534525279</v>
+        <v>0.2461860386159328</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3969261870541537</v>
+        <v>-0.7458563691729444</v>
       </c>
     </row>
     <row r="12">
@@ -657,19 +657,19 @@
         <v>45642</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.9591562543131644</v>
+        <v>2.622930471071168</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.714000195623278</v>
+        <v>0.677970570041096</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.07914537389139445</v>
+        <v>1.484404478503547</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4013220824162444</v>
+        <v>-0.9369944656610847</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2443052795916671</v>
+        <v>-0.4027367705716371</v>
       </c>
     </row>
     <row r="13">
@@ -677,19 +677,19 @@
         <v>45643</v>
       </c>
       <c r="B13" t="n">
-        <v>3.675703199664823</v>
+        <v>-6.211999923070231</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3104541366706348</v>
+        <v>0.4080603944971845</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1711690314571827</v>
+        <v>1.431232105145615</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1926426073886052</v>
+        <v>0.450393746169415</v>
       </c>
       <c r="F13" t="n">
-        <v>0.09574193345509699</v>
+        <v>1.097220006447339</v>
       </c>
     </row>
     <row r="14">
@@ -697,19 +697,19 @@
         <v>45644</v>
       </c>
       <c r="B14" t="n">
-        <v>2.704141645799291</v>
+        <v>-4.252572568769071</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1855313454160554</v>
+        <v>1.327315688302058</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7132068534684286</v>
+        <v>0.4405527728966124</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2022939462518787</v>
+        <v>0.1542989791115331</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2613992954016857</v>
+        <v>0.09875379497854654</v>
       </c>
     </row>
     <row r="15">
@@ -717,19 +717,19 @@
         <v>45645</v>
       </c>
       <c r="B15" t="n">
-        <v>1.59293920888317</v>
+        <v>-2.595676141199938</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.1530137021280542</v>
+        <v>0.148443501430573</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1185930502136967</v>
+        <v>0.6914805545768372</v>
       </c>
       <c r="E15" t="n">
-        <v>0.006957790608417502</v>
+        <v>0.06656079188620799</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2604227902345344</v>
+        <v>-0.3840957577870419</v>
       </c>
     </row>
     <row r="16">
@@ -737,19 +737,19 @@
         <v>45646</v>
       </c>
       <c r="B16" t="n">
-        <v>1.66705829757284</v>
+        <v>-2.721747771055405</v>
       </c>
       <c r="C16" t="n">
-        <v>0.02497439237810851</v>
+        <v>-0.3362875916527265</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2707210967981196</v>
+        <v>1.234175575217167</v>
       </c>
       <c r="E16" t="n">
-        <v>0.09929325894470289</v>
+        <v>-0.3703960813003068</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4395977683441961</v>
+        <v>0.04398086317268424</v>
       </c>
     </row>
     <row r="17">
@@ -757,19 +757,19 @@
         <v>45649</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.5153538982007982</v>
+        <v>1.143240353202331</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2965005737925094</v>
+        <v>1.256867434680127</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1904147230348672</v>
+        <v>-0.7319569187745799</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1765872085248101</v>
+        <v>0.004969471931055081</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3379270810317909</v>
+        <v>-0.2610321332044171</v>
       </c>
     </row>
     <row r="18">
@@ -777,19 +777,19 @@
         <v>45652</v>
       </c>
       <c r="B18" t="n">
-        <v>0.156434201446434</v>
+        <v>0.5154314617883302</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.4034782489333208</v>
+        <v>-0.5341429364687007</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3519760131175526</v>
+        <v>2.412209528288968</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2509260690656418</v>
+        <v>-0.4991006139100773</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7318422309410031</v>
+        <v>-0.005665527931501946</v>
       </c>
     </row>
     <row r="19">
@@ -797,19 +797,19 @@
         <v>45653</v>
       </c>
       <c r="B19" t="n">
-        <v>1.682689372286276</v>
+        <v>-1.931358322290735</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.5151577669984192</v>
+        <v>0.2046239386788555</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6900609995663041</v>
+        <v>1.21105432722745</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1551177501678043</v>
+        <v>0.7726850888826733</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2582173660091493</v>
+        <v>0.1267581043519591</v>
       </c>
     </row>
     <row r="20">
@@ -817,19 +817,19 @@
         <v>45656</v>
       </c>
       <c r="B20" t="n">
-        <v>0.3182446870078257</v>
+        <v>0.9745828131046468</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8292107051129336</v>
+        <v>3.313289923622048</v>
       </c>
       <c r="D20" t="n">
-        <v>1.433302194547047</v>
+        <v>0.6799856276098595</v>
       </c>
       <c r="E20" t="n">
-        <v>0.214368525983533</v>
+        <v>0.8811188071924783</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.04750742793115519</v>
+        <v>1.307681216077266</v>
       </c>
     </row>
     <row r="21">
@@ -837,19 +837,19 @@
         <v>45659</v>
       </c>
       <c r="B21" t="n">
-        <v>2.261644982756497</v>
+        <v>-4.030494608216963</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1991517827327137</v>
+        <v>0.2437691898095145</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3558970884774415</v>
+        <v>-0.253602265322192</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.05783571107804835</v>
+        <v>-0.1623543314888815</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.04393406063755148</v>
+        <v>0.4105526683468534</v>
       </c>
     </row>
     <row r="22">
@@ -857,19 +857,19 @@
         <v>45660</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.2762625561798449</v>
+        <v>-0.05661025446422672</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4268023586161522</v>
+        <v>1.46838271916951</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1955815054311736</v>
+        <v>-1.421860889129233</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.09889526531096696</v>
+        <v>1.220728915389206</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8080297839771152</v>
+        <v>-1.324208216113289</v>
       </c>
     </row>
     <row r="23">
@@ -877,19 +877,19 @@
         <v>45663</v>
       </c>
       <c r="B23" t="n">
-        <v>1.998867383387668</v>
+        <v>-4.932690479768279</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2386121481594057</v>
+        <v>-2.894336467479489</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.08419368982315777</v>
+        <v>-1.312992861102113</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1713520924007513</v>
+        <v>-0.5757629782167097</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3151460420465029</v>
+        <v>0.7927192891829713</v>
       </c>
     </row>
     <row r="24">
@@ -897,19 +897,19 @@
         <v>45664</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.1843844519801889</v>
+        <v>0.7915936178563658</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.4008004537803188</v>
+        <v>-1.216080887895055</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5271452365263206</v>
+        <v>1.726163577587232</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.07512813831310658</v>
+        <v>-0.5009490617179327</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4449981544749843</v>
+        <v>-0.2396601662984609</v>
       </c>
     </row>
     <row r="25">
@@ -917,19 +917,19 @@
         <v>45665</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.5386955220853565</v>
+        <v>1.101268170514453</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8393177501635954</v>
+        <v>1.264788159281592</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.004685384267538889</v>
+        <v>-0.8304469971464785</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2874323643573888</v>
+        <v>0.1836919102590907</v>
       </c>
       <c r="F25" t="n">
-        <v>0.03984215008774414</v>
+        <v>0.1900867378750703</v>
       </c>
     </row>
     <row r="26">
@@ -937,19 +937,19 @@
         <v>45666</v>
       </c>
       <c r="B26" t="n">
-        <v>-2.094832664640359</v>
+        <v>4.56079544404723</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6216954833915764</v>
+        <v>2.11536815212697</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4316465769552436</v>
+        <v>0.3094103316339329</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2851559284108562</v>
+        <v>1.095324646379912</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.3033815971780771</v>
+        <v>0.0287988528652094</v>
       </c>
     </row>
     <row r="27">
@@ -957,19 +957,19 @@
         <v>45667</v>
       </c>
       <c r="B27" t="n">
-        <v>1.099618410702528</v>
+        <v>-2.659115716978549</v>
       </c>
       <c r="C27" t="n">
-        <v>0.3328237261707437</v>
+        <v>0.04070053632561477</v>
       </c>
       <c r="D27" t="n">
-        <v>0.04469840606976523</v>
+        <v>-1.681745180396541</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.08759520528617559</v>
+        <v>-0.745853710137791</v>
       </c>
       <c r="F27" t="n">
-        <v>0.07632967382268641</v>
+        <v>-0.3572089524370765</v>
       </c>
     </row>
     <row r="28">
@@ -977,19 +977,19 @@
         <v>45670</v>
       </c>
       <c r="B28" t="n">
-        <v>-0.4668832185390526</v>
+        <v>1.290384880384979</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1437222650634651</v>
+        <v>-0.4690939528913169</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3092702438841473</v>
+        <v>0.6365442853632086</v>
       </c>
       <c r="E28" t="n">
-        <v>0.04868333812434932</v>
+        <v>-0.3436651360331399</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2676903208365754</v>
+        <v>-0.07974869910825515</v>
       </c>
     </row>
     <row r="29">
@@ -997,19 +997,19 @@
         <v>45671</v>
       </c>
       <c r="B29" t="n">
-        <v>2.441780347415474</v>
+        <v>-4.944617096165411</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1308041538098364</v>
+        <v>0.430089204983086</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1399371003986459</v>
+        <v>-0.7893531318890399</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1289771144100338</v>
+        <v>-0.2750662804849366</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1492721429071309</v>
+        <v>-0.5019722481948042</v>
       </c>
     </row>
     <row r="30">
@@ -1017,19 +1017,19 @@
         <v>45672</v>
       </c>
       <c r="B30" t="n">
-        <v>1.096850836250794</v>
+        <v>-2.662382922769793</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2926413858833911</v>
+        <v>-3.000459011122396</v>
       </c>
       <c r="D30" t="n">
-        <v>0.004682396671152667</v>
+        <v>-1.134990669270515</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1241872797183776</v>
+        <v>1.016033616790659</v>
       </c>
       <c r="F30" t="n">
-        <v>0.04564222656996915</v>
+        <v>0.7892884004386831</v>
       </c>
     </row>
     <row r="31">
@@ -1037,19 +1037,19 @@
         <v>45673</v>
       </c>
       <c r="B31" t="n">
-        <v>-0.7624912783059458</v>
+        <v>2.353367519817517</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3876117793426322</v>
+        <v>1.656216742518608</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2013013269929982</v>
+        <v>1.310695538037921</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3477423835680314</v>
+        <v>-0.9318134774917326</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2186282358818374</v>
+        <v>-0.4061253279451801</v>
       </c>
     </row>
     <row r="32">
@@ -1057,19 +1057,19 @@
         <v>45674</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.793183072740931</v>
+        <v>1.782504896803305</v>
       </c>
       <c r="C32" t="n">
-        <v>-1.468270835351477</v>
+        <v>0.08271120294625334</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1357366466195688</v>
+        <v>1.07135571230995</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.3373681328239043</v>
+        <v>-1.243804303696012</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.05860028280423625</v>
+        <v>-0.985697089866175</v>
       </c>
     </row>
     <row r="33">
@@ -1077,19 +1077,19 @@
         <v>45677</v>
       </c>
       <c r="B33" t="n">
-        <v>0.3239106212613694</v>
+        <v>0.2234111220570207</v>
       </c>
       <c r="C33" t="n">
-        <v>-1.092476013371869</v>
+        <v>-1.48308402004962</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.05576755761455892</v>
+        <v>2.163609564216747</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.03905580626631065</v>
+        <v>-0.6674494898178355</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5073672760076651</v>
+        <v>0.623928326267243</v>
       </c>
     </row>
     <row r="34">
@@ -1097,19 +1097,19 @@
         <v>45678</v>
       </c>
       <c r="B34" t="n">
-        <v>-0.3751591033773422</v>
+        <v>1.775756747283255</v>
       </c>
       <c r="C34" t="n">
-        <v>-1.19670746964222</v>
+        <v>-0.01108230538455679</v>
       </c>
       <c r="D34" t="n">
-        <v>0.09010683617692811</v>
+        <v>2.093783886465162</v>
       </c>
       <c r="E34" t="n">
-        <v>0.164579128166342</v>
+        <v>-0.248600652752588</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.04953820455415278</v>
+        <v>-0.02800511022655958</v>
       </c>
     </row>
     <row r="35">
@@ -1117,19 +1117,19 @@
         <v>45679</v>
       </c>
       <c r="B35" t="n">
-        <v>-0.9040013262353958</v>
+        <v>2.275386396176594</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.9408635321422816</v>
+        <v>0.7636216010352277</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1146856323649111</v>
+        <v>1.036744814295043</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.2697592992399717</v>
+        <v>-0.7201615040239654</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.1660266788875626</v>
+        <v>-0.8578993561221154</v>
       </c>
     </row>
     <row r="36">
@@ -1137,19 +1137,19 @@
         <v>45680</v>
       </c>
       <c r="B36" t="n">
-        <v>1.177878025268143</v>
+        <v>-2.463367900363986</v>
       </c>
       <c r="C36" t="n">
-        <v>0.01972172497577101</v>
+        <v>-0.6240417376090606</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1153735483662444</v>
+        <v>-0.5392298213836383</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.03124523694789088</v>
+        <v>0.1370037348875481</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.3342373044516582</v>
+        <v>-0.6259162361516355</v>
       </c>
     </row>
     <row r="37">
@@ -1157,19 +1157,19 @@
         <v>45681</v>
       </c>
       <c r="B37" t="n">
-        <v>-0.9901445505520226</v>
+        <v>3.165223146724338</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.8445011652166076</v>
+        <v>0.12144045182652</v>
       </c>
       <c r="D37" t="n">
-        <v>0.5892347830926653</v>
+        <v>2.509859698106996</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1342749222797341</v>
+        <v>0.670421439912511</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2275908449324106</v>
+        <v>0.7395975908217021</v>
       </c>
     </row>
     <row r="38">
@@ -1177,19 +1177,19 @@
         <v>45684</v>
       </c>
       <c r="B38" t="n">
-        <v>0.6161812467856032</v>
+        <v>-1.140911884744513</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.5800853525735681</v>
+        <v>-2.366990045267569</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.003293513501177614</v>
+        <v>1.298720820004365</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.2767377707936176</v>
+        <v>-0.5353048741273639</v>
       </c>
       <c r="F38" t="n">
-        <v>0.428760669756848</v>
+        <v>1.095098520794485</v>
       </c>
     </row>
     <row r="39">
@@ -1197,19 +1197,19 @@
         <v>45685</v>
       </c>
       <c r="B39" t="n">
-        <v>-1.973658903773158</v>
+        <v>3.74151772593736</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1773051736865769</v>
+        <v>0.4586151911821063</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1235017956398193</v>
+        <v>-0.01324192892430389</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1609096189855631</v>
+        <v>-1.422045428500784</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5459869896282039</v>
+        <v>0.2085399249330455</v>
       </c>
     </row>
     <row r="40">
@@ -1217,19 +1217,19 @@
         <v>45686</v>
       </c>
       <c r="B40" t="n">
-        <v>-0.219236536537644</v>
+        <v>1.501014622777574</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.8043656124368419</v>
+        <v>-0.9572407066648693</v>
       </c>
       <c r="D40" t="n">
-        <v>0.6199378385152159</v>
+        <v>1.409883263387712</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.1385585971787631</v>
+        <v>1.151791320718816</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.1125956238170956</v>
+        <v>0.3389508582482919</v>
       </c>
     </row>
     <row r="41">
@@ -1237,19 +1237,19 @@
         <v>45687</v>
       </c>
       <c r="B41" t="n">
-        <v>1.380674352874246</v>
+        <v>-3.029108896171412</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3395752222774661</v>
+        <v>-3.105993622404912</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2932612836154425</v>
+        <v>0.4037390259913954</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.1505052252813207</v>
+        <v>0.144732661805242</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3953753939262285</v>
+        <v>0.4470541422635529</v>
       </c>
     </row>
     <row r="42">
@@ -1257,19 +1257,19 @@
         <v>45688</v>
       </c>
       <c r="B42" t="n">
-        <v>0.2457567418654774</v>
+        <v>0.7204089894531632</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.9681618830746284</v>
+        <v>0.877926343880705</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2810145858875045</v>
+        <v>1.72147445269842</v>
       </c>
       <c r="E42" t="n">
-        <v>0.09911780837291971</v>
+        <v>-0.7681399410012691</v>
       </c>
       <c r="F42" t="n">
-        <v>0.03780681551086673</v>
+        <v>-0.5770903395729926</v>
       </c>
     </row>
     <row r="43">
@@ -1277,19 +1277,19 @@
         <v>45691</v>
       </c>
       <c r="B43" t="n">
-        <v>1.234321184111209</v>
+        <v>-1.05176207369789</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.932350814316129</v>
+        <v>-1.686182469732446</v>
       </c>
       <c r="D43" t="n">
-        <v>0.5236622535093466</v>
+        <v>2.460243650138777</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.1554685834693134</v>
+        <v>0.465276760565957</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5545216699871582</v>
+        <v>1.262618949025381</v>
       </c>
     </row>
     <row r="44">
@@ -1297,19 +1297,19 @@
         <v>45692</v>
       </c>
       <c r="B44" t="n">
-        <v>0.08703772671582018</v>
+        <v>-0.6765495811758773</v>
       </c>
       <c r="C44" t="n">
-        <v>0.6864522481046156</v>
+        <v>-0.7836503030607744</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.228490799756413</v>
+        <v>-1.240382165423168</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1701207551950865</v>
+        <v>1.19843675434565</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.3357214092774188</v>
+        <v>0.1052090720176488</v>
       </c>
     </row>
     <row r="45">
@@ -1317,19 +1317,19 @@
         <v>45693</v>
       </c>
       <c r="B45" t="n">
-        <v>0.626505287212203</v>
+        <v>-0.653087522249954</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.1300894526480614</v>
+        <v>0.4972784626955721</v>
       </c>
       <c r="D45" t="n">
-        <v>0.2332768487408687</v>
+        <v>0.1544368023097674</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.07138708409127403</v>
+        <v>0.4693025830127999</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.4340115118825238</v>
+        <v>-0.2005972022916279</v>
       </c>
     </row>
     <row r="46">
@@ -1337,19 +1337,19 @@
         <v>45694</v>
       </c>
       <c r="B46" t="n">
-        <v>0.2565099394655986</v>
+        <v>0.1061569610706832</v>
       </c>
       <c r="C46" t="n">
-        <v>0.04629233544494468</v>
+        <v>0.9604873201156047</v>
       </c>
       <c r="D46" t="n">
-        <v>0.4802802925234269</v>
+        <v>-0.3267662050390633</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1798187038556461</v>
+        <v>0.8834278042256873</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.3404379390472033</v>
+        <v>0.03130009268116823</v>
       </c>
     </row>
     <row r="47">
@@ -1357,19 +1357,19 @@
         <v>45695</v>
       </c>
       <c r="B47" t="n">
-        <v>0.4105717541311224</v>
+        <v>0.2480358355610003</v>
       </c>
       <c r="C47" t="n">
-        <v>0.5544537865571664</v>
+        <v>3.171979038597261</v>
       </c>
       <c r="D47" t="n">
-        <v>1.557164652935914</v>
+        <v>0.2837243327513314</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1251109461978779</v>
+        <v>0.01705801153993356</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.2290777167327447</v>
+        <v>0.7747877562021442</v>
       </c>
     </row>
     <row r="48">
@@ -1377,19 +1377,19 @@
         <v>45698</v>
       </c>
       <c r="B48" t="n">
-        <v>-0.2709270234183199</v>
+        <v>-0.0331516850894781</v>
       </c>
       <c r="C48" t="n">
-        <v>0.4965292296736621</v>
+        <v>-1.830081742585943</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.08380083601196978</v>
+        <v>-0.9883544294984201</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.2638072126876518</v>
+        <v>-0.3629289409778953</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1630085750053369</v>
+        <v>0.9484557075715604</v>
       </c>
     </row>
     <row r="49">
@@ -1397,19 +1397,19 @@
         <v>45699</v>
       </c>
       <c r="B49" t="n">
-        <v>-1.45553332804174</v>
+        <v>2.347662042862233</v>
       </c>
       <c r="C49" t="n">
-        <v>0.1640584697108377</v>
+        <v>-1.07498195323444</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.90859255568885</v>
+        <v>-0.8947087881618153</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.1538333786218876</v>
+        <v>-0.4546287139078482</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.08535839515852879</v>
+        <v>-1.000990540420973</v>
       </c>
     </row>
     <row r="50">
@@ -1417,19 +1417,19 @@
         <v>45700</v>
       </c>
       <c r="B50" t="n">
-        <v>2.487833854228257</v>
+        <v>-5.589571586281059</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1606678831994951</v>
+        <v>1.176350932064976</v>
       </c>
       <c r="D50" t="n">
-        <v>0.252307129748061</v>
+        <v>-2.221476884683788</v>
       </c>
       <c r="E50" t="n">
-        <v>0.05440609957181837</v>
+        <v>-1.310804708203813</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.05798187461778595</v>
+        <v>-0.798240635362196</v>
       </c>
     </row>
     <row r="51">
@@ -1437,19 +1437,19 @@
         <v>45701</v>
       </c>
       <c r="B51" t="n">
-        <v>-0.8012367081973729</v>
+        <v>1.770188509559536</v>
       </c>
       <c r="C51" t="n">
-        <v>0.5411414231860535</v>
+        <v>-0.0482880931625326</v>
       </c>
       <c r="D51" t="n">
-        <v>0.6393748432773743</v>
+        <v>-0.3146932563368607</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.374309509627364</v>
+        <v>0.814461767496432</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.2985528902523466</v>
+        <v>1.345986932035207</v>
       </c>
     </row>
     <row r="52">
@@ -1457,19 +1457,19 @@
         <v>45702</v>
       </c>
       <c r="B52" t="n">
-        <v>-0.2223330697682003</v>
+        <v>-0.02777332397786845</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.603912870695649</v>
+        <v>-3.332176629509355</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.9581580908395108</v>
+        <v>1.602820984351921</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.1264663042834583</v>
+        <v>-0.5842216694405634</v>
       </c>
       <c r="F52" t="n">
-        <v>0.6333970145403257</v>
+        <v>-0.3457830955276362</v>
       </c>
     </row>
     <row r="53">
@@ -1477,19 +1477,19 @@
         <v>45705</v>
       </c>
       <c r="B53" t="n">
-        <v>-3.053993742490919</v>
+        <v>6.452506446573011</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.9384266504241714</v>
+        <v>0.6243087709507904</v>
       </c>
       <c r="D53" t="n">
-        <v>0.4105857187286178</v>
+        <v>2.630645498830507</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.02243396243704745</v>
+        <v>0.5069539535613375</v>
       </c>
       <c r="F53" t="n">
-        <v>0.2480859591404626</v>
+        <v>0.3910487330763602</v>
       </c>
     </row>
     <row r="54">
@@ -1497,19 +1497,19 @@
         <v>45706</v>
       </c>
       <c r="B54" t="n">
-        <v>-1.695711314712448</v>
+        <v>2.955630800838541</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1901539097066554</v>
+        <v>0.5540678019474028</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4712351606973265</v>
+        <v>-0.690260233483399</v>
       </c>
       <c r="E54" t="n">
-        <v>0.3246369582601036</v>
+        <v>-1.213524114110972</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2377446414727068</v>
+        <v>-0.4059176357237694</v>
       </c>
     </row>
     <row r="55">
@@ -1517,19 +1517,19 @@
         <v>45707</v>
       </c>
       <c r="B55" t="n">
-        <v>-1.181068691323866</v>
+        <v>2.670345928681336</v>
       </c>
       <c r="C55" t="n">
-        <v>0.7761760628090801</v>
+        <v>2.441273717195963</v>
       </c>
       <c r="D55" t="n">
-        <v>0.3757994885164608</v>
+        <v>-0.4025048700320404</v>
       </c>
       <c r="E55" t="n">
-        <v>0.1601890567091248</v>
+        <v>0.01319387586378413</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.08734243360796645</v>
+        <v>0.01865861965505253</v>
       </c>
     </row>
     <row r="56">
@@ -1537,19 +1537,19 @@
         <v>45708</v>
       </c>
       <c r="B56" t="n">
-        <v>-1.465211028781511</v>
+        <v>3.011939780069228</v>
       </c>
       <c r="C56" t="n">
-        <v>0.8919005227855122</v>
+        <v>1.136922007315454</v>
       </c>
       <c r="D56" t="n">
-        <v>0.07258369036235013</v>
+        <v>-0.4405265361214353</v>
       </c>
       <c r="E56" t="n">
-        <v>0.1807776970096865</v>
+        <v>0.7199444565460422</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.2435591635041794</v>
+        <v>0.3337468827596628</v>
       </c>
     </row>
     <row r="57">
@@ -1557,19 +1557,19 @@
         <v>45709</v>
       </c>
       <c r="B57" t="n">
-        <v>0.5207416725656645</v>
+        <v>-0.4055652861896114</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.7338483161626335</v>
+        <v>0.8539598391781905</v>
       </c>
       <c r="D57" t="n">
-        <v>0.05209693122459891</v>
+        <v>0.6511861248916028</v>
       </c>
       <c r="E57" t="n">
-        <v>0.1879302589431966</v>
+        <v>-1.300995863538663</v>
       </c>
       <c r="F57" t="n">
-        <v>0.08997898218667133</v>
+        <v>-0.8275358914433888</v>
       </c>
     </row>
     <row r="58">
@@ -1577,19 +1577,19 @@
         <v>45712</v>
       </c>
       <c r="B58" t="n">
-        <v>-0.08904866894223885</v>
+        <v>0.71036984354651</v>
       </c>
       <c r="C58" t="n">
-        <v>0.3541758329583452</v>
+        <v>1.211411184828908</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.001387548070331124</v>
+        <v>0.2189088897930626</v>
       </c>
       <c r="E58" t="n">
-        <v>0.02870494200055775</v>
+        <v>0.2168036961922376</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.0975444354250258</v>
+        <v>-0.2331099209574832</v>
       </c>
     </row>
     <row r="59">
@@ -1597,19 +1597,19 @@
         <v>45713</v>
       </c>
       <c r="B59" t="n">
-        <v>0.7958353257038218</v>
+        <v>-0.1585156079680797</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.7753319757982796</v>
+        <v>-0.7614162792275446</v>
       </c>
       <c r="D59" t="n">
-        <v>0.8990868960933744</v>
+        <v>1.716254112998014</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.1852460197236498</v>
+        <v>1.150232995794678</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1563179303809563</v>
+        <v>1.294406954582104</v>
       </c>
     </row>
     <row r="60">
@@ -1617,19 +1617,19 @@
         <v>45714</v>
       </c>
       <c r="B60" t="n">
-        <v>-0.7997912754948946</v>
+        <v>2.370663670180016</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.3393935668487038</v>
+        <v>1.923906116307584</v>
       </c>
       <c r="D60" t="n">
-        <v>0.9573966583451784</v>
+        <v>0.8996407836691788</v>
       </c>
       <c r="E60" t="n">
-        <v>0.07808686212548221</v>
+        <v>-0.9528699559689383</v>
       </c>
       <c r="F60" t="n">
-        <v>0.1309449550736399</v>
+        <v>0.4450714837039688</v>
       </c>
     </row>
     <row r="61">
@@ -1637,19 +1637,19 @@
         <v>45715</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.03928566665788821</v>
+        <v>0.3477280193383002</v>
       </c>
       <c r="C61" t="n">
-        <v>0.07129318849963866</v>
+        <v>-0.1168469971480257</v>
       </c>
       <c r="D61" t="n">
-        <v>0.3334926994386951</v>
+        <v>-0.2304780705693723</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.08767025392142619</v>
+        <v>-0.3326263316667976</v>
       </c>
       <c r="F61" t="n">
-        <v>0.05813753738296432</v>
+        <v>0.7750425634513973</v>
       </c>
     </row>
     <row r="62">
@@ -1657,19 +1657,19 @@
         <v>45716</v>
       </c>
       <c r="B62" t="n">
-        <v>1.039540877753068</v>
+        <v>-1.760075572321569</v>
       </c>
       <c r="C62" t="n">
-        <v>0.6095138740790741</v>
+        <v>0.2392889435799217</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.1089155626557533</v>
+        <v>-0.1005601359031991</v>
       </c>
       <c r="E62" t="n">
-        <v>0.2181587983623835</v>
+        <v>0.1184433590390849</v>
       </c>
       <c r="F62" t="n">
-        <v>0.09469704612002972</v>
+        <v>0.3960803800910696</v>
       </c>
     </row>
     <row r="63">
@@ -1677,19 +1677,19 @@
         <v>45722</v>
       </c>
       <c r="B63" t="n">
-        <v>3.816640168256153</v>
+        <v>-7.752262985699446</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.02420954658539128</v>
+        <v>-1.874935813484387</v>
       </c>
       <c r="D63" t="n">
-        <v>0.04181813253365636</v>
+        <v>0.5260597279963209</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.2249701721448458</v>
+        <v>-0.221813738434865</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.06954103224616413</v>
+        <v>0.2920296218668792</v>
       </c>
     </row>
     <row r="64">
@@ -1697,19 +1697,19 @@
         <v>45723</v>
       </c>
       <c r="B64" t="n">
-        <v>2.532537241487398</v>
+        <v>-5.797329400334047</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.2463068307082065</v>
+        <v>-1.823467610969767</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.1235792562861355</v>
+        <v>-1.636382785256189</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.2008779997834255</v>
+        <v>0.1728931989404471</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.1700397887561399</v>
+        <v>-0.2967190446200994</v>
       </c>
     </row>
     <row r="65">
@@ -1717,19 +1717,19 @@
         <v>45726</v>
       </c>
       <c r="B65" t="n">
-        <v>1.49819538328567</v>
+        <v>-2.976787387531346</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.4200743303023082</v>
+        <v>-0.6628329639697321</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.05999411099551075</v>
+        <v>-0.2553927967178576</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.1124937013907254</v>
+        <v>-1.863494859669455</v>
       </c>
       <c r="F65" t="n">
-        <v>0.377124753873094</v>
+        <v>-0.09923913851698525</v>
       </c>
     </row>
     <row r="66">
@@ -1737,19 +1737,19 @@
         <v>45727</v>
       </c>
       <c r="B66" t="n">
-        <v>-0.2472968045204452</v>
+        <v>0.4605349168169706</v>
       </c>
       <c r="C66" t="n">
-        <v>0.01927167576000488</v>
+        <v>1.185873154568803</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.08138455702706546</v>
+        <v>-0.6674748134720169</v>
       </c>
       <c r="E66" t="n">
-        <v>0.05655420616640441</v>
+        <v>-0.5516195942809804</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.2231980935915365</v>
+        <v>-1.033499873681275</v>
       </c>
     </row>
     <row r="67">
@@ -1757,19 +1757,19 @@
         <v>45728</v>
       </c>
       <c r="B67" t="n">
-        <v>1.61870195056887</v>
+        <v>-1.656979367162924</v>
       </c>
       <c r="C67" t="n">
-        <v>0.1579961187745502</v>
+        <v>1.768074567996607</v>
       </c>
       <c r="D67" t="n">
-        <v>0.7184100987357888</v>
+        <v>1.174155066473476</v>
       </c>
       <c r="E67" t="n">
-        <v>0.1970298472129438</v>
+        <v>0.05600713236103099</v>
       </c>
       <c r="F67" t="n">
-        <v>0.1620755771493016</v>
+        <v>0.7280134602934328</v>
       </c>
     </row>
     <row r="68">
@@ -1777,19 +1777,19 @@
         <v>45729</v>
       </c>
       <c r="B68" t="n">
-        <v>-0.8810794286732705</v>
+        <v>1.359644181725009</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.4837583414309807</v>
+        <v>-3.069185564863993</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.5328646396464823</v>
+        <v>0.8570580491119009</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.2199428302531757</v>
+        <v>-0.1642061664638841</v>
       </c>
       <c r="F68" t="n">
-        <v>0.3144634557002974</v>
+        <v>0.3180062686331673</v>
       </c>
     </row>
     <row r="69">
@@ -1797,19 +1797,19 @@
         <v>45730</v>
       </c>
       <c r="B69" t="n">
-        <v>-0.05873225778701514</v>
+        <v>0.4990001035693637</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.3960501013435009</v>
+        <v>-1.352897566341228</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.09624787915035565</v>
+        <v>1.253204823761507</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.2946016045693314</v>
+        <v>-0.1522689108479695</v>
       </c>
       <c r="F69" t="n">
-        <v>0.4592313161177262</v>
+        <v>0.5285803340721026</v>
       </c>
     </row>
     <row r="70">
@@ -1817,19 +1817,19 @@
         <v>45733</v>
       </c>
       <c r="B70" t="n">
-        <v>-0.787083313936452</v>
+        <v>1.550457094232317</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.2411337554871508</v>
+        <v>-1.090484149592219</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.5111374906773151</v>
+        <v>0.9560748725197661</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.04007497037881436</v>
+        <v>-1.112729068373867</v>
       </c>
       <c r="F70" t="n">
-        <v>0.2952682304376695</v>
+        <v>0.2382990257996219</v>
       </c>
     </row>
     <row r="71">
@@ -1837,19 +1837,19 @@
         <v>45734</v>
       </c>
       <c r="B71" t="n">
-        <v>1.596923143312957</v>
+        <v>-3.053573027047911</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.03183938720809467</v>
+        <v>-1.391054332022187</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.3192274453214608</v>
+        <v>0.8388963686398896</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.01206515987725312</v>
+        <v>-0.8364312163429212</v>
       </c>
       <c r="F71" t="n">
-        <v>0.3658799935905577</v>
+        <v>0.1955224900617659</v>
       </c>
     </row>
     <row r="72">
@@ -1857,19 +1857,19 @@
         <v>45735</v>
       </c>
       <c r="B72" t="n">
-        <v>0.6504982808875597</v>
+        <v>-0.6237326299969035</v>
       </c>
       <c r="C72" t="n">
-        <v>0.05436820541509618</v>
+        <v>0.6310435681223884</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.266536372983686</v>
+        <v>1.163218246489455</v>
       </c>
       <c r="E72" t="n">
-        <v>0.1683763181887765</v>
+        <v>-0.9510136800488675</v>
       </c>
       <c r="F72" t="n">
-        <v>0.4723098779075295</v>
+        <v>-0.3377490651043535</v>
       </c>
     </row>
     <row r="73">
@@ -1877,19 +1877,19 @@
         <v>45736</v>
       </c>
       <c r="B73" t="n">
-        <v>-1.631081880835517</v>
+        <v>3.398186620089535</v>
       </c>
       <c r="C73" t="n">
-        <v>0.9050441523305534</v>
+        <v>1.995285189357389</v>
       </c>
       <c r="D73" t="n">
-        <v>0.0545239520290548</v>
+        <v>-0.4476384885348378</v>
       </c>
       <c r="E73" t="n">
-        <v>0.134231295021914</v>
+        <v>0.8606666813682898</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.4940012634603214</v>
+        <v>-0.4410484189569715</v>
       </c>
     </row>
     <row r="74">
@@ -1897,19 +1897,19 @@
         <v>45737</v>
       </c>
       <c r="B74" t="n">
-        <v>-1.81867231372127</v>
+        <v>3.604777679140551</v>
       </c>
       <c r="C74" t="n">
-        <v>0.8403690059200026</v>
+        <v>1.836308431056245</v>
       </c>
       <c r="D74" t="n">
-        <v>0.2060969098237351</v>
+        <v>-0.8408901032296566</v>
       </c>
       <c r="E74" t="n">
-        <v>0.2222904630980441</v>
+        <v>0.7281714997187376</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.4646596171814876</v>
+        <v>-0.1351740448410702</v>
       </c>
     </row>
     <row r="75">
@@ -1917,19 +1917,19 @@
         <v>45740</v>
       </c>
       <c r="B75" t="n">
-        <v>-0.6799517345240296</v>
+        <v>0.4647685545256413</v>
       </c>
       <c r="C75" t="n">
-        <v>0.2555048933528325</v>
+        <v>0.2579678504413289</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.6119844056481196</v>
+        <v>-2.147858944254037</v>
       </c>
       <c r="E75" t="n">
-        <v>0.09550913220116877</v>
+        <v>-0.7267721814125808</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.378205019802497</v>
+        <v>-1.439206556856067</v>
       </c>
     </row>
     <row r="76">
@@ -1937,19 +1937,19 @@
         <v>45741</v>
       </c>
       <c r="B76" t="n">
-        <v>0.0669311402207463</v>
+        <v>-0.2591947808190816</v>
       </c>
       <c r="C76" t="n">
-        <v>0.5319514947239291</v>
+        <v>0.0007117945935392723</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.5476329653076928</v>
+        <v>-0.4264732324809061</v>
       </c>
       <c r="E76" t="n">
-        <v>0.06648576181263154</v>
+        <v>0.07283266488250049</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.2794050887598595</v>
+        <v>-0.7000814437237083</v>
       </c>
     </row>
     <row r="77">
@@ -1957,19 +1957,19 @@
         <v>45742</v>
       </c>
       <c r="B77" t="n">
-        <v>0.06384092164896329</v>
+        <v>0.2155148177854758</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.1417466552307262</v>
+        <v>0.7284078965449209</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.4360994110091364</v>
+        <v>0.2171374051732887</v>
       </c>
       <c r="E77" t="n">
-        <v>0.03750464627452673</v>
+        <v>-0.01493491889460317</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.3123174805452509</v>
+        <v>-1.288221739664694</v>
       </c>
     </row>
     <row r="78">
@@ -1977,19 +1977,19 @@
         <v>45743</v>
       </c>
       <c r="B78" t="n">
-        <v>0.7053232652110411</v>
+        <v>-2.556291150369133</v>
       </c>
       <c r="C78" t="n">
-        <v>0.3976163081946904</v>
+        <v>-0.763130718719442</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.4890500398053919</v>
+        <v>-2.610586077190939</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.06165993716872711</v>
+        <v>-0.8638655762410004</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.2577325663014059</v>
+        <v>-0.6263988164201346</v>
       </c>
     </row>
     <row r="79">
@@ -1997,19 +1997,19 @@
         <v>45744</v>
       </c>
       <c r="B79" t="n">
-        <v>0.8499358884300527</v>
+        <v>-1.91220041520139</v>
       </c>
       <c r="C79" t="n">
-        <v>0.4891358553266447</v>
+        <v>-0.4016899561931169</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.2923391153320671</v>
+        <v>-0.8599704784454794</v>
       </c>
       <c r="E79" t="n">
-        <v>0.1960971453345188</v>
+        <v>1.202094826500048</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.2328532213921351</v>
+        <v>-0.1903290437263519</v>
       </c>
     </row>
     <row r="80">
@@ -2017,19 +2017,19 @@
         <v>45747</v>
       </c>
       <c r="B80" t="n">
-        <v>-0.08608079109392669</v>
+        <v>-0.04933596607231816</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.326628249280985</v>
+        <v>-0.9072094543895027</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.1518528912230419</v>
+        <v>-0.6521056481623324</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.3343177815744171</v>
+        <v>-0.5544538812357324</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.1668145836413026</v>
+        <v>-0.601216850106043</v>
       </c>
     </row>
     <row r="81">
@@ -2037,19 +2037,19 @@
         <v>45748</v>
       </c>
       <c r="B81" t="n">
-        <v>0.1948852577856293</v>
+        <v>-0.4475562715287616</v>
       </c>
       <c r="C81" t="n">
-        <v>0.3098753562324631</v>
+        <v>-1.30447538890012</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.1712330458427886</v>
+        <v>-0.1894599013359508</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.2962669299533111</v>
+        <v>-0.2108124810118255</v>
       </c>
       <c r="F81" t="n">
-        <v>0.2497433080553304</v>
+        <v>0.3695701004248428</v>
       </c>
     </row>
     <row r="82">
@@ -2057,19 +2057,19 @@
         <v>45749</v>
       </c>
       <c r="B82" t="n">
-        <v>-1.208909763768373</v>
+        <v>1.854048774242071</v>
       </c>
       <c r="C82" t="n">
-        <v>0.04344288250661628</v>
+        <v>0.3563801410645266</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.2350024207893406</v>
+        <v>-1.443391356217815</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.2443716273038776</v>
+        <v>-0.4120463057768307</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.4149459553692483</v>
+        <v>-0.896291666915884</v>
       </c>
     </row>
     <row r="83">
@@ -2077,19 +2077,19 @@
         <v>45750</v>
       </c>
       <c r="B83" t="n">
-        <v>3.693390709958256</v>
+        <v>-8.857591663744252</v>
       </c>
       <c r="C83" t="n">
-        <v>0.003949174645286668</v>
+        <v>-1.570014532414011</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.1520959576617896</v>
+        <v>-1.565827211604508</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.2439378313088915</v>
+        <v>-0.6365879834742174</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.005295632624586411</v>
+        <v>-0.4649958412903366</v>
       </c>
     </row>
     <row r="84">
@@ -2097,19 +2097,19 @@
         <v>45751</v>
       </c>
       <c r="B84" t="n">
-        <v>5.702981487508214</v>
+        <v>-13.71633687469764</v>
       </c>
       <c r="C84" t="n">
-        <v>0.5117638172255188</v>
+        <v>-0.8414249720589929</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.4772245719451786</v>
+        <v>-1.605632043759393</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.1321021560108453</v>
+        <v>-0.4436300935034767</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.03835140741635321</v>
+        <v>0.5126333634649222</v>
       </c>
     </row>
     <row r="85">
@@ -2117,19 +2117,19 @@
         <v>45754</v>
       </c>
       <c r="B85" t="n">
-        <v>7.753915357006658</v>
+        <v>-21.04078534484285</v>
       </c>
       <c r="C85" t="n">
-        <v>0.3247610368883143</v>
+        <v>-1.147815554947517</v>
       </c>
       <c r="D85" t="n">
-        <v>-1.240731046454655</v>
+        <v>-0.9178549312895328</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.3176340715241578</v>
+        <v>-0.5527612596286172</v>
       </c>
       <c r="F85" t="n">
-        <v>0.2277610279184989</v>
+        <v>-1.077255273155946</v>
       </c>
     </row>
     <row r="86">
@@ -2137,19 +2137,19 @@
         <v>45755</v>
       </c>
       <c r="B86" t="n">
-        <v>6.265965083866666</v>
+        <v>-13.90027934044885</v>
       </c>
       <c r="C86" t="n">
-        <v>0.3149779631234399</v>
+        <v>-0.585345969380095</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.7383799153710857</v>
+        <v>1.163173701811475</v>
       </c>
       <c r="E86" t="n">
-        <v>0.1436833517941641</v>
+        <v>0.8428771910344932</v>
       </c>
       <c r="F86" t="n">
-        <v>0.01411667928060609</v>
+        <v>1.059578561531741</v>
       </c>
     </row>
     <row r="87">
@@ -2157,19 +2157,19 @@
         <v>45756</v>
       </c>
       <c r="B87" t="n">
-        <v>7.751523347998763</v>
+        <v>-20.83538688241709</v>
       </c>
       <c r="C87" t="n">
-        <v>0.1203560214151638</v>
+        <v>-2.036897226745345</v>
       </c>
       <c r="D87" t="n">
-        <v>-1.325091802246758</v>
+        <v>-0.1765125285750532</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.3918969350463771</v>
+        <v>0.01261342505276151</v>
       </c>
       <c r="F87" t="n">
-        <v>0.2860272790423098</v>
+        <v>-0.306022058098429</v>
       </c>
     </row>
     <row r="88">
@@ -2177,19 +2177,19 @@
         <v>45757</v>
       </c>
       <c r="B88" t="n">
-        <v>6.768797941785852</v>
+        <v>-13.78767857897568</v>
       </c>
       <c r="C88" t="n">
-        <v>0.05093337523159731</v>
+        <v>0.03846680823877727</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.167783181800939</v>
+        <v>1.074099348047453</v>
       </c>
       <c r="E88" t="n">
-        <v>0.1045026771482899</v>
+        <v>0.6654598910388647</v>
       </c>
       <c r="F88" t="n">
-        <v>-0.02286389112905507</v>
+        <v>1.031451102454163</v>
       </c>
     </row>
     <row r="89">
@@ -2197,19 +2197,19 @@
         <v>45758</v>
       </c>
       <c r="B89" t="n">
-        <v>4.787869232808615</v>
+        <v>-9.626929437155654</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.1328250783199198</v>
+        <v>-1.103056713930718</v>
       </c>
       <c r="D89" t="n">
-        <v>0.124461606999987</v>
+        <v>0.2806099852507014</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.1106930539151926</v>
+        <v>-0.3215752591124238</v>
       </c>
       <c r="F89" t="n">
-        <v>0.1423654349857649</v>
+        <v>0.612384351410187</v>
       </c>
     </row>
     <row r="90">
@@ -2217,19 +2217,19 @@
         <v>45761</v>
       </c>
       <c r="B90" t="n">
-        <v>3.348587841389024</v>
+        <v>-6.442405177496946</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.02407856597157555</v>
+        <v>-2.169264160495025</v>
       </c>
       <c r="D90" t="n">
-        <v>0.2818490848042678</v>
+        <v>-0.07355566982988293</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.002749526845766026</v>
+        <v>1.224679971403521</v>
       </c>
       <c r="F90" t="n">
-        <v>0.2445209576116457</v>
+        <v>1.213972653046394</v>
       </c>
     </row>
     <row r="91">
@@ -2237,19 +2237,19 @@
         <v>45762</v>
       </c>
       <c r="B91" t="n">
-        <v>2.258048136063703</v>
+        <v>-3.57256116039238</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.3270316417921605</v>
+        <v>1.621937979516635</v>
       </c>
       <c r="D91" t="n">
-        <v>0.128747937938428</v>
+        <v>0.8910008149340494</v>
       </c>
       <c r="E91" t="n">
-        <v>0.02938954157090642</v>
+        <v>0.1772035047048537</v>
       </c>
       <c r="F91" t="n">
-        <v>-0.140012071151506</v>
+        <v>-0.8333156084351174</v>
       </c>
     </row>
     <row r="92">
@@ -2257,19 +2257,19 @@
         <v>45763</v>
       </c>
       <c r="B92" t="n">
-        <v>3.706421676882869</v>
+        <v>-6.214522256945862</v>
       </c>
       <c r="C92" t="n">
-        <v>0.173949345500166</v>
+        <v>0.1099670931923901</v>
       </c>
       <c r="D92" t="n">
-        <v>0.10929764079564</v>
+        <v>2.024278714439127</v>
       </c>
       <c r="E92" t="n">
-        <v>0.1553426839100053</v>
+        <v>-0.3067868243165231</v>
       </c>
       <c r="F92" t="n">
-        <v>0.5424884532289153</v>
+        <v>0.7625009536768008</v>
       </c>
     </row>
     <row r="93">
@@ -2277,19 +2277,19 @@
         <v>45764</v>
       </c>
       <c r="B93" t="n">
-        <v>2.056155193253538</v>
+        <v>-3.087896449956135</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.7791678735761374</v>
+        <v>-0.02223420032644681</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.08416302985684371</v>
+        <v>1.365481630552864</v>
       </c>
       <c r="E93" t="n">
-        <v>0.2217515026660151</v>
+        <v>1.168267744505403</v>
       </c>
       <c r="F93" t="n">
-        <v>0.008029248892161212</v>
+        <v>-0.3337254299295841</v>
       </c>
     </row>
     <row r="94">
@@ -2297,19 +2297,19 @@
         <v>45769</v>
       </c>
       <c r="B94" t="n">
-        <v>1.935424835246344</v>
+        <v>-2.832867734609572</v>
       </c>
       <c r="C94" t="n">
-        <v>-1.086842508910671</v>
+        <v>0.03574633871886723</v>
       </c>
       <c r="D94" t="n">
-        <v>0.1754115214330866</v>
+        <v>1.504654435033311</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.1252585099458357</v>
+        <v>-0.3910204036964274</v>
       </c>
       <c r="F94" t="n">
-        <v>0.1862575482500856</v>
+        <v>-0.2250484683389946</v>
       </c>
     </row>
     <row r="95">
@@ -2317,19 +2317,19 @@
         <v>45770</v>
       </c>
       <c r="B95" t="n">
-        <v>3.165598371313482</v>
+        <v>-5.646917552449637</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1417926778139887</v>
+        <v>-1.44842120611401</v>
       </c>
       <c r="D95" t="n">
-        <v>0.2572320718718302</v>
+        <v>0.9571320930417697</v>
       </c>
       <c r="E95" t="n">
-        <v>0.08418488578724542</v>
+        <v>0.8260907683405758</v>
       </c>
       <c r="F95" t="n">
-        <v>0.3986850573970315</v>
+        <v>1.263890830596459</v>
       </c>
     </row>
     <row r="96">
@@ -2337,19 +2337,19 @@
         <v>45771</v>
       </c>
       <c r="B96" t="n">
-        <v>1.408051793945887</v>
+        <v>-2.629419643242011</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.5323738244680053</v>
+        <v>-2.16817632696277</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.1956837549557082</v>
+        <v>1.055709213695343</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.2789257190805907</v>
+        <v>-0.2339212517944363</v>
       </c>
       <c r="F96" t="n">
-        <v>0.2966567068431503</v>
+        <v>0.3230663101045701</v>
       </c>
     </row>
     <row r="97">
@@ -2357,19 +2357,19 @@
         <v>45772</v>
       </c>
       <c r="B97" t="n">
-        <v>0.1096992999385887</v>
+        <v>0.525692616493759</v>
       </c>
       <c r="C97" t="n">
-        <v>0.408407825888404</v>
+        <v>1.358237564751136</v>
       </c>
       <c r="D97" t="n">
-        <v>0.3320391569195111</v>
+        <v>-0.05745584296716873</v>
       </c>
       <c r="E97" t="n">
-        <v>0.2590390169914137</v>
+        <v>0.08745677869631883</v>
       </c>
       <c r="F97" t="n">
-        <v>-0.008101934926892086</v>
+        <v>0.3439624526533619</v>
       </c>
     </row>
     <row r="98">
@@ -2377,19 +2377,19 @@
         <v>45775</v>
       </c>
       <c r="B98" t="n">
-        <v>0.4041349803111598</v>
+        <v>-0.4412306685380978</v>
       </c>
       <c r="C98" t="n">
-        <v>0.05603244245034587</v>
+        <v>0.1661519111591276</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.134026423969089</v>
+        <v>0.1930775211309994</v>
       </c>
       <c r="E98" t="n">
-        <v>0.06205156201747591</v>
+        <v>0.1900839126523083</v>
       </c>
       <c r="F98" t="n">
-        <v>-0.1623412900067152</v>
+        <v>-0.3503290828119547</v>
       </c>
     </row>
     <row r="99">
@@ -2397,19 +2397,19 @@
         <v>45776</v>
       </c>
       <c r="B99" t="n">
-        <v>0.08853671575095484</v>
+        <v>0.6809051120701772</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.925493911181246</v>
+        <v>-0.5140051683067425</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.2168332910128939</v>
+        <v>1.874343569683774</v>
       </c>
       <c r="E99" t="n">
-        <v>0.01304402766044672</v>
+        <v>-0.6015461647529469</v>
       </c>
       <c r="F99" t="n">
-        <v>0.1646049199490361</v>
+        <v>-0.3987863619987744</v>
       </c>
     </row>
     <row r="100">
@@ -2417,19 +2417,19 @@
         <v>45777</v>
       </c>
       <c r="B100" t="n">
-        <v>1.24095465732718</v>
+        <v>-2.265041562707024</v>
       </c>
       <c r="C100" t="n">
-        <v>-0.4509550112883535</v>
+        <v>1.137497727872646</v>
       </c>
       <c r="D100" t="n">
-        <v>0.2072519201087671</v>
+        <v>-0.6280668104435506</v>
       </c>
       <c r="E100" t="n">
-        <v>0.00880895550770853</v>
+        <v>-0.6117454825333043</v>
       </c>
       <c r="F100" t="n">
-        <v>-0.1775427699593791</v>
+        <v>-1.001047527397714</v>
       </c>
     </row>
     <row r="101">
@@ -2437,19 +2437,19 @@
         <v>45779</v>
       </c>
       <c r="B101" t="n">
-        <v>0.8840852384289154</v>
+        <v>-1.691555837599752</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.2372663702033896</v>
+        <v>-0.1529315662454109</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.09860876857865999</v>
+        <v>-0.03779067745770764</v>
       </c>
       <c r="E101" t="n">
-        <v>0.01023521665831415</v>
+        <v>-0.9548737310820702</v>
       </c>
       <c r="F101" t="n">
-        <v>0.09134476924464585</v>
+        <v>-0.5283491872507927</v>
       </c>
     </row>
     <row r="102">
@@ -2457,19 +2457,19 @@
         <v>45782</v>
       </c>
       <c r="B102" t="n">
-        <v>-0.0203373876813996</v>
+        <v>-0.5043097933745269</v>
       </c>
       <c r="C102" t="n">
-        <v>0.2875698067303353</v>
+        <v>0.07541984916627031</v>
       </c>
       <c r="D102" t="n">
-        <v>0.01168282453687748</v>
+        <v>-1.266449500666641</v>
       </c>
       <c r="E102" t="n">
-        <v>-0.4181597133826435</v>
+        <v>0.1225120693088184</v>
       </c>
       <c r="F102" t="n">
-        <v>-0.4570696755193601</v>
+        <v>-0.6848851532595166</v>
       </c>
     </row>
     <row r="103">
@@ -2477,19 +2477,19 @@
         <v>45783</v>
       </c>
       <c r="B103" t="n">
-        <v>-0.1560317876560216</v>
+        <v>0.8504734100434332</v>
       </c>
       <c r="C103" t="n">
-        <v>0.5471830091883391</v>
+        <v>1.252589382139078</v>
       </c>
       <c r="D103" t="n">
-        <v>0.7556067858988629</v>
+        <v>-0.5214488943055348</v>
       </c>
       <c r="E103" t="n">
-        <v>-0.1943857369066581</v>
+        <v>1.082988684150345</v>
       </c>
       <c r="F103" t="n">
-        <v>-0.4187111170219868</v>
+        <v>0.6355066402897652</v>
       </c>
     </row>
     <row r="104">
@@ -2497,19 +2497,19 @@
         <v>45784</v>
       </c>
       <c r="B104" t="n">
-        <v>-0.3891159099161144</v>
+        <v>1.661404205931486</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.2742630589643018</v>
+        <v>2.117944657921889</v>
       </c>
       <c r="D104" t="n">
-        <v>0.2827888459923859</v>
+        <v>1.259356708936013</v>
       </c>
       <c r="E104" t="n">
-        <v>0.2612079155143409</v>
+        <v>-0.667465920528257</v>
       </c>
       <c r="F104" t="n">
-        <v>0.08499933500885881</v>
+        <v>-0.581004330373297</v>
       </c>
     </row>
     <row r="105">
@@ -2517,19 +2517,19 @@
         <v>45785</v>
       </c>
       <c r="B105" t="n">
-        <v>3.013564685026451</v>
+        <v>-6.982938908685049</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.1292374065566477</v>
+        <v>-4.048026451994155</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.2916218560529432</v>
+        <v>-0.2009802599600288</v>
       </c>
       <c r="E105" t="n">
-        <v>-0.1796464871260008</v>
+        <v>0.2108072939438896</v>
       </c>
       <c r="F105" t="n">
-        <v>0.3395749674023548</v>
+        <v>0.666236250579356</v>
       </c>
     </row>
     <row r="106">
@@ -2537,19 +2537,19 @@
         <v>45786</v>
       </c>
       <c r="B106" t="n">
-        <v>-1.971213302964143</v>
+        <v>4.020354756149344</v>
       </c>
       <c r="C106" t="n">
-        <v>0.7146851402453325</v>
+        <v>1.248324483707238</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.1514059190852687</v>
+        <v>-0.2855599417788711</v>
       </c>
       <c r="E106" t="n">
-        <v>-0.1636362732268403</v>
+        <v>0.126990467882958</v>
       </c>
       <c r="F106" t="n">
-        <v>0.04943020485638612</v>
+        <v>-0.3232760956889982</v>
       </c>
     </row>
     <row r="107">
@@ -2557,19 +2557,19 @@
         <v>45789</v>
       </c>
       <c r="B107" t="n">
-        <v>0.5015690680789299</v>
+        <v>-1.030347581797169</v>
       </c>
       <c r="C107" t="n">
-        <v>0.5320853785794339</v>
+        <v>-0.9919697393363411</v>
       </c>
       <c r="D107" t="n">
-        <v>0.1541483844590449</v>
+        <v>-0.9635402226294945</v>
       </c>
       <c r="E107" t="n">
-        <v>0.086465089204648</v>
+        <v>1.41747269852427</v>
       </c>
       <c r="F107" t="n">
-        <v>-0.0258383660637745</v>
+        <v>0.6378398303614088</v>
       </c>
     </row>
     <row r="108">
@@ -2577,19 +2577,19 @@
         <v>45790</v>
       </c>
       <c r="B108" t="n">
-        <v>0.07389101107395445</v>
+        <v>0.3694461324886809</v>
       </c>
       <c r="C108" t="n">
-        <v>-1.318598160159417</v>
+        <v>-1.720685339659084</v>
       </c>
       <c r="D108" t="n">
-        <v>-0.5785546520750821</v>
+        <v>3.487103097309346</v>
       </c>
       <c r="E108" t="n">
-        <v>-0.2674316504433466</v>
+        <v>-1.051526238005176</v>
       </c>
       <c r="F108" t="n">
-        <v>1.042503365705866</v>
+        <v>0.3894461917976583</v>
       </c>
     </row>
     <row r="109">
@@ -2597,19 +2597,19 @@
         <v>45791</v>
       </c>
       <c r="B109" t="n">
-        <v>-0.008297976823126203</v>
+        <v>1.093178748502707</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.2069236147526669</v>
+        <v>0.6793546144610021</v>
       </c>
       <c r="D109" t="n">
-        <v>0.3827476787158569</v>
+        <v>1.416240435891887</v>
       </c>
       <c r="E109" t="n">
-        <v>0.1024629084368905</v>
+        <v>0.06006112391540319</v>
       </c>
       <c r="F109" t="n">
-        <v>0.3532458699043903</v>
+        <v>0.4867874415670101</v>
       </c>
     </row>
     <row r="110">
@@ -2617,19 +2617,19 @@
         <v>45792</v>
       </c>
       <c r="B110" t="n">
-        <v>1.316696407679176</v>
+        <v>-1.494329986933975</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.4201489646309194</v>
+        <v>0.6583639348872634</v>
       </c>
       <c r="D110" t="n">
-        <v>0.4248016854917327</v>
+        <v>0.6482939204653114</v>
       </c>
       <c r="E110" t="n">
-        <v>0.02823652106545886</v>
+        <v>0.8202099786990775</v>
       </c>
       <c r="F110" t="n">
-        <v>-0.2945338831753359</v>
+        <v>0.04113934095659359</v>
       </c>
     </row>
     <row r="111">
@@ -2637,19 +2637,19 @@
         <v>45793</v>
       </c>
       <c r="B111" t="n">
-        <v>1.738279018224222</v>
+        <v>-3.145038892566254</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.3682445425725385</v>
+        <v>0.4266216705040196</v>
       </c>
       <c r="D111" t="n">
-        <v>0.3892156853674106</v>
+        <v>-0.6987796305270182</v>
       </c>
       <c r="E111" t="n">
-        <v>-0.01283483203981412</v>
+        <v>-1.015494389189258</v>
       </c>
       <c r="F111" t="n">
-        <v>0.0973918545723463</v>
+        <v>0.3280345091614427</v>
       </c>
     </row>
     <row r="112">
@@ -2657,19 +2657,19 @@
         <v>45796</v>
       </c>
       <c r="B112" t="n">
-        <v>-0.9280643500510728</v>
+        <v>2.611063664189384</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.1928636081022567</v>
+        <v>0.5862742596366743</v>
       </c>
       <c r="D112" t="n">
-        <v>0.6434071900598011</v>
+        <v>0.7791834137888141</v>
       </c>
       <c r="E112" t="n">
-        <v>0.1367271298073006</v>
+        <v>0.1475965488187151</v>
       </c>
       <c r="F112" t="n">
-        <v>0.1336374372636855</v>
+        <v>1.37436786955572</v>
       </c>
     </row>
     <row r="113">
@@ -2677,19 +2677,19 @@
         <v>45797</v>
       </c>
       <c r="B113" t="n">
-        <v>0.1072439837823551</v>
+        <v>0.7708424596949111</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.307020765269013</v>
+        <v>0.0628945113085112</v>
       </c>
       <c r="D113" t="n">
-        <v>0.7285497795297496</v>
+        <v>0.6861350703900231</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.03853700781425165</v>
+        <v>1.414302757545485</v>
       </c>
       <c r="F113" t="n">
-        <v>-0.4968798776834986</v>
+        <v>0.672132951780135</v>
       </c>
     </row>
     <row r="114">
@@ -2697,19 +2697,19 @@
         <v>45798</v>
       </c>
       <c r="B114" t="n">
-        <v>0.9071003069725188</v>
+        <v>-0.5181195605479377</v>
       </c>
       <c r="C114" t="n">
-        <v>0.1833768176910077</v>
+        <v>3.37849745380168</v>
       </c>
       <c r="D114" t="n">
-        <v>0.8019861536271823</v>
+        <v>1.421352326068069</v>
       </c>
       <c r="E114" t="n">
-        <v>0.4335315168453663</v>
+        <v>0.7759988098936857</v>
       </c>
       <c r="F114" t="n">
-        <v>-0.5830934643463884</v>
+        <v>-0.323748641424749</v>
       </c>
     </row>
     <row r="115">
@@ -2717,19 +2717,19 @@
         <v>45799</v>
       </c>
       <c r="B115" t="n">
-        <v>1.916677550313644</v>
+        <v>-3.631081035506907</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.3185562984268398</v>
+        <v>-0.3922208125281255</v>
       </c>
       <c r="D115" t="n">
-        <v>0.00396613628368927</v>
+        <v>-0.06742056400215778</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.03801480768567853</v>
+        <v>0.7043083386372699</v>
       </c>
       <c r="F115" t="n">
-        <v>-0.1695834056330006</v>
+        <v>-0.6626576025533581</v>
       </c>
     </row>
     <row r="116">
@@ -2737,19 +2737,19 @@
         <v>45800</v>
       </c>
       <c r="B116" t="n">
-        <v>3.887093952814809</v>
+        <v>-8.217947066679724</v>
       </c>
       <c r="C116" t="n">
-        <v>0.01524259716836188</v>
+        <v>0.7272642683144448</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.2130680263718615</v>
+        <v>-1.49470324327693</v>
       </c>
       <c r="E116" t="n">
-        <v>0.004570201476872793</v>
+        <v>-1.495108699587361</v>
       </c>
       <c r="F116" t="n">
-        <v>0.06144580464187879</v>
+        <v>-0.2524111750699658</v>
       </c>
     </row>
     <row r="117">
@@ -2757,19 +2757,19 @@
         <v>45803</v>
       </c>
       <c r="B117" t="n">
-        <v>-0.8032080059701712</v>
+        <v>1.232656895492062</v>
       </c>
       <c r="C117" t="n">
-        <v>0.01080191160752289</v>
+        <v>-0.8393141168051823</v>
       </c>
       <c r="D117" t="n">
-        <v>-1.036996785165446</v>
+        <v>-0.4486061263599552</v>
       </c>
       <c r="E117" t="n">
-        <v>0.07482714977117165</v>
+        <v>-0.350867917845252</v>
       </c>
       <c r="F117" t="n">
-        <v>-0.1432118154709662</v>
+        <v>-1.34106416787543</v>
       </c>
     </row>
     <row r="118">
@@ -2777,19 +2777,19 @@
         <v>45804</v>
       </c>
       <c r="B118" t="n">
-        <v>1.127845258014332</v>
+        <v>-2.836928169444979</v>
       </c>
       <c r="C118" t="n">
-        <v>0.1421125071723678</v>
+        <v>-2.94916087639713</v>
       </c>
       <c r="D118" t="n">
-        <v>0.02590653049291389</v>
+        <v>-0.9304599269533725</v>
       </c>
       <c r="E118" t="n">
-        <v>-0.1642006267478471</v>
+        <v>1.474244649161888</v>
       </c>
       <c r="F118" t="n">
-        <v>0.1385020559246322</v>
+        <v>1.110769895105718</v>
       </c>
     </row>
     <row r="119">
@@ -2797,19 +2797,19 @@
         <v>45805</v>
       </c>
       <c r="B119" t="n">
-        <v>-1.056710583165386</v>
+        <v>2.090361560105866</v>
       </c>
       <c r="C119" t="n">
-        <v>0.293256050138712</v>
+        <v>1.567901698214481</v>
       </c>
       <c r="D119" t="n">
-        <v>0.28929654554793</v>
+        <v>-0.818033010512926</v>
       </c>
       <c r="E119" t="n">
-        <v>0.1997970142023723</v>
+        <v>-0.9065586164736985</v>
       </c>
       <c r="F119" t="n">
-        <v>0.1231321063360832</v>
+        <v>0.08660323865609816</v>
       </c>
     </row>
     <row r="120">
@@ -2817,19 +2817,19 @@
         <v>45806</v>
       </c>
       <c r="B120" t="n">
-        <v>0.3984681766586362</v>
+        <v>-0.06981452497487424</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.3063044967219933</v>
+        <v>0.7293310563546591</v>
       </c>
       <c r="D120" t="n">
-        <v>0.2225707851127043</v>
+        <v>0.6914630009763983</v>
       </c>
       <c r="E120" t="n">
-        <v>0.2678420102473527</v>
+        <v>-0.6008035499489813</v>
       </c>
       <c r="F120" t="n">
-        <v>0.2755204428323254</v>
+        <v>0.1013839455227026</v>
       </c>
     </row>
     <row r="121">
@@ -2837,19 +2837,19 @@
         <v>45807</v>
       </c>
       <c r="B121" t="n">
-        <v>1.020603031682482</v>
+        <v>-1.272563356557896</v>
       </c>
       <c r="C121" t="n">
-        <v>0.3049915895328164</v>
+        <v>3.405250323462795</v>
       </c>
       <c r="D121" t="n">
-        <v>1.047173499114912</v>
+        <v>-0.2574939332362183</v>
       </c>
       <c r="E121" t="n">
-        <v>0.1815101198116993</v>
+        <v>0.585994963996923</v>
       </c>
       <c r="F121" t="n">
-        <v>-0.673509480919488</v>
+        <v>-0.5683018678895809</v>
       </c>
     </row>
     <row r="122">
@@ -2857,19 +2857,19 @@
         <v>45810</v>
       </c>
       <c r="B122" t="n">
-        <v>2.060282096564862</v>
+        <v>-4.668604973480686</v>
       </c>
       <c r="C122" t="n">
-        <v>0.2904877838487179</v>
+        <v>-1.192228813385269</v>
       </c>
       <c r="D122" t="n">
-        <v>0.01455658560075994</v>
+        <v>-1.514732910108969</v>
       </c>
       <c r="E122" t="n">
-        <v>0.1087338854226945</v>
+        <v>1.107137487102952</v>
       </c>
       <c r="F122" t="n">
-        <v>-0.09327084524445294</v>
+        <v>0.0891330152390669</v>
       </c>
     </row>
     <row r="123">
@@ -2877,19 +2877,19 @@
         <v>45811</v>
       </c>
       <c r="B123" t="n">
-        <v>0.4265241047329653</v>
+        <v>-1.479088269586642</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.5901907178819892</v>
+        <v>-2.116508171366684</v>
       </c>
       <c r="D123" t="n">
-        <v>-0.9233731809052454</v>
+        <v>-0.3557272334885134</v>
       </c>
       <c r="E123" t="n">
-        <v>-0.1292500351156522</v>
+        <v>-1.042592811155046</v>
       </c>
       <c r="F123" t="n">
-        <v>0.2273127318232681</v>
+        <v>-1.326872265671486</v>
       </c>
     </row>
     <row r="124">
@@ -2897,19 +2897,19 @@
         <v>45812</v>
       </c>
       <c r="B124" t="n">
-        <v>1.351208824589682</v>
+        <v>-1.886894750495536</v>
       </c>
       <c r="C124" t="n">
-        <v>0.1151920519217169</v>
+        <v>0.3779844451107072</v>
       </c>
       <c r="D124" t="n">
-        <v>0.3150490267449748</v>
+        <v>0.4693829996825909</v>
       </c>
       <c r="E124" t="n">
-        <v>0.08564036779418796</v>
+        <v>0.8138845480824024</v>
       </c>
       <c r="F124" t="n">
-        <v>-0.1027485284029205</v>
+        <v>0.1437988691473295</v>
       </c>
     </row>
     <row r="125">
@@ -2917,19 +2917,19 @@
         <v>45813</v>
       </c>
       <c r="B125" t="n">
-        <v>-0.06564633766064319</v>
+        <v>1.284024024779573</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.2587143226877545</v>
+        <v>0.6225514170295177</v>
       </c>
       <c r="D125" t="n">
-        <v>0.2897005291850875</v>
+        <v>1.483147469260887</v>
       </c>
       <c r="E125" t="n">
-        <v>0.03985367487677609</v>
+        <v>0.6948967509390225</v>
       </c>
       <c r="F125" t="n">
-        <v>-0.1791922054158217</v>
+        <v>-0.04912863875625444</v>
       </c>
     </row>
     <row r="126">
@@ -2937,19 +2937,19 @@
         <v>45814</v>
       </c>
       <c r="B126" t="n">
-        <v>0.9250171838060341</v>
+        <v>-1.446756723139216</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.105015428346702</v>
+        <v>0.5997336558295769</v>
       </c>
       <c r="D126" t="n">
-        <v>0.03358068895481222</v>
+        <v>0.1201613956503071</v>
       </c>
       <c r="E126" t="n">
-        <v>-0.187052709805567</v>
+        <v>0.5699240750161133</v>
       </c>
       <c r="F126" t="n">
-        <v>-0.3673134263738089</v>
+        <v>-0.7052415303871359</v>
       </c>
     </row>
     <row r="127">
@@ -2957,19 +2957,19 @@
         <v>45817</v>
       </c>
       <c r="B127" t="n">
-        <v>1.810480555167409</v>
+        <v>-3.794773351191459</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.2519749375216077</v>
+        <v>-0.1568145960711025</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.3200852039738067</v>
+        <v>-0.4643765086116431</v>
       </c>
       <c r="E127" t="n">
-        <v>-0.0909313335605003</v>
+        <v>-0.698679296140468</v>
       </c>
       <c r="F127" t="n">
-        <v>-0.1070498007112713</v>
+        <v>-1.031697774725912</v>
       </c>
     </row>
     <row r="128">
@@ -2977,19 +2977,19 @@
         <v>45818</v>
       </c>
       <c r="B128" t="n">
-        <v>0.6142460798612109</v>
+        <v>-0.4835829067568562</v>
       </c>
       <c r="C128" t="n">
-        <v>0.1104594446870641</v>
+        <v>1.05842042623629</v>
       </c>
       <c r="D128" t="n">
-        <v>-0.04699175002903352</v>
+        <v>0.7014878152674653</v>
       </c>
       <c r="E128" t="n">
-        <v>0.1291819401263677</v>
+        <v>-0.210310193591065</v>
       </c>
       <c r="F128" t="n">
-        <v>0.2286556698730859</v>
+        <v>-0.2945527620261487</v>
       </c>
     </row>
     <row r="129">
@@ -2997,19 +2997,19 @@
         <v>45819</v>
       </c>
       <c r="B129" t="n">
-        <v>2.188850997656571</v>
+        <v>-3.867879975633832</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.1824673668986856</v>
+        <v>1.451761335173108</v>
       </c>
       <c r="D129" t="n">
-        <v>0.1920272056242741</v>
+        <v>-0.3774100262670002</v>
       </c>
       <c r="E129" t="n">
-        <v>-0.02194747402352316</v>
+        <v>-0.6809663064571293</v>
       </c>
       <c r="F129" t="n">
-        <v>0.01654969148092733</v>
+        <v>-0.7466549878670955</v>
       </c>
     </row>
     <row r="130">
@@ -3017,19 +3017,19 @@
         <v>45820</v>
       </c>
       <c r="B130" t="n">
-        <v>0.05774616172889706</v>
+        <v>0.4067597668413697</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.3785933084729058</v>
+        <v>1.251006231854967</v>
       </c>
       <c r="D130" t="n">
-        <v>0.4451519407565243</v>
+        <v>-0.4020593762083653</v>
       </c>
       <c r="E130" t="n">
-        <v>0.07416375307884644</v>
+        <v>0.2252579998387541</v>
       </c>
       <c r="F130" t="n">
-        <v>-0.4463771424884124</v>
+        <v>-0.315454270403956</v>
       </c>
     </row>
     <row r="131">
@@ -3037,19 +3037,19 @@
         <v>45821</v>
       </c>
       <c r="B131" t="n">
-        <v>0.1855870291819618</v>
+        <v>-0.6843635298676521</v>
       </c>
       <c r="C131" t="n">
-        <v>0.7971786121239632</v>
+        <v>1.657158616542238</v>
       </c>
       <c r="D131" t="n">
-        <v>-0.06483842131992285</v>
+        <v>-2.063217601718333</v>
       </c>
       <c r="E131" t="n">
-        <v>0.2106183035736895</v>
+        <v>-0.2407053407188615</v>
       </c>
       <c r="F131" t="n">
-        <v>-0.2612175830769494</v>
+        <v>-0.7714838022632731</v>
       </c>
     </row>
     <row r="132">
@@ -3057,19 +3057,19 @@
         <v>45824</v>
       </c>
       <c r="B132" t="n">
-        <v>-0.7670117672826676</v>
+        <v>1.423961437089044</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.3135798106331384</v>
+        <v>-2.827227197024561</v>
       </c>
       <c r="D132" t="n">
-        <v>-0.1166056183355359</v>
+        <v>1.106775631773901</v>
       </c>
       <c r="E132" t="n">
-        <v>-0.2642373707167957</v>
+        <v>0.3506384528509841</v>
       </c>
       <c r="F132" t="n">
-        <v>0.7597572019067659</v>
+        <v>1.360348362494627</v>
       </c>
     </row>
     <row r="133">
@@ -3077,19 +3077,19 @@
         <v>45825</v>
       </c>
       <c r="B133" t="n">
-        <v>-0.5518536558181613</v>
+        <v>1.86896658968343</v>
       </c>
       <c r="C133" t="n">
-        <v>0.09011441465814791</v>
+        <v>1.238040205645196</v>
       </c>
       <c r="D133" t="n">
-        <v>0.3206110837735383</v>
+        <v>0.7067069092168938</v>
       </c>
       <c r="E133" t="n">
-        <v>0.3708831566480574</v>
+        <v>0.3128940130435202</v>
       </c>
       <c r="F133" t="n">
-        <v>-0.08723733941149706</v>
+        <v>0.2448272191748622</v>
       </c>
     </row>
     <row r="134">
@@ -3097,19 +3097,19 @@
         <v>45826</v>
       </c>
       <c r="B134" t="n">
-        <v>0.6959480671956993</v>
+        <v>-0.4625085509628304</v>
       </c>
       <c r="C134" t="n">
-        <v>0.4776400927899166</v>
+        <v>0.05660666380264861</v>
       </c>
       <c r="D134" t="n">
-        <v>0.8110389313818103</v>
+        <v>0.4955783754646211</v>
       </c>
       <c r="E134" t="n">
-        <v>0.1676056173026281</v>
+        <v>1.424933311371405</v>
       </c>
       <c r="F134" t="n">
-        <v>0.2233126095894057</v>
+        <v>1.475085871054479</v>
       </c>
     </row>
     <row r="135">
@@ -3117,19 +3117,19 @@
         <v>45828</v>
       </c>
       <c r="B135" t="n">
-        <v>0.6821237773134434</v>
+        <v>-1.299579864781375</v>
       </c>
       <c r="C135" t="n">
-        <v>0.3130324351331663</v>
+        <v>1.218687167001992</v>
       </c>
       <c r="D135" t="n">
-        <v>0.4011448339066626</v>
+        <v>-1.292927391264772</v>
       </c>
       <c r="E135" t="n">
-        <v>0.03333485098567735</v>
+        <v>-1.329896711428594</v>
       </c>
       <c r="F135" t="n">
-        <v>0.1179527386444464</v>
+        <v>0.5522427407275387</v>
       </c>
     </row>
     <row r="136">
@@ -3137,19 +3137,19 @@
         <v>45831</v>
       </c>
       <c r="B136" t="n">
-        <v>-1.75183496811186</v>
+        <v>3.966316056216108</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.6523263916946785</v>
+        <v>-0.2285924757450426</v>
       </c>
       <c r="D136" t="n">
-        <v>0.180084050071551</v>
+        <v>0.9977647142743425</v>
       </c>
       <c r="E136" t="n">
-        <v>-0.2541074724926205</v>
+        <v>0.4940912466302803</v>
       </c>
       <c r="F136" t="n">
-        <v>-0.4449934716158108</v>
+        <v>0.01265583555484007</v>
       </c>
     </row>
     <row r="137">
@@ -3157,19 +3157,19 @@
         <v>45832</v>
       </c>
       <c r="B137" t="n">
-        <v>0.5287489457337694</v>
+        <v>-1.006545083876223</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.5130986830935899</v>
+        <v>-0.1757633791009197</v>
       </c>
       <c r="D137" t="n">
-        <v>-0.01932808158900891</v>
+        <v>-0.1004376317878339</v>
       </c>
       <c r="E137" t="n">
-        <v>-0.07629082460400356</v>
+        <v>-0.278149641558912</v>
       </c>
       <c r="F137" t="n">
-        <v>0.03712228007487375</v>
+        <v>-0.7175585747699866</v>
       </c>
     </row>
     <row r="138">
@@ -3177,19 +3177,19 @@
         <v>45833</v>
       </c>
       <c r="B138" t="n">
-        <v>-0.578741404116373</v>
+        <v>1.298866359812219</v>
       </c>
       <c r="C138" t="n">
-        <v>0.07663375497394848</v>
+        <v>0.6500939457580648</v>
       </c>
       <c r="D138" t="n">
-        <v>0.09529614510578165</v>
+        <v>-0.4721936145341228</v>
       </c>
       <c r="E138" t="n">
-        <v>0.07880467102553351</v>
+        <v>-0.2250389961939651</v>
       </c>
       <c r="F138" t="n">
-        <v>-0.1460717113280547</v>
+        <v>-0.1501977542590983</v>
       </c>
     </row>
     <row r="139">
@@ -3197,19 +3197,19 @@
         <v>45834</v>
       </c>
       <c r="B139" t="n">
-        <v>-1.482752251204714</v>
+        <v>3.394723693122898</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.5635775415258678</v>
+        <v>-0.5750432135661621</v>
       </c>
       <c r="D139" t="n">
-        <v>0.04556415556606256</v>
+        <v>1.562376678983916</v>
       </c>
       <c r="E139" t="n">
-        <v>-0.009007322045448385</v>
+        <v>0.1437522571233902</v>
       </c>
       <c r="F139" t="n">
-        <v>0.2952423430886569</v>
+        <v>0.5897286177370009</v>
       </c>
     </row>
     <row r="140">
@@ -3217,19 +3217,19 @@
         <v>45835</v>
       </c>
       <c r="B140" t="n">
-        <v>-0.9286727634885656</v>
+        <v>2.277640572177042</v>
       </c>
       <c r="C140" t="n">
-        <v>0.06671486958975253</v>
+        <v>0.6207783518012464</v>
       </c>
       <c r="D140" t="n">
-        <v>-0.03119566156949398</v>
+        <v>0.322574913494643</v>
       </c>
       <c r="E140" t="n">
-        <v>0.02428828422217795</v>
+        <v>0.1899021982858818</v>
       </c>
       <c r="F140" t="n">
-        <v>-0.1708871916664469</v>
+        <v>-0.1589462336499265</v>
       </c>
     </row>
     <row r="141">
@@ -3237,19 +3237,19 @@
         <v>45838</v>
       </c>
       <c r="B141" t="n">
-        <v>0.356977993512092</v>
+        <v>-0.7099423812016167</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.3993225953078244</v>
+        <v>-1.425876222561707</v>
       </c>
       <c r="D141" t="n">
-        <v>0.2474867106305875</v>
+        <v>-0.3814965888723092</v>
       </c>
       <c r="E141" t="n">
-        <v>-0.1904627789449156</v>
+        <v>-0.39236155108568</v>
       </c>
       <c r="F141" t="n">
-        <v>-0.08147279459292193</v>
+        <v>1.014032489194853</v>
       </c>
     </row>
     <row r="142">
@@ -3257,19 +3257,19 @@
         <v>45839</v>
       </c>
       <c r="B142" t="n">
-        <v>-0.5422137501246564</v>
+        <v>1.891236282292674</v>
       </c>
       <c r="C142" t="n">
-        <v>-0.5805699251868496</v>
+        <v>-0.2503732148754527</v>
       </c>
       <c r="D142" t="n">
-        <v>0.494796930781588</v>
+        <v>0.9662357621919551</v>
       </c>
       <c r="E142" t="n">
-        <v>0.03716766961517703</v>
+        <v>0.8257286096737547</v>
       </c>
       <c r="F142" t="n">
-        <v>-0.3044152975188026</v>
+        <v>0.639952659387912</v>
       </c>
     </row>
     <row r="143">
@@ -3277,19 +3277,19 @@
         <v>45840</v>
       </c>
       <c r="B143" t="n">
-        <v>-0.9921191424971042</v>
+        <v>1.503389925694478</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.1500151354290998</v>
+        <v>0.8717558758192333</v>
       </c>
       <c r="D143" t="n">
-        <v>-0.122172483876116</v>
+        <v>-1.344963378417168</v>
       </c>
       <c r="E143" t="n">
-        <v>-0.0105378136103658</v>
+        <v>-0.601753529097058</v>
       </c>
       <c r="F143" t="n">
-        <v>-0.5439621439741255</v>
+        <v>-1.342313378756129</v>
       </c>
     </row>
     <row r="144">
@@ -3297,19 +3297,19 @@
         <v>45841</v>
       </c>
       <c r="B144" t="n">
-        <v>-0.6899044744917117</v>
+        <v>0.7976457015634488</v>
       </c>
       <c r="C144" t="n">
-        <v>0.08685629050185206</v>
+        <v>-2.206432518303699</v>
       </c>
       <c r="D144" t="n">
-        <v>-0.1377959817618133</v>
+        <v>-1.09072224363674</v>
       </c>
       <c r="E144" t="n">
-        <v>-0.1060392992694068</v>
+        <v>0.7925072225972883</v>
       </c>
       <c r="F144" t="n">
-        <v>-0.03330886276768537</v>
+        <v>0.2304281828643151</v>
       </c>
     </row>
     <row r="145">
@@ -3317,19 +3317,19 @@
         <v>45842</v>
       </c>
       <c r="B145" t="n">
-        <v>-5.383356781794961</v>
+        <v>9.462284055037781</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.3698027855289011</v>
+        <v>-0.8150410726082197</v>
       </c>
       <c r="D145" t="n">
-        <v>-1.141495853908466</v>
+        <v>0.6026325261723526</v>
       </c>
       <c r="E145" t="n">
-        <v>0.04709050361254246</v>
+        <v>-0.2815257818652042</v>
       </c>
       <c r="F145" t="n">
-        <v>-0.1048962059393918</v>
+        <v>-0.1641820382509548</v>
       </c>
     </row>
     <row r="146">
@@ -3337,19 +3337,19 @@
         <v>45845</v>
       </c>
       <c r="B146" t="n">
-        <v>-2.331313689098647</v>
+        <v>4.652032038423202</v>
       </c>
       <c r="C146" t="n">
-        <v>1.379179398046614</v>
+        <v>3.88770085625519</v>
       </c>
       <c r="D146" t="n">
-        <v>0.985741006052307</v>
+        <v>-0.172350288996139</v>
       </c>
       <c r="E146" t="n">
-        <v>0.4676385241376236</v>
+        <v>0.4743007591017552</v>
       </c>
       <c r="F146" t="n">
-        <v>-0.1417625540022639</v>
+        <v>1.013176264615137</v>
       </c>
     </row>
     <row r="147">
@@ -3357,19 +3357,19 @@
         <v>45846</v>
       </c>
       <c r="B147" t="n">
-        <v>0.08217780576241616</v>
+        <v>0.3802934526488015</v>
       </c>
       <c r="C147" t="n">
-        <v>0.1326460480796834</v>
+        <v>-0.1179731894687616</v>
       </c>
       <c r="D147" t="n">
-        <v>0.2491529003874813</v>
+        <v>0.2941672201471269</v>
       </c>
       <c r="E147" t="n">
-        <v>-0.05725846539112552</v>
+        <v>0.7041096398315565</v>
       </c>
       <c r="F147" t="n">
-        <v>-0.2104213380657888</v>
+        <v>0.3383366447024953</v>
       </c>
     </row>
     <row r="148">
@@ -3377,19 +3377,19 @@
         <v>45847</v>
       </c>
       <c r="B148" t="n">
-        <v>-1.097743090680726</v>
+        <v>2.037804062523072</v>
       </c>
       <c r="C148" t="n">
-        <v>0.6282202896485646</v>
+        <v>1.857535957279651</v>
       </c>
       <c r="D148" t="n">
-        <v>-0.02165401317636109</v>
+        <v>-1.039797463132315</v>
       </c>
       <c r="E148" t="n">
-        <v>0.1425299523020429</v>
+        <v>-0.6328637541391641</v>
       </c>
       <c r="F148" t="n">
-        <v>0.04504981436002569</v>
+        <v>-0.3698898097971827</v>
       </c>
     </row>
     <row r="149">
@@ -3397,19 +3397,19 @@
         <v>45848</v>
       </c>
       <c r="B149" t="n">
-        <v>2.021277832496201</v>
+        <v>-4.563015470806369</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.2967734829111403</v>
+        <v>-0.3201415454991148</v>
       </c>
       <c r="D149" t="n">
-        <v>-0.1086941598508166</v>
+        <v>-1.496444838863825</v>
       </c>
       <c r="E149" t="n">
-        <v>-0.1013893585993429</v>
+        <v>-1.81207960269282</v>
       </c>
       <c r="F149" t="n">
-        <v>0.1128076966523472</v>
+        <v>-0.385462248872953</v>
       </c>
     </row>
     <row r="150">
@@ -3417,19 +3417,19 @@
         <v>45849</v>
       </c>
       <c r="B150" t="n">
-        <v>-1.77784335172491</v>
+        <v>3.479182408988788</v>
       </c>
       <c r="C150" t="n">
-        <v>0.5957180249721582</v>
+        <v>-0.02328466854994074</v>
       </c>
       <c r="D150" t="n">
-        <v>0.05128836867760716</v>
+        <v>-0.2476097987170431</v>
       </c>
       <c r="E150" t="n">
-        <v>0.1431399263583774</v>
+        <v>0.9811415007985556</v>
       </c>
       <c r="F150" t="n">
-        <v>0.2735665555613528</v>
+        <v>0.4937701166214419</v>
       </c>
     </row>
     <row r="151">
@@ -3437,19 +3437,19 @@
         <v>45852</v>
       </c>
       <c r="B151" t="n">
-        <v>-1.530540132762689</v>
+        <v>2.190393313878433</v>
       </c>
       <c r="C151" t="n">
-        <v>0.6764141835726156</v>
+        <v>2.878416891350483</v>
       </c>
       <c r="D151" t="n">
-        <v>-0.0323050760080438</v>
+        <v>-1.95630197945238</v>
       </c>
       <c r="E151" t="n">
-        <v>-0.02445075408311607</v>
+        <v>0.4820266709589027</v>
       </c>
       <c r="F151" t="n">
-        <v>-0.9398811822125357</v>
+        <v>-2.01320189421009</v>
       </c>
     </row>
     <row r="152">
@@ -3457,19 +3457,19 @@
         <v>45853</v>
       </c>
       <c r="B152" t="n">
-        <v>0.6163581579278929</v>
+        <v>-0.8199398360856824</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.3106720279439172</v>
+        <v>0.6155633127328218</v>
       </c>
       <c r="D152" t="n">
-        <v>0.03812632761331951</v>
+        <v>-0.0005438756568566738</v>
       </c>
       <c r="E152" t="n">
-        <v>-0.01039602823012773</v>
+        <v>-0.1737201267329165</v>
       </c>
       <c r="F152" t="n">
-        <v>-0.1559870957657522</v>
+        <v>-0.7394316826244322</v>
       </c>
     </row>
     <row r="153">
@@ -3477,19 +3477,19 @@
         <v>45854</v>
       </c>
       <c r="B153" t="n">
-        <v>0.8121955277251708</v>
+        <v>-1.773587833392475</v>
       </c>
       <c r="C153" t="n">
-        <v>-0.1067170556818969</v>
+        <v>0.200233969019086</v>
       </c>
       <c r="D153" t="n">
-        <v>-0.008164920303130475</v>
+        <v>-0.5422392075247806</v>
       </c>
       <c r="E153" t="n">
-        <v>-0.1402546908436291</v>
+        <v>-0.7250632652643012</v>
       </c>
       <c r="F153" t="n">
-        <v>0.1596740898281709</v>
+        <v>-0.8317853680118312</v>
       </c>
     </row>
     <row r="154">
@@ -3497,19 +3497,19 @@
         <v>45855</v>
       </c>
       <c r="B154" t="n">
-        <v>0.9546081723701939</v>
+        <v>-1.110417481093018</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.472491040072152</v>
+        <v>0.1053186481964334</v>
       </c>
       <c r="D154" t="n">
-        <v>0.3828854776149173</v>
+        <v>0.5571126846357147</v>
       </c>
       <c r="E154" t="n">
-        <v>0.1302712174817462</v>
+        <v>-0.10238381991239</v>
       </c>
       <c r="F154" t="n">
-        <v>0.06924003643309248</v>
+        <v>0.2523615381767466</v>
       </c>
     </row>
     <row r="155">
@@ -3517,19 +3517,19 @@
         <v>45856</v>
       </c>
       <c r="B155" t="n">
-        <v>0.04871055084569401</v>
+        <v>-0.3173562694420948</v>
       </c>
       <c r="C155" t="n">
-        <v>0.2319555343713409</v>
+        <v>0.6557122003143148</v>
       </c>
       <c r="D155" t="n">
-        <v>-0.02459451467472942</v>
+        <v>-1.079276786963434</v>
       </c>
       <c r="E155" t="n">
-        <v>0.06279312660890565</v>
+        <v>0.5149524453224255</v>
       </c>
       <c r="F155" t="n">
-        <v>-0.4497245447540031</v>
+        <v>-0.8267263044530484</v>
       </c>
     </row>
     <row r="156">
@@ -3537,19 +3537,19 @@
         <v>45859</v>
       </c>
       <c r="B156" t="n">
-        <v>-0.1793600665264673</v>
+        <v>0.4889779382766768</v>
       </c>
       <c r="C156" t="n">
-        <v>-0.6741629991067661</v>
+        <v>-2.669303273179724</v>
       </c>
       <c r="D156" t="n">
-        <v>0.2014047224234199</v>
+        <v>0.6758111243373117</v>
       </c>
       <c r="E156" t="n">
-        <v>-0.2171985581379304</v>
+        <v>0.6589414296032517</v>
       </c>
       <c r="F156" t="n">
-        <v>0.2944233103610238</v>
+        <v>0.8910273229364276</v>
       </c>
     </row>
     <row r="157">
@@ -3557,19 +3557,19 @@
         <v>45860</v>
       </c>
       <c r="B157" t="n">
-        <v>0.5652785873178593</v>
+        <v>0.1068829103345189</v>
       </c>
       <c r="C157" t="n">
-        <v>-0.06708349864849505</v>
+        <v>0.08924823154445588</v>
       </c>
       <c r="D157" t="n">
-        <v>0.815219800634382</v>
+        <v>1.244522643558519</v>
       </c>
       <c r="E157" t="n">
-        <v>-0.1179056001712282</v>
+        <v>1.266076876036555</v>
       </c>
       <c r="F157" t="n">
-        <v>-0.1302525278636478</v>
+        <v>0.9530387850047897</v>
       </c>
     </row>
     <row r="158">
@@ -3577,19 +3577,19 @@
         <v>45861</v>
       </c>
       <c r="B158" t="n">
-        <v>-0.1609898281457661</v>
+        <v>-0.1389037398526872</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.2885639153564538</v>
+        <v>-2.866206747871169</v>
       </c>
       <c r="D158" t="n">
-        <v>-0.1967671885638723</v>
+        <v>-0.1184071842336026</v>
       </c>
       <c r="E158" t="n">
-        <v>-0.4709582195253678</v>
+        <v>-0.1493417770695311</v>
       </c>
       <c r="F158" t="n">
-        <v>-0.007534496021101289</v>
+        <v>0.6225512971246367</v>
       </c>
     </row>
     <row r="159">
@@ -3597,19 +3597,19 @@
         <v>45862</v>
       </c>
       <c r="B159" t="n">
-        <v>-2.23961823995939</v>
+        <v>4.313782215036052</v>
       </c>
       <c r="C159" t="n">
-        <v>0.3942587506343892</v>
+        <v>2.34230018864382</v>
       </c>
       <c r="D159" t="n">
-        <v>0.2407390054239654</v>
+        <v>-0.3563783072941797</v>
       </c>
       <c r="E159" t="n">
-        <v>-0.1787067646082179</v>
+        <v>-0.3715076991857683</v>
       </c>
       <c r="F159" t="n">
-        <v>-0.2024943805862063</v>
+        <v>-0.463915630087812</v>
       </c>
     </row>
     <row r="160">
@@ -3617,19 +3617,19 @@
         <v>45863</v>
       </c>
       <c r="B160" t="n">
-        <v>-1.71252394199846</v>
+        <v>3.653326587663688</v>
       </c>
       <c r="C160" t="n">
-        <v>1.121732466841923</v>
+        <v>1.722386237735603</v>
       </c>
       <c r="D160" t="n">
-        <v>0.5000634779344549</v>
+        <v>-0.307702444155059</v>
       </c>
       <c r="E160" t="n">
-        <v>0.09615853140190787</v>
+        <v>1.380055641170995</v>
       </c>
       <c r="F160" t="n">
-        <v>-0.154583182905777</v>
+        <v>0.8081681052348633</v>
       </c>
     </row>
     <row r="161">
@@ -3637,19 +3637,19 @@
         <v>45866</v>
       </c>
       <c r="B161" t="n">
-        <v>-1.743668184313267</v>
+        <v>2.77161924504975</v>
       </c>
       <c r="C161" t="n">
-        <v>0.9667881736975407</v>
+        <v>2.338709035661615</v>
       </c>
       <c r="D161" t="n">
-        <v>-0.3456819214460952</v>
+        <v>-1.91049978146904</v>
       </c>
       <c r="E161" t="n">
-        <v>0.4353150290063004</v>
+        <v>0.1551244292038607</v>
       </c>
       <c r="F161" t="n">
-        <v>-0.499414832881959</v>
+        <v>-0.9102032679459233</v>
       </c>
     </row>
     <row r="162">
@@ -3657,19 +3657,19 @@
         <v>45867</v>
       </c>
       <c r="B162" t="n">
-        <v>-2.289528194505851</v>
+        <v>4.533825585574937</v>
       </c>
       <c r="C162" t="n">
-        <v>0.08265218415785788</v>
+        <v>0.4136024522429413</v>
       </c>
       <c r="D162" t="n">
-        <v>0.06477308937633257</v>
+        <v>0.07933610921190688</v>
       </c>
       <c r="E162" t="n">
-        <v>-0.2124418999007593</v>
+        <v>0.3345068251979744</v>
       </c>
       <c r="F162" t="n">
-        <v>-0.08302637297719713</v>
+        <v>0.1607512046736038</v>
       </c>
     </row>
     <row r="163">
@@ -3677,19 +3677,19 @@
         <v>45868</v>
       </c>
       <c r="B163" t="n">
-        <v>4.33258917584777</v>
+        <v>-10.37578554875634</v>
       </c>
       <c r="C163" t="n">
-        <v>0.3033506527743213</v>
+        <v>-3.331679875620452</v>
       </c>
       <c r="D163" t="n">
-        <v>-0.1534456968852648</v>
+        <v>-1.243544452700423</v>
       </c>
       <c r="E163" t="n">
-        <v>-0.1324909053913303</v>
+        <v>-0.3379137638876234</v>
       </c>
       <c r="F163" t="n">
-        <v>0.09458077303924065</v>
+        <v>0.7424114467865067</v>
       </c>
     </row>
     <row r="164">
@@ -3697,19 +3697,19 @@
         <v>45869</v>
       </c>
       <c r="B164" t="n">
-        <v>1.587447915689395</v>
+        <v>-2.998054824407309</v>
       </c>
       <c r="C164" t="n">
-        <v>0.05775922448645279</v>
+        <v>0.6218938769889112</v>
       </c>
       <c r="D164" t="n">
-        <v>0.2523131537965338</v>
+        <v>-0.6836411332212248</v>
       </c>
       <c r="E164" t="n">
-        <v>0.1504185756217038</v>
+        <v>-2.015631633535889</v>
       </c>
       <c r="F164" t="n">
-        <v>0.4947737752838731</v>
+        <v>0.8660235380118391</v>
       </c>
     </row>
     <row r="165">
@@ -3717,19 +3717,19 @@
         <v>45873</v>
       </c>
       <c r="B165" t="n">
-        <v>1.71261746008725</v>
+        <v>-4.023300671073682</v>
       </c>
       <c r="C165" t="n">
-        <v>0.1219606905435736</v>
+        <v>-1.295862615632176</v>
       </c>
       <c r="D165" t="n">
-        <v>-0.1956179990675279</v>
+        <v>-1.371335310934611</v>
       </c>
       <c r="E165" t="n">
-        <v>0.1031044709185413</v>
+        <v>1.373941480013158</v>
       </c>
       <c r="F165" t="n">
-        <v>-0.2666383983178233</v>
+        <v>-0.3840747107885353</v>
       </c>
     </row>
     <row r="166">
@@ -3737,19 +3737,19 @@
         <v>45874</v>
       </c>
       <c r="B166" t="n">
-        <v>1.56405891376041</v>
+        <v>-2.464922784072057</v>
       </c>
       <c r="C166" t="n">
-        <v>-0.09828154719920479</v>
+        <v>-0.6334331950645096</v>
       </c>
       <c r="D166" t="n">
-        <v>0.4934352041103157</v>
+        <v>0.08720227981904918</v>
       </c>
       <c r="E166" t="n">
-        <v>0.02652299380207305</v>
+        <v>0.6506894866819629</v>
       </c>
       <c r="F166" t="n">
-        <v>0.09474868772262866</v>
+        <v>0.831634270795449</v>
       </c>
     </row>
     <row r="167">
@@ -3757,19 +3757,19 @@
         <v>45875</v>
       </c>
       <c r="B167" t="n">
-        <v>1.1790986490365</v>
+        <v>-2.103874239373782</v>
       </c>
       <c r="C167" t="n">
-        <v>-0.3393494532773552</v>
+        <v>-2.140696158757645</v>
       </c>
       <c r="D167" t="n">
-        <v>0.1674759002399645</v>
+        <v>0.2367011407547828</v>
       </c>
       <c r="E167" t="n">
-        <v>-0.2676010107037695</v>
+        <v>0.6858918432683083</v>
       </c>
       <c r="F167" t="n">
-        <v>-0.1283771141308196</v>
+        <v>0.5666097009844461</v>
       </c>
     </row>
     <row r="168">
@@ -3777,19 +3777,19 @@
         <v>45876</v>
       </c>
       <c r="B168" t="n">
-        <v>0.4650838734870963</v>
+        <v>-0.6085475475171371</v>
       </c>
       <c r="C168" t="n">
-        <v>0.03534483074378098</v>
+        <v>-1.730546348167835</v>
       </c>
       <c r="D168" t="n">
-        <v>0.2917411784168142</v>
+        <v>0.7445880046391035</v>
       </c>
       <c r="E168" t="n">
-        <v>-0.07339231797057236</v>
+        <v>0.5957040012880358</v>
       </c>
       <c r="F168" t="n">
-        <v>0.3075396359024621</v>
+        <v>1.135397280051736</v>
       </c>
     </row>
     <row r="169">
@@ -3797,19 +3797,19 @@
         <v>45877</v>
       </c>
       <c r="B169" t="n">
-        <v>-0.4321887759356882</v>
+        <v>1.637932504809495</v>
       </c>
       <c r="C169" t="n">
-        <v>-0.1152714758364387</v>
+        <v>1.979157278488256</v>
       </c>
       <c r="D169" t="n">
-        <v>0.7820448814212309</v>
+        <v>0.468291030320013</v>
       </c>
       <c r="E169" t="n">
-        <v>0.3178692463030215</v>
+        <v>-0.3951835803821913</v>
       </c>
       <c r="F169" t="n">
-        <v>-0.0522123780162807</v>
+        <v>0.2844929387042723</v>
       </c>
     </row>
     <row r="170">
@@ -3817,19 +3817,19 @@
         <v>45880</v>
       </c>
       <c r="B170" t="n">
-        <v>-0.6662016139019559</v>
+        <v>1.832489709126789</v>
       </c>
       <c r="C170" t="n">
-        <v>-0.3075566918521289</v>
+        <v>0.3215418106595467</v>
       </c>
       <c r="D170" t="n">
-        <v>-0.08179658459641398</v>
+        <v>0.6932762058116699</v>
       </c>
       <c r="E170" t="n">
-        <v>-0.1061681870989471</v>
+        <v>-0.4358480491585668</v>
       </c>
       <c r="F170" t="n">
-        <v>0.06664944110616036</v>
+        <v>-0.1806407807274298</v>
       </c>
     </row>
     <row r="171">
@@ -3837,19 +3837,19 @@
         <v>45881</v>
       </c>
       <c r="B171" t="n">
-        <v>0.8752292354531845</v>
+        <v>-1.898060788485386</v>
       </c>
       <c r="C171" t="n">
-        <v>-0.4496838241183196</v>
+        <v>-2.808200774886263</v>
       </c>
       <c r="D171" t="n">
-        <v>0.01662717371105953</v>
+        <v>0.08092085226512076</v>
       </c>
       <c r="E171" t="n">
-        <v>-0.1569941634810992</v>
+        <v>1.353822233937632</v>
       </c>
       <c r="F171" t="n">
-        <v>0.2734763504076931</v>
+        <v>0.8420023750832766</v>
       </c>
     </row>
     <row r="172">
@@ -3857,19 +3857,19 @@
         <v>45882</v>
       </c>
       <c r="B172" t="n">
-        <v>-0.9900588193843824</v>
+        <v>2.127343704444425</v>
       </c>
       <c r="C172" t="n">
-        <v>0.05719294041323708</v>
+        <v>1.183600942092655</v>
       </c>
       <c r="D172" t="n">
-        <v>0.6049089084212573</v>
+        <v>-0.301333780600338</v>
       </c>
       <c r="E172" t="n">
-        <v>0.0004615137340601511</v>
+        <v>-0.4406517249138608</v>
       </c>
       <c r="F172" t="n">
-        <v>-0.03214103672580931</v>
+        <v>0.3577780751716153</v>
       </c>
     </row>
     <row r="173">
@@ -3877,19 +3877,19 @@
         <v>45883</v>
       </c>
       <c r="B173" t="n">
-        <v>0.9885302089767862</v>
+        <v>-2.003330058537357</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.01698855892138255</v>
+        <v>0.2837715275354061</v>
       </c>
       <c r="D173" t="n">
-        <v>0.1158254650960429</v>
+        <v>-0.9439196442383893</v>
       </c>
       <c r="E173" t="n">
-        <v>0.04101626700581701</v>
+        <v>-1.524519230499025</v>
       </c>
       <c r="F173" t="n">
-        <v>0.3743054085466838</v>
+        <v>0.1875720381876195</v>
       </c>
     </row>
     <row r="174">
@@ -3897,19 +3897,19 @@
         <v>45884</v>
       </c>
       <c r="B174" t="n">
-        <v>-0.1856748413800654</v>
+        <v>1.542618460769455</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.1265526578866625</v>
+        <v>2.322493788674824</v>
       </c>
       <c r="D174" t="n">
-        <v>0.6277004473260143</v>
+        <v>1.212637716145299</v>
       </c>
       <c r="E174" t="n">
-        <v>0.1443015395418269</v>
+        <v>0.3189264591522006</v>
       </c>
       <c r="F174" t="n">
-        <v>-0.256539391628523</v>
+        <v>-0.2779961627111779</v>
       </c>
     </row>
     <row r="175">
@@ -3917,19 +3917,19 @@
         <v>45887</v>
       </c>
       <c r="B175" t="n">
-        <v>-2.515909679089398</v>
+        <v>4.485139529388952</v>
       </c>
       <c r="C175" t="n">
-        <v>0.4131988655750557</v>
+        <v>0.5553274212000895</v>
       </c>
       <c r="D175" t="n">
-        <v>-0.01724933452738471</v>
+        <v>-1.195357948276786</v>
       </c>
       <c r="E175" t="n">
-        <v>-0.1276210294472931</v>
+        <v>-0.08097963970829608</v>
       </c>
       <c r="F175" t="n">
-        <v>-0.2042750656928097</v>
+        <v>0.3061873300602567</v>
       </c>
     </row>
     <row r="176">
@@ -3937,19 +3937,19 @@
         <v>45888</v>
       </c>
       <c r="B176" t="n">
-        <v>1.746608532097565</v>
+        <v>-4.1539929321573</v>
       </c>
       <c r="C176" t="n">
-        <v>0.1439386956909497</v>
+        <v>1.353468241792646</v>
       </c>
       <c r="D176" t="n">
-        <v>0.3642593746333693</v>
+        <v>-2.070720313000577</v>
       </c>
       <c r="E176" t="n">
-        <v>-0.01057387383083037</v>
+        <v>-1.978178314221555</v>
       </c>
       <c r="F176" t="n">
-        <v>-0.05656822830588751</v>
+        <v>-0.3169833486966969</v>
       </c>
     </row>
     <row r="177">
@@ -3957,19 +3957,19 @@
         <v>45889</v>
       </c>
       <c r="B177" t="n">
-        <v>-2.173270023250737</v>
+        <v>3.482471997016169</v>
       </c>
       <c r="C177" t="n">
-        <v>0.09063074003577337</v>
+        <v>0.6778117630339888</v>
       </c>
       <c r="D177" t="n">
-        <v>-0.06985118351099713</v>
+        <v>-1.64512051238302</v>
       </c>
       <c r="E177" t="n">
-        <v>-0.1448449512359731</v>
+        <v>-1.213968558854701</v>
       </c>
       <c r="F177" t="n">
-        <v>0.09229100857680744</v>
+        <v>-0.234113777875757</v>
       </c>
     </row>
     <row r="178">
@@ -3977,19 +3977,19 @@
         <v>45890</v>
       </c>
       <c r="B178" t="n">
-        <v>-0.5686049288831715</v>
+        <v>-0.08799063462428967</v>
       </c>
       <c r="C178" t="n">
-        <v>0.5969734116357678</v>
+        <v>-0.7604453440621876</v>
       </c>
       <c r="D178" t="n">
-        <v>-0.5431273580610697</v>
+        <v>-2.715628602618908</v>
       </c>
       <c r="E178" t="n">
-        <v>-0.1825804955802858</v>
+        <v>0.2726489602182005</v>
       </c>
       <c r="F178" t="n">
-        <v>-0.4063736675587061</v>
+        <v>-0.9677010569603159</v>
       </c>
     </row>
     <row r="179">
@@ -3997,19 +3997,19 @@
         <v>45891</v>
       </c>
       <c r="B179" t="n">
-        <v>1.26041985431246</v>
+        <v>-2.838736568920916</v>
       </c>
       <c r="C179" t="n">
-        <v>-0.6805622631417789</v>
+        <v>-3.881604998464985</v>
       </c>
       <c r="D179" t="n">
-        <v>-0.2925830398026744</v>
+        <v>0.8337665651579681</v>
       </c>
       <c r="E179" t="n">
-        <v>-0.2372996859704661</v>
+        <v>0.6376769460612531</v>
       </c>
       <c r="F179" t="n">
-        <v>0.4235821019329965</v>
+        <v>0.8733313786346675</v>
       </c>
     </row>
     <row r="180">
@@ -4017,19 +4017,19 @@
         <v>45894</v>
       </c>
       <c r="B180" t="n">
-        <v>-2.971456720512025</v>
+        <v>5.961907813686081</v>
       </c>
       <c r="C180" t="n">
-        <v>-0.07483199008661788</v>
+        <v>1.492981922817761</v>
       </c>
       <c r="D180" t="n">
-        <v>-0.02811164229173082</v>
+        <v>0.8757296554067637</v>
       </c>
       <c r="E180" t="n">
-        <v>0.1904950793765071</v>
+        <v>-0.5953469684573109</v>
       </c>
       <c r="F180" t="n">
-        <v>0.3392699937876536</v>
+        <v>0.2024019759558068</v>
       </c>
     </row>
     <row r="181">
@@ -4037,19 +4037,19 @@
         <v>45895</v>
       </c>
       <c r="B181" t="n">
-        <v>-3.214915752024393</v>
+        <v>5.824674441863754</v>
       </c>
       <c r="C181" t="n">
-        <v>0.6376214808308933</v>
+        <v>1.971537472408926</v>
       </c>
       <c r="D181" t="n">
-        <v>-0.005421957607603201</v>
+        <v>-0.9526514534011499</v>
       </c>
       <c r="E181" t="n">
-        <v>0.1328918671862318</v>
+        <v>0.1554628417714699</v>
       </c>
       <c r="F181" t="n">
-        <v>-0.4626275686991094</v>
+        <v>-0.3682586123257674</v>
       </c>
     </row>
     <row r="182">
@@ -4057,19 +4057,19 @@
         <v>45896</v>
       </c>
       <c r="B182" t="n">
-        <v>-1.073321623254885</v>
+        <v>2.971077222322296</v>
       </c>
       <c r="C182" t="n">
-        <v>-0.1867055887256232</v>
+        <v>1.411135416190552</v>
       </c>
       <c r="D182" t="n">
-        <v>0.6381386949667326</v>
+        <v>0.7911020294157025</v>
       </c>
       <c r="E182" t="n">
-        <v>0.1906645969083219</v>
+        <v>0.1002362484351063</v>
       </c>
       <c r="F182" t="n">
-        <v>0.05011135034631709</v>
+        <v>0.7743627369368333</v>
       </c>
     </row>
     <row r="183">
@@ -4077,19 +4077,19 @@
         <v>45897</v>
       </c>
       <c r="B183" t="n">
-        <v>-0.5493903085023391</v>
+        <v>0.2538022158557318</v>
       </c>
       <c r="C183" t="n">
-        <v>-0.1973030503914248</v>
+        <v>-4.041090871545534</v>
       </c>
       <c r="D183" t="n">
-        <v>-0.802853598538661</v>
+        <v>0.3240309741232412</v>
       </c>
       <c r="E183" t="n">
-        <v>-0.2319769917136636</v>
+        <v>-0.5581094235485046</v>
       </c>
       <c r="F183" t="n">
-        <v>0.5735021968183937</v>
+        <v>0.4582979986779774</v>
       </c>
     </row>
     <row r="184">
@@ -4097,19 +4097,19 @@
         <v>45898</v>
       </c>
       <c r="B184" t="n">
-        <v>-3.447728371325899</v>
+        <v>5.893527119455492</v>
       </c>
       <c r="C184" t="n">
-        <v>-0.1249348604057633</v>
+        <v>-1.495666784677624</v>
       </c>
       <c r="D184" t="n">
-        <v>-0.8220282686591344</v>
+        <v>-0.1902164750219716</v>
       </c>
       <c r="E184" t="n">
-        <v>-0.4824438509701528</v>
+        <v>-0.4166697891339176</v>
       </c>
       <c r="F184" t="n">
-        <v>-0.3051969213827814</v>
+        <v>-0.0631093328817636</v>
       </c>
     </row>
     <row r="185">
@@ -4117,19 +4117,19 @@
         <v>45901</v>
       </c>
       <c r="B185" t="n">
-        <v>-3.696311447055777</v>
+        <v>6.035549210558008</v>
       </c>
       <c r="C185" t="n">
-        <v>0.7997184175582387</v>
+        <v>-0.126358692172652</v>
       </c>
       <c r="D185" t="n">
-        <v>-0.4223731825128053</v>
+        <v>-1.820853825836144</v>
       </c>
       <c r="E185" t="n">
-        <v>-0.03085671852544194</v>
+        <v>0.7042126987393491</v>
       </c>
       <c r="F185" t="n">
-        <v>-0.4545229430335914</v>
+        <v>0.1599124768704739</v>
       </c>
     </row>
     <row r="186">
@@ -4137,19 +4137,19 @@
         <v>45902</v>
       </c>
       <c r="B186" t="n">
-        <v>0.4279641229209725</v>
+        <v>-2.748042584160815</v>
       </c>
       <c r="C186" t="n">
-        <v>0.5438766057952711</v>
+        <v>-0.9791953457372031</v>
       </c>
       <c r="D186" t="n">
-        <v>-0.4766303779314582</v>
+        <v>-3.838494985110863</v>
       </c>
       <c r="E186" t="n">
-        <v>-0.2718359151241675</v>
+        <v>-0.5511270471870546</v>
       </c>
       <c r="F186" t="n">
-        <v>-0.4210637927331002</v>
+        <v>-1.157879376431683</v>
       </c>
     </row>
     <row r="187">
@@ -4157,19 +4157,19 @@
         <v>45903</v>
       </c>
       <c r="B187" t="n">
-        <v>-3.025827823056569</v>
+        <v>5.417102083953507</v>
       </c>
       <c r="C187" t="n">
-        <v>0.9119874725410645</v>
+        <v>0.5135432443992416</v>
       </c>
       <c r="D187" t="n">
-        <v>-0.5846030018330165</v>
+        <v>-1.018602993006294</v>
       </c>
       <c r="E187" t="n">
-        <v>0.2255919621076009</v>
+        <v>0.7296735449019067</v>
       </c>
       <c r="F187" t="n">
-        <v>0.07585203858489704</v>
+        <v>-0.05934227818741866</v>
       </c>
     </row>
     <row r="188">
@@ -4177,19 +4177,19 @@
         <v>45904</v>
       </c>
       <c r="B188" t="n">
-        <v>-2.251808256564417</v>
+        <v>5.108524388820856</v>
       </c>
       <c r="C188" t="n">
-        <v>-0.1018787345931577</v>
+        <v>1.109177508797371</v>
       </c>
       <c r="D188" t="n">
-        <v>0.53164910430426</v>
+        <v>1.980691975162719</v>
       </c>
       <c r="E188" t="n">
-        <v>0.1691674238908579</v>
+        <v>-0.01244575670348898</v>
       </c>
       <c r="F188" t="n">
-        <v>0.943267109543519</v>
+        <v>1.326060302600105</v>
       </c>
     </row>
     <row r="189">
@@ -4197,19 +4197,19 @@
         <v>45905</v>
       </c>
       <c r="B189" t="n">
-        <v>1.71065797356899</v>
+        <v>-4.748109455574225</v>
       </c>
       <c r="C189" t="n">
-        <v>0.1716599073080129</v>
+        <v>-3.041491744750856</v>
       </c>
       <c r="D189" t="n">
-        <v>-0.2699252523701314</v>
+        <v>-2.302303225279144</v>
       </c>
       <c r="E189" t="n">
-        <v>-0.06367367809087664</v>
+        <v>0.6616521946384349</v>
       </c>
       <c r="F189" t="n">
-        <v>-0.03404434386023652</v>
+        <v>0.06241881672022701</v>
       </c>
     </row>
     <row r="190">
@@ -4217,19 +4217,19 @@
         <v>45908</v>
       </c>
       <c r="B190" t="n">
-        <v>-2.183515219080632</v>
+        <v>3.716816994757737</v>
       </c>
       <c r="C190" t="n">
-        <v>0.2753278427955329</v>
+        <v>1.973142340987607</v>
       </c>
       <c r="D190" t="n">
-        <v>0.028319225735875</v>
+        <v>-0.9269754724936075</v>
       </c>
       <c r="E190" t="n">
-        <v>-0.3624575154164416</v>
+        <v>-0.01108112356920765</v>
       </c>
       <c r="F190" t="n">
-        <v>-0.5293811293568045</v>
+        <v>-1.196583477260425</v>
       </c>
     </row>
     <row r="191">
@@ -4237,19 +4237,19 @@
         <v>45909</v>
       </c>
       <c r="B191" t="n">
-        <v>-4.738346932046585</v>
+        <v>8.76684784597575</v>
       </c>
       <c r="C191" t="n">
-        <v>0.46182030076367</v>
+        <v>1.667857298994578</v>
       </c>
       <c r="D191" t="n">
-        <v>-0.01208367846394163</v>
+        <v>0.561707219376401</v>
       </c>
       <c r="E191" t="n">
-        <v>0.3134914071573399</v>
+        <v>0.2185045166635835</v>
       </c>
       <c r="F191" t="n">
-        <v>0.6097326363988773</v>
+        <v>1.020913831447243</v>
       </c>
     </row>
     <row r="192">
@@ -4257,19 +4257,19 @@
         <v>45910</v>
       </c>
       <c r="B192" t="n">
-        <v>-0.6844969033321631</v>
+        <v>0.8728456149897941</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.5108450344921718</v>
+        <v>-1.443749494969399</v>
       </c>
       <c r="D192" t="n">
-        <v>-0.2898485528593697</v>
+        <v>-0.8044638005938834</v>
       </c>
       <c r="E192" t="n">
-        <v>-0.2145156877181637</v>
+        <v>-0.04931370289283219</v>
       </c>
       <c r="F192" t="n">
-        <v>-0.3766831840312727</v>
+        <v>-0.7257113932872109</v>
       </c>
     </row>
     <row r="193">
@@ -4277,19 +4277,19 @@
         <v>45911</v>
       </c>
       <c r="B193" t="n">
-        <v>-1.0614145930621</v>
+        <v>1.732540460996448</v>
       </c>
       <c r="C193" t="n">
-        <v>0.5640512334147697</v>
+        <v>0.2429114300950976</v>
       </c>
       <c r="D193" t="n">
-        <v>-0.6602176252470702</v>
+        <v>-1.204680842687488</v>
       </c>
       <c r="E193" t="n">
-        <v>0.05765733982952869</v>
+        <v>0.4424233651188536</v>
       </c>
       <c r="F193" t="n">
-        <v>-0.4195849647850753</v>
+        <v>-1.145113289948819</v>
       </c>
     </row>
     <row r="194">
@@ -4297,19 +4297,19 @@
         <v>45912</v>
       </c>
       <c r="B194" t="n">
-        <v>-0.6054606104436144</v>
+        <v>1.469708613335118</v>
       </c>
       <c r="C194" t="n">
-        <v>0.1992003431438102</v>
+        <v>0.6527558519406996</v>
       </c>
       <c r="D194" t="n">
-        <v>-0.4120210650162763</v>
+        <v>0.3065653748741468</v>
       </c>
       <c r="E194" t="n">
-        <v>0.1472614235755429</v>
+        <v>-1.240418708173408</v>
       </c>
       <c r="F194" t="n">
-        <v>0.5591514020174149</v>
+        <v>-0.2354031374123317</v>
       </c>
     </row>
     <row r="195">
@@ -4317,19 +4317,19 @@
         <v>45915</v>
       </c>
       <c r="B195" t="n">
-        <v>-0.6212781170781537</v>
+        <v>1.089320712283038</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.345938588708828</v>
+        <v>-1.504142692472346</v>
       </c>
       <c r="D195" t="n">
-        <v>-0.7264964081493506</v>
+        <v>0.1815227405022971</v>
       </c>
       <c r="E195" t="n">
-        <v>0.01907507569327464</v>
+        <v>-0.3589103430846071</v>
       </c>
       <c r="F195" t="n">
-        <v>0.07347776442610952</v>
+        <v>-0.6544276324604357</v>
       </c>
     </row>
     <row r="196">
@@ -4337,19 +4337,19 @@
         <v>45916</v>
       </c>
       <c r="B196" t="n">
-        <v>-1.674177874516192</v>
+        <v>2.992709152342205</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.4813151094507968</v>
+        <v>-1.406011624981086</v>
       </c>
       <c r="D196" t="n">
-        <v>-0.9042958633597689</v>
+        <v>0.3284719059012566</v>
       </c>
       <c r="E196" t="n">
-        <v>-0.2787622194297795</v>
+        <v>-1.207250645535832</v>
       </c>
       <c r="F196" t="n">
-        <v>0.2009310007815496</v>
+        <v>-0.5258718669955024</v>
       </c>
     </row>
     <row r="197">
@@ -4357,19 +4357,19 @@
         <v>45917</v>
       </c>
       <c r="B197" t="n">
-        <v>2.450071817647831</v>
+        <v>-4.609274151656233</v>
       </c>
       <c r="C197" t="n">
-        <v>0.1744938894654877</v>
+        <v>0.4912682477104122</v>
       </c>
       <c r="D197" t="n">
-        <v>0.07211988855978167</v>
+        <v>-0.6704204816146417</v>
       </c>
       <c r="E197" t="n">
-        <v>-0.01777010428674108</v>
+        <v>0.02282625999407788</v>
       </c>
       <c r="F197" t="n">
-        <v>-0.183545655520967</v>
+        <v>-0.1863374862500791</v>
       </c>
     </row>
     <row r="198">
@@ -4377,19 +4377,19 @@
         <v>45918</v>
       </c>
       <c r="B198" t="n">
-        <v>-2.534533387660709</v>
+        <v>4.908844075428929</v>
       </c>
       <c r="C198" t="n">
-        <v>-0.07186330726736932</v>
+        <v>0.8825669723974422</v>
       </c>
       <c r="D198" t="n">
-        <v>0.2265203077204896</v>
+        <v>0.01280937167531429</v>
       </c>
       <c r="E198" t="n">
-        <v>-0.2519690580868696</v>
+        <v>-0.0316530227725707</v>
       </c>
       <c r="F198" t="n">
-        <v>-0.2677606931247703</v>
+        <v>0.2576160434411853</v>
       </c>
     </row>
     <row r="199">
@@ -4397,19 +4397,19 @@
         <v>45919</v>
       </c>
       <c r="B199" t="n">
-        <v>-2.949629524719738</v>
+        <v>5.567801147676679</v>
       </c>
       <c r="C199" t="n">
-        <v>0.6383834168925928</v>
+        <v>1.273959352298097</v>
       </c>
       <c r="D199" t="n">
-        <v>-0.0733800798835028</v>
+        <v>-0.1908975438196495</v>
       </c>
       <c r="E199" t="n">
-        <v>0.5517816730008793</v>
+        <v>1.555051704057524</v>
       </c>
       <c r="F199" t="n">
-        <v>-0.6297682262293608</v>
+        <v>-0.4134022406559192</v>
       </c>
     </row>
     <row r="200">
@@ -4417,19 +4417,19 @@
         <v>45922</v>
       </c>
       <c r="B200" t="n">
-        <v>-0.9075042323142011</v>
+        <v>0.9622710526926119</v>
       </c>
       <c r="C200" t="n">
-        <v>0.20493378396812</v>
+        <v>1.577081956046363</v>
       </c>
       <c r="D200" t="n">
-        <v>-0.1593835568505169</v>
+        <v>-2.026269075299695</v>
       </c>
       <c r="E200" t="n">
-        <v>-0.2010842064134737</v>
+        <v>-0.813203972495524</v>
       </c>
       <c r="F200" t="n">
-        <v>-0.3922396535515209</v>
+        <v>-1.73646179165284</v>
       </c>
     </row>
     <row r="201">
@@ -4437,19 +4437,19 @@
         <v>45923</v>
       </c>
       <c r="B201" t="n">
-        <v>0.5834739280411964</v>
+        <v>-1.41900833932156</v>
       </c>
       <c r="C201" t="n">
-        <v>0.6725128556593227</v>
+        <v>-1.378980338970176</v>
       </c>
       <c r="D201" t="n">
-        <v>-0.1508503277304674</v>
+        <v>-0.5318465121882661</v>
       </c>
       <c r="E201" t="n">
-        <v>-0.08877371303164337</v>
+        <v>-0.3759626495168932</v>
       </c>
       <c r="F201" t="n">
-        <v>0.2773475728303846</v>
+        <v>0.7162406614531145</v>
       </c>
     </row>
     <row r="202">
@@ -4457,19 +4457,19 @@
         <v>45924</v>
       </c>
       <c r="B202" t="n">
-        <v>-6.297547292174846</v>
+        <v>11.0512765989542</v>
       </c>
       <c r="C202" t="n">
-        <v>0.07654619785901995</v>
+        <v>1.602459890881402</v>
       </c>
       <c r="D202" t="n">
-        <v>0.1968038318187791</v>
+        <v>1.242101917724315</v>
       </c>
       <c r="E202" t="n">
-        <v>-0.306511615401991</v>
+        <v>0.6092075297889999</v>
       </c>
       <c r="F202" t="n">
-        <v>0.08684558713585702</v>
+        <v>0.5532739222394708</v>
       </c>
     </row>
     <row r="203">
@@ -4477,19 +4477,19 @@
         <v>45925</v>
       </c>
       <c r="B203" t="n">
-        <v>-0.3219742040988771</v>
+        <v>0.7362259429081353</v>
       </c>
       <c r="C203" t="n">
-        <v>-0.2991417920062846</v>
+        <v>1.056148395885945</v>
       </c>
       <c r="D203" t="n">
-        <v>-0.09760953002855424</v>
+        <v>-0.1847125102705054</v>
       </c>
       <c r="E203" t="n">
-        <v>0.1147336769416405</v>
+        <v>-0.6121922980696102</v>
       </c>
       <c r="F203" t="n">
-        <v>-0.270931664553843</v>
+        <v>-1.308544500835976</v>
       </c>
     </row>
     <row r="204">
@@ -4497,19 +4497,19 @@
         <v>45926</v>
       </c>
       <c r="B204" t="n">
-        <v>-2.531299790123219</v>
+        <v>4.326577434296061</v>
       </c>
       <c r="C204" t="n">
-        <v>0.05707728885874807</v>
+        <v>0.5766497406662544</v>
       </c>
       <c r="D204" t="n">
-        <v>-0.6135393705350093</v>
+        <v>-1.142589311881724</v>
       </c>
       <c r="E204" t="n">
-        <v>-0.368703444975158</v>
+        <v>0.0288317450541009</v>
       </c>
       <c r="F204" t="n">
-        <v>-0.75340512381326</v>
+        <v>-1.730969383981901</v>
       </c>
     </row>
     <row r="205">
@@ -4517,19 +4517,19 @@
         <v>45929</v>
       </c>
       <c r="B205" t="n">
-        <v>0.3954251139512736</v>
+        <v>-0.8449521183629511</v>
       </c>
       <c r="C205" t="n">
-        <v>-0.1187514398925325</v>
+        <v>-1.792836146437534</v>
       </c>
       <c r="D205" t="n">
-        <v>0.1924030087222057</v>
+        <v>-0.3657451109595272</v>
       </c>
       <c r="E205" t="n">
-        <v>0.01679551785581305</v>
+        <v>1.450764397078582</v>
       </c>
       <c r="F205" t="n">
-        <v>0.04552430716538522</v>
+        <v>0.5812018244787617</v>
       </c>
     </row>
     <row r="206">
@@ -4537,19 +4537,19 @@
         <v>45930</v>
       </c>
       <c r="B206" t="n">
-        <v>-2.914273539202701</v>
+        <v>4.886039880647311</v>
       </c>
       <c r="C206" t="n">
-        <v>0.7793047837173476</v>
+        <v>0.6679995147464504</v>
       </c>
       <c r="D206" t="n">
-        <v>0.1840670040276237</v>
+        <v>-1.489195137555907</v>
       </c>
       <c r="E206" t="n">
-        <v>0.03419175143287147</v>
+        <v>1.477844073315474</v>
       </c>
       <c r="F206" t="n">
-        <v>-0.4593075942286253</v>
+        <v>0.0884544960606652</v>
       </c>
     </row>
     <row r="207">
@@ -4557,19 +4557,19 @@
         <v>45931</v>
       </c>
       <c r="B207" t="n">
-        <v>-1.710866044102786</v>
+        <v>2.988471084546784</v>
       </c>
       <c r="C207" t="n">
-        <v>0.8048101324421881</v>
+        <v>1.613760429534267</v>
       </c>
       <c r="D207" t="n">
-        <v>0.08430742790676878</v>
+        <v>-1.457189907645314</v>
       </c>
       <c r="E207" t="n">
-        <v>0.2528496456893921</v>
+        <v>0.2537214403761722</v>
       </c>
       <c r="F207" t="n">
-        <v>-0.2265328271002217</v>
+        <v>-0.05415357608703486</v>
       </c>
     </row>
     <row r="208">
@@ -4577,19 +4577,19 @@
         <v>45932</v>
       </c>
       <c r="B208" t="n">
-        <v>-2.087351741023841</v>
+        <v>3.104003412433172</v>
       </c>
       <c r="C208" t="n">
-        <v>0.4117245872168268</v>
+        <v>1.126253385235213</v>
       </c>
       <c r="D208" t="n">
-        <v>-0.4601653888210097</v>
+        <v>-2.095010809154773</v>
       </c>
       <c r="E208" t="n">
-        <v>0.2007858759286318</v>
+        <v>-0.3242138988483541</v>
       </c>
       <c r="F208" t="n">
-        <v>-0.4162185617986158</v>
+        <v>-1.453011831146618</v>
       </c>
     </row>
     <row r="209">
@@ -4597,19 +4597,19 @@
         <v>45933</v>
       </c>
       <c r="B209" t="n">
-        <v>-1.050806023613709</v>
+        <v>3.370879627725478</v>
       </c>
       <c r="C209" t="n">
-        <v>-0.6944794015519338</v>
+        <v>0.7057770919065839</v>
       </c>
       <c r="D209" t="n">
-        <v>1.332202865265116</v>
+        <v>1.991829188646545</v>
       </c>
       <c r="E209" t="n">
-        <v>-0.01810077841738867</v>
+        <v>1.156301264009021</v>
       </c>
       <c r="F209" t="n">
-        <v>-0.1080473034317879</v>
+        <v>1.754497227657834</v>
       </c>
     </row>
     <row r="210">
@@ -4617,19 +4617,19 @@
         <v>45936</v>
       </c>
       <c r="B210" t="n">
-        <v>-1.634711930726086</v>
+        <v>3.196240509082936</v>
       </c>
       <c r="C210" t="n">
-        <v>0.5003743255233143</v>
+        <v>1.242011500247174</v>
       </c>
       <c r="D210" t="n">
-        <v>-0.03752690994080857</v>
+        <v>-0.6350305492434661</v>
       </c>
       <c r="E210" t="n">
-        <v>0.09092697572985849</v>
+        <v>0.3664432677847068</v>
       </c>
       <c r="F210" t="n">
-        <v>-0.3880119341915245</v>
+        <v>-0.2558868356783385</v>
       </c>
     </row>
     <row r="211">
@@ -4637,19 +4637,19 @@
         <v>45937</v>
       </c>
       <c r="B211" t="n">
-        <v>-2.070941604286682</v>
+        <v>3.638994954024823</v>
       </c>
       <c r="C211" t="n">
-        <v>0.5955772477519699</v>
+        <v>2.369827743294339</v>
       </c>
       <c r="D211" t="n">
-        <v>0.442765473086649</v>
+        <v>-1.284145504349046</v>
       </c>
       <c r="E211" t="n">
-        <v>0.2892434049225592</v>
+        <v>-0.705095402521815</v>
       </c>
       <c r="F211" t="n">
-        <v>-0.1773214722526585</v>
+        <v>0.1911167515352796</v>
       </c>
     </row>
     <row r="212">
@@ -4657,19 +4657,19 @@
         <v>45938</v>
       </c>
       <c r="B212" t="n">
-        <v>-2.276599590014448</v>
+        <v>3.930625717250782</v>
       </c>
       <c r="C212" t="n">
-        <v>-0.02805101317237917</v>
+        <v>0.5591095711983443</v>
       </c>
       <c r="D212" t="n">
-        <v>-0.1753647346749362</v>
+        <v>-0.8334429973326576</v>
       </c>
       <c r="E212" t="n">
-        <v>-0.06206199310980945</v>
+        <v>-0.8454066796056776</v>
       </c>
       <c r="F212" t="n">
-        <v>-0.01042003981142936</v>
+        <v>-0.2607368610280176</v>
       </c>
     </row>
     <row r="213">
@@ -4677,19 +4677,19 @@
         <v>45939</v>
       </c>
       <c r="B213" t="n">
-        <v>0.04782401717377755</v>
+        <v>-0.02741992539971154</v>
       </c>
       <c r="C213" t="n">
-        <v>0.3708938601915637</v>
+        <v>1.205080364027252</v>
       </c>
       <c r="D213" t="n">
-        <v>-0.6628708403063059</v>
+        <v>0.001565940916205033</v>
       </c>
       <c r="E213" t="n">
-        <v>0.3298649499554607</v>
+        <v>-0.3031407216640701</v>
       </c>
       <c r="F213" t="n">
-        <v>0.0363684095173953</v>
+        <v>-1.027576041164678</v>
       </c>
     </row>
     <row r="214">
@@ -4697,19 +4697,19 @@
         <v>45940</v>
       </c>
       <c r="B214" t="n">
-        <v>2.140759533504715</v>
+        <v>-5.131804971052766</v>
       </c>
       <c r="C214" t="n">
-        <v>0.3535613438490656</v>
+        <v>0.6017067243866256</v>
       </c>
       <c r="D214" t="n">
-        <v>-0.2662612286945185</v>
+        <v>-1.648716164700685</v>
       </c>
       <c r="E214" t="n">
-        <v>-0.1079205046580203</v>
+        <v>-0.2385123346250629</v>
       </c>
       <c r="F214" t="n">
-        <v>-0.2604246228217327</v>
+        <v>-1.124282308281258</v>
       </c>
     </row>
     <row r="215">
@@ -4717,19 +4717,19 @@
         <v>45943</v>
       </c>
       <c r="B215" t="n">
-        <v>-2.07575330060977</v>
+        <v>3.728966559256195</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.1193486407831044</v>
+        <v>-0.8351922143369548</v>
       </c>
       <c r="D215" t="n">
-        <v>-0.8143705462199066</v>
+        <v>-0.1155102541075624</v>
       </c>
       <c r="E215" t="n">
-        <v>0.2000024689615586</v>
+        <v>-0.5412188435380256</v>
       </c>
       <c r="F215" t="n">
-        <v>0.2652804216779672</v>
+        <v>-0.673718278557767</v>
       </c>
     </row>
     <row r="216">
@@ -4737,19 +4737,19 @@
         <v>45944</v>
       </c>
       <c r="B216" t="n">
-        <v>0.6999949440902908</v>
+        <v>-1.000299505903742</v>
       </c>
       <c r="C216" t="n">
-        <v>0.289440760183724</v>
+        <v>1.484773658133782</v>
       </c>
       <c r="D216" t="n">
-        <v>-0.2677225467186031</v>
+        <v>-0.03270007329108156</v>
       </c>
       <c r="E216" t="n">
-        <v>0.2005451734604392</v>
+        <v>0.488425770163901</v>
       </c>
       <c r="F216" t="n">
-        <v>-0.5009062927605143</v>
+        <v>-0.9616045785581439</v>
       </c>
     </row>
     <row r="217">
@@ -4757,19 +4757,19 @@
         <v>45945</v>
       </c>
       <c r="B217" t="n">
-        <v>1.900657639780356</v>
+        <v>-3.659915325120792</v>
       </c>
       <c r="C217" t="n">
-        <v>0.2841504920338793</v>
+        <v>-0.833893430491375</v>
       </c>
       <c r="D217" t="n">
-        <v>-0.206738949388639</v>
+        <v>0.6869409526726642</v>
       </c>
       <c r="E217" t="n">
-        <v>-0.05467556320872742</v>
+        <v>-0.6689860063183732</v>
       </c>
       <c r="F217" t="n">
-        <v>0.2028123489324695</v>
+        <v>0.2127768992641437</v>
       </c>
     </row>
     <row r="218">
@@ -4777,19 +4777,19 @@
         <v>45946</v>
       </c>
       <c r="B218" t="n">
-        <v>1.777282034853192</v>
+        <v>-2.713546783891437</v>
       </c>
       <c r="C218" t="n">
-        <v>0.4924072863301048</v>
+        <v>1.201467721256519</v>
       </c>
       <c r="D218" t="n">
-        <v>0.5552176521996843</v>
+        <v>0.1206162955412523</v>
       </c>
       <c r="E218" t="n">
-        <v>0.02892784830660235</v>
+        <v>-0.4773673096872775</v>
       </c>
       <c r="F218" t="n">
-        <v>0.2755507272272639</v>
+        <v>0.5435902852015002</v>
       </c>
     </row>
     <row r="219">
@@ -4797,19 +4797,19 @@
         <v>45947</v>
       </c>
       <c r="B219" t="n">
-        <v>0.01502874014037494</v>
+        <v>-0.284450777415736</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.1231398720647346</v>
+        <v>-1.952346277953026</v>
       </c>
       <c r="D219" t="n">
-        <v>-0.4579677606310396</v>
+        <v>0.1920331180126925</v>
       </c>
       <c r="E219" t="n">
-        <v>-0.154034466263422</v>
+        <v>-0.1931069151602737</v>
       </c>
       <c r="F219" t="n">
-        <v>-0.1732760094654512</v>
+        <v>-0.2281582574778526</v>
       </c>
     </row>
     <row r="220">
@@ -4817,19 +4817,19 @@
         <v>45950</v>
       </c>
       <c r="B220" t="n">
-        <v>-0.9209903079025001</v>
+        <v>1.609877277578335</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.217280357783749</v>
+        <v>-1.663865221755886</v>
       </c>
       <c r="D220" t="n">
-        <v>-0.6822315089488671</v>
+        <v>0.6736287355622694</v>
       </c>
       <c r="E220" t="n">
-        <v>-0.3036406143846917</v>
+        <v>-1.193889326923375</v>
       </c>
       <c r="F220" t="n">
-        <v>0.4351841492290774</v>
+        <v>0.1158719259022615</v>
       </c>
     </row>
     <row r="221">
@@ -4837,19 +4837,19 @@
         <v>45951</v>
       </c>
       <c r="B221" t="n">
-        <v>-0.753507707855174</v>
+        <v>1.849317727983196</v>
       </c>
       <c r="C221" t="n">
-        <v>0.2082379997478805</v>
+        <v>0.01778495673119693</v>
       </c>
       <c r="D221" t="n">
-        <v>0.1271849495841383</v>
+        <v>0.2275749979891864</v>
       </c>
       <c r="E221" t="n">
-        <v>-0.2421375183874123</v>
+        <v>0.7150104557062322</v>
       </c>
       <c r="F221" t="n">
-        <v>-0.1910980288954792</v>
+        <v>0.1372389908833435</v>
       </c>
     </row>
     <row r="222">
@@ -4857,19 +4857,19 @@
         <v>45952</v>
       </c>
       <c r="B222" t="n">
-        <v>0.5999867806664464</v>
+        <v>-1.000780414999209</v>
       </c>
       <c r="C222" t="n">
-        <v>-0.03383811595418932</v>
+        <v>0.439306568492405</v>
       </c>
       <c r="D222" t="n">
-        <v>-0.5525021746451969</v>
+        <v>0.2656206017244826</v>
       </c>
       <c r="E222" t="n">
-        <v>0.1069155653413755</v>
+        <v>-0.4850691397025387</v>
       </c>
       <c r="F222" t="n">
-        <v>-0.03670418027655429</v>
+        <v>-1.083678791993642</v>
       </c>
     </row>
     <row r="223">
@@ -4877,19 +4877,19 @@
         <v>45953</v>
       </c>
       <c r="B223" t="n">
-        <v>-1.247159067284244</v>
+        <v>1.676208576146675</v>
       </c>
       <c r="C223" t="n">
-        <v>-0.4118843609216323</v>
+        <v>-1.770458325417522</v>
       </c>
       <c r="D223" t="n">
-        <v>-0.4689820310660755</v>
+        <v>-1.35230010693924</v>
       </c>
       <c r="E223" t="n">
-        <v>-0.1064853097547468</v>
+        <v>-0.1306448193838316</v>
       </c>
       <c r="F223" t="n">
-        <v>-0.05864807697352938</v>
+        <v>-0.5120978148491807</v>
       </c>
     </row>
     <row r="224">
@@ -4897,19 +4897,19 @@
         <v>45954</v>
       </c>
       <c r="B224" t="n">
-        <v>-2.369563193156486</v>
+        <v>3.321138608992827</v>
       </c>
       <c r="C224" t="n">
-        <v>0.6285745161634658</v>
+        <v>-1.251768041101863</v>
       </c>
       <c r="D224" t="n">
-        <v>-0.8975372878901345</v>
+        <v>-2.475075258448518</v>
       </c>
       <c r="E224" t="n">
-        <v>-0.1950498335455451</v>
+        <v>-0.5792536386926525</v>
       </c>
       <c r="F224" t="n">
-        <v>0.02717408432268138</v>
+        <v>-0.5130932476732035</v>
       </c>
     </row>
     <row r="225">
@@ -4917,19 +4917,19 @@
         <v>45957</v>
       </c>
       <c r="B225" t="n">
-        <v>0.3522100428762269</v>
+        <v>-1.73291650174577</v>
       </c>
       <c r="C225" t="n">
-        <v>0.11334603139515</v>
+        <v>-2.6667636825924</v>
       </c>
       <c r="D225" t="n">
-        <v>-0.450858292433906</v>
+        <v>-1.968004291103354</v>
       </c>
       <c r="E225" t="n">
-        <v>-0.1458518720940135</v>
+        <v>0.712123779206962</v>
       </c>
       <c r="F225" t="n">
-        <v>-0.05906199926993408</v>
+        <v>-0.002525840304976246</v>
       </c>
     </row>
     <row r="226">
@@ -4937,19 +4937,19 @@
         <v>45958</v>
       </c>
       <c r="B226" t="n">
-        <v>-2.581426835899712</v>
+        <v>5.549085036140089</v>
       </c>
       <c r="C226" t="n">
-        <v>0.2355156345853537</v>
+        <v>1.7789565150425</v>
       </c>
       <c r="D226" t="n">
-        <v>0.2711056378061173</v>
+        <v>1.400246114360035</v>
       </c>
       <c r="E226" t="n">
-        <v>0.5148558796473041</v>
+        <v>0.4072146705396058</v>
       </c>
       <c r="F226" t="n">
-        <v>0.3283523326520931</v>
+        <v>-0.0005628849211503529</v>
       </c>
     </row>
     <row r="227">
@@ -4957,19 +4957,19 @@
         <v>45959</v>
       </c>
       <c r="B227" t="n">
-        <v>-1.721717037881546</v>
+        <v>3.180627803702885</v>
       </c>
       <c r="C227" t="n">
-        <v>-0.05239842319374719</v>
+        <v>-0.2135418922414128</v>
       </c>
       <c r="D227" t="n">
-        <v>0.02157434110725502</v>
+        <v>-0.1465559945284717</v>
       </c>
       <c r="E227" t="n">
-        <v>-0.115256529837628</v>
+        <v>-0.8879991604227858</v>
       </c>
       <c r="F227" t="n">
-        <v>0.4456412773654366</v>
+        <v>0.8320738442465379</v>
       </c>
     </row>
     <row r="228">
@@ -4977,19 +4977,19 @@
         <v>45960</v>
       </c>
       <c r="B228" t="n">
-        <v>-4.5351475842247</v>
+        <v>7.823989228847082</v>
       </c>
       <c r="C228" t="n">
-        <v>-0.6542742382147089</v>
+        <v>-2.435835099986408</v>
       </c>
       <c r="D228" t="n">
-        <v>-0.7025418266907723</v>
+        <v>1.092176999276155</v>
       </c>
       <c r="E228" t="n">
-        <v>-0.4117127880093595</v>
+        <v>0.463132920530421</v>
       </c>
       <c r="F228" t="n">
-        <v>0.3857522554032749</v>
+        <v>1.033013528735853</v>
       </c>
     </row>
     <row r="229">
@@ -4997,19 +4997,19 @@
         <v>45961</v>
       </c>
       <c r="B229" t="n">
-        <v>-2.98838231108765</v>
+        <v>5.836859938669091</v>
       </c>
       <c r="C229" t="n">
-        <v>0.007867535281111683</v>
+        <v>0.3514267700035409</v>
       </c>
       <c r="D229" t="n">
-        <v>-0.2505931382713364</v>
+        <v>0.6060407711489222</v>
       </c>
       <c r="E229" t="n">
-        <v>-0.1671644121241369</v>
+        <v>-0.2100558836702329</v>
       </c>
       <c r="F229" t="n">
-        <v>0.4559605553662908</v>
+        <v>0.2963497142910045</v>
       </c>
     </row>
     <row r="230">
@@ -5017,19 +5017,19 @@
         <v>45964</v>
       </c>
       <c r="B230" t="n">
-        <v>-2.346188083418166</v>
+        <v>3.43315070150887</v>
       </c>
       <c r="C230" t="n">
-        <v>0.5303244064263714</v>
+        <v>-1.498745384536905</v>
       </c>
       <c r="D230" t="n">
-        <v>-0.8382614384765779</v>
+        <v>-1.607103741078189</v>
       </c>
       <c r="E230" t="n">
-        <v>-0.6209909191247116</v>
+        <v>-0.7882511600902211</v>
       </c>
       <c r="F230" t="n">
-        <v>0.06807167575128041</v>
+        <v>0.1030955284610563</v>
       </c>
     </row>
     <row r="231">
@@ -5037,19 +5037,19 @@
         <v>45965</v>
       </c>
       <c r="B231" t="n">
-        <v>-3.681116842820394</v>
+        <v>7.270013278461952</v>
       </c>
       <c r="C231" t="n">
-        <v>-1.053588390626492</v>
+        <v>-0.09480820724625404</v>
       </c>
       <c r="D231" t="n">
-        <v>-0.2072013626670121</v>
+        <v>2.109060038893799</v>
       </c>
       <c r="E231" t="n">
-        <v>0.1925423340263723</v>
+        <v>0.3255546648037266</v>
       </c>
       <c r="F231" t="n">
-        <v>-0.3216169020475645</v>
+        <v>-0.3363571012543239</v>
       </c>
     </row>
     <row r="232">
@@ -5057,19 +5057,19 @@
         <v>45966</v>
       </c>
       <c r="B232" t="n">
-        <v>-0.3306020568159274</v>
+        <v>1.308442695986503</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.8647230298141353</v>
+        <v>-0.8117668967613567</v>
       </c>
       <c r="D232" t="n">
-        <v>-0.402269204245686</v>
+        <v>2.330218908590123</v>
       </c>
       <c r="E232" t="n">
-        <v>-0.03708175764971409</v>
+        <v>0.06277808998247361</v>
       </c>
       <c r="F232" t="n">
-        <v>0.3841948959702755</v>
+        <v>-0.4798554193395904</v>
       </c>
     </row>
     <row r="233">
@@ -5077,19 +5077,19 @@
         <v>45967</v>
       </c>
       <c r="B233" t="n">
-        <v>-1.907894865084573</v>
+        <v>4.051298472608657</v>
       </c>
       <c r="C233" t="n">
-        <v>-0.6350256956975322</v>
+        <v>-0.7065771745023844</v>
       </c>
       <c r="D233" t="n">
-        <v>0.4716969819967471</v>
+        <v>1.172725275829332</v>
       </c>
       <c r="E233" t="n">
-        <v>0.01929573277221168</v>
+        <v>1.308233986022669</v>
       </c>
       <c r="F233" t="n">
-        <v>-0.02410535648741577</v>
+        <v>0.3226651658850571</v>
       </c>
     </row>
     <row r="234">
@@ -5097,19 +5097,19 @@
         <v>45968</v>
       </c>
       <c r="B234" t="n">
-        <v>-0.8868557723981649</v>
+        <v>2.416840025287019</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.0707176482711272</v>
+        <v>0.04360283912595149</v>
       </c>
       <c r="D234" t="n">
-        <v>-0.1005260553386499</v>
+        <v>1.492433387685008</v>
       </c>
       <c r="E234" t="n">
-        <v>0.1067960628495768</v>
+        <v>0.2284369327664718</v>
       </c>
       <c r="F234" t="n">
-        <v>0.4310432372021495</v>
+        <v>0.1044487573897326</v>
       </c>
     </row>
     <row r="235">
@@ -5117,19 +5117,19 @@
         <v>45971</v>
       </c>
       <c r="B235" t="n">
-        <v>-0.9922395903927509</v>
+        <v>1.948384557771417</v>
       </c>
       <c r="C235" t="n">
-        <v>-0.2593682558416231</v>
+        <v>-2.213887046739577</v>
       </c>
       <c r="D235" t="n">
-        <v>0.08641819727612608</v>
+        <v>0.3329740953539406</v>
       </c>
       <c r="E235" t="n">
-        <v>-0.1123971362413664</v>
+        <v>0.9013172518582622</v>
       </c>
       <c r="F235" t="n">
-        <v>0.441821091575237</v>
+        <v>1.317830021023187</v>
       </c>
     </row>
     <row r="236">
@@ -5137,19 +5137,19 @@
         <v>45972</v>
       </c>
       <c r="B236" t="n">
-        <v>0.6309887456354399</v>
+        <v>-1.709864556998218</v>
       </c>
       <c r="C236" t="n">
-        <v>-0.3508214148417312</v>
+        <v>-2.601108626565366</v>
       </c>
       <c r="D236" t="n">
-        <v>-0.6419936740784231</v>
+        <v>-0.2197011639706711</v>
       </c>
       <c r="E236" t="n">
-        <v>-0.07561681866849959</v>
+        <v>0.002438073825550724</v>
       </c>
       <c r="F236" t="n">
-        <v>0.2463592964157716</v>
+        <v>-0.421292782056794</v>
       </c>
     </row>
     <row r="237">
@@ -5157,19 +5157,19 @@
         <v>45973</v>
       </c>
       <c r="B237" t="n">
-        <v>-1.406785027630518</v>
+        <v>3.265378975845286</v>
       </c>
       <c r="C237" t="n">
-        <v>-0.716042194201753</v>
+        <v>0.8725816899818639</v>
       </c>
       <c r="D237" t="n">
-        <v>-0.3358224416269123</v>
+        <v>1.415146820495347</v>
       </c>
       <c r="E237" t="n">
-        <v>0.5812642899588444</v>
+        <v>-1.149717324916672</v>
       </c>
       <c r="F237" t="n">
-        <v>0.2382675572139614</v>
+        <v>-0.7860078962725336</v>
       </c>
     </row>
     <row r="238">
@@ -5177,19 +5177,19 @@
         <v>45974</v>
       </c>
       <c r="B238" t="n">
-        <v>1.461067756312908</v>
+        <v>-2.443912347038425</v>
       </c>
       <c r="C238" t="n">
-        <v>-0.1317788087952286</v>
+        <v>-0.03971241476376837</v>
       </c>
       <c r="D238" t="n">
-        <v>0.3286586838721245</v>
+        <v>-0.1072570755382389</v>
       </c>
       <c r="E238" t="n">
-        <v>-0.07005557918587826</v>
+        <v>0.06917868759142985</v>
       </c>
       <c r="F238" t="n">
-        <v>-0.06021151587895799</v>
+        <v>-0.04615885049669124</v>
       </c>
     </row>
     <row r="239">
@@ -5197,19 +5197,19 @@
         <v>45975</v>
       </c>
       <c r="B239" t="n">
-        <v>1.291498772492993</v>
+        <v>-1.563809605014748</v>
       </c>
       <c r="C239" t="n">
-        <v>0.3000024686587256</v>
+        <v>0.9309495850062272</v>
       </c>
       <c r="D239" t="n">
-        <v>-0.005640940691179841</v>
+        <v>1.101304783555278</v>
       </c>
       <c r="E239" t="n">
-        <v>0.240161703155844</v>
+        <v>0.2460724283920808</v>
       </c>
       <c r="F239" t="n">
-        <v>0.1852486169155247</v>
+        <v>0.07688777573851716</v>
       </c>
     </row>
     <row r="240">
@@ -5217,19 +5217,19 @@
         <v>45978</v>
       </c>
       <c r="B240" t="n">
-        <v>-0.5350855210267859</v>
+        <v>1.843483591206507</v>
       </c>
       <c r="C240" t="n">
-        <v>0.04470379942360492</v>
+        <v>1.56364249687566</v>
       </c>
       <c r="D240" t="n">
-        <v>-0.06458603061867177</v>
+        <v>1.075238812403748</v>
       </c>
       <c r="E240" t="n">
-        <v>0.2656404460514068</v>
+        <v>-0.7033328407315363</v>
       </c>
       <c r="F240" t="n">
-        <v>0.4748363795519729</v>
+        <v>-0.202357892973145</v>
       </c>
     </row>
     <row r="241">
@@ -5237,19 +5237,19 @@
         <v>45979</v>
       </c>
       <c r="B241" t="n">
-        <v>-1.573354455210081</v>
+        <v>3.027538313652547</v>
       </c>
       <c r="C241" t="n">
-        <v>0.6155164040204982</v>
+        <v>0.02819482373023596</v>
       </c>
       <c r="D241" t="n">
-        <v>-0.117105341354985</v>
+        <v>-0.5645669262965926</v>
       </c>
       <c r="E241" t="n">
-        <v>0.2241485225671854</v>
+        <v>1.155546540602589</v>
       </c>
       <c r="F241" t="n">
-        <v>-0.04561072558823893</v>
+        <v>-0.2345270345941302</v>
       </c>
     </row>
     <row r="242">
@@ -5257,19 +5257,19 @@
         <v>45980</v>
       </c>
       <c r="B242" t="n">
-        <v>-3.389281172677512</v>
+        <v>6.872611515165445</v>
       </c>
       <c r="C242" t="n">
-        <v>-0.6026096952669554</v>
+        <v>-0.0001773687675752811</v>
       </c>
       <c r="D242" t="n">
-        <v>0.151710245781621</v>
+        <v>1.769140859890703</v>
       </c>
       <c r="E242" t="n">
-        <v>0.2898268509809501</v>
+        <v>0.5974327770504231</v>
       </c>
       <c r="F242" t="n">
-        <v>0.002907219296607888</v>
+        <v>0.7207041990984541</v>
       </c>
     </row>
     <row r="243">
@@ -5277,19 +5277,19 @@
         <v>45982</v>
       </c>
       <c r="B243" t="n">
-        <v>1.104153806226211</v>
+        <v>-2.117608017228803</v>
       </c>
       <c r="C243" t="n">
-        <v>0.6902115607498003</v>
+        <v>0.8437594739726054</v>
       </c>
       <c r="D243" t="n">
-        <v>-0.3995500200893105</v>
+        <v>-0.06076207656771276</v>
       </c>
       <c r="E243" t="n">
-        <v>0.09215615882528277</v>
+        <v>-0.7030597760141953</v>
       </c>
       <c r="F243" t="n">
-        <v>0.2163506069957939</v>
+        <v>-0.3854477602073757</v>
       </c>
     </row>
     <row r="244">
@@ -5297,19 +5297,19 @@
         <v>45985</v>
       </c>
       <c r="B244" t="n">
-        <v>-2.451338484446031</v>
+        <v>4.288994296934245</v>
       </c>
       <c r="C244" t="n">
-        <v>-0.5458182328748997</v>
+        <v>-1.691477309986898</v>
       </c>
       <c r="D244" t="n">
-        <v>-0.6583871119247247</v>
+        <v>-0.05876364092194484</v>
       </c>
       <c r="E244" t="n">
-        <v>-0.2149174571543608</v>
+        <v>-0.7766970082436506</v>
       </c>
       <c r="F244" t="n">
-        <v>0.1993139595370421</v>
+        <v>0.3171627697469253</v>
       </c>
     </row>
     <row r="245">
@@ -5317,19 +5317,19 @@
         <v>45986</v>
       </c>
       <c r="B245" t="n">
-        <v>0.3633446751339967</v>
+        <v>-1.141839571348519</v>
       </c>
       <c r="C245" t="n">
-        <v>0.5276568956947721</v>
+        <v>0.5030801908633208</v>
       </c>
       <c r="D245" t="n">
-        <v>-0.6730103361471836</v>
+        <v>-0.9602063157552583</v>
       </c>
       <c r="E245" t="n">
-        <v>0.1896887073147089</v>
+        <v>-0.6569156728683503</v>
       </c>
       <c r="F245" t="n">
-        <v>-0.07247485886560848</v>
+        <v>-1.145806923188427</v>
       </c>
     </row>
     <row r="246">
@@ -5337,19 +5337,19 @@
         <v>45987</v>
       </c>
       <c r="B246" t="n">
-        <v>-1.505049851505921</v>
+        <v>3.433741458292041</v>
       </c>
       <c r="C246" t="n">
-        <v>0.104440809205417</v>
+        <v>0.4509597245219032</v>
       </c>
       <c r="D246" t="n">
-        <v>0.1309322153630848</v>
+        <v>0.4685240418669199</v>
       </c>
       <c r="E246" t="n">
-        <v>0.0126962716479941</v>
+        <v>-0.3694632449001294</v>
       </c>
       <c r="F246" t="n">
-        <v>0.3260271217603985</v>
+        <v>0.8389870908978999</v>
       </c>
     </row>
     <row r="247">
@@ -5357,19 +5357,19 @@
         <v>45988</v>
       </c>
       <c r="B247" t="n">
-        <v>-7.009968677461611</v>
+        <v>11.78332167847231</v>
       </c>
       <c r="C247" t="n">
-        <v>1.002045400820988</v>
+        <v>2.773310329990914</v>
       </c>
       <c r="D247" t="n">
-        <v>-0.5282074044982406</v>
+        <v>-0.6374017990218658</v>
       </c>
       <c r="E247" t="n">
-        <v>0.1119974667015727</v>
+        <v>0.6200927027004166</v>
       </c>
       <c r="F247" t="n">
-        <v>-0.922618170580602</v>
+        <v>-0.9239767973087158</v>
       </c>
     </row>
     <row r="248">
@@ -5377,19 +5377,19 @@
         <v>45989</v>
       </c>
       <c r="B248" t="n">
-        <v>-1.217288329701981</v>
+        <v>2.425987369426313</v>
       </c>
       <c r="C248" t="n">
-        <v>-0.5200956935277581</v>
+        <v>-0.8036811466993671</v>
       </c>
       <c r="D248" t="n">
-        <v>-0.476826653837937</v>
+        <v>0.2532200936832126</v>
       </c>
       <c r="E248" t="n">
-        <v>-0.1777278570892195</v>
+        <v>0.05186050069462349</v>
       </c>
       <c r="F248" t="n">
-        <v>-0.09928029126672749</v>
+        <v>-0.8167994916655976</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/dfpc_scores.xlsx
+++ b/data/processed/dfpc_scores.xlsx
@@ -457,19 +457,19 @@
         <v>45628</v>
       </c>
       <c r="B2" t="n">
-        <v>-2.006633394345457</v>
+        <v>0.2821326660627726</v>
       </c>
       <c r="C2" t="n">
-        <v>1.319768808748043</v>
+        <v>0.1567987066696343</v>
       </c>
       <c r="D2" t="n">
-        <v>1.63174846114812</v>
+        <v>0.1065953416508541</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8296891249952568</v>
+        <v>0.06132264026128702</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3800487511232226</v>
+        <v>0.009074191754997143</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         <v>45629</v>
       </c>
       <c r="B3" t="n">
-        <v>-1.69863111722018</v>
+        <v>0.1361968425291906</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.07435551177384</v>
+        <v>0.03302657167712622</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.5118241701369847</v>
+        <v>0.008346757492413289</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1077806476544865</v>
+        <v>-0.002715454158738759</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.01748693235170382</v>
+        <v>0.009644220953579828</v>
       </c>
     </row>
     <row r="4">
@@ -497,19 +497,19 @@
         <v>45630</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7504726312310206</v>
+        <v>0.1192486583423305</v>
       </c>
       <c r="C4" t="n">
-        <v>1.119734527944098</v>
+        <v>0.05844894066913877</v>
       </c>
       <c r="D4" t="n">
-        <v>1.756729225505997</v>
+        <v>0.06433078625197522</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9594177843132897</v>
+        <v>0.02145112974656651</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9944956400580924</v>
+        <v>-0.00521074887877331</v>
       </c>
     </row>
     <row r="5">
@@ -517,19 +517,19 @@
         <v>45631</v>
       </c>
       <c r="B5" t="n">
-        <v>2.214950382811713</v>
+        <v>-0.01981220149593619</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.562204059392919</v>
+        <v>0.02528338608662679</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3498244816622934</v>
+        <v>0.05500728034388428</v>
       </c>
       <c r="E5" t="n">
-        <v>1.684743888129653</v>
+        <v>-0.01315492798672809</v>
       </c>
       <c r="F5" t="n">
-        <v>1.417104832657332</v>
+        <v>0.01966264751051948</v>
       </c>
     </row>
     <row r="6">
@@ -537,19 +537,19 @@
         <v>45632</v>
       </c>
       <c r="B6" t="n">
-        <v>1.975190185627391</v>
+        <v>-0.01893373355113359</v>
       </c>
       <c r="C6" t="n">
-        <v>3.265003752210386</v>
+        <v>-0.07960805107371227</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4163850425206512</v>
+        <v>0.1317873585665399</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9558658611202699</v>
+        <v>-0.05355539309657607</v>
       </c>
       <c r="F6" t="n">
-        <v>1.112752067004814</v>
+        <v>-0.0205044102102541</v>
       </c>
     </row>
     <row r="7">
@@ -557,19 +557,19 @@
         <v>45635</v>
       </c>
       <c r="B7" t="n">
-        <v>-1.115379130520231</v>
+        <v>0.05121361916942991</v>
       </c>
       <c r="C7" t="n">
-        <v>-2.390002870876613</v>
+        <v>0.03389038911975476</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5133536711508996</v>
+        <v>0.01067469677176112</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8536670594661619</v>
+        <v>-0.02323683812981765</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7530329409741205</v>
+        <v>0.0200408566946649</v>
       </c>
     </row>
     <row r="8">
@@ -577,19 +577,19 @@
         <v>45636</v>
       </c>
       <c r="B8" t="n">
-        <v>1.806403463695434</v>
+        <v>-0.05841344262343538</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.5884674942580979</v>
+        <v>7.915809305674463e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4499057612054456</v>
+        <v>0.06119622273489825</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2479402471180217</v>
+        <v>-0.03993191920445074</v>
       </c>
       <c r="F8" t="n">
-        <v>1.074700623442185</v>
+        <v>-0.004050314602954358</v>
       </c>
     </row>
     <row r="9">
@@ -597,19 +597,19 @@
         <v>45637</v>
       </c>
       <c r="B9" t="n">
-        <v>-10.17432154652104</v>
+        <v>0.2599922744982764</v>
       </c>
       <c r="C9" t="n">
-        <v>-2.976519948813888</v>
+        <v>-0.05841309736043783</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.85797959081672</v>
+        <v>-0.01689455580419016</v>
       </c>
       <c r="E9" t="n">
-        <v>0.779641503884048</v>
+        <v>-0.032445809660886</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3114310886992422</v>
+        <v>0.06739985089632994</v>
       </c>
     </row>
     <row r="10">
@@ -617,19 +617,19 @@
         <v>45638</v>
       </c>
       <c r="B10" t="n">
-        <v>-2.531870838538045</v>
+        <v>0.1355053255416902</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.01201296255972557</v>
+        <v>-0.0009315283780838492</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.791381590677452</v>
+        <v>0.02486430640107751</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.406065963692346</v>
+        <v>-0.01702515836383115</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1366775689240997</v>
+        <v>0.06171147275297292</v>
       </c>
     </row>
     <row r="11">
@@ -637,19 +637,19 @@
         <v>45639</v>
       </c>
       <c r="B11" t="n">
-        <v>2.258735389985342</v>
+        <v>0.004888165429490229</v>
       </c>
       <c r="C11" t="n">
-        <v>2.9718521323506</v>
+        <v>-0.0159514276843414</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7287797097844092</v>
+        <v>0.04701241660750772</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2461860386159328</v>
+        <v>-0.004717413084445487</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7458563691729444</v>
+        <v>0.01896215842656246</v>
       </c>
     </row>
     <row r="12">
@@ -657,19 +657,19 @@
         <v>45642</v>
       </c>
       <c r="B12" t="n">
-        <v>2.622930471071168</v>
+        <v>-0.03702116916296824</v>
       </c>
       <c r="C12" t="n">
-        <v>0.677970570041096</v>
+        <v>0.02812980652245355</v>
       </c>
       <c r="D12" t="n">
-        <v>1.484404478503547</v>
+        <v>-0.03991223761804815</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9369944656610847</v>
+        <v>-0.003690911005628102</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4027367705716371</v>
+        <v>0.02608566809606437</v>
       </c>
     </row>
     <row r="13">
@@ -677,19 +677,19 @@
         <v>45643</v>
       </c>
       <c r="B13" t="n">
-        <v>-6.211999923070231</v>
+        <v>0.3439159407446131</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4080603944971845</v>
+        <v>-0.02400661068891616</v>
       </c>
       <c r="D13" t="n">
-        <v>1.431232105145615</v>
+        <v>0.01272247161399508</v>
       </c>
       <c r="E13" t="n">
-        <v>0.450393746169415</v>
+        <v>0.005031544123876466</v>
       </c>
       <c r="F13" t="n">
-        <v>1.097220006447339</v>
+        <v>0.003359367970579693</v>
       </c>
     </row>
     <row r="14">
@@ -697,19 +697,19 @@
         <v>45644</v>
       </c>
       <c r="B14" t="n">
-        <v>-4.252572568769071</v>
+        <v>0.2708511722892337</v>
       </c>
       <c r="C14" t="n">
-        <v>1.327315688302058</v>
+        <v>0.02641708662886671</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4405527728966124</v>
+        <v>0.05824661106064131</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1542989791115331</v>
+        <v>0.01112892982695568</v>
       </c>
       <c r="F14" t="n">
-        <v>0.09875379497854654</v>
+        <v>-0.01159739765725083</v>
       </c>
     </row>
     <row r="15">
@@ -717,19 +717,19 @@
         <v>45645</v>
       </c>
       <c r="B15" t="n">
-        <v>-2.595676141199938</v>
+        <v>0.1767620045796244</v>
       </c>
       <c r="C15" t="n">
-        <v>0.148443501430573</v>
+        <v>0.0142139430337526</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6914805545768372</v>
+        <v>-0.004739069424003869</v>
       </c>
       <c r="E15" t="n">
-        <v>0.06656079188620799</v>
+        <v>0.04256331127013058</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3840957577870419</v>
+        <v>-0.04100282173407562</v>
       </c>
     </row>
     <row r="16">
@@ -737,19 +737,19 @@
         <v>45646</v>
       </c>
       <c r="B16" t="n">
-        <v>-2.721747771055405</v>
+        <v>0.2098957736521708</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.3362875916527265</v>
+        <v>-0.0009216460771257523</v>
       </c>
       <c r="D16" t="n">
-        <v>1.234175575217167</v>
+        <v>-0.02339532701197808</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3703960813003068</v>
+        <v>-0.01669151822012461</v>
       </c>
       <c r="F16" t="n">
-        <v>0.04398086317268424</v>
+        <v>-0.03899704413915187</v>
       </c>
     </row>
     <row r="17">
@@ -757,19 +757,19 @@
         <v>45649</v>
       </c>
       <c r="B17" t="n">
-        <v>1.143240353202331</v>
+        <v>0.06929235339076263</v>
       </c>
       <c r="C17" t="n">
-        <v>1.256867434680127</v>
+        <v>-0.02808448122415893</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7319569187745799</v>
+        <v>0.02567802308219945</v>
       </c>
       <c r="E17" t="n">
-        <v>0.004969471931055081</v>
+        <v>0.02978219990521976</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2610321332044171</v>
+        <v>-0.02742234837378891</v>
       </c>
     </row>
     <row r="18">
@@ -777,19 +777,19 @@
         <v>45652</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5154314617883302</v>
+        <v>0.06392672689680237</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.5341429364687007</v>
+        <v>0.01752267643030347</v>
       </c>
       <c r="D18" t="n">
-        <v>2.412209528288968</v>
+        <v>-0.0470416840727578</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4991006139100773</v>
+        <v>-0.02446326928782876</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.005665527931501946</v>
+        <v>-0.04152106583723253</v>
       </c>
     </row>
     <row r="19">
@@ -797,19 +797,19 @@
         <v>45653</v>
       </c>
       <c r="B19" t="n">
-        <v>-1.931358322290735</v>
+        <v>0.1740745786201389</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2046239386788555</v>
+        <v>0.078602487991804</v>
       </c>
       <c r="D19" t="n">
-        <v>1.21105432722745</v>
+        <v>0.02072017608717965</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7726850888826733</v>
+        <v>0.02825670806241106</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1267581043519591</v>
+        <v>-0.01253443769504385</v>
       </c>
     </row>
     <row r="20">
@@ -817,19 +817,19 @@
         <v>45656</v>
       </c>
       <c r="B20" t="n">
-        <v>0.9745828131046468</v>
+        <v>0.08742391616275701</v>
       </c>
       <c r="C20" t="n">
-        <v>3.313289923622048</v>
+        <v>-0.00885289427810382</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6799856276098595</v>
+        <v>0.1470226907887477</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8811188071924783</v>
+        <v>-0.04496363295198056</v>
       </c>
       <c r="F20" t="n">
-        <v>1.307681216077266</v>
+        <v>-0.01762703502790902</v>
       </c>
     </row>
     <row r="21">
@@ -837,19 +837,19 @@
         <v>45659</v>
       </c>
       <c r="B21" t="n">
-        <v>-4.030494608216963</v>
+        <v>0.2029313628432965</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2437691898095145</v>
+        <v>0.01859519782041844</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.253602265322192</v>
+        <v>0.07047436771501316</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1623543314888815</v>
+        <v>-0.009633190255977623</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4105526683468534</v>
+        <v>-0.01046785650921353</v>
       </c>
     </row>
     <row r="22">
@@ -857,19 +857,19 @@
         <v>45660</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.05661025446422672</v>
+        <v>0.03769517485637008</v>
       </c>
       <c r="C22" t="n">
-        <v>1.46838271916951</v>
+        <v>-0.02233737189805312</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.421860889129233</v>
+        <v>0.04192626680909677</v>
       </c>
       <c r="E22" t="n">
-        <v>1.220728915389206</v>
+        <v>0.0527069448070765</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.324208216113289</v>
+        <v>-0.005350250812025783</v>
       </c>
     </row>
     <row r="23">
@@ -877,19 +877,19 @@
         <v>45663</v>
       </c>
       <c r="B23" t="n">
-        <v>-4.932690479768279</v>
+        <v>0.1978569353714391</v>
       </c>
       <c r="C23" t="n">
-        <v>-2.894336467479489</v>
+        <v>-0.02082284936805482</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.312992861102113</v>
+        <v>0.04700652040974803</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5757629782167097</v>
+        <v>-0.02346571773687885</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7927192891829713</v>
+        <v>0.02385655534309034</v>
       </c>
     </row>
     <row r="24">
@@ -897,19 +897,19 @@
         <v>45664</v>
       </c>
       <c r="B24" t="n">
-        <v>0.7915936178563658</v>
+        <v>0.01982664730358508</v>
       </c>
       <c r="C24" t="n">
-        <v>-1.216080887895055</v>
+        <v>0.002893513350227646</v>
       </c>
       <c r="D24" t="n">
-        <v>1.726163577587232</v>
+        <v>-0.04676851933748602</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.5009490617179327</v>
+        <v>0.004049565384335296</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2396601662984609</v>
+        <v>-0.01409103460629191</v>
       </c>
     </row>
     <row r="25">
@@ -917,19 +917,19 @@
         <v>45665</v>
       </c>
       <c r="B25" t="n">
-        <v>1.101268170514453</v>
+        <v>-0.0133778832738144</v>
       </c>
       <c r="C25" t="n">
-        <v>1.264788159281592</v>
+        <v>-0.05975190270286626</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.8304469971464785</v>
+        <v>0.06326427094397623</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1836919102590907</v>
+        <v>-0.04700931185145894</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1900867378750703</v>
+        <v>-0.01959479990678364</v>
       </c>
     </row>
     <row r="26">
@@ -937,19 +937,19 @@
         <v>45666</v>
       </c>
       <c r="B26" t="n">
-        <v>4.56079544404723</v>
+        <v>-0.1482171917142642</v>
       </c>
       <c r="C26" t="n">
-        <v>2.11536815212697</v>
+        <v>-0.04790306516159391</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3094103316339329</v>
+        <v>0.05852969400292119</v>
       </c>
       <c r="E26" t="n">
-        <v>1.095324646379912</v>
+        <v>0.01593012812927019</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0287988528652094</v>
+        <v>-0.01836231348040379</v>
       </c>
     </row>
     <row r="27">
@@ -957,19 +957,19 @@
         <v>45667</v>
       </c>
       <c r="B27" t="n">
-        <v>-2.659115716978549</v>
+        <v>0.0522318503530357</v>
       </c>
       <c r="C27" t="n">
-        <v>0.04070053632561477</v>
+        <v>-0.05211992100090668</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.681745180396541</v>
+        <v>0.02095310055404612</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.745853710137791</v>
+        <v>-0.02370568732988368</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.3572089524370765</v>
+        <v>0.008678507987878144</v>
       </c>
     </row>
     <row r="28">
@@ -977,19 +977,19 @@
         <v>45670</v>
       </c>
       <c r="B28" t="n">
-        <v>1.290384880384979</v>
+        <v>-0.08456143473844764</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.4690939528913169</v>
+        <v>-0.0247057820231772</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6365442853632086</v>
+        <v>-0.01908691754536251</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.3436651360331399</v>
+        <v>-0.01780654946046355</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.07974869910825515</v>
+        <v>-0.02071430070394543</v>
       </c>
     </row>
     <row r="29">
@@ -997,19 +997,19 @@
         <v>45671</v>
       </c>
       <c r="B29" t="n">
-        <v>-4.944617096165411</v>
+        <v>0.1468728013142586</v>
       </c>
       <c r="C29" t="n">
-        <v>0.430089204983086</v>
+        <v>-0.03724889729028218</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7893531318890399</v>
+        <v>0.02138648498437236</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2750662804849366</v>
+        <v>-0.03415174467945018</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.5019722481948042</v>
+        <v>-0.01045724785993307</v>
       </c>
     </row>
     <row r="30">
@@ -1017,19 +1017,19 @@
         <v>45672</v>
       </c>
       <c r="B30" t="n">
-        <v>-2.662382922769793</v>
+        <v>0.09087978119143962</v>
       </c>
       <c r="C30" t="n">
-        <v>-3.000459011122396</v>
+        <v>0.001861724703466734</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.134990669270515</v>
+        <v>-0.01264998727309165</v>
       </c>
       <c r="E30" t="n">
-        <v>1.016033616790659</v>
+        <v>-0.007901765973901005</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7892884004386831</v>
+        <v>0.03647190304006481</v>
       </c>
     </row>
     <row r="31">
@@ -1037,19 +1037,19 @@
         <v>45673</v>
       </c>
       <c r="B31" t="n">
-        <v>2.353367519817517</v>
+        <v>-0.008435141946986134</v>
       </c>
       <c r="C31" t="n">
-        <v>1.656216742518608</v>
+        <v>0.02926831411627452</v>
       </c>
       <c r="D31" t="n">
-        <v>1.310695538037921</v>
+        <v>-0.008348379723586759</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.9318134774917326</v>
+        <v>-0.03130340722479406</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.4061253279451801</v>
+        <v>0.005763205018476308</v>
       </c>
     </row>
     <row r="32">
@@ -1057,19 +1057,19 @@
         <v>45674</v>
       </c>
       <c r="B32" t="n">
-        <v>1.782504896803305</v>
+        <v>-0.03226942660009176</v>
       </c>
       <c r="C32" t="n">
-        <v>0.08271120294625334</v>
+        <v>0.1008034428776306</v>
       </c>
       <c r="D32" t="n">
-        <v>1.07135571230995</v>
+        <v>-0.0823442430505671</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.243804303696012</v>
+        <v>0.03850968415535067</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.985697089866175</v>
+        <v>0.03814771462240184</v>
       </c>
     </row>
     <row r="33">
@@ -1077,19 +1077,19 @@
         <v>45677</v>
       </c>
       <c r="B33" t="n">
-        <v>0.2234111220570207</v>
+        <v>0.05578407660744766</v>
       </c>
       <c r="C33" t="n">
-        <v>-1.48308402004962</v>
+        <v>0.1289791528498434</v>
       </c>
       <c r="D33" t="n">
-        <v>2.163609564216747</v>
+        <v>-0.05479851883960767</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6674494898178355</v>
+        <v>-0.01214516415352281</v>
       </c>
       <c r="F33" t="n">
-        <v>0.623928326267243</v>
+        <v>0.02108464330271426</v>
       </c>
     </row>
     <row r="34">
@@ -1097,19 +1097,19 @@
         <v>45678</v>
       </c>
       <c r="B34" t="n">
-        <v>1.775756747283255</v>
+        <v>-0.01470268120688359</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.01108230538455679</v>
+        <v>0.1480582438767367</v>
       </c>
       <c r="D34" t="n">
-        <v>2.093783886465162</v>
+        <v>-0.05156889551768517</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.248600652752588</v>
+        <v>0.03263555542232209</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.02800511022655958</v>
+        <v>0.02097282758888335</v>
       </c>
     </row>
     <row r="35">
@@ -1117,19 +1117,19 @@
         <v>45679</v>
       </c>
       <c r="B35" t="n">
-        <v>2.275386396176594</v>
+        <v>-0.08126749938261685</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7636216010352277</v>
+        <v>0.1212749205811836</v>
       </c>
       <c r="D35" t="n">
-        <v>1.036744814295043</v>
+        <v>-0.04503836890006969</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7201615040239654</v>
+        <v>0.01425080246162997</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.8578993561221154</v>
+        <v>0.01027869442350254</v>
       </c>
     </row>
     <row r="36">
@@ -1137,19 +1137,19 @@
         <v>45680</v>
       </c>
       <c r="B36" t="n">
-        <v>-2.463367900363986</v>
+        <v>0.04412088233277407</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.6240417376090606</v>
+        <v>0.07375826137537481</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.5392298213836383</v>
+        <v>-0.03447181212026638</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1370037348875481</v>
+        <v>0.04540472981460586</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.6259162361516355</v>
+        <v>-0.007274893898852874</v>
       </c>
     </row>
     <row r="37">
@@ -1157,19 +1157,19 @@
         <v>45681</v>
       </c>
       <c r="B37" t="n">
-        <v>3.165223146724338</v>
+        <v>-0.05124189730017822</v>
       </c>
       <c r="C37" t="n">
-        <v>0.12144045182652</v>
+        <v>0.1418276335777817</v>
       </c>
       <c r="D37" t="n">
-        <v>2.509859698106996</v>
+        <v>-0.006896588706036981</v>
       </c>
       <c r="E37" t="n">
-        <v>0.670421439912511</v>
+        <v>0.01850692776411525</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7395975908217021</v>
+        <v>-0.007208678867294518</v>
       </c>
     </row>
     <row r="38">
@@ -1177,19 +1177,19 @@
         <v>45684</v>
       </c>
       <c r="B38" t="n">
-        <v>-1.140911884744513</v>
+        <v>0.04036173387015034</v>
       </c>
       <c r="C38" t="n">
-        <v>-2.366990045267569</v>
+        <v>0.1015441072910079</v>
       </c>
       <c r="D38" t="n">
-        <v>1.298720820004365</v>
+        <v>-0.01522005609097251</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.5353048741273639</v>
+        <v>-0.01691587283010917</v>
       </c>
       <c r="F38" t="n">
-        <v>1.095098520794485</v>
+        <v>0.001924532549931335</v>
       </c>
     </row>
     <row r="39">
@@ -1197,19 +1197,19 @@
         <v>45685</v>
       </c>
       <c r="B39" t="n">
-        <v>3.74151772593736</v>
+        <v>-0.1515537826046625</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4586151911821063</v>
+        <v>0.03350509387739945</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.01324192892430389</v>
+        <v>-0.03062885350596069</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.422045428500784</v>
+        <v>-0.008344538961824431</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2085399249330455</v>
+        <v>-0.005138481501832457</v>
       </c>
     </row>
     <row r="40">
@@ -1217,19 +1217,19 @@
         <v>45686</v>
       </c>
       <c r="B40" t="n">
-        <v>1.501014622777574</v>
+        <v>-0.02691825941640765</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.9572407066648693</v>
+        <v>0.09550972410255042</v>
       </c>
       <c r="D40" t="n">
-        <v>1.409883263387712</v>
+        <v>-0.03635638367484399</v>
       </c>
       <c r="E40" t="n">
-        <v>1.151791320718816</v>
+        <v>0.05708050349139766</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3389508582482919</v>
+        <v>0.01322091872441485</v>
       </c>
     </row>
     <row r="41">
@@ -1237,19 +1237,19 @@
         <v>45687</v>
       </c>
       <c r="B41" t="n">
-        <v>-3.029108896171412</v>
+        <v>0.06600774346988864</v>
       </c>
       <c r="C41" t="n">
-        <v>-3.105993622404912</v>
+        <v>0.05584995862385555</v>
       </c>
       <c r="D41" t="n">
-        <v>0.4037390259913954</v>
+        <v>-0.04936190145303254</v>
       </c>
       <c r="E41" t="n">
-        <v>0.144732661805242</v>
+        <v>-0.01608998694812028</v>
       </c>
       <c r="F41" t="n">
-        <v>0.4470541422635529</v>
+        <v>0.01504733862353128</v>
       </c>
     </row>
     <row r="42">
@@ -1257,19 +1257,19 @@
         <v>45688</v>
       </c>
       <c r="B42" t="n">
-        <v>0.7204089894531632</v>
+        <v>0.01511102398391146</v>
       </c>
       <c r="C42" t="n">
-        <v>0.877926343880705</v>
+        <v>0.09835876448571428</v>
       </c>
       <c r="D42" t="n">
-        <v>1.72147445269842</v>
+        <v>-0.05564014488573275</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.7681399410012691</v>
+        <v>0.02835327938170231</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.5770903395729926</v>
+        <v>0.007548659104665188</v>
       </c>
     </row>
     <row r="43">
@@ -1277,19 +1277,19 @@
         <v>45691</v>
       </c>
       <c r="B43" t="n">
-        <v>-1.05176207369789</v>
+        <v>0.09782089499673959</v>
       </c>
       <c r="C43" t="n">
-        <v>-1.686182469732446</v>
+        <v>0.1187413530473864</v>
       </c>
       <c r="D43" t="n">
-        <v>2.460243650138777</v>
+        <v>-0.0422291725263423</v>
       </c>
       <c r="E43" t="n">
-        <v>0.465276760565957</v>
+        <v>-0.003473869706923277</v>
       </c>
       <c r="F43" t="n">
-        <v>1.262618949025381</v>
+        <v>0.01559787705234609</v>
       </c>
     </row>
     <row r="44">
@@ -1297,19 +1297,19 @@
         <v>45692</v>
       </c>
       <c r="B44" t="n">
-        <v>-0.6765495811758773</v>
+        <v>0.02117344989617493</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.7836503030607744</v>
+        <v>-0.01588052732651717</v>
       </c>
       <c r="D44" t="n">
-        <v>-1.240382165423168</v>
+        <v>-0.003977771680258573</v>
       </c>
       <c r="E44" t="n">
-        <v>1.19843675434565</v>
+        <v>0.007180577384332583</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1052090720176488</v>
+        <v>-0.008348579921401774</v>
       </c>
     </row>
     <row r="45">
@@ -1317,19 +1317,19 @@
         <v>45693</v>
       </c>
       <c r="B45" t="n">
-        <v>-0.653087522249954</v>
+        <v>0.08875864919972205</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4972784626955721</v>
+        <v>0.06147085733679369</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1544368023097674</v>
+        <v>0.02786048192558143</v>
       </c>
       <c r="E45" t="n">
-        <v>0.4693025830127999</v>
+        <v>0.01210683040506063</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.2005972022916279</v>
+        <v>-0.004923197217290147</v>
       </c>
     </row>
     <row r="46">
@@ -1337,19 +1337,19 @@
         <v>45694</v>
       </c>
       <c r="B46" t="n">
-        <v>0.1061569610706832</v>
+        <v>0.06106520671047466</v>
       </c>
       <c r="C46" t="n">
-        <v>0.9604873201156047</v>
+        <v>0.03494562479388284</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3267662050390633</v>
+        <v>0.0529412179891566</v>
       </c>
       <c r="E46" t="n">
-        <v>0.8834278042256873</v>
+        <v>0.01494191505203407</v>
       </c>
       <c r="F46" t="n">
-        <v>0.03130009268116823</v>
+        <v>-0.0009075614689912103</v>
       </c>
     </row>
     <row r="47">
@@ -1357,19 +1357,19 @@
         <v>45695</v>
       </c>
       <c r="B47" t="n">
-        <v>0.2480358355610003</v>
+        <v>0.1014755593370867</v>
       </c>
       <c r="C47" t="n">
-        <v>3.171979038597261</v>
+        <v>0.03103567652091592</v>
       </c>
       <c r="D47" t="n">
-        <v>0.2837243327513314</v>
+        <v>0.1550208974679591</v>
       </c>
       <c r="E47" t="n">
-        <v>0.01705801153993356</v>
+        <v>-0.0200808291014329</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7747877562021442</v>
+        <v>0.007884910603677643</v>
       </c>
     </row>
     <row r="48">
@@ -1377,19 +1377,19 @@
         <v>45698</v>
       </c>
       <c r="B48" t="n">
-        <v>-0.0331516850894781</v>
+        <v>-0.01055038972535258</v>
       </c>
       <c r="C48" t="n">
-        <v>-1.830081742585943</v>
+        <v>-0.03196002167162561</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.9883544294984201</v>
+        <v>0.0580113984409227</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.3629289409778953</v>
+        <v>-0.02093228426849603</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9484557075715604</v>
+        <v>0.008646814291941037</v>
       </c>
     </row>
     <row r="49">
@@ -1397,19 +1397,19 @@
         <v>45699</v>
       </c>
       <c r="B49" t="n">
-        <v>2.347662042862233</v>
+        <v>-0.1425587040518214</v>
       </c>
       <c r="C49" t="n">
-        <v>-1.07498195323444</v>
+        <v>-0.04984410347080948</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.8947087881618153</v>
+        <v>-0.03662957328530613</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.4546287139078482</v>
+        <v>0.008588731863813386</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.000990540420973</v>
+        <v>-0.01420885879882096</v>
       </c>
     </row>
     <row r="50">
@@ -1417,19 +1417,19 @@
         <v>45700</v>
       </c>
       <c r="B50" t="n">
-        <v>-5.589571586281059</v>
+        <v>0.1749658111797474</v>
       </c>
       <c r="C50" t="n">
-        <v>1.176350932064976</v>
+        <v>-0.03633943760274081</v>
       </c>
       <c r="D50" t="n">
-        <v>-2.221476884683788</v>
+        <v>0.04029229434075692</v>
       </c>
       <c r="E50" t="n">
-        <v>-1.310804708203813</v>
+        <v>-0.001550882046351073</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.798240635362196</v>
+        <v>0.02326412156872769</v>
       </c>
     </row>
     <row r="51">
@@ -1437,19 +1437,19 @@
         <v>45701</v>
       </c>
       <c r="B51" t="n">
-        <v>1.770188509559536</v>
+        <v>-0.02861243290079307</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.0482880931625326</v>
+        <v>-0.01879633725476081</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3146932563368607</v>
+        <v>0.1056471791699905</v>
       </c>
       <c r="E51" t="n">
-        <v>0.814461767496432</v>
+        <v>-0.01555064456886913</v>
       </c>
       <c r="F51" t="n">
-        <v>1.345986932035207</v>
+        <v>0.01200439151807086</v>
       </c>
     </row>
     <row r="52">
@@ -1457,19 +1457,19 @@
         <v>45702</v>
       </c>
       <c r="B52" t="n">
-        <v>-0.02777332397786845</v>
+        <v>-0.06924915619565263</v>
       </c>
       <c r="C52" t="n">
-        <v>-3.332176629509355</v>
+        <v>-0.004507891523760527</v>
       </c>
       <c r="D52" t="n">
-        <v>1.602820984351921</v>
+        <v>-0.1131534170031405</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.5842216694405634</v>
+        <v>-0.01371102525352236</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.3457830955276362</v>
+        <v>-0.003639703911616717</v>
       </c>
     </row>
     <row r="53">
@@ -1477,19 +1477,19 @@
         <v>45705</v>
       </c>
       <c r="B53" t="n">
-        <v>6.452506446573011</v>
+        <v>-0.215573342358935</v>
       </c>
       <c r="C53" t="n">
-        <v>0.6243087709507904</v>
+        <v>0.05785427660427025</v>
       </c>
       <c r="D53" t="n">
-        <v>2.630645498830507</v>
+        <v>-0.03997315797071718</v>
       </c>
       <c r="E53" t="n">
-        <v>0.5069539535613375</v>
+        <v>0.0267922095680516</v>
       </c>
       <c r="F53" t="n">
-        <v>0.3910487330763602</v>
+        <v>0.008483668010326956</v>
       </c>
     </row>
     <row r="54">
@@ -1497,19 +1497,19 @@
         <v>45706</v>
       </c>
       <c r="B54" t="n">
-        <v>2.955630800838541</v>
+        <v>-0.1660320771069764</v>
       </c>
       <c r="C54" t="n">
-        <v>0.5540678019474028</v>
+        <v>-0.0163011999083023</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.690260233483399</v>
+        <v>-0.0301141531580921</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.213524114110972</v>
+        <v>0.000673394240981578</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.4059176357237694</v>
+        <v>-0.001616839606155228</v>
       </c>
     </row>
     <row r="55">
@@ -1517,19 +1517,19 @@
         <v>45707</v>
       </c>
       <c r="B55" t="n">
-        <v>2.670345928681336</v>
+        <v>-0.1718566939349986</v>
       </c>
       <c r="C55" t="n">
-        <v>2.441273717195963</v>
+        <v>-0.05469001297971426</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4025048700320404</v>
+        <v>0.01884748222268862</v>
       </c>
       <c r="E55" t="n">
-        <v>0.01319387586378413</v>
+        <v>0.01905982672681287</v>
       </c>
       <c r="F55" t="n">
-        <v>0.01865861965505253</v>
+        <v>-0.01992361409706165</v>
       </c>
     </row>
     <row r="56">
@@ -1537,19 +1537,19 @@
         <v>45708</v>
       </c>
       <c r="B56" t="n">
-        <v>3.011939780069228</v>
+        <v>-0.1972239168941018</v>
       </c>
       <c r="C56" t="n">
-        <v>1.136922007315454</v>
+        <v>-0.04465655475452972</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4405265361214353</v>
+        <v>0.0397366874112322</v>
       </c>
       <c r="E56" t="n">
-        <v>0.7199444565460422</v>
+        <v>-0.0008818074655561688</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3337468827596628</v>
+        <v>-0.03044214884192323</v>
       </c>
     </row>
     <row r="57">
@@ -1557,19 +1557,19 @@
         <v>45709</v>
       </c>
       <c r="B57" t="n">
-        <v>-0.4055652861896114</v>
+        <v>-0.06212920224911111</v>
       </c>
       <c r="C57" t="n">
-        <v>0.8539598391781905</v>
+        <v>0.02916306348746114</v>
       </c>
       <c r="D57" t="n">
-        <v>0.6511861248916028</v>
+        <v>-0.0401784374178434</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.300995863538663</v>
+        <v>0.01862348514254489</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.8275358914433888</v>
+        <v>-0.01897385672439067</v>
       </c>
     </row>
     <row r="58">
@@ -1577,19 +1577,19 @@
         <v>45712</v>
       </c>
       <c r="B58" t="n">
-        <v>0.71036984354651</v>
+        <v>-0.070996077968789</v>
       </c>
       <c r="C58" t="n">
-        <v>1.211411184828908</v>
+        <v>-0.04753233271742997</v>
       </c>
       <c r="D58" t="n">
-        <v>0.2189088897930626</v>
+        <v>0.02532378899975243</v>
       </c>
       <c r="E58" t="n">
-        <v>0.2168036961922376</v>
+        <v>-0.01139800157957857</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.2331099209574832</v>
+        <v>-0.03347020428233013</v>
       </c>
     </row>
     <row r="59">
@@ -1597,19 +1597,19 @@
         <v>45713</v>
       </c>
       <c r="B59" t="n">
-        <v>-0.1585156079680797</v>
+        <v>0.0620966873640305</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.7614162792275446</v>
+        <v>0.0806153184199144</v>
       </c>
       <c r="D59" t="n">
-        <v>1.716254112998014</v>
+        <v>0.03844264706652351</v>
       </c>
       <c r="E59" t="n">
-        <v>1.150232995794678</v>
+        <v>-0.003538001444122672</v>
       </c>
       <c r="F59" t="n">
-        <v>1.294406954582104</v>
+        <v>0.009077715815794805</v>
       </c>
     </row>
     <row r="60">
@@ -1617,19 +1617,19 @@
         <v>45714</v>
       </c>
       <c r="B60" t="n">
-        <v>2.370663670180016</v>
+        <v>-0.02983243334724842</v>
       </c>
       <c r="C60" t="n">
-        <v>1.923906116307584</v>
+        <v>0.05848392355073757</v>
       </c>
       <c r="D60" t="n">
-        <v>0.8996407836691788</v>
+        <v>0.04361099965625278</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.9528699559689383</v>
+        <v>-0.01019351142125348</v>
       </c>
       <c r="F60" t="n">
-        <v>0.4450714837039688</v>
+        <v>0.005855818228037535</v>
       </c>
     </row>
     <row r="61">
@@ -1637,19 +1637,19 @@
         <v>45715</v>
       </c>
       <c r="B61" t="n">
-        <v>0.3477280193383002</v>
+        <v>0.01991771226714071</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.1168469971480257</v>
+        <v>0.05444511814740276</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.2304780705693723</v>
+        <v>0.04887558029076775</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.3326263316667976</v>
+        <v>-0.006341431903989169</v>
       </c>
       <c r="F61" t="n">
-        <v>0.7750425634513973</v>
+        <v>0.003514371313123508</v>
       </c>
     </row>
     <row r="62">
@@ -1657,19 +1657,19 @@
         <v>45716</v>
       </c>
       <c r="B62" t="n">
-        <v>-1.760075572321569</v>
+        <v>0.06790491990376839</v>
       </c>
       <c r="C62" t="n">
-        <v>0.2392889435799217</v>
+        <v>-0.01482172350974854</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.1005601359031991</v>
+        <v>0.04737603015292309</v>
       </c>
       <c r="E62" t="n">
-        <v>0.1184433590390849</v>
+        <v>-0.02765856381213275</v>
       </c>
       <c r="F62" t="n">
-        <v>0.3960803800910696</v>
+        <v>-0.02310049775270954</v>
       </c>
     </row>
     <row r="63">
@@ -1677,19 +1677,19 @@
         <v>45722</v>
       </c>
       <c r="B63" t="n">
-        <v>-7.752262985699446</v>
+        <v>0.3064156146981225</v>
       </c>
       <c r="C63" t="n">
-        <v>-1.874935813484387</v>
+        <v>0.04920849966972</v>
       </c>
       <c r="D63" t="n">
-        <v>0.5260597279963209</v>
+        <v>0.01034452201593942</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.221813738434865</v>
+        <v>0.01516729375468783</v>
       </c>
       <c r="F63" t="n">
-        <v>0.2920296218668792</v>
+        <v>-0.004231005243854848</v>
       </c>
     </row>
     <row r="64">
@@ -1697,19 +1697,19 @@
         <v>45723</v>
       </c>
       <c r="B64" t="n">
-        <v>-5.797329400334047</v>
+        <v>0.2430958551167186</v>
       </c>
       <c r="C64" t="n">
-        <v>-1.823467610969767</v>
+        <v>0.01217619638694915</v>
       </c>
       <c r="D64" t="n">
-        <v>-1.636382785256189</v>
+        <v>-0.009772792847234544</v>
       </c>
       <c r="E64" t="n">
-        <v>0.1728931989404471</v>
+        <v>0.008842686861035095</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.2967190446200994</v>
+        <v>0.0172429864491352</v>
       </c>
     </row>
     <row r="65">
@@ -1717,19 +1717,19 @@
         <v>45726</v>
       </c>
       <c r="B65" t="n">
-        <v>-2.976787387531346</v>
+        <v>0.2011295486047781</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.6628329639697321</v>
+        <v>0.03358986603870279</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.2553927967178576</v>
+        <v>-0.03741264111843816</v>
       </c>
       <c r="E65" t="n">
-        <v>-1.863494859669455</v>
+        <v>-0.01184515324216311</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.09923913851698525</v>
+        <v>0.01095834655398459</v>
       </c>
     </row>
     <row r="66">
@@ -1737,19 +1737,19 @@
         <v>45727</v>
       </c>
       <c r="B66" t="n">
-        <v>0.4605349168169706</v>
+        <v>0.07114924255110286</v>
       </c>
       <c r="C66" t="n">
-        <v>1.185873154568803</v>
+        <v>-0.002614993172650132</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.6674748134720169</v>
+        <v>-0.005261310293239074</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.5516195942809804</v>
+        <v>0.00808715514150571</v>
       </c>
       <c r="F66" t="n">
-        <v>-1.033499873681275</v>
+        <v>-0.008528508149675533</v>
       </c>
     </row>
     <row r="67">
@@ -1757,19 +1757,19 @@
         <v>45728</v>
       </c>
       <c r="B67" t="n">
-        <v>-1.656979367162924</v>
+        <v>0.2306556863333392</v>
       </c>
       <c r="C67" t="n">
-        <v>1.768074567996607</v>
+        <v>0.02256946989753827</v>
       </c>
       <c r="D67" t="n">
-        <v>1.174155066473476</v>
+        <v>0.06129285607717533</v>
       </c>
       <c r="E67" t="n">
-        <v>0.05600713236103099</v>
+        <v>-0.01926575196572632</v>
       </c>
       <c r="F67" t="n">
-        <v>0.7280134602934328</v>
+        <v>-0.01055156297806758</v>
       </c>
     </row>
     <row r="68">
@@ -1777,19 +1777,19 @@
         <v>45729</v>
       </c>
       <c r="B68" t="n">
-        <v>1.359644181725009</v>
+        <v>-0.02441231514599105</v>
       </c>
       <c r="C68" t="n">
-        <v>-3.069185564863993</v>
+        <v>0.03854436254151066</v>
       </c>
       <c r="D68" t="n">
-        <v>0.8570580491119009</v>
+        <v>-0.07262411527499332</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.1642061664638841</v>
+        <v>0.002615407433946154</v>
       </c>
       <c r="F68" t="n">
-        <v>0.3180062686331673</v>
+        <v>0.00444118319389301</v>
       </c>
     </row>
     <row r="69">
@@ -1797,19 +1797,19 @@
         <v>45730</v>
       </c>
       <c r="B69" t="n">
-        <v>0.4990001035693637</v>
+        <v>0.01386670857730008</v>
       </c>
       <c r="C69" t="n">
-        <v>-1.352897566341228</v>
+        <v>0.028716454130724</v>
       </c>
       <c r="D69" t="n">
-        <v>1.253204823761507</v>
+        <v>-0.03656103994574225</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.1522689108479695</v>
+        <v>-0.009754916626661376</v>
       </c>
       <c r="F69" t="n">
-        <v>0.5285803340721026</v>
+        <v>-0.007938455150233675</v>
       </c>
     </row>
     <row r="70">
@@ -1817,19 +1817,19 @@
         <v>45733</v>
       </c>
       <c r="B70" t="n">
-        <v>1.550457094232317</v>
+        <v>-0.06914458150291564</v>
       </c>
       <c r="C70" t="n">
-        <v>-1.090484149592219</v>
+        <v>0.03192768483176232</v>
       </c>
       <c r="D70" t="n">
-        <v>0.9560748725197661</v>
+        <v>-0.0159161577384153</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.112729068373867</v>
+        <v>-0.04977084094278944</v>
       </c>
       <c r="F70" t="n">
-        <v>0.2382990257996219</v>
+        <v>-0.02494364083259029</v>
       </c>
     </row>
     <row r="71">
@@ -1837,19 +1837,19 @@
         <v>45734</v>
       </c>
       <c r="B71" t="n">
-        <v>-3.053573027047911</v>
+        <v>0.1024698719115919</v>
       </c>
       <c r="C71" t="n">
-        <v>-1.391054332022187</v>
+        <v>0.01223919591140577</v>
       </c>
       <c r="D71" t="n">
-        <v>0.8388963686398896</v>
+        <v>-0.0451387832379114</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.8364312163429212</v>
+        <v>-0.02344665837575172</v>
       </c>
       <c r="F71" t="n">
-        <v>0.1955224900617659</v>
+        <v>-0.02781989628059185</v>
       </c>
     </row>
     <row r="72">
@@ -1857,19 +1857,19 @@
         <v>45735</v>
       </c>
       <c r="B72" t="n">
-        <v>-0.6237326299969035</v>
+        <v>0.01835448866583714</v>
       </c>
       <c r="C72" t="n">
-        <v>0.6310435681223884</v>
+        <v>-0.00721509761603831</v>
       </c>
       <c r="D72" t="n">
-        <v>1.163218246489455</v>
+        <v>-0.04439495616965142</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.9510136800488675</v>
+        <v>-0.05278728774553727</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.3377490651043535</v>
+        <v>-0.03875788643191804</v>
       </c>
     </row>
     <row r="73">
@@ -1877,19 +1877,19 @@
         <v>45736</v>
       </c>
       <c r="B73" t="n">
-        <v>3.398186620089535</v>
+        <v>-0.143607191595945</v>
       </c>
       <c r="C73" t="n">
-        <v>1.995285189357389</v>
+        <v>-0.06418284046258164</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.4476384885348378</v>
+        <v>-0.0003349372081619571</v>
       </c>
       <c r="E73" t="n">
-        <v>0.8606666813682898</v>
+        <v>0.04563807332389729</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.4410484189569715</v>
+        <v>-0.045164186330114</v>
       </c>
     </row>
     <row r="74">
@@ -1897,19 +1897,19 @@
         <v>45737</v>
       </c>
       <c r="B74" t="n">
-        <v>3.604777679140551</v>
+        <v>-0.1712054580283473</v>
       </c>
       <c r="C74" t="n">
-        <v>1.836308431056245</v>
+        <v>-0.07679437906564185</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.8408901032296566</v>
+        <v>0.02184416467131051</v>
       </c>
       <c r="E74" t="n">
-        <v>0.7281714997187376</v>
+        <v>0.02922168620172919</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.1351740448410702</v>
+        <v>-0.03259853294841564</v>
       </c>
     </row>
     <row r="75">
@@ -1917,19 +1917,19 @@
         <v>45740</v>
       </c>
       <c r="B75" t="n">
-        <v>0.4647685545256413</v>
+        <v>-0.1182295638093926</v>
       </c>
       <c r="C75" t="n">
-        <v>0.2579678504413289</v>
+        <v>-0.05137060887694196</v>
       </c>
       <c r="D75" t="n">
-        <v>-2.147858944254037</v>
+        <v>-0.02574316931783268</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.7267721814125808</v>
+        <v>0.03216306016050049</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.439206556856067</v>
+        <v>-0.01844337947191381</v>
       </c>
     </row>
     <row r="76">
@@ -1937,19 +1937,19 @@
         <v>45741</v>
       </c>
       <c r="B76" t="n">
-        <v>-0.2591947808190816</v>
+        <v>-0.09741646801408908</v>
       </c>
       <c r="C76" t="n">
-        <v>0.0007117945935392723</v>
+        <v>-0.07338672885903581</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.4264732324809061</v>
+        <v>-0.01957261068709613</v>
       </c>
       <c r="E76" t="n">
-        <v>0.07283266488250049</v>
+        <v>0.02937874453385456</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.7000814437237083</v>
+        <v>-0.04308975521593806</v>
       </c>
     </row>
     <row r="77">
@@ -1957,19 +1957,19 @@
         <v>45742</v>
       </c>
       <c r="B77" t="n">
-        <v>0.2155148177854758</v>
+        <v>-0.1038033326342487</v>
       </c>
       <c r="C77" t="n">
-        <v>0.7284078965449209</v>
+        <v>-0.03796823105194698</v>
       </c>
       <c r="D77" t="n">
-        <v>0.2171374051732887</v>
+        <v>-0.05787006141210811</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.01493491889460317</v>
+        <v>0.06032403951738997</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.288221739664694</v>
+        <v>-0.03621121418403517</v>
       </c>
     </row>
     <row r="78">
@@ -1977,19 +1977,19 @@
         <v>45743</v>
       </c>
       <c r="B78" t="n">
-        <v>-2.556291150369133</v>
+        <v>-0.02986273542859296</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.763130718719442</v>
+        <v>-0.05592548922883482</v>
       </c>
       <c r="D78" t="n">
-        <v>-2.610586077190939</v>
+        <v>-0.0181601885633092</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.8638655762410004</v>
+        <v>0.03444815450734792</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.6263988164201346</v>
+        <v>0.002799353618056639</v>
       </c>
     </row>
     <row r="79">
@@ -1997,19 +1997,19 @@
         <v>45744</v>
       </c>
       <c r="B79" t="n">
-        <v>-1.91220041520139</v>
+        <v>0.01456611950641527</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.4016899561931169</v>
+        <v>-0.07632993568702803</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.8599704784454794</v>
+        <v>-0.02616881614694573</v>
       </c>
       <c r="E79" t="n">
-        <v>1.202094826500048</v>
+        <v>0.0348206053151498</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.1903290437263519</v>
+        <v>-0.02532083199987496</v>
       </c>
     </row>
     <row r="80">
@@ -2017,19 +2017,19 @@
         <v>45747</v>
       </c>
       <c r="B80" t="n">
-        <v>-0.04933596607231816</v>
+        <v>-0.02058057452887709</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.9072094543895027</v>
+        <v>-0.001264509821653413</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.6521056481623324</v>
+        <v>-0.04270417243473407</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.5544538812357324</v>
+        <v>0.03591878627060308</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.601216850106043</v>
+        <v>0.001161980566859295</v>
       </c>
     </row>
     <row r="81">
@@ -2037,19 +2037,19 @@
         <v>45748</v>
       </c>
       <c r="B81" t="n">
-        <v>-0.4475562715287616</v>
+        <v>-0.006244022350382373</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.30447538890012</v>
+        <v>-0.04408902233219545</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.1894599013359508</v>
+        <v>-0.02563252757828665</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.2108124810118255</v>
+        <v>-0.0002182823740207522</v>
       </c>
       <c r="F81" t="n">
-        <v>0.3695701004248428</v>
+        <v>-0.001312760218619744</v>
       </c>
     </row>
     <row r="82">
@@ -2057,19 +2057,19 @@
         <v>45749</v>
       </c>
       <c r="B82" t="n">
-        <v>1.854048774242071</v>
+        <v>-0.1005484962078494</v>
       </c>
       <c r="C82" t="n">
-        <v>0.3563801410645266</v>
+        <v>-0.01034791799853098</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.443391356217815</v>
+        <v>0.004401828482745954</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.4120463057768307</v>
+        <v>0.02634310107589915</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.896291666915884</v>
+        <v>0.01090133726671141</v>
       </c>
     </row>
     <row r="83">
@@ -2077,19 +2077,19 @@
         <v>45750</v>
       </c>
       <c r="B83" t="n">
-        <v>-8.857591663744252</v>
+        <v>0.2632314321103676</v>
       </c>
       <c r="C83" t="n">
-        <v>-1.570014532414011</v>
+        <v>-0.03446137306558907</v>
       </c>
       <c r="D83" t="n">
-        <v>-1.565827211604508</v>
+        <v>-0.03140593619209148</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.6365879834742174</v>
+        <v>0.001019305267005482</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.4649958412903366</v>
+        <v>0.006295207392973022</v>
       </c>
     </row>
     <row r="84">
@@ -2097,19 +2097,19 @@
         <v>45751</v>
       </c>
       <c r="B84" t="n">
-        <v>-13.71633687469764</v>
+        <v>0.5048831925665174</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.8414249720589929</v>
+        <v>-0.1021682826361293</v>
       </c>
       <c r="D84" t="n">
-        <v>-1.605632043759393</v>
+        <v>-0.06052687072791965</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.4436300935034767</v>
+        <v>0.007847315448198803</v>
       </c>
       <c r="F84" t="n">
-        <v>0.5126333634649222</v>
+        <v>0.01869942872603262</v>
       </c>
     </row>
     <row r="85">
@@ -2117,19 +2117,19 @@
         <v>45754</v>
       </c>
       <c r="B85" t="n">
-        <v>-21.04078534484285</v>
+        <v>0.8455429399037894</v>
       </c>
       <c r="C85" t="n">
-        <v>-1.147815554947517</v>
+        <v>-0.1360596051985264</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.9178549312895328</v>
+        <v>-0.140646972767716</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.5527612596286172</v>
+        <v>-0.01429535562311242</v>
       </c>
       <c r="F85" t="n">
-        <v>-1.077255273155946</v>
+        <v>0.01203241155099504</v>
       </c>
     </row>
     <row r="86">
@@ -2137,19 +2137,19 @@
         <v>45755</v>
       </c>
       <c r="B86" t="n">
-        <v>-13.90027934044885</v>
+        <v>0.822828399161913</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.585345969380095</v>
+        <v>-0.108873086409229</v>
       </c>
       <c r="D86" t="n">
-        <v>1.163173701811475</v>
+        <v>-0.03701317290256767</v>
       </c>
       <c r="E86" t="n">
-        <v>0.8428771910344932</v>
+        <v>-0.02401680253406691</v>
       </c>
       <c r="F86" t="n">
-        <v>1.059578561531741</v>
+        <v>-0.00387142754829938</v>
       </c>
     </row>
     <row r="87">
@@ -2157,19 +2157,19 @@
         <v>45756</v>
       </c>
       <c r="B87" t="n">
-        <v>-20.83538688241709</v>
+        <v>1.153764522581482</v>
       </c>
       <c r="C87" t="n">
-        <v>-2.036897226745345</v>
+        <v>-0.03021824376864963</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.1765125285750532</v>
+        <v>-0.05892581298698019</v>
       </c>
       <c r="E87" t="n">
-        <v>0.01261342505276151</v>
+        <v>-0.01465731690356266</v>
       </c>
       <c r="F87" t="n">
-        <v>-0.306022058098429</v>
+        <v>0.01111945852985289</v>
       </c>
     </row>
     <row r="88">
@@ -2177,19 +2177,19 @@
         <v>45757</v>
       </c>
       <c r="B88" t="n">
-        <v>-13.78767857897568</v>
+        <v>1.056999767282792</v>
       </c>
       <c r="C88" t="n">
-        <v>0.03846680823877727</v>
+        <v>0.03338766440407794</v>
       </c>
       <c r="D88" t="n">
-        <v>1.074099348047453</v>
+        <v>0.08456077919825573</v>
       </c>
       <c r="E88" t="n">
-        <v>0.6654598910388647</v>
+        <v>-0.03718695654934808</v>
       </c>
       <c r="F88" t="n">
-        <v>1.031451102454163</v>
+        <v>0.008892623259748711</v>
       </c>
     </row>
     <row r="89">
@@ -2197,19 +2197,19 @@
         <v>45758</v>
       </c>
       <c r="B89" t="n">
-        <v>-9.626929437155654</v>
+        <v>0.8281250680663214</v>
       </c>
       <c r="C89" t="n">
-        <v>-1.103056713930718</v>
+        <v>0.02560007258977942</v>
       </c>
       <c r="D89" t="n">
-        <v>0.2806099852507014</v>
+        <v>0.02052980066725052</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.3215752591124238</v>
+        <v>-0.0450201700748266</v>
       </c>
       <c r="F89" t="n">
-        <v>0.612384351410187</v>
+        <v>-0.002766218473184085</v>
       </c>
     </row>
     <row r="90">
@@ -2217,19 +2217,19 @@
         <v>45761</v>
       </c>
       <c r="B90" t="n">
-        <v>-6.442405177496946</v>
+        <v>0.6231865659779406</v>
       </c>
       <c r="C90" t="n">
-        <v>-2.169264160495025</v>
+        <v>0.0149972334008972</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.07355566982988293</v>
+        <v>0.02107768355843691</v>
       </c>
       <c r="E90" t="n">
-        <v>1.224679971403521</v>
+        <v>-0.04023025261947214</v>
       </c>
       <c r="F90" t="n">
-        <v>1.213972653046394</v>
+        <v>0.02279038712085193</v>
       </c>
     </row>
     <row r="91">
@@ -2237,19 +2237,19 @@
         <v>45762</v>
       </c>
       <c r="B91" t="n">
-        <v>-3.57256116039238</v>
+        <v>0.4698684376427613</v>
       </c>
       <c r="C91" t="n">
-        <v>1.621937979516635</v>
+        <v>0.004137188545627996</v>
       </c>
       <c r="D91" t="n">
-        <v>0.8910008149340494</v>
+        <v>0.02087841171703488</v>
       </c>
       <c r="E91" t="n">
-        <v>0.1772035047048537</v>
+        <v>0.03346153127880167</v>
       </c>
       <c r="F91" t="n">
-        <v>-0.8333156084351174</v>
+        <v>-0.004910200875223378</v>
       </c>
     </row>
     <row r="92">
@@ -2257,19 +2257,19 @@
         <v>45763</v>
       </c>
       <c r="B92" t="n">
-        <v>-6.214522256945862</v>
+        <v>0.544063002190586</v>
       </c>
       <c r="C92" t="n">
-        <v>0.1099670931923901</v>
+        <v>0.04994024964947531</v>
       </c>
       <c r="D92" t="n">
-        <v>2.024278714439127</v>
+        <v>0.03397339674530604</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.3067868243165231</v>
+        <v>-0.05046794055084796</v>
       </c>
       <c r="F92" t="n">
-        <v>0.7625009536768008</v>
+        <v>-0.01424426122081568</v>
       </c>
     </row>
     <row r="93">
@@ -2277,19 +2277,19 @@
         <v>45764</v>
       </c>
       <c r="B93" t="n">
-        <v>-3.087896449956135</v>
+        <v>0.3539128882714861</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.02223420032644681</v>
+        <v>0.06135424778755059</v>
       </c>
       <c r="D93" t="n">
-        <v>1.365481630552864</v>
+        <v>-0.001860585127119572</v>
       </c>
       <c r="E93" t="n">
-        <v>1.168267744505403</v>
+        <v>0.05726982515141636</v>
       </c>
       <c r="F93" t="n">
-        <v>-0.3337254299295841</v>
+        <v>-0.003703325003674687</v>
       </c>
     </row>
     <row r="94">
@@ -2297,19 +2297,19 @@
         <v>45769</v>
       </c>
       <c r="B94" t="n">
-        <v>-2.832867734609572</v>
+        <v>0.310478731212094</v>
       </c>
       <c r="C94" t="n">
-        <v>0.03574633871886723</v>
+        <v>0.1151814203873741</v>
       </c>
       <c r="D94" t="n">
-        <v>1.504654435033311</v>
+        <v>-0.004925359809328053</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.3910204036964274</v>
+        <v>0.0342340638020528</v>
       </c>
       <c r="F94" t="n">
-        <v>-0.2250484683389946</v>
+        <v>0.004601728126276092</v>
       </c>
     </row>
     <row r="95">
@@ -2317,19 +2317,19 @@
         <v>45770</v>
       </c>
       <c r="B95" t="n">
-        <v>-5.646917552449637</v>
+        <v>0.3916655087368283</v>
       </c>
       <c r="C95" t="n">
-        <v>-1.44842120611401</v>
+        <v>0.03623540062223811</v>
       </c>
       <c r="D95" t="n">
-        <v>0.9571320930417697</v>
+        <v>0.02887808934078939</v>
       </c>
       <c r="E95" t="n">
-        <v>0.8260907683405758</v>
+        <v>-0.02369409811338004</v>
       </c>
       <c r="F95" t="n">
-        <v>1.263890830596459</v>
+        <v>-0.006794975195962042</v>
       </c>
     </row>
     <row r="96">
@@ -2337,19 +2337,19 @@
         <v>45771</v>
       </c>
       <c r="B96" t="n">
-        <v>-2.629419643242011</v>
+        <v>0.2458890128312182</v>
       </c>
       <c r="C96" t="n">
-        <v>-2.16817632696277</v>
+        <v>0.07141197036049525</v>
       </c>
       <c r="D96" t="n">
-        <v>1.055709213695343</v>
+        <v>-0.04467007444490883</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.2339212517944363</v>
+        <v>0.001656601493853028</v>
       </c>
       <c r="F96" t="n">
-        <v>0.3230663101045701</v>
+        <v>-0.006430788597746569</v>
       </c>
     </row>
     <row r="97">
@@ -2357,19 +2357,19 @@
         <v>45772</v>
       </c>
       <c r="B97" t="n">
-        <v>0.525692616493759</v>
+        <v>0.1063122299702835</v>
       </c>
       <c r="C97" t="n">
-        <v>1.358237564751136</v>
+        <v>-0.004171519581836969</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.05745584296716873</v>
+        <v>0.03798764485068078</v>
       </c>
       <c r="E97" t="n">
-        <v>0.08745677869631883</v>
+        <v>-0.03504999296491013</v>
       </c>
       <c r="F97" t="n">
-        <v>0.3439624526533619</v>
+        <v>-0.01993532042405066</v>
       </c>
     </row>
     <row r="98">
@@ -2377,19 +2377,19 @@
         <v>45775</v>
       </c>
       <c r="B98" t="n">
-        <v>-0.4412306685380978</v>
+        <v>0.1018261968228473</v>
       </c>
       <c r="C98" t="n">
-        <v>0.1661519111591276</v>
+        <v>0.01933465181655544</v>
       </c>
       <c r="D98" t="n">
-        <v>0.1930775211309994</v>
+        <v>0.01614241208529438</v>
       </c>
       <c r="E98" t="n">
-        <v>0.1900839126523083</v>
+        <v>-0.01827727824324526</v>
       </c>
       <c r="F98" t="n">
-        <v>-0.3503290828119547</v>
+        <v>-0.02413433266180936</v>
       </c>
     </row>
     <row r="99">
@@ -2397,19 +2397,19 @@
         <v>45776</v>
       </c>
       <c r="B99" t="n">
-        <v>0.6809051120701772</v>
+        <v>0.06152570531190765</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.5140051683067425</v>
+        <v>0.08291402473322172</v>
       </c>
       <c r="D99" t="n">
-        <v>1.874343569683774</v>
+        <v>-0.05026169534305163</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.6015461647529469</v>
+        <v>0.0141843260023928</v>
       </c>
       <c r="F99" t="n">
-        <v>-0.3987863619987744</v>
+        <v>-0.01540208874507434</v>
       </c>
     </row>
     <row r="100">
@@ -2417,19 +2417,19 @@
         <v>45777</v>
       </c>
       <c r="B100" t="n">
-        <v>-2.265041562707024</v>
+        <v>0.1160912202648417</v>
       </c>
       <c r="C100" t="n">
-        <v>1.137497727872646</v>
+        <v>0.05546480753766987</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.6280668104435506</v>
+        <v>-0.009385353665957762</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.6117454825333043</v>
+        <v>0.04139149868610448</v>
       </c>
       <c r="F100" t="n">
-        <v>-1.001047527397714</v>
+        <v>0.0008031531251592166</v>
       </c>
     </row>
     <row r="101">
@@ -2437,19 +2437,19 @@
         <v>45779</v>
       </c>
       <c r="B101" t="n">
-        <v>-1.691555837599752</v>
+        <v>0.08003708907772743</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.1529315662454109</v>
+        <v>0.04443885558268643</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.03779067745770764</v>
+        <v>-0.005171542770567281</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.9548737310820702</v>
+        <v>0.003458332301031191</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.5283491872507927</v>
+        <v>-0.01423726928891055</v>
       </c>
     </row>
     <row r="102">
@@ -2457,19 +2457,19 @@
         <v>45782</v>
       </c>
       <c r="B102" t="n">
-        <v>-0.5043097933745269</v>
+        <v>0.02202841335830757</v>
       </c>
       <c r="C102" t="n">
-        <v>0.07541984916627031</v>
+        <v>0.02837924654096568</v>
       </c>
       <c r="D102" t="n">
-        <v>-1.266449500666641</v>
+        <v>0.02048785011127469</v>
       </c>
       <c r="E102" t="n">
-        <v>0.1225120693088184</v>
+        <v>0.008360181666492881</v>
       </c>
       <c r="F102" t="n">
-        <v>-0.6848851532595166</v>
+        <v>-7.704383091505635e-05</v>
       </c>
     </row>
     <row r="103">
@@ -2477,19 +2477,19 @@
         <v>45783</v>
       </c>
       <c r="B103" t="n">
-        <v>0.8504734100434332</v>
+        <v>0.02912770134832982</v>
       </c>
       <c r="C103" t="n">
-        <v>1.252589382139078</v>
+        <v>0.01682775801123951</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.5214488943055348</v>
+        <v>0.08763134424133653</v>
       </c>
       <c r="E103" t="n">
-        <v>1.082988684150345</v>
+        <v>0.00907444029781293</v>
       </c>
       <c r="F103" t="n">
-        <v>0.6355066402897652</v>
+        <v>0.003661381345154416</v>
       </c>
     </row>
     <row r="104">
@@ -2497,19 +2497,19 @@
         <v>45784</v>
       </c>
       <c r="B104" t="n">
-        <v>1.661404205931486</v>
+        <v>0.0004595918653193551</v>
       </c>
       <c r="C104" t="n">
-        <v>2.117944657921889</v>
+        <v>0.02751044621527919</v>
       </c>
       <c r="D104" t="n">
-        <v>1.259356708936013</v>
+        <v>0.01748695765941476</v>
       </c>
       <c r="E104" t="n">
-        <v>-0.667465920528257</v>
+        <v>-0.007124605675708616</v>
       </c>
       <c r="F104" t="n">
-        <v>-0.581004330373297</v>
+        <v>-0.01036999412005512</v>
       </c>
     </row>
     <row r="105">
@@ -2517,19 +2517,19 @@
         <v>45785</v>
       </c>
       <c r="B105" t="n">
-        <v>-6.982938908685049</v>
+        <v>0.2226844485375475</v>
       </c>
       <c r="C105" t="n">
-        <v>-4.048026451994155</v>
+        <v>0.003634243682789832</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.2009802599600288</v>
+        <v>-0.02289352501186258</v>
       </c>
       <c r="E105" t="n">
-        <v>0.2108072939438896</v>
+        <v>-0.01942382748945953</v>
       </c>
       <c r="F105" t="n">
-        <v>0.666236250579356</v>
+        <v>0.02904688997162841</v>
       </c>
     </row>
     <row r="106">
@@ -2537,19 +2537,19 @@
         <v>45786</v>
       </c>
       <c r="B106" t="n">
-        <v>4.020354756149344</v>
+        <v>-0.1502146861671533</v>
       </c>
       <c r="C106" t="n">
-        <v>1.248324483707238</v>
+        <v>-0.09631071008490823</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.2855599417788711</v>
+        <v>-0.009255814128185897</v>
       </c>
       <c r="E106" t="n">
-        <v>0.126990467882958</v>
+        <v>-0.001193820010713586</v>
       </c>
       <c r="F106" t="n">
-        <v>-0.3232760956889982</v>
+        <v>0.002282019639711557</v>
       </c>
     </row>
     <row r="107">
@@ -2557,19 +2557,19 @@
         <v>45789</v>
       </c>
       <c r="B107" t="n">
-        <v>-1.030347581797169</v>
+        <v>0.02878074175349769</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.9919697393363411</v>
+        <v>-0.06411453083921609</v>
       </c>
       <c r="D107" t="n">
-        <v>-0.9635402226294945</v>
+        <v>0.02754945072536361</v>
       </c>
       <c r="E107" t="n">
-        <v>1.41747269852427</v>
+        <v>-0.01255114235051665</v>
       </c>
       <c r="F107" t="n">
-        <v>0.6378398303614088</v>
+        <v>0.01972472741072582</v>
       </c>
     </row>
     <row r="108">
@@ -2577,19 +2577,19 @@
         <v>45790</v>
       </c>
       <c r="B108" t="n">
-        <v>0.3694461324886809</v>
+        <v>-0.0004967562413503693</v>
       </c>
       <c r="C108" t="n">
-        <v>-1.720685339659084</v>
+        <v>0.05014919092549946</v>
       </c>
       <c r="D108" t="n">
-        <v>3.487103097309346</v>
+        <v>-0.1157764713007161</v>
       </c>
       <c r="E108" t="n">
-        <v>-1.051526238005176</v>
+        <v>-0.04985099759734336</v>
       </c>
       <c r="F108" t="n">
-        <v>0.3894461917976583</v>
+        <v>0.00788552610101491</v>
       </c>
     </row>
     <row r="109">
@@ -2597,19 +2597,19 @@
         <v>45791</v>
       </c>
       <c r="B109" t="n">
-        <v>1.093178748502707</v>
+        <v>0.01402002465320694</v>
       </c>
       <c r="C109" t="n">
-        <v>0.6793546144610021</v>
+        <v>-0.001158682817033429</v>
       </c>
       <c r="D109" t="n">
-        <v>1.416240435891887</v>
+        <v>-0.01115483364891714</v>
       </c>
       <c r="E109" t="n">
-        <v>0.06006112391540319</v>
+        <v>-0.04405871192487744</v>
       </c>
       <c r="F109" t="n">
-        <v>0.4867874415670101</v>
+        <v>0.008103484238522685</v>
       </c>
     </row>
     <row r="110">
@@ -2617,19 +2617,19 @@
         <v>45792</v>
       </c>
       <c r="B110" t="n">
-        <v>-1.494329986933975</v>
+        <v>0.08677186516358927</v>
       </c>
       <c r="C110" t="n">
-        <v>0.6583639348872634</v>
+        <v>0.04208246637934149</v>
       </c>
       <c r="D110" t="n">
-        <v>0.6482939204653114</v>
+        <v>-0.01217483820278871</v>
       </c>
       <c r="E110" t="n">
-        <v>0.8202099786990775</v>
+        <v>0.04419049278140839</v>
       </c>
       <c r="F110" t="n">
-        <v>0.04113934095659359</v>
+        <v>-0.004578157531536053</v>
       </c>
     </row>
     <row r="111">
@@ -2637,19 +2637,19 @@
         <v>45793</v>
       </c>
       <c r="B111" t="n">
-        <v>-3.145038892566254</v>
+        <v>0.168260239666116</v>
       </c>
       <c r="C111" t="n">
-        <v>0.4266216705040196</v>
+        <v>0.04813142499106146</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.6987796305270182</v>
+        <v>-0.01271046250779344</v>
       </c>
       <c r="E111" t="n">
-        <v>-1.015494389189258</v>
+        <v>0.01644186275293666</v>
       </c>
       <c r="F111" t="n">
-        <v>0.3280345091614427</v>
+        <v>0.02433984451039372</v>
       </c>
     </row>
     <row r="112">
@@ -2657,19 +2657,19 @@
         <v>45796</v>
       </c>
       <c r="B112" t="n">
-        <v>2.611063664189384</v>
+        <v>-0.006318561637842245</v>
       </c>
       <c r="C112" t="n">
-        <v>0.5862742596366743</v>
+        <v>0.06913249917443981</v>
       </c>
       <c r="D112" t="n">
-        <v>0.7791834137888141</v>
+        <v>0.05476550580495456</v>
       </c>
       <c r="E112" t="n">
-        <v>0.1475965488187151</v>
+        <v>-0.0534250089459584</v>
       </c>
       <c r="F112" t="n">
-        <v>1.37436786955572</v>
+        <v>0.001146369679131485</v>
       </c>
     </row>
     <row r="113">
@@ -2677,19 +2677,19 @@
         <v>45797</v>
       </c>
       <c r="B113" t="n">
-        <v>0.7708424596949111</v>
+        <v>0.06034836822870143</v>
       </c>
       <c r="C113" t="n">
-        <v>0.0628945113085112</v>
+        <v>0.08333876665129591</v>
       </c>
       <c r="D113" t="n">
-        <v>0.6861350703900231</v>
+        <v>0.07153081724060162</v>
       </c>
       <c r="E113" t="n">
-        <v>1.414302757545485</v>
+        <v>0.03441756897802708</v>
       </c>
       <c r="F113" t="n">
-        <v>0.672132951780135</v>
+        <v>0.001675345511341406</v>
       </c>
     </row>
     <row r="114">
@@ -2697,19 +2697,19 @@
         <v>45798</v>
       </c>
       <c r="B114" t="n">
-        <v>-0.5181195605479377</v>
+        <v>0.1240577804057286</v>
       </c>
       <c r="C114" t="n">
-        <v>3.37849745380168</v>
+        <v>0.03439193388254407</v>
       </c>
       <c r="D114" t="n">
-        <v>1.421352326068069</v>
+        <v>0.09044499151184748</v>
       </c>
       <c r="E114" t="n">
-        <v>0.7759988098936857</v>
+        <v>0.03707237301651471</v>
       </c>
       <c r="F114" t="n">
-        <v>-0.323748641424749</v>
+        <v>-0.02390087997613973</v>
       </c>
     </row>
     <row r="115">
@@ -2717,19 +2717,19 @@
         <v>45799</v>
       </c>
       <c r="B115" t="n">
-        <v>-3.631081035506907</v>
+        <v>0.1721233129918538</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.3922208125281255</v>
+        <v>0.04902816939668592</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.06742056400215778</v>
+        <v>0.02621361799397335</v>
       </c>
       <c r="E115" t="n">
-        <v>0.7043083386372699</v>
+        <v>0.0156829115811362</v>
       </c>
       <c r="F115" t="n">
-        <v>-0.6626576025533581</v>
+        <v>-0.0008380580984333373</v>
       </c>
     </row>
     <row r="116">
@@ -2737,19 +2737,19 @@
         <v>45800</v>
       </c>
       <c r="B116" t="n">
-        <v>-8.217947066679724</v>
+        <v>0.3189036422552745</v>
       </c>
       <c r="C116" t="n">
-        <v>0.7272642683144448</v>
+        <v>-0.0185296501832192</v>
       </c>
       <c r="D116" t="n">
-        <v>-1.49470324327693</v>
+        <v>0.01600814820214204</v>
       </c>
       <c r="E116" t="n">
-        <v>-1.495108699587361</v>
+        <v>-0.01163581672076538</v>
       </c>
       <c r="F116" t="n">
-        <v>-0.2524111750699658</v>
+        <v>0.0005821198887655393</v>
       </c>
     </row>
     <row r="117">
@@ -2757,19 +2757,19 @@
         <v>45803</v>
       </c>
       <c r="B117" t="n">
-        <v>1.232656895492062</v>
+        <v>-0.02627671854608504</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.8393141168051823</v>
+        <v>-0.02966991086353553</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.4486061263599552</v>
+        <v>-0.09022472552789282</v>
       </c>
       <c r="E117" t="n">
-        <v>-0.350867917845252</v>
+        <v>0.03997032121374579</v>
       </c>
       <c r="F117" t="n">
-        <v>-1.34106416787543</v>
+        <v>-0.01889349141048717</v>
       </c>
     </row>
     <row r="118">
@@ -2777,19 +2777,19 @@
         <v>45804</v>
       </c>
       <c r="B118" t="n">
-        <v>-2.836928169444979</v>
+        <v>0.1718220532181002</v>
       </c>
       <c r="C118" t="n">
-        <v>-2.94916087639713</v>
+        <v>-0.01890637372266905</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.9304599269533725</v>
+        <v>-0.01422732180726106</v>
       </c>
       <c r="E118" t="n">
-        <v>1.474244649161888</v>
+        <v>0.0005860521435787481</v>
       </c>
       <c r="F118" t="n">
-        <v>1.110769895105718</v>
+        <v>0.04789990576637375</v>
       </c>
     </row>
     <row r="119">
@@ -2797,19 +2797,19 @@
         <v>45805</v>
       </c>
       <c r="B119" t="n">
-        <v>2.090361560105866</v>
+        <v>-0.02099488140844974</v>
       </c>
       <c r="C119" t="n">
-        <v>1.567901698214481</v>
+        <v>-0.03393768570264181</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.818033010512926</v>
+        <v>0.004170524725229771</v>
       </c>
       <c r="E119" t="n">
-        <v>-0.9065586164736985</v>
+        <v>-0.02357644562635942</v>
       </c>
       <c r="F119" t="n">
-        <v>0.08660323865609816</v>
+        <v>0.01297769753486852</v>
       </c>
     </row>
     <row r="120">
@@ -2817,19 +2817,19 @@
         <v>45806</v>
       </c>
       <c r="B120" t="n">
-        <v>-0.06981452497487424</v>
+        <v>0.06504454705932024</v>
       </c>
       <c r="C120" t="n">
-        <v>0.7293310563546591</v>
+        <v>0.005809888744354856</v>
       </c>
       <c r="D120" t="n">
-        <v>0.6914630009763983</v>
+        <v>-0.02453333676058255</v>
       </c>
       <c r="E120" t="n">
-        <v>-0.6008035499489813</v>
+        <v>-0.01515326530010135</v>
       </c>
       <c r="F120" t="n">
-        <v>0.1013839455227026</v>
+        <v>0.01345796448040528</v>
       </c>
     </row>
     <row r="121">
@@ -2837,19 +2837,19 @@
         <v>45807</v>
       </c>
       <c r="B121" t="n">
-        <v>-1.272563356557896</v>
+        <v>0.09854868415906781</v>
       </c>
       <c r="C121" t="n">
-        <v>3.405250323462795</v>
+        <v>0.0053172327641013</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.2574939332362183</v>
+        <v>0.09795665135941285</v>
       </c>
       <c r="E121" t="n">
-        <v>0.585994963996923</v>
+        <v>0.02524647807259736</v>
       </c>
       <c r="F121" t="n">
-        <v>-0.5683018678895809</v>
+        <v>0.01335531675128764</v>
       </c>
     </row>
     <row r="122">
@@ -2857,19 +2857,19 @@
         <v>45810</v>
       </c>
       <c r="B122" t="n">
-        <v>-4.668604973480686</v>
+        <v>0.1799545549307318</v>
       </c>
       <c r="C122" t="n">
-        <v>-1.192228813385269</v>
+        <v>-0.02900096929760979</v>
       </c>
       <c r="D122" t="n">
-        <v>-1.514732910108969</v>
+        <v>0.03004667950979491</v>
       </c>
       <c r="E122" t="n">
-        <v>1.107137487102952</v>
+        <v>-0.007297434898003438</v>
       </c>
       <c r="F122" t="n">
-        <v>0.0891330152390669</v>
+        <v>0.03879102722007955</v>
       </c>
     </row>
     <row r="123">
@@ -2877,19 +2877,19 @@
         <v>45811</v>
       </c>
       <c r="B123" t="n">
-        <v>-1.479088269586642</v>
+        <v>0.01655799569366794</v>
       </c>
       <c r="C123" t="n">
-        <v>-2.116508171366684</v>
+        <v>0.005545299798213849</v>
       </c>
       <c r="D123" t="n">
-        <v>-0.3557272334885134</v>
+        <v>-0.09043223681837054</v>
       </c>
       <c r="E123" t="n">
-        <v>-1.042592811155046</v>
+        <v>0.02276824401548094</v>
       </c>
       <c r="F123" t="n">
-        <v>-1.326872265671486</v>
+        <v>0.01410063115110555</v>
       </c>
     </row>
     <row r="124">
@@ -2897,19 +2897,19 @@
         <v>45812</v>
       </c>
       <c r="B124" t="n">
-        <v>-1.886894750495536</v>
+        <v>0.1533845866521059</v>
       </c>
       <c r="C124" t="n">
-        <v>0.3779844451107072</v>
+        <v>0.006460993191875409</v>
       </c>
       <c r="D124" t="n">
-        <v>0.4693829996825909</v>
+        <v>0.02797367262541939</v>
       </c>
       <c r="E124" t="n">
-        <v>0.8138845480824024</v>
+        <v>0.008841995695313026</v>
       </c>
       <c r="F124" t="n">
-        <v>0.1437988691473295</v>
+        <v>0.001787664956990957</v>
       </c>
     </row>
     <row r="125">
@@ -2917,19 +2917,19 @@
         <v>45813</v>
       </c>
       <c r="B125" t="n">
-        <v>1.284024024779573</v>
+        <v>0.04944437234136236</v>
       </c>
       <c r="C125" t="n">
-        <v>0.6225514170295177</v>
+        <v>0.01910076452441108</v>
       </c>
       <c r="D125" t="n">
-        <v>1.483147469260887</v>
+        <v>-0.01348383987174955</v>
       </c>
       <c r="E125" t="n">
-        <v>0.6948967509390225</v>
+        <v>0.06275899605137276</v>
       </c>
       <c r="F125" t="n">
-        <v>-0.04912863875625444</v>
+        <v>-0.00111494554285432</v>
       </c>
     </row>
     <row r="126">
@@ -2937,19 +2937,19 @@
         <v>45814</v>
       </c>
       <c r="B126" t="n">
-        <v>-1.446756723139216</v>
+        <v>0.1052753454947454</v>
       </c>
       <c r="C126" t="n">
-        <v>0.5997336558295769</v>
+        <v>0.007294838582726897</v>
       </c>
       <c r="D126" t="n">
-        <v>0.1201613956503071</v>
+        <v>-0.01098041562572176</v>
       </c>
       <c r="E126" t="n">
-        <v>0.5699240750161133</v>
+        <v>0.03232398654398425</v>
       </c>
       <c r="F126" t="n">
-        <v>-0.7052415303871359</v>
+        <v>-0.001676945099247347</v>
       </c>
     </row>
     <row r="127">
@@ -2957,19 +2957,19 @@
         <v>45817</v>
       </c>
       <c r="B127" t="n">
-        <v>-3.794773351191459</v>
+        <v>0.1414582487657005</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.1568145960711025</v>
+        <v>0.01865427856049779</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.4643765086116431</v>
+        <v>-0.05292466076685172</v>
       </c>
       <c r="E127" t="n">
-        <v>-0.698679296140468</v>
+        <v>0.04752313818120962</v>
       </c>
       <c r="F127" t="n">
-        <v>-1.031697774725912</v>
+        <v>-0.01370334851308859</v>
       </c>
     </row>
     <row r="128">
@@ -2977,19 +2977,19 @@
         <v>45818</v>
       </c>
       <c r="B128" t="n">
-        <v>-0.4835829067568562</v>
+        <v>0.08318496971076685</v>
       </c>
       <c r="C128" t="n">
-        <v>1.05842042623629</v>
+        <v>-0.005669539733448826</v>
       </c>
       <c r="D128" t="n">
-        <v>0.7014878152674653</v>
+        <v>0.00666923542178361</v>
       </c>
       <c r="E128" t="n">
-        <v>-0.210310193591065</v>
+        <v>-0.01038964709134387</v>
       </c>
       <c r="F128" t="n">
-        <v>-0.2945527620261487</v>
+        <v>-0.03191544790246486</v>
       </c>
     </row>
     <row r="129">
@@ -2997,19 +2997,19 @@
         <v>45819</v>
       </c>
       <c r="B129" t="n">
-        <v>-3.867879975633832</v>
+        <v>0.2061861205293944</v>
       </c>
       <c r="C129" t="n">
-        <v>1.451761335173108</v>
+        <v>0.02252533630593676</v>
       </c>
       <c r="D129" t="n">
-        <v>-0.3774100262670002</v>
+        <v>0.009571671412870773</v>
       </c>
       <c r="E129" t="n">
-        <v>-0.6809663064571293</v>
+        <v>0.02942191228351258</v>
       </c>
       <c r="F129" t="n">
-        <v>-0.7466549878670955</v>
+        <v>-0.01134986758342945</v>
       </c>
     </row>
     <row r="130">
@@ -3017,19 +3017,19 @@
         <v>45820</v>
       </c>
       <c r="B130" t="n">
-        <v>0.4067597668413697</v>
+        <v>0.07056970618340216</v>
       </c>
       <c r="C130" t="n">
-        <v>1.251006231854967</v>
+        <v>0.03947075029002601</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.4020593762083653</v>
+        <v>0.01417386492801147</v>
       </c>
       <c r="E130" t="n">
-        <v>0.2252579998387541</v>
+        <v>0.07972962933890315</v>
       </c>
       <c r="F130" t="n">
-        <v>-0.315454270403956</v>
+        <v>-0.0002007932470625942</v>
       </c>
     </row>
     <row r="131">
@@ -3037,19 +3037,19 @@
         <v>45821</v>
       </c>
       <c r="B131" t="n">
-        <v>-0.6843635298676521</v>
+        <v>0.02953343614693172</v>
       </c>
       <c r="C131" t="n">
-        <v>1.657158616542238</v>
+        <v>-0.07308692199536729</v>
       </c>
       <c r="D131" t="n">
-        <v>-2.063217601718333</v>
+        <v>0.01430387848318375</v>
       </c>
       <c r="E131" t="n">
-        <v>-0.2407053407188615</v>
+        <v>0.01642402771620472</v>
       </c>
       <c r="F131" t="n">
-        <v>-0.7714838022632731</v>
+        <v>-0.02020050909577501</v>
       </c>
     </row>
     <row r="132">
@@ -3057,19 +3057,19 @@
         <v>45824</v>
       </c>
       <c r="B132" t="n">
-        <v>1.423961437089044</v>
+        <v>-0.02655901985411836</v>
       </c>
       <c r="C132" t="n">
-        <v>-2.827227197024561</v>
+        <v>0.01046694270715932</v>
       </c>
       <c r="D132" t="n">
-        <v>1.106775631773901</v>
+        <v>-0.02779545298678621</v>
       </c>
       <c r="E132" t="n">
-        <v>0.3506384528509841</v>
+        <v>-0.03752926006326102</v>
       </c>
       <c r="F132" t="n">
-        <v>1.360348362494627</v>
+        <v>0.004969521604959512</v>
       </c>
     </row>
     <row r="133">
@@ -3077,19 +3077,19 @@
         <v>45825</v>
       </c>
       <c r="B133" t="n">
-        <v>1.86896658968343</v>
+        <v>-0.01769425317638542</v>
       </c>
       <c r="C133" t="n">
-        <v>1.238040205645196</v>
+        <v>0.005252687748154107</v>
       </c>
       <c r="D133" t="n">
-        <v>0.7067069092168938</v>
+        <v>0.0242779312264208</v>
       </c>
       <c r="E133" t="n">
-        <v>0.3128940130435202</v>
+        <v>0.003735401199516626</v>
       </c>
       <c r="F133" t="n">
-        <v>0.2448272191748622</v>
+        <v>-0.02151379430312801</v>
       </c>
     </row>
     <row r="134">
@@ -3097,19 +3097,19 @@
         <v>45826</v>
       </c>
       <c r="B134" t="n">
-        <v>-0.4625085509628304</v>
+        <v>0.05379218015006391</v>
       </c>
       <c r="C134" t="n">
-        <v>0.05660666380264861</v>
+        <v>-0.02481417548764166</v>
       </c>
       <c r="D134" t="n">
-        <v>0.4955783754646211</v>
+        <v>0.07341962246100557</v>
       </c>
       <c r="E134" t="n">
-        <v>1.424933311371405</v>
+        <v>-0.03307633490085932</v>
       </c>
       <c r="F134" t="n">
-        <v>1.475085871054479</v>
+        <v>-0.002391815739540746</v>
       </c>
     </row>
     <row r="135">
@@ -3117,19 +3117,19 @@
         <v>45828</v>
       </c>
       <c r="B135" t="n">
-        <v>-1.299579864781375</v>
+        <v>0.04807624477599784</v>
       </c>
       <c r="C135" t="n">
-        <v>1.218687167001992</v>
+        <v>-0.03960980590543746</v>
       </c>
       <c r="D135" t="n">
-        <v>-1.292927391264772</v>
+        <v>0.04114479265267237</v>
       </c>
       <c r="E135" t="n">
-        <v>-1.329896711428594</v>
+        <v>-0.02172868076213724</v>
       </c>
       <c r="F135" t="n">
-        <v>0.5522427407275387</v>
+        <v>0.009954219280280055</v>
       </c>
     </row>
     <row r="136">
@@ -3137,19 +3137,19 @@
         <v>45831</v>
       </c>
       <c r="B136" t="n">
-        <v>3.966316056216108</v>
+        <v>-0.1146550835482331</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.2285924757450426</v>
+        <v>0.07926498560760395</v>
       </c>
       <c r="D136" t="n">
-        <v>0.9977647142743425</v>
+        <v>0.01608002234922475</v>
       </c>
       <c r="E136" t="n">
-        <v>0.4940912466302803</v>
+        <v>0.02630405169263614</v>
       </c>
       <c r="F136" t="n">
-        <v>0.01265583555484007</v>
+        <v>0.01453212842918646</v>
       </c>
     </row>
     <row r="137">
@@ -3157,19 +3157,19 @@
         <v>45832</v>
       </c>
       <c r="B137" t="n">
-        <v>-1.006545083876223</v>
+        <v>0.02907384690406389</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.1757633791009197</v>
+        <v>0.04011960536664597</v>
       </c>
       <c r="D137" t="n">
-        <v>-0.1004376317878339</v>
+        <v>0.004807958082395813</v>
       </c>
       <c r="E137" t="n">
-        <v>-0.278149641558912</v>
+        <v>-0.006509744008443522</v>
       </c>
       <c r="F137" t="n">
-        <v>-0.7175585747699866</v>
+        <v>0.005569975575788038</v>
       </c>
     </row>
     <row r="138">
@@ -3177,19 +3177,19 @@
         <v>45833</v>
       </c>
       <c r="B138" t="n">
-        <v>1.298866359812219</v>
+        <v>-0.04148892142992826</v>
       </c>
       <c r="C138" t="n">
-        <v>0.6500939457580648</v>
+        <v>0.01575080593825047</v>
       </c>
       <c r="D138" t="n">
-        <v>-0.4721936145341228</v>
+        <v>0.02081641250406971</v>
       </c>
       <c r="E138" t="n">
-        <v>-0.2250389961939651</v>
+        <v>0.006447155208175202</v>
       </c>
       <c r="F138" t="n">
-        <v>-0.1501977542590983</v>
+        <v>0.000272424720140168</v>
       </c>
     </row>
     <row r="139">
@@ -3197,19 +3197,19 @@
         <v>45834</v>
       </c>
       <c r="B139" t="n">
-        <v>3.394723693122898</v>
+        <v>-0.1149455542085683</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.5750432135661621</v>
+        <v>0.06342842738694265</v>
       </c>
       <c r="D139" t="n">
-        <v>1.562376678983916</v>
+        <v>-0.01001277328657561</v>
       </c>
       <c r="E139" t="n">
-        <v>0.1437522571233902</v>
+        <v>-0.008436930477020571</v>
       </c>
       <c r="F139" t="n">
-        <v>0.5897286177370009</v>
+        <v>0.003239319241208839</v>
       </c>
     </row>
     <row r="140">
@@ -3217,19 +3217,19 @@
         <v>45835</v>
       </c>
       <c r="B140" t="n">
-        <v>2.277640572177042</v>
+        <v>-0.1123005645379645</v>
       </c>
       <c r="C140" t="n">
-        <v>0.6207783518012464</v>
+        <v>0.02394954845619365</v>
       </c>
       <c r="D140" t="n">
-        <v>0.322574913494643</v>
+        <v>0.003679924653727166</v>
       </c>
       <c r="E140" t="n">
-        <v>0.1899021982858818</v>
+        <v>0.006968658806405351</v>
       </c>
       <c r="F140" t="n">
-        <v>-0.1589462336499265</v>
+        <v>-0.008191688389877523</v>
       </c>
     </row>
     <row r="141">
@@ -3237,19 +3237,19 @@
         <v>45838</v>
       </c>
       <c r="B141" t="n">
-        <v>-0.7099423812016167</v>
+        <v>0.009960473745093021</v>
       </c>
       <c r="C141" t="n">
-        <v>-1.425876222561707</v>
+        <v>0.0733607122467415</v>
       </c>
       <c r="D141" t="n">
-        <v>-0.3814965888723092</v>
+        <v>0.03025379198188891</v>
       </c>
       <c r="E141" t="n">
-        <v>-0.39236155108568</v>
+        <v>-0.007352461345696874</v>
       </c>
       <c r="F141" t="n">
-        <v>1.014032489194853</v>
+        <v>0.01679499702074878</v>
       </c>
     </row>
     <row r="142">
@@ -3257,19 +3257,19 @@
         <v>45839</v>
       </c>
       <c r="B142" t="n">
-        <v>1.891236282292674</v>
+        <v>-0.04872476216290732</v>
       </c>
       <c r="C142" t="n">
-        <v>-0.2503732148754527</v>
+        <v>0.1062553913242591</v>
       </c>
       <c r="D142" t="n">
-        <v>0.9662357621919551</v>
+        <v>0.04388638777683214</v>
       </c>
       <c r="E142" t="n">
-        <v>0.8257286096737547</v>
+        <v>0.02064053325614592</v>
       </c>
       <c r="F142" t="n">
-        <v>0.639952659387912</v>
+        <v>0.004706924310000225</v>
       </c>
     </row>
     <row r="143">
@@ -3277,19 +3277,19 @@
         <v>45840</v>
       </c>
       <c r="B143" t="n">
-        <v>1.503389925694478</v>
+        <v>-0.1102317639391638</v>
       </c>
       <c r="C143" t="n">
-        <v>0.8717558758192333</v>
+        <v>0.05814867256635014</v>
       </c>
       <c r="D143" t="n">
-        <v>-1.344963378417168</v>
+        <v>-0.0001076094149107938</v>
       </c>
       <c r="E143" t="n">
-        <v>-0.601753529097058</v>
+        <v>0.03757958515993716</v>
       </c>
       <c r="F143" t="n">
-        <v>-1.342313378756129</v>
+        <v>0.01655668898976077</v>
       </c>
     </row>
     <row r="144">
@@ -3297,19 +3297,19 @@
         <v>45841</v>
       </c>
       <c r="B144" t="n">
-        <v>0.7976457015634488</v>
+        <v>-0.0917792477279579</v>
       </c>
       <c r="C144" t="n">
-        <v>-2.206432518303699</v>
+        <v>0.01392282615646756</v>
       </c>
       <c r="D144" t="n">
-        <v>-1.09072224363674</v>
+        <v>-0.006545004524336076</v>
       </c>
       <c r="E144" t="n">
-        <v>0.7925072225972883</v>
+        <v>0.01216719691957874</v>
       </c>
       <c r="F144" t="n">
-        <v>0.2304281828643151</v>
+        <v>0.01946587240334738</v>
       </c>
     </row>
     <row r="145">
@@ -3317,19 +3317,19 @@
         <v>45842</v>
       </c>
       <c r="B145" t="n">
-        <v>9.462284055037781</v>
+        <v>-0.4297111819554323</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.8150410726082197</v>
+        <v>0.0457054328860316</v>
       </c>
       <c r="D145" t="n">
-        <v>0.6026325261723526</v>
+        <v>-0.07342573327783149</v>
       </c>
       <c r="E145" t="n">
-        <v>-0.2815257818652042</v>
+        <v>0.007936214229150255</v>
       </c>
       <c r="F145" t="n">
-        <v>-0.1641820382509548</v>
+        <v>0.0003520091838210883</v>
       </c>
     </row>
     <row r="146">
@@ -3337,19 +3337,19 @@
         <v>45845</v>
       </c>
       <c r="B146" t="n">
-        <v>4.652032038423202</v>
+        <v>-0.2462496070745798</v>
       </c>
       <c r="C146" t="n">
-        <v>3.88770085625519</v>
+        <v>-0.08450295086457073</v>
       </c>
       <c r="D146" t="n">
-        <v>-0.172350288996139</v>
+        <v>0.07652117976202559</v>
       </c>
       <c r="E146" t="n">
-        <v>0.4743007591017552</v>
+        <v>-0.003975760946972229</v>
       </c>
       <c r="F146" t="n">
-        <v>1.013176264615137</v>
+        <v>-0.01687041452624888</v>
       </c>
     </row>
     <row r="147">
@@ -3357,19 +3357,19 @@
         <v>45846</v>
       </c>
       <c r="B147" t="n">
-        <v>0.3802934526488015</v>
+        <v>-0.1053670284103708</v>
       </c>
       <c r="C147" t="n">
-        <v>-0.1179731894687616</v>
+        <v>-0.01878352727929859</v>
       </c>
       <c r="D147" t="n">
-        <v>0.2941672201471269</v>
+        <v>0.02995725347684069</v>
       </c>
       <c r="E147" t="n">
-        <v>0.7041096398315565</v>
+        <v>0.004380168121765697</v>
       </c>
       <c r="F147" t="n">
-        <v>0.3383366447024953</v>
+        <v>-0.01042018257582497</v>
       </c>
     </row>
     <row r="148">
@@ -3377,19 +3377,19 @@
         <v>45847</v>
       </c>
       <c r="B148" t="n">
-        <v>2.037804062523072</v>
+        <v>-0.2030312418719014</v>
       </c>
       <c r="C148" t="n">
-        <v>1.857535957279651</v>
+        <v>-0.08534698557126939</v>
       </c>
       <c r="D148" t="n">
-        <v>-1.039797463132315</v>
+        <v>0.02231298843578986</v>
       </c>
       <c r="E148" t="n">
-        <v>-0.6328637541391641</v>
+        <v>0.004919629711061753</v>
       </c>
       <c r="F148" t="n">
-        <v>-0.3698898097971827</v>
+        <v>-0.02081325810588266</v>
       </c>
     </row>
     <row r="149">
@@ -3397,19 +3397,19 @@
         <v>45848</v>
       </c>
       <c r="B149" t="n">
-        <v>-4.563015470806369</v>
+        <v>0.03353108042481119</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.3201415454991148</v>
+        <v>-0.03961325696583141</v>
       </c>
       <c r="D149" t="n">
-        <v>-1.496444838863825</v>
+        <v>-0.0299969849913362</v>
       </c>
       <c r="E149" t="n">
-        <v>-1.81207960269282</v>
+        <v>-0.01296089491121501</v>
       </c>
       <c r="F149" t="n">
-        <v>-0.385462248872953</v>
+        <v>0.02063659293241146</v>
       </c>
     </row>
     <row r="150">
@@ -3417,19 +3417,19 @@
         <v>45849</v>
       </c>
       <c r="B150" t="n">
-        <v>3.479182408988788</v>
+        <v>-0.1629803293788029</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.02328466854994074</v>
+        <v>-0.0822327257426984</v>
       </c>
       <c r="D150" t="n">
-        <v>-0.2476097987170431</v>
+        <v>0.02345852158310824</v>
       </c>
       <c r="E150" t="n">
-        <v>0.9811415007985556</v>
+        <v>-0.01204835868706397</v>
       </c>
       <c r="F150" t="n">
-        <v>0.4937701166214419</v>
+        <v>-0.006544037620460528</v>
       </c>
     </row>
     <row r="151">
@@ -3437,19 +3437,19 @@
         <v>45852</v>
       </c>
       <c r="B151" t="n">
-        <v>2.190393313878433</v>
+        <v>-0.1388112513516579</v>
       </c>
       <c r="C151" t="n">
-        <v>2.878416891350483</v>
+        <v>-0.05562947693151182</v>
       </c>
       <c r="D151" t="n">
-        <v>-1.95630197945238</v>
+        <v>0.04906979618568951</v>
       </c>
       <c r="E151" t="n">
-        <v>0.4820266709589027</v>
+        <v>0.04635765714681387</v>
       </c>
       <c r="F151" t="n">
-        <v>-2.01320189421009</v>
+        <v>-0.0004839672612308358</v>
       </c>
     </row>
     <row r="152">
@@ -3457,19 +3457,19 @@
         <v>45853</v>
       </c>
       <c r="B152" t="n">
-        <v>-0.8199398360856824</v>
+        <v>0.000329044685442042</v>
       </c>
       <c r="C152" t="n">
-        <v>0.6155633127328218</v>
+        <v>-0.007319294065719922</v>
       </c>
       <c r="D152" t="n">
-        <v>-0.0005438756568566738</v>
+        <v>-0.01724457363613857</v>
       </c>
       <c r="E152" t="n">
-        <v>-0.1737201267329165</v>
+        <v>0.02914543544968559</v>
       </c>
       <c r="F152" t="n">
-        <v>-0.7394316826244322</v>
+        <v>-0.003220007968559271</v>
       </c>
     </row>
     <row r="153">
@@ -3477,19 +3477,19 @@
         <v>45854</v>
       </c>
       <c r="B153" t="n">
-        <v>-1.773587833392475</v>
+        <v>0.03789057554088147</v>
       </c>
       <c r="C153" t="n">
-        <v>0.200233969019086</v>
+        <v>-0.01863445809133131</v>
       </c>
       <c r="D153" t="n">
-        <v>-0.5422392075247806</v>
+        <v>-0.003579015039623878</v>
       </c>
       <c r="E153" t="n">
-        <v>-0.7250632652643012</v>
+        <v>-0.007263886441604686</v>
       </c>
       <c r="F153" t="n">
-        <v>-0.8317853680118312</v>
+        <v>0.006835355569356058</v>
       </c>
     </row>
     <row r="154">
@@ -3497,19 +3497,19 @@
         <v>45855</v>
       </c>
       <c r="B154" t="n">
-        <v>-1.110417481093018</v>
+        <v>0.05282155337434827</v>
       </c>
       <c r="C154" t="n">
-        <v>0.1053186481964334</v>
+        <v>0.03676759102529393</v>
       </c>
       <c r="D154" t="n">
-        <v>0.5571126846357147</v>
+        <v>0.0149713763517428</v>
       </c>
       <c r="E154" t="n">
-        <v>-0.10238381991239</v>
+        <v>0.004817583851706219</v>
       </c>
       <c r="F154" t="n">
-        <v>0.2523615381767466</v>
+        <v>-0.003353916835594013</v>
       </c>
     </row>
     <row r="155">
@@ -3517,19 +3517,19 @@
         <v>45856</v>
       </c>
       <c r="B155" t="n">
-        <v>-0.3173562694420948</v>
+        <v>-0.0009852775463075466</v>
       </c>
       <c r="C155" t="n">
-        <v>0.6557122003143148</v>
+        <v>-0.01127336017909971</v>
       </c>
       <c r="D155" t="n">
-        <v>-1.079276786963434</v>
+        <v>0.01930873427337111</v>
       </c>
       <c r="E155" t="n">
-        <v>0.5149524453224255</v>
+        <v>0.02520239069581338</v>
       </c>
       <c r="F155" t="n">
-        <v>-0.8267263044530484</v>
+        <v>-0.006814380219772822</v>
       </c>
     </row>
     <row r="156">
@@ -3537,19 +3537,19 @@
         <v>45859</v>
       </c>
       <c r="B156" t="n">
-        <v>0.4889779382766768</v>
+        <v>0.01032174159694871</v>
       </c>
       <c r="C156" t="n">
-        <v>-2.669303273179724</v>
+        <v>0.06262504611352789</v>
       </c>
       <c r="D156" t="n">
-        <v>0.6758111243373117</v>
+        <v>-0.03661319465042434</v>
       </c>
       <c r="E156" t="n">
-        <v>0.6589414296032517</v>
+        <v>0.01589274717269572</v>
       </c>
       <c r="F156" t="n">
-        <v>0.8910273229364276</v>
+        <v>0.01612862177534729</v>
       </c>
     </row>
     <row r="157">
@@ -3557,19 +3557,19 @@
         <v>45860</v>
       </c>
       <c r="B157" t="n">
-        <v>0.1068829103345189</v>
+        <v>0.07855246348782768</v>
       </c>
       <c r="C157" t="n">
-        <v>0.08924823154445588</v>
+        <v>0.05387983292322841</v>
       </c>
       <c r="D157" t="n">
-        <v>1.244522643558519</v>
+        <v>0.03997864373472816</v>
       </c>
       <c r="E157" t="n">
-        <v>1.266076876036555</v>
+        <v>0.03143035644861792</v>
       </c>
       <c r="F157" t="n">
-        <v>0.9530387850047897</v>
+        <v>0.0009776752534238365</v>
       </c>
     </row>
     <row r="158">
@@ -3577,19 +3577,19 @@
         <v>45861</v>
       </c>
       <c r="B158" t="n">
-        <v>-0.1389037398526872</v>
+        <v>-0.004640039078549864</v>
       </c>
       <c r="C158" t="n">
-        <v>-2.866206747871169</v>
+        <v>0.04728544788419975</v>
       </c>
       <c r="D158" t="n">
-        <v>-0.1184071842336026</v>
+        <v>-0.02218234629396426</v>
       </c>
       <c r="E158" t="n">
-        <v>-0.1493417770695311</v>
+        <v>0.02027630638677614</v>
       </c>
       <c r="F158" t="n">
-        <v>0.6225512971246367</v>
+        <v>0.019641716855683</v>
       </c>
     </row>
     <row r="159">
@@ -3597,19 +3597,19 @@
         <v>45862</v>
       </c>
       <c r="B159" t="n">
-        <v>4.313782215036052</v>
+        <v>-0.1637727984295882</v>
       </c>
       <c r="C159" t="n">
-        <v>2.34230018864382</v>
+        <v>-0.02476872277778127</v>
       </c>
       <c r="D159" t="n">
-        <v>-0.3563783072941797</v>
+        <v>0.02849372193502014</v>
       </c>
       <c r="E159" t="n">
-        <v>-0.3715076991857683</v>
+        <v>-0.007930598514923542</v>
       </c>
       <c r="F159" t="n">
-        <v>-0.463915630087812</v>
+        <v>0.005379183461917267</v>
       </c>
     </row>
     <row r="160">
@@ -3617,19 +3617,19 @@
         <v>45863</v>
       </c>
       <c r="B160" t="n">
-        <v>3.653326587663688</v>
+        <v>-0.141911365228346</v>
       </c>
       <c r="C160" t="n">
-        <v>1.722386237735603</v>
+        <v>-0.05484945321300182</v>
       </c>
       <c r="D160" t="n">
-        <v>-0.307702444155059</v>
+        <v>0.07488843715381573</v>
       </c>
       <c r="E160" t="n">
-        <v>1.380055641170995</v>
+        <v>0.01048034287784956</v>
       </c>
       <c r="F160" t="n">
-        <v>0.8081681052348633</v>
+        <v>-0.01281835538765531</v>
       </c>
     </row>
     <row r="161">
@@ -3637,19 +3637,19 @@
         <v>45866</v>
       </c>
       <c r="B161" t="n">
-        <v>2.77161924504975</v>
+        <v>-0.1953000292354294</v>
       </c>
       <c r="C161" t="n">
-        <v>2.338709035661615</v>
+        <v>-0.07551480669429139</v>
       </c>
       <c r="D161" t="n">
-        <v>-1.91049978146904</v>
+        <v>0.04753776378934382</v>
       </c>
       <c r="E161" t="n">
-        <v>0.1551244292038607</v>
+        <v>0.02592974471641733</v>
       </c>
       <c r="F161" t="n">
-        <v>-0.9102032679459233</v>
+        <v>-0.0227076934419403</v>
       </c>
     </row>
     <row r="162">
@@ -3657,19 +3657,19 @@
         <v>45867</v>
       </c>
       <c r="B162" t="n">
-        <v>4.533825585574937</v>
+        <v>-0.2521765909832155</v>
       </c>
       <c r="C162" t="n">
-        <v>0.4136024522429413</v>
+        <v>-0.04441149732013438</v>
       </c>
       <c r="D162" t="n">
-        <v>0.07933610921190688</v>
+        <v>-0.0009573699448156266</v>
       </c>
       <c r="E162" t="n">
-        <v>0.3345068251979744</v>
+        <v>0.01468736833456952</v>
       </c>
       <c r="F162" t="n">
-        <v>0.1607512046736038</v>
+        <v>-0.002038597029062646</v>
       </c>
     </row>
     <row r="163">
@@ -3677,19 +3677,19 @@
         <v>45868</v>
       </c>
       <c r="B163" t="n">
-        <v>-10.37578554875634</v>
+        <v>0.2040620505075545</v>
       </c>
       <c r="C163" t="n">
-        <v>-3.331679875620452</v>
+        <v>-0.1018418193076225</v>
       </c>
       <c r="D163" t="n">
-        <v>-1.243544452700423</v>
+        <v>-0.02386774762904318</v>
       </c>
       <c r="E163" t="n">
-        <v>-0.3379137638876234</v>
+        <v>-0.013711027750585</v>
       </c>
       <c r="F163" t="n">
-        <v>0.7424114467865067</v>
+        <v>0.01539951266459866</v>
       </c>
     </row>
     <row r="164">
@@ -3697,19 +3697,19 @@
         <v>45869</v>
       </c>
       <c r="B164" t="n">
-        <v>-2.998054824407309</v>
+        <v>0.09415615423728331</v>
       </c>
       <c r="C164" t="n">
-        <v>0.6218938769889112</v>
+        <v>-0.07131289913149584</v>
       </c>
       <c r="D164" t="n">
-        <v>-0.6836411332212248</v>
+        <v>-0.004850051761113514</v>
       </c>
       <c r="E164" t="n">
-        <v>-2.015631633535889</v>
+        <v>-0.02939898296613329</v>
       </c>
       <c r="F164" t="n">
-        <v>0.8660235380118391</v>
+        <v>0.01415366720654586</v>
       </c>
     </row>
     <row r="165">
@@ -3717,19 +3717,19 @@
         <v>45873</v>
       </c>
       <c r="B165" t="n">
-        <v>-4.023300671073682</v>
+        <v>0.1397577650626506</v>
       </c>
       <c r="C165" t="n">
-        <v>-1.295862615632176</v>
+        <v>-0.05727950941061454</v>
       </c>
       <c r="D165" t="n">
-        <v>-1.371335310934611</v>
+        <v>-0.01972481913566419</v>
       </c>
       <c r="E165" t="n">
-        <v>1.373941480013158</v>
+        <v>0.003699981435698718</v>
       </c>
       <c r="F165" t="n">
-        <v>-0.3840747107885353</v>
+        <v>0.02632588840481538</v>
       </c>
     </row>
     <row r="166">
@@ -3737,19 +3737,19 @@
         <v>45874</v>
       </c>
       <c r="B166" t="n">
-        <v>-2.464922784072057</v>
+        <v>0.1891095739951157</v>
       </c>
       <c r="C166" t="n">
-        <v>-0.6334331950645096</v>
+        <v>-0.009092319996190219</v>
       </c>
       <c r="D166" t="n">
-        <v>0.08720227981904918</v>
+        <v>0.01178440501371838</v>
       </c>
       <c r="E166" t="n">
-        <v>0.6506894866819629</v>
+        <v>-0.0001757220324269464</v>
       </c>
       <c r="F166" t="n">
-        <v>0.831634270795449</v>
+        <v>0.02484314552793844</v>
       </c>
     </row>
     <row r="167">
@@ -3757,19 +3757,19 @@
         <v>45875</v>
       </c>
       <c r="B167" t="n">
-        <v>-2.103874239373782</v>
+        <v>0.2010328479383444</v>
       </c>
       <c r="C167" t="n">
-        <v>-2.140696158757645</v>
+        <v>0.0332724406287143</v>
       </c>
       <c r="D167" t="n">
-        <v>0.2367011407547828</v>
+        <v>-0.01205986616679008</v>
       </c>
       <c r="E167" t="n">
-        <v>0.6858918432683083</v>
+        <v>0.03275541727105186</v>
       </c>
       <c r="F167" t="n">
-        <v>0.5666097009844461</v>
+        <v>0.02384889411001621</v>
       </c>
     </row>
     <row r="168">
@@ -3777,19 +3777,19 @@
         <v>45876</v>
       </c>
       <c r="B168" t="n">
-        <v>-0.6085475475171371</v>
+        <v>0.1143829670700692</v>
       </c>
       <c r="C168" t="n">
-        <v>-1.730546348167835</v>
+        <v>0.01568680075955955</v>
       </c>
       <c r="D168" t="n">
-        <v>0.7445880046391035</v>
+        <v>0.0250825156670119</v>
       </c>
       <c r="E168" t="n">
-        <v>0.5957040012880358</v>
+        <v>-0.01786008876053279</v>
       </c>
       <c r="F168" t="n">
-        <v>1.135397280051736</v>
+        <v>0.008131473013394499</v>
       </c>
     </row>
     <row r="169">
@@ -3797,19 +3797,19 @@
         <v>45877</v>
       </c>
       <c r="B169" t="n">
-        <v>1.637932504809495</v>
+        <v>0.04588093638143429</v>
       </c>
       <c r="C169" t="n">
-        <v>1.979157278488256</v>
+        <v>0.04721940158527161</v>
       </c>
       <c r="D169" t="n">
-        <v>0.468291030320013</v>
+        <v>0.06821547606806128</v>
       </c>
       <c r="E169" t="n">
-        <v>-0.3951835803821913</v>
+        <v>-0.006286545243329094</v>
       </c>
       <c r="F169" t="n">
-        <v>0.2844929387042723</v>
+        <v>0.008120333143635182</v>
       </c>
     </row>
     <row r="170">
@@ -3817,19 +3817,19 @@
         <v>45880</v>
       </c>
       <c r="B170" t="n">
-        <v>1.832489709126789</v>
+        <v>-0.01995920627469302</v>
       </c>
       <c r="C170" t="n">
-        <v>0.3215418106595467</v>
+        <v>0.03562079595701879</v>
       </c>
       <c r="D170" t="n">
-        <v>0.6932762058116699</v>
+        <v>-0.01050823077190445</v>
       </c>
       <c r="E170" t="n">
-        <v>-0.4358480491585668</v>
+        <v>0.0001793961628317456</v>
       </c>
       <c r="F170" t="n">
-        <v>-0.1806407807274298</v>
+        <v>-0.003443147342093183</v>
       </c>
     </row>
     <row r="171">
@@ -3837,19 +3837,19 @@
         <v>45881</v>
       </c>
       <c r="B171" t="n">
-        <v>-1.898060788485386</v>
+        <v>0.08421047779785745</v>
       </c>
       <c r="C171" t="n">
-        <v>-2.808200774886263</v>
+        <v>0.03715193754820181</v>
       </c>
       <c r="D171" t="n">
-        <v>0.08092085226512076</v>
+        <v>-0.02708983421703774</v>
       </c>
       <c r="E171" t="n">
-        <v>1.353822233937632</v>
+        <v>-0.002247300723622649</v>
       </c>
       <c r="F171" t="n">
-        <v>0.8420023750832766</v>
+        <v>0.04386446673596909</v>
       </c>
     </row>
     <row r="172">
@@ -3857,19 +3857,19 @@
         <v>45882</v>
       </c>
       <c r="B172" t="n">
-        <v>2.127343704444425</v>
+        <v>-0.04527901791613874</v>
       </c>
       <c r="C172" t="n">
-        <v>1.183600942092655</v>
+        <v>0.03417338216892134</v>
       </c>
       <c r="D172" t="n">
-        <v>-0.301333780600338</v>
+        <v>0.05553150337925793</v>
       </c>
       <c r="E172" t="n">
-        <v>-0.4406517249138608</v>
+        <v>-0.01614557880949686</v>
       </c>
       <c r="F172" t="n">
-        <v>0.3577780751716153</v>
+        <v>0.02479158628605882</v>
       </c>
     </row>
     <row r="173">
@@ -3877,19 +3877,19 @@
         <v>45883</v>
       </c>
       <c r="B173" t="n">
-        <v>-2.003330058537357</v>
+        <v>0.05952841977620652</v>
       </c>
       <c r="C173" t="n">
-        <v>0.2837715275354061</v>
+        <v>-0.001251943685276165</v>
       </c>
       <c r="D173" t="n">
-        <v>-0.9439196442383893</v>
+        <v>0.002074094156613722</v>
       </c>
       <c r="E173" t="n">
-        <v>-1.524519230499025</v>
+        <v>-0.02474632491783459</v>
       </c>
       <c r="F173" t="n">
-        <v>0.1875720381876195</v>
+        <v>0.02534824189554439</v>
       </c>
     </row>
     <row r="174">
@@ -3897,19 +3897,19 @@
         <v>45884</v>
       </c>
       <c r="B174" t="n">
-        <v>1.542618460769455</v>
+        <v>0.005514894803715128</v>
       </c>
       <c r="C174" t="n">
-        <v>2.322493788674824</v>
+        <v>0.02403212827543181</v>
       </c>
       <c r="D174" t="n">
-        <v>1.212637716145299</v>
+        <v>0.02728409150747388</v>
       </c>
       <c r="E174" t="n">
-        <v>0.3189264591522006</v>
+        <v>0.02293311200238939</v>
       </c>
       <c r="F174" t="n">
-        <v>-0.2779961627111779</v>
+        <v>0.005870452949354818</v>
       </c>
     </row>
     <row r="175">
@@ -3917,19 +3917,19 @@
         <v>45887</v>
       </c>
       <c r="B175" t="n">
-        <v>4.485139529388952</v>
+        <v>-0.1775282651888689</v>
       </c>
       <c r="C175" t="n">
-        <v>0.5553274212000895</v>
+        <v>-0.03478125640010356</v>
       </c>
       <c r="D175" t="n">
-        <v>-1.195357948276786</v>
+        <v>0.03614645326236954</v>
       </c>
       <c r="E175" t="n">
-        <v>-0.08097963970829608</v>
+        <v>-0.01436878173623157</v>
       </c>
       <c r="F175" t="n">
-        <v>0.3061873300602567</v>
+        <v>0.01958099259887471</v>
       </c>
     </row>
     <row r="176">
@@ -3937,19 +3937,19 @@
         <v>45888</v>
       </c>
       <c r="B176" t="n">
-        <v>-4.1539929321573</v>
+        <v>0.1226067663117323</v>
       </c>
       <c r="C176" t="n">
-        <v>1.353468241792646</v>
+        <v>-0.02674166836903335</v>
       </c>
       <c r="D176" t="n">
-        <v>-2.070720313000577</v>
+        <v>0.03123953510438938</v>
       </c>
       <c r="E176" t="n">
-        <v>-1.978178314221555</v>
+        <v>-0.01004785275715</v>
       </c>
       <c r="F176" t="n">
-        <v>-0.3169833486966969</v>
+        <v>0.04449577559698549</v>
       </c>
     </row>
     <row r="177">
@@ -3957,19 +3957,19 @@
         <v>45889</v>
       </c>
       <c r="B177" t="n">
-        <v>3.482471997016169</v>
+        <v>-0.1688057145869944</v>
       </c>
       <c r="C177" t="n">
-        <v>0.6778117630339888</v>
+        <v>-0.0464989532806234</v>
       </c>
       <c r="D177" t="n">
-        <v>-1.64512051238302</v>
+        <v>0.01445769238893465</v>
       </c>
       <c r="E177" t="n">
-        <v>-1.213968558854701</v>
+        <v>-0.02754071926286236</v>
       </c>
       <c r="F177" t="n">
-        <v>-0.234113777875757</v>
+        <v>0.02993769485998949</v>
       </c>
     </row>
     <row r="178">
@@ -3977,19 +3977,19 @@
         <v>45890</v>
       </c>
       <c r="B178" t="n">
-        <v>-0.08799063462428967</v>
+        <v>-0.1196055434115626</v>
       </c>
       <c r="C178" t="n">
-        <v>-0.7604453440621876</v>
+        <v>-0.0765906624585245</v>
       </c>
       <c r="D178" t="n">
-        <v>-2.715628602618908</v>
+        <v>0.01871629117728072</v>
       </c>
       <c r="E178" t="n">
-        <v>0.2726489602182005</v>
+        <v>0.0005463945028712801</v>
       </c>
       <c r="F178" t="n">
-        <v>-0.9677010569603159</v>
+        <v>0.02542386881564783</v>
       </c>
     </row>
     <row r="179">
@@ -3997,19 +3997,19 @@
         <v>45891</v>
       </c>
       <c r="B179" t="n">
-        <v>-2.838736568920916</v>
+        <v>0.04687389917074106</v>
       </c>
       <c r="C179" t="n">
-        <v>-3.881604998464985</v>
+        <v>0.002466274413556564</v>
       </c>
       <c r="D179" t="n">
-        <v>0.8337665651579681</v>
+        <v>-0.04594182232347826</v>
       </c>
       <c r="E179" t="n">
-        <v>0.6376769460612531</v>
+        <v>-0.02422284756050365</v>
       </c>
       <c r="F179" t="n">
-        <v>0.8733313786346675</v>
+        <v>0.04688136936603741</v>
       </c>
     </row>
     <row r="180">
@@ -4017,19 +4017,19 @@
         <v>45894</v>
       </c>
       <c r="B180" t="n">
-        <v>5.961907813686081</v>
+        <v>-0.2195010622732331</v>
       </c>
       <c r="C180" t="n">
-        <v>1.492981922817761</v>
+        <v>-0.02552347018971561</v>
       </c>
       <c r="D180" t="n">
-        <v>0.8757296554067637</v>
+        <v>0.006013468192133378</v>
       </c>
       <c r="E180" t="n">
-        <v>-0.5953469684573109</v>
+        <v>-0.05489607074363075</v>
       </c>
       <c r="F180" t="n">
-        <v>0.2024019759558068</v>
+        <v>0.01621998407670412</v>
       </c>
     </row>
     <row r="181">
@@ -4037,19 +4037,19 @@
         <v>45895</v>
       </c>
       <c r="B181" t="n">
-        <v>5.824674441863754</v>
+        <v>-0.2992086068637245</v>
       </c>
       <c r="C181" t="n">
-        <v>1.971537472408926</v>
+        <v>-0.04665098177248037</v>
       </c>
       <c r="D181" t="n">
-        <v>-0.9526514534011499</v>
+        <v>0.03187503244925383</v>
       </c>
       <c r="E181" t="n">
-        <v>0.1554628417714699</v>
+        <v>0.01437721869446152</v>
       </c>
       <c r="F181" t="n">
-        <v>-0.3682586123257674</v>
+        <v>0.01239069069752749</v>
       </c>
     </row>
     <row r="182">
@@ -4057,19 +4057,19 @@
         <v>45896</v>
       </c>
       <c r="B182" t="n">
-        <v>2.971077222322296</v>
+        <v>-0.126498456722697</v>
       </c>
       <c r="C182" t="n">
-        <v>1.411135416190552</v>
+        <v>0.01327445804144473</v>
       </c>
       <c r="D182" t="n">
-        <v>0.7911020294157025</v>
+        <v>0.03290757571158665</v>
       </c>
       <c r="E182" t="n">
-        <v>0.1002362484351063</v>
+        <v>-0.01107702578391296</v>
       </c>
       <c r="F182" t="n">
-        <v>0.7743627369368333</v>
+        <v>0.009039111432559593</v>
       </c>
     </row>
     <row r="183">
@@ -4077,19 +4077,19 @@
         <v>45897</v>
       </c>
       <c r="B183" t="n">
-        <v>0.2538022158557318</v>
+        <v>-0.14375631507178</v>
       </c>
       <c r="C183" t="n">
-        <v>-4.041090871545534</v>
+        <v>-0.004493374541719917</v>
       </c>
       <c r="D183" t="n">
-        <v>0.3240309741232412</v>
+        <v>-0.05446040890809383</v>
       </c>
       <c r="E183" t="n">
-        <v>-0.5581094235485046</v>
+        <v>-0.02691224549274295</v>
       </c>
       <c r="F183" t="n">
-        <v>0.4582979986779774</v>
+        <v>0.02293610725910928</v>
       </c>
     </row>
     <row r="184">
@@ -4097,19 +4097,19 @@
         <v>45898</v>
       </c>
       <c r="B184" t="n">
-        <v>5.893527119455492</v>
+        <v>-0.3603264531526427</v>
       </c>
       <c r="C184" t="n">
-        <v>-1.495666784677624</v>
+        <v>0.00959676806237824</v>
       </c>
       <c r="D184" t="n">
-        <v>-0.1902164750219716</v>
+        <v>-0.04033345467085145</v>
       </c>
       <c r="E184" t="n">
-        <v>-0.4166697891339176</v>
+        <v>0.01226350847914576</v>
       </c>
       <c r="F184" t="n">
-        <v>-0.0631093328817636</v>
+        <v>0.009027643365107113</v>
       </c>
     </row>
     <row r="185">
@@ -4117,19 +4117,19 @@
         <v>45901</v>
       </c>
       <c r="B185" t="n">
-        <v>6.035549210558008</v>
+        <v>-0.3783446114104213</v>
       </c>
       <c r="C185" t="n">
-        <v>-0.126358692172652</v>
+        <v>-0.03273025645875193</v>
       </c>
       <c r="D185" t="n">
-        <v>-1.820853825836144</v>
+        <v>0.01117976749331198</v>
       </c>
       <c r="E185" t="n">
-        <v>0.7042126987393491</v>
+        <v>0.03269647600008771</v>
       </c>
       <c r="F185" t="n">
-        <v>0.1599124768704739</v>
+        <v>0.01096239779816903</v>
       </c>
     </row>
     <row r="186">
@@ -4137,19 +4137,19 @@
         <v>45902</v>
       </c>
       <c r="B186" t="n">
-        <v>-2.748042584160815</v>
+        <v>-0.1182342852655772</v>
       </c>
       <c r="C186" t="n">
-        <v>-0.9791953457372031</v>
+        <v>-0.04345705398248192</v>
       </c>
       <c r="D186" t="n">
-        <v>-3.838494985110863</v>
+        <v>-0.02404966729068258</v>
       </c>
       <c r="E186" t="n">
-        <v>-0.5511270471870546</v>
+        <v>0.0162792742263194</v>
       </c>
       <c r="F186" t="n">
-        <v>-1.157879376431683</v>
+        <v>0.03765378798559369</v>
       </c>
     </row>
     <row r="187">
@@ -4157,19 +4157,19 @@
         <v>45903</v>
       </c>
       <c r="B187" t="n">
-        <v>5.417102083953507</v>
+        <v>-0.3646133164085937</v>
       </c>
       <c r="C187" t="n">
-        <v>0.5135432443992416</v>
+        <v>-0.1028540468709103</v>
       </c>
       <c r="D187" t="n">
-        <v>-1.018602993006294</v>
+        <v>-0.006756475330272244</v>
       </c>
       <c r="E187" t="n">
-        <v>0.7296735449019067</v>
+        <v>-0.003633985591928422</v>
       </c>
       <c r="F187" t="n">
-        <v>-0.05934227818741866</v>
+        <v>-0.001051173839052105</v>
       </c>
     </row>
     <row r="188">
@@ -4177,19 +4177,19 @@
         <v>45904</v>
       </c>
       <c r="B188" t="n">
-        <v>5.108524388820856</v>
+        <v>-0.2667846873523189</v>
       </c>
       <c r="C188" t="n">
-        <v>1.109177508797371</v>
+        <v>-0.02623973743749651</v>
       </c>
       <c r="D188" t="n">
-        <v>1.980691975162719</v>
+        <v>0.03049492969675844</v>
       </c>
       <c r="E188" t="n">
-        <v>-0.01244575670348898</v>
+        <v>-0.05926122391225441</v>
       </c>
       <c r="F188" t="n">
-        <v>1.326060302600105</v>
+        <v>0.002866254583425532</v>
       </c>
     </row>
     <row r="189">
@@ -4197,19 +4197,19 @@
         <v>45905</v>
       </c>
       <c r="B189" t="n">
-        <v>-4.748109455574225</v>
+        <v>-0.007949315478976782</v>
       </c>
       <c r="C189" t="n">
-        <v>-3.041491744750856</v>
+        <v>-0.06409088342714341</v>
       </c>
       <c r="D189" t="n">
-        <v>-2.302303225279144</v>
+        <v>-0.0342332951426317</v>
       </c>
       <c r="E189" t="n">
-        <v>0.6616521946384349</v>
+        <v>-0.01311036290698173</v>
       </c>
       <c r="F189" t="n">
-        <v>0.06241881672022701</v>
+        <v>0.04939200151873915</v>
       </c>
     </row>
     <row r="190">
@@ -4217,19 +4217,19 @@
         <v>45908</v>
       </c>
       <c r="B190" t="n">
-        <v>3.716816994757737</v>
+        <v>-0.2067272808312185</v>
       </c>
       <c r="C190" t="n">
-        <v>1.973142340987607</v>
+        <v>-0.04612157551413396</v>
       </c>
       <c r="D190" t="n">
-        <v>-0.9269754724936075</v>
+        <v>0.02426991120193657</v>
       </c>
       <c r="E190" t="n">
-        <v>-0.01108112356920765</v>
+        <v>0.00596058149674478</v>
       </c>
       <c r="F190" t="n">
-        <v>-1.196583477260425</v>
+        <v>0.02935719539189317</v>
       </c>
     </row>
     <row r="191">
@@ -4237,19 +4237,19 @@
         <v>45909</v>
       </c>
       <c r="B191" t="n">
-        <v>8.76684784597575</v>
+        <v>-0.4024612569384927</v>
       </c>
       <c r="C191" t="n">
-        <v>1.667857298994578</v>
+        <v>-0.0698091281357109</v>
       </c>
       <c r="D191" t="n">
-        <v>0.561707219376401</v>
+        <v>0.04963345101570382</v>
       </c>
       <c r="E191" t="n">
-        <v>0.2185045166635835</v>
+        <v>-0.07138324497485335</v>
       </c>
       <c r="F191" t="n">
-        <v>1.020913831447243</v>
+        <v>0.01772786824997775</v>
       </c>
     </row>
     <row r="192">
@@ -4257,19 +4257,19 @@
         <v>45910</v>
       </c>
       <c r="B192" t="n">
-        <v>0.8728456149897941</v>
+        <v>-0.1581556892515101</v>
       </c>
       <c r="C192" t="n">
-        <v>-1.443749494969399</v>
+        <v>0.01205204756869112</v>
       </c>
       <c r="D192" t="n">
-        <v>-0.8044638005938834</v>
+        <v>-0.05215705481687748</v>
       </c>
       <c r="E192" t="n">
-        <v>-0.04931370289283219</v>
+        <v>0.002825834938311156</v>
       </c>
       <c r="F192" t="n">
-        <v>-0.7257113932872109</v>
+        <v>0.04145847019247492</v>
       </c>
     </row>
     <row r="193">
@@ -4277,19 +4277,19 @@
         <v>45911</v>
       </c>
       <c r="B193" t="n">
-        <v>1.732540460996448</v>
+        <v>-0.2023784934286524</v>
       </c>
       <c r="C193" t="n">
-        <v>0.2429114300950976</v>
+        <v>-0.07141488956152865</v>
       </c>
       <c r="D193" t="n">
-        <v>-1.204680842687488</v>
+        <v>-0.03675391845795156</v>
       </c>
       <c r="E193" t="n">
-        <v>0.4424233651188536</v>
+        <v>0.02014601923465869</v>
       </c>
       <c r="F193" t="n">
-        <v>-1.145113289948819</v>
+        <v>0.01012738605418622</v>
       </c>
     </row>
     <row r="194">
@@ -4297,19 +4297,19 @@
         <v>45912</v>
       </c>
       <c r="B194" t="n">
-        <v>1.469708613335118</v>
+        <v>-0.1993283110325867</v>
       </c>
       <c r="C194" t="n">
-        <v>0.6527558519406996</v>
+        <v>-0.06798719518821505</v>
       </c>
       <c r="D194" t="n">
-        <v>0.3065653748741468</v>
+        <v>-0.02664542525863832</v>
       </c>
       <c r="E194" t="n">
-        <v>-1.240418708173408</v>
+        <v>-0.03766760408956513</v>
       </c>
       <c r="F194" t="n">
-        <v>-0.2354031374123317</v>
+        <v>-0.02697760373440311</v>
       </c>
     </row>
     <row r="195">
@@ -4317,19 +4317,19 @@
         <v>45915</v>
       </c>
       <c r="B195" t="n">
-        <v>1.089320712283038</v>
+        <v>-0.1835862231721446</v>
       </c>
       <c r="C195" t="n">
-        <v>-1.504142692472346</v>
+        <v>-0.007204155014701029</v>
       </c>
       <c r="D195" t="n">
-        <v>0.1815227405022971</v>
+        <v>-0.05966084578073866</v>
       </c>
       <c r="E195" t="n">
-        <v>-0.3589103430846071</v>
+        <v>-0.02143149245065679</v>
       </c>
       <c r="F195" t="n">
-        <v>-0.6544276324604357</v>
+        <v>-0.01152217266755895</v>
       </c>
     </row>
     <row r="196">
@@ -4337,19 +4337,19 @@
         <v>45916</v>
       </c>
       <c r="B196" t="n">
-        <v>2.992709152342205</v>
+        <v>-0.2179660854258138</v>
       </c>
       <c r="C196" t="n">
-        <v>-1.406011624981086</v>
+        <v>0.009813076165761228</v>
       </c>
       <c r="D196" t="n">
-        <v>0.3284719059012566</v>
+        <v>-0.07597662962148644</v>
       </c>
       <c r="E196" t="n">
-        <v>-1.207250645535832</v>
+        <v>-0.02236574071466958</v>
       </c>
       <c r="F196" t="n">
-        <v>-0.5258718669955024</v>
+        <v>-0.01681511582772478</v>
       </c>
     </row>
     <row r="197">
@@ -4357,19 +4357,19 @@
         <v>45917</v>
       </c>
       <c r="B197" t="n">
-        <v>-4.609274151656233</v>
+        <v>0.1194326882841057</v>
       </c>
       <c r="C197" t="n">
-        <v>0.4912682477104122</v>
+        <v>-0.005742777421748055</v>
       </c>
       <c r="D197" t="n">
-        <v>-0.6704204816146417</v>
+        <v>-0.01145538612579643</v>
       </c>
       <c r="E197" t="n">
-        <v>0.02282625999407788</v>
+        <v>0.003897654976808001</v>
       </c>
       <c r="F197" t="n">
-        <v>-0.1863374862500791</v>
+        <v>-0.02248233238798551</v>
       </c>
     </row>
     <row r="198">
@@ -4377,19 +4377,19 @@
         <v>45918</v>
       </c>
       <c r="B198" t="n">
-        <v>4.908844075428929</v>
+        <v>-0.2019651281014698</v>
       </c>
       <c r="C198" t="n">
-        <v>0.8825669723974422</v>
+        <v>0.0181873819920312</v>
       </c>
       <c r="D198" t="n">
-        <v>0.01280937167531429</v>
+        <v>-0.006974522192144517</v>
       </c>
       <c r="E198" t="n">
-        <v>-0.0316530227725707</v>
+        <v>0.0162554486647453</v>
       </c>
       <c r="F198" t="n">
-        <v>0.2576160434411853</v>
+        <v>0.002901198297031208</v>
       </c>
     </row>
     <row r="199">
@@ -4397,19 +4397,19 @@
         <v>45919</v>
       </c>
       <c r="B199" t="n">
-        <v>5.567801147676679</v>
+        <v>-0.2621330482881801</v>
       </c>
       <c r="C199" t="n">
-        <v>1.273959352298097</v>
+        <v>-0.006768500284122881</v>
       </c>
       <c r="D199" t="n">
-        <v>-0.1908975438196495</v>
+        <v>0.01551298228952583</v>
       </c>
       <c r="E199" t="n">
-        <v>1.555051704057524</v>
+        <v>0.04366161463929065</v>
       </c>
       <c r="F199" t="n">
-        <v>-0.4134022406559192</v>
+        <v>-0.02926388736828592</v>
       </c>
     </row>
     <row r="200">
@@ -4417,19 +4417,19 @@
         <v>45922</v>
       </c>
       <c r="B200" t="n">
-        <v>0.9622710526926119</v>
+        <v>-0.1492865119418017</v>
       </c>
       <c r="C200" t="n">
-        <v>1.577081956046363</v>
+        <v>-0.01886033114328752</v>
       </c>
       <c r="D200" t="n">
-        <v>-2.026269075299695</v>
+        <v>-0.007368575709610586</v>
       </c>
       <c r="E200" t="n">
-        <v>-0.813203972495524</v>
+        <v>0.01632944443337024</v>
       </c>
       <c r="F200" t="n">
-        <v>-1.73646179165284</v>
+        <v>0.005152859580247139</v>
       </c>
     </row>
     <row r="201">
@@ -4437,19 +4437,19 @@
         <v>45923</v>
       </c>
       <c r="B201" t="n">
-        <v>-1.41900833932156</v>
+        <v>-0.04414932299484202</v>
       </c>
       <c r="C201" t="n">
-        <v>-1.378980338970176</v>
+        <v>-0.07516823923202276</v>
       </c>
       <c r="D201" t="n">
-        <v>-0.5318465121882661</v>
+        <v>0.01406618772271111</v>
       </c>
       <c r="E201" t="n">
-        <v>-0.3759626495168932</v>
+        <v>-0.02852872470647645</v>
       </c>
       <c r="F201" t="n">
-        <v>0.7162406614531145</v>
+        <v>-0.01756317012684891</v>
       </c>
     </row>
     <row r="202">
@@ -4457,19 +4457,19 @@
         <v>45924</v>
       </c>
       <c r="B202" t="n">
-        <v>11.0512765989542</v>
+        <v>-0.4941451112577341</v>
       </c>
       <c r="C202" t="n">
-        <v>1.602459890881402</v>
+        <v>-0.02501449319152148</v>
       </c>
       <c r="D202" t="n">
-        <v>1.242101917724315</v>
+        <v>-0.001059829500693465</v>
       </c>
       <c r="E202" t="n">
-        <v>0.6092075297889999</v>
+        <v>-0.004423083040885771</v>
       </c>
       <c r="F202" t="n">
-        <v>0.5532739222394708</v>
+        <v>0.01028333702949195</v>
       </c>
     </row>
     <row r="203">
@@ -4477,19 +4477,19 @@
         <v>45925</v>
       </c>
       <c r="B203" t="n">
-        <v>0.7362259429081353</v>
+        <v>-0.1530942749441769</v>
       </c>
       <c r="C203" t="n">
-        <v>1.056148395885945</v>
+        <v>-0.0068316721796274</v>
       </c>
       <c r="D203" t="n">
-        <v>-0.1847125102705054</v>
+        <v>-0.009088972924298468</v>
       </c>
       <c r="E203" t="n">
-        <v>-0.6121922980696102</v>
+        <v>0.01107040732633053</v>
       </c>
       <c r="F203" t="n">
-        <v>-1.308544500835976</v>
+        <v>-0.005640151127046869</v>
       </c>
     </row>
     <row r="204">
@@ -4497,19 +4497,19 @@
         <v>45926</v>
       </c>
       <c r="B204" t="n">
-        <v>4.326577434296061</v>
+        <v>-0.3155635200033899</v>
       </c>
       <c r="C204" t="n">
-        <v>0.5766497406662544</v>
+        <v>-0.03783501044324376</v>
       </c>
       <c r="D204" t="n">
-        <v>-1.142589311881724</v>
+        <v>-0.06379199786076661</v>
       </c>
       <c r="E204" t="n">
-        <v>0.0288317450541009</v>
+        <v>0.05123547359947592</v>
       </c>
       <c r="F204" t="n">
-        <v>-1.730969383981901</v>
+        <v>0.006345832681256971</v>
       </c>
     </row>
     <row r="205">
@@ -4517,19 +4517,19 @@
         <v>45929</v>
       </c>
       <c r="B205" t="n">
-        <v>-0.8449521183629511</v>
+        <v>-0.07435369745446668</v>
       </c>
       <c r="C205" t="n">
-        <v>-1.792836146437534</v>
+        <v>-0.02998426569247355</v>
       </c>
       <c r="D205" t="n">
-        <v>-0.3657451109595272</v>
+        <v>-0.02704620001123909</v>
       </c>
       <c r="E205" t="n">
-        <v>1.450764397078582</v>
+        <v>0.002080756994574183</v>
       </c>
       <c r="F205" t="n">
-        <v>0.5812018244787617</v>
+        <v>0.03216636658845128</v>
       </c>
     </row>
     <row r="206">
@@ -4537,19 +4537,19 @@
         <v>45930</v>
       </c>
       <c r="B206" t="n">
-        <v>4.886039880647311</v>
+        <v>-0.3127129870048886</v>
       </c>
       <c r="C206" t="n">
-        <v>0.6679995147464504</v>
+        <v>-0.05955765246277415</v>
       </c>
       <c r="D206" t="n">
-        <v>-1.489195137555907</v>
+        <v>0.02604463204475158</v>
       </c>
       <c r="E206" t="n">
-        <v>1.477844073315474</v>
+        <v>0.01012205196378218</v>
       </c>
       <c r="F206" t="n">
-        <v>0.0884544960606652</v>
+        <v>0.02613217858380415</v>
       </c>
     </row>
     <row r="207">
@@ -4557,19 +4557,19 @@
         <v>45931</v>
       </c>
       <c r="B207" t="n">
-        <v>2.988471084546784</v>
+        <v>-0.2053494840824015</v>
       </c>
       <c r="C207" t="n">
-        <v>1.613760429534267</v>
+        <v>-0.07736315244395589</v>
       </c>
       <c r="D207" t="n">
-        <v>-1.457189907645314</v>
+        <v>0.05073373973978611</v>
       </c>
       <c r="E207" t="n">
-        <v>0.2537214403761722</v>
+        <v>-0.02336595055327263</v>
       </c>
       <c r="F207" t="n">
-        <v>-0.05415357608703486</v>
+        <v>0.008720449650018518</v>
       </c>
     </row>
     <row r="208">
@@ -4577,19 +4577,19 @@
         <v>45932</v>
       </c>
       <c r="B208" t="n">
-        <v>3.104003412433172</v>
+        <v>-0.2588621384485807</v>
       </c>
       <c r="C208" t="n">
-        <v>1.126253385235213</v>
+        <v>-0.04156970916999359</v>
       </c>
       <c r="D208" t="n">
-        <v>-2.095010809154773</v>
+        <v>0.02518606079364929</v>
       </c>
       <c r="E208" t="n">
-        <v>-0.3242138988483541</v>
+        <v>0.02103825262828674</v>
       </c>
       <c r="F208" t="n">
-        <v>-1.453011831146618</v>
+        <v>0.01280064033021065</v>
       </c>
     </row>
     <row r="209">
@@ -4597,19 +4597,19 @@
         <v>45933</v>
       </c>
       <c r="B209" t="n">
-        <v>3.370879627725478</v>
+        <v>-0.09416446102114821</v>
       </c>
       <c r="C209" t="n">
-        <v>0.7057770919065839</v>
+        <v>0.09717072672427476</v>
       </c>
       <c r="D209" t="n">
-        <v>1.991829188646545</v>
+        <v>0.09808151202868644</v>
       </c>
       <c r="E209" t="n">
-        <v>1.156301264009021</v>
+        <v>-0.01294264798178702</v>
       </c>
       <c r="F209" t="n">
-        <v>1.754497227657834</v>
+        <v>0.03241936582270278</v>
       </c>
     </row>
     <row r="210">
@@ -4617,19 +4617,19 @@
         <v>45936</v>
       </c>
       <c r="B210" t="n">
-        <v>3.196240509082936</v>
+        <v>-0.214718463444179</v>
       </c>
       <c r="C210" t="n">
-        <v>1.242011500247174</v>
+        <v>-0.03107495747883686</v>
       </c>
       <c r="D210" t="n">
-        <v>-0.6350305492434661</v>
+        <v>0.05314426979510874</v>
       </c>
       <c r="E210" t="n">
-        <v>0.3664432677847068</v>
+        <v>0.003999942047202877</v>
       </c>
       <c r="F210" t="n">
-        <v>-0.2558868356783385</v>
+        <v>-0.004488318349323325</v>
       </c>
     </row>
     <row r="211">
@@ -4637,19 +4637,19 @@
         <v>45937</v>
       </c>
       <c r="B211" t="n">
-        <v>3.638994954024823</v>
+        <v>-0.207048229659546</v>
       </c>
       <c r="C211" t="n">
-        <v>2.369827743294339</v>
+        <v>-0.02117138194921553</v>
       </c>
       <c r="D211" t="n">
-        <v>-1.284145504349046</v>
+        <v>0.07547595734609008</v>
       </c>
       <c r="E211" t="n">
-        <v>-0.705095402521815</v>
+        <v>0.005463140665219917</v>
       </c>
       <c r="F211" t="n">
-        <v>0.1911167515352796</v>
+        <v>0.0002577046804691276</v>
       </c>
     </row>
     <row r="212">
@@ -4657,19 +4657,19 @@
         <v>45938</v>
       </c>
       <c r="B212" t="n">
-        <v>3.930625717250782</v>
+        <v>-0.2392137047286522</v>
       </c>
       <c r="C212" t="n">
-        <v>0.5591095711983443</v>
+        <v>0.003411375609513231</v>
       </c>
       <c r="D212" t="n">
-        <v>-0.8334429973326576</v>
+        <v>0.04682319091940956</v>
       </c>
       <c r="E212" t="n">
-        <v>-0.8454066796056776</v>
+        <v>-0.01855143880741399</v>
       </c>
       <c r="F212" t="n">
-        <v>-0.2607368610280176</v>
+        <v>0.003488624113478305</v>
       </c>
     </row>
     <row r="213">
@@ -4677,19 +4677,19 @@
         <v>45939</v>
       </c>
       <c r="B213" t="n">
-        <v>-0.02741992539971154</v>
+        <v>-0.1180402826823772</v>
       </c>
       <c r="C213" t="n">
-        <v>1.205080364027252</v>
+        <v>-0.04154475055671886</v>
       </c>
       <c r="D213" t="n">
-        <v>0.001565940916205033</v>
+        <v>0.02297775207029476</v>
       </c>
       <c r="E213" t="n">
-        <v>-0.3031407216640701</v>
+        <v>-0.01926480414605005</v>
       </c>
       <c r="F213" t="n">
-        <v>-1.027576041164678</v>
+        <v>-0.04195508244414203</v>
       </c>
     </row>
     <row r="214">
@@ -4697,19 +4697,19 @@
         <v>45940</v>
       </c>
       <c r="B214" t="n">
-        <v>-5.131804971052766</v>
+        <v>0.04733108697251027</v>
       </c>
       <c r="C214" t="n">
-        <v>0.6017067243866256</v>
+        <v>-0.06932490148329037</v>
       </c>
       <c r="D214" t="n">
-        <v>-1.648716164700685</v>
+        <v>-0.001841203587977887</v>
       </c>
       <c r="E214" t="n">
-        <v>-0.2385123346250629</v>
+        <v>0.006605544125913061</v>
       </c>
       <c r="F214" t="n">
-        <v>-1.124282308281258</v>
+        <v>-0.01697610404937466</v>
       </c>
     </row>
     <row r="215">
@@ -4717,19 +4717,19 @@
         <v>45943</v>
       </c>
       <c r="B215" t="n">
-        <v>3.728966559256195</v>
+        <v>-0.2404708261425824</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.8351922143369548</v>
+        <v>-0.04373825744306721</v>
       </c>
       <c r="D215" t="n">
-        <v>-0.1155102541075624</v>
+        <v>-0.05921612851115015</v>
       </c>
       <c r="E215" t="n">
-        <v>-0.5412188435380256</v>
+        <v>-0.01062712417785425</v>
       </c>
       <c r="F215" t="n">
-        <v>-0.673718278557767</v>
+        <v>-0.02198758853801728</v>
       </c>
     </row>
     <row r="216">
@@ -4737,19 +4737,19 @@
         <v>45944</v>
       </c>
       <c r="B216" t="n">
-        <v>-1.000299505903742</v>
+        <v>-0.01949542452847295</v>
       </c>
       <c r="C216" t="n">
-        <v>1.484773658133782</v>
+        <v>-0.04552165921263376</v>
       </c>
       <c r="D216" t="n">
-        <v>-0.03270007329108156</v>
+        <v>-0.02818375561364621</v>
       </c>
       <c r="E216" t="n">
-        <v>0.488425770163901</v>
+        <v>0.03985039588085771</v>
       </c>
       <c r="F216" t="n">
-        <v>-0.9616045785581439</v>
+        <v>-0.0467121466295058</v>
       </c>
     </row>
     <row r="217">
@@ -4757,19 +4757,19 @@
         <v>45945</v>
       </c>
       <c r="B217" t="n">
-        <v>-3.659915325120792</v>
+        <v>0.1211289791604526</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.833893430491375</v>
+        <v>-0.05118304264792459</v>
       </c>
       <c r="D217" t="n">
-        <v>0.6869409526726642</v>
+        <v>-0.02708505516682532</v>
       </c>
       <c r="E217" t="n">
-        <v>-0.6689860063183732</v>
+        <v>-0.01158403925848488</v>
       </c>
       <c r="F217" t="n">
-        <v>0.2127768992641437</v>
+        <v>-0.03842812120586993</v>
       </c>
     </row>
     <row r="218">
@@ -4777,19 +4777,19 @@
         <v>45946</v>
       </c>
       <c r="B218" t="n">
-        <v>-2.713546783891437</v>
+        <v>0.1585467567281258</v>
       </c>
       <c r="C218" t="n">
-        <v>1.201467721256519</v>
+        <v>-0.04815705038079494</v>
       </c>
       <c r="D218" t="n">
-        <v>0.1206162955412523</v>
+        <v>0.05876980292317108</v>
       </c>
       <c r="E218" t="n">
-        <v>-0.4773673096872775</v>
+        <v>-0.04267469369984704</v>
       </c>
       <c r="F218" t="n">
-        <v>0.5435902852015002</v>
+        <v>-0.02496506489253466</v>
       </c>
     </row>
     <row r="219">
@@ -4797,19 +4797,19 @@
         <v>45947</v>
       </c>
       <c r="B219" t="n">
-        <v>-0.284450777415736</v>
+        <v>-0.003397723397727973</v>
       </c>
       <c r="C219" t="n">
-        <v>-1.952346277953026</v>
+        <v>0.007347905512214883</v>
       </c>
       <c r="D219" t="n">
-        <v>0.1920331180126925</v>
+        <v>-0.02825740657790294</v>
       </c>
       <c r="E219" t="n">
-        <v>-0.1931069151602737</v>
+        <v>0.01307325644289035</v>
       </c>
       <c r="F219" t="n">
-        <v>-0.2281582574778526</v>
+        <v>-0.02729885407427911</v>
       </c>
     </row>
     <row r="220">
@@ -4817,19 +4817,19 @@
         <v>45950</v>
       </c>
       <c r="B220" t="n">
-        <v>1.609877277578335</v>
+        <v>-0.05107161727361834</v>
       </c>
       <c r="C220" t="n">
-        <v>-1.663865221755886</v>
+        <v>-0.0004571181629999543</v>
       </c>
       <c r="D220" t="n">
-        <v>0.6736287355622694</v>
+        <v>-0.04955236955906522</v>
       </c>
       <c r="E220" t="n">
-        <v>-1.193889326923375</v>
+        <v>-0.03014412023591893</v>
       </c>
       <c r="F220" t="n">
-        <v>0.1158719259022615</v>
+        <v>-0.02356126551083323</v>
       </c>
     </row>
     <row r="221">
@@ -4837,19 +4837,19 @@
         <v>45951</v>
       </c>
       <c r="B221" t="n">
-        <v>1.849317727983196</v>
+        <v>-0.04165383183316496</v>
       </c>
       <c r="C221" t="n">
-        <v>0.01778495673119693</v>
+        <v>-0.01528112801907996</v>
       </c>
       <c r="D221" t="n">
-        <v>0.2275749979891864</v>
+        <v>-0.004957274994805236</v>
       </c>
       <c r="E221" t="n">
-        <v>0.7150104557062322</v>
+        <v>0.02465218318319129</v>
       </c>
       <c r="F221" t="n">
-        <v>0.1372389908833435</v>
+        <v>-0.0195550375728627</v>
       </c>
     </row>
     <row r="222">
@@ -4857,19 +4857,19 @@
         <v>45952</v>
       </c>
       <c r="B222" t="n">
-        <v>-1.000780414999209</v>
+        <v>0.00551132296097021</v>
       </c>
       <c r="C222" t="n">
-        <v>0.439306568492405</v>
+        <v>-0.01379461256087052</v>
       </c>
       <c r="D222" t="n">
-        <v>0.2656206017244826</v>
+        <v>-0.04399598045797377</v>
       </c>
       <c r="E222" t="n">
-        <v>-0.4850691397025387</v>
+        <v>0.005843283996158296</v>
       </c>
       <c r="F222" t="n">
-        <v>-1.083678791993642</v>
+        <v>-0.03939076461554049</v>
       </c>
     </row>
     <row r="223">
@@ -4877,19 +4877,19 @@
         <v>45953</v>
       </c>
       <c r="B223" t="n">
-        <v>1.676208576146675</v>
+        <v>-0.1540253077069443</v>
       </c>
       <c r="C223" t="n">
-        <v>-1.770458325417522</v>
+        <v>-0.002664132845247072</v>
       </c>
       <c r="D223" t="n">
-        <v>-1.35230010693924</v>
+        <v>-0.07786148514447376</v>
       </c>
       <c r="E223" t="n">
-        <v>-0.1306448193838316</v>
+        <v>0.005378613054339832</v>
       </c>
       <c r="F223" t="n">
-        <v>-0.5120978148491807</v>
+        <v>0.01914402613529755</v>
       </c>
     </row>
     <row r="224">
@@ -4897,19 +4897,19 @@
         <v>45954</v>
       </c>
       <c r="B224" t="n">
-        <v>3.321138608992827</v>
+        <v>-0.2797734359793893</v>
       </c>
       <c r="C224" t="n">
-        <v>-1.251768041101863</v>
+        <v>-0.07328320115665252</v>
       </c>
       <c r="D224" t="n">
-        <v>-2.475075258448518</v>
+        <v>-0.05622244495659974</v>
       </c>
       <c r="E224" t="n">
-        <v>-0.5792536386926525</v>
+        <v>0.009262097033663883</v>
       </c>
       <c r="F224" t="n">
-        <v>-0.5130932476732035</v>
+        <v>-0.0006741931281352705</v>
       </c>
     </row>
     <row r="225">
@@ -4917,19 +4917,19 @@
         <v>45957</v>
       </c>
       <c r="B225" t="n">
-        <v>-1.73291650174577</v>
+        <v>-0.06031030579055199</v>
       </c>
       <c r="C225" t="n">
-        <v>-2.6667636825924</v>
+        <v>-0.04165160178403479</v>
       </c>
       <c r="D225" t="n">
-        <v>-1.968004291103354</v>
+        <v>-0.0535783028660901</v>
       </c>
       <c r="E225" t="n">
-        <v>0.712123779206962</v>
+        <v>0.01039096281694093</v>
       </c>
       <c r="F225" t="n">
-        <v>-0.002525840304976246</v>
+        <v>0.03938973932723161</v>
       </c>
     </row>
     <row r="226">
@@ -4937,19 +4937,19 @@
         <v>45958</v>
       </c>
       <c r="B226" t="n">
-        <v>5.549085036140089</v>
+        <v>-0.2387569924391744</v>
       </c>
       <c r="C226" t="n">
-        <v>1.7789565150425</v>
+        <v>-0.0375137130760428</v>
       </c>
       <c r="D226" t="n">
-        <v>1.400246114360035</v>
+        <v>-0.01415616497360834</v>
       </c>
       <c r="E226" t="n">
-        <v>0.4072146705396058</v>
+        <v>-0.0008474240983110612</v>
       </c>
       <c r="F226" t="n">
-        <v>-0.0005628849211503529</v>
+        <v>-0.01496297981305328</v>
       </c>
     </row>
     <row r="227">
@@ -4957,19 +4957,19 @@
         <v>45959</v>
       </c>
       <c r="B227" t="n">
-        <v>3.180627803702885</v>
+        <v>-0.207349189834831</v>
       </c>
       <c r="C227" t="n">
-        <v>-0.2135418922414128</v>
+        <v>-0.02299604241579692</v>
       </c>
       <c r="D227" t="n">
-        <v>-0.1465559945284717</v>
+        <v>-0.01188440677336121</v>
       </c>
       <c r="E227" t="n">
-        <v>-0.8879991604227858</v>
+        <v>-0.01839858976632158</v>
       </c>
       <c r="F227" t="n">
-        <v>0.8320738442465379</v>
+        <v>0.02112441468172905</v>
       </c>
     </row>
     <row r="228">
@@ -4977,19 +4977,19 @@
         <v>45960</v>
       </c>
       <c r="B228" t="n">
-        <v>7.823989228847082</v>
+        <v>-0.4094376152682719</v>
       </c>
       <c r="C228" t="n">
-        <v>-2.435835099986408</v>
+        <v>0.02095086944118166</v>
       </c>
       <c r="D228" t="n">
-        <v>1.092176999276155</v>
+        <v>-0.05051554305304311</v>
       </c>
       <c r="E228" t="n">
-        <v>0.463132920530421</v>
+        <v>-0.00126465001339277</v>
       </c>
       <c r="F228" t="n">
-        <v>1.033013528735853</v>
+        <v>0.03129077740484664</v>
       </c>
     </row>
     <row r="229">
@@ -4997,19 +4997,19 @@
         <v>45961</v>
       </c>
       <c r="B229" t="n">
-        <v>5.836859938669091</v>
+        <v>-0.3317842320012797</v>
       </c>
       <c r="C229" t="n">
-        <v>0.3514267700035409</v>
+        <v>-0.04052752879279784</v>
       </c>
       <c r="D229" t="n">
-        <v>0.6060407711489222</v>
+        <v>-0.03582894634243218</v>
       </c>
       <c r="E229" t="n">
-        <v>-0.2100558836702329</v>
+        <v>-0.02170577431342538</v>
       </c>
       <c r="F229" t="n">
-        <v>0.2963497142910045</v>
+        <v>0.004581514967804686</v>
       </c>
     </row>
     <row r="230">
@@ -5017,19 +5017,19 @@
         <v>45964</v>
       </c>
       <c r="B230" t="n">
-        <v>3.43315070150887</v>
+        <v>-0.3466155226505833</v>
       </c>
       <c r="C230" t="n">
-        <v>-1.498745384536905</v>
+        <v>-0.05542859389633319</v>
       </c>
       <c r="D230" t="n">
-        <v>-1.607103741078189</v>
+        <v>-0.003092290518939739</v>
       </c>
       <c r="E230" t="n">
-        <v>-0.7882511600902211</v>
+        <v>-0.01345354363764923</v>
       </c>
       <c r="F230" t="n">
-        <v>0.1030955284610563</v>
+        <v>0.0004053201098304595</v>
       </c>
     </row>
     <row r="231">
@@ -5037,19 +5037,19 @@
         <v>45965</v>
       </c>
       <c r="B231" t="n">
-        <v>7.270013278461952</v>
+        <v>-0.3909710268861553</v>
       </c>
       <c r="C231" t="n">
-        <v>-0.09480820724625404</v>
+        <v>0.09320472971952819</v>
       </c>
       <c r="D231" t="n">
-        <v>2.109060038893799</v>
+        <v>-0.04520479162715614</v>
       </c>
       <c r="E231" t="n">
-        <v>0.3255546648037266</v>
+        <v>0.02687973887799468</v>
       </c>
       <c r="F231" t="n">
-        <v>-0.3363571012543239</v>
+        <v>-0.00882364215775178</v>
       </c>
     </row>
     <row r="232">
@@ -5057,19 +5057,19 @@
         <v>45966</v>
       </c>
       <c r="B232" t="n">
-        <v>1.308442695986503</v>
+        <v>-0.2230011270509072</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.8117668967613567</v>
+        <v>0.05215087517146702</v>
       </c>
       <c r="D232" t="n">
-        <v>2.330218908590123</v>
+        <v>-0.1247804541807555</v>
       </c>
       <c r="E232" t="n">
-        <v>0.06277808998247361</v>
+        <v>0.005250495718043218</v>
       </c>
       <c r="F232" t="n">
-        <v>-0.4798554193395904</v>
+        <v>-0.02719745577746206</v>
       </c>
     </row>
     <row r="233">
@@ -5077,19 +5077,19 @@
         <v>45967</v>
       </c>
       <c r="B233" t="n">
-        <v>4.051298472608657</v>
+        <v>-0.2455543835147191</v>
       </c>
       <c r="C233" t="n">
-        <v>-0.7065771745023844</v>
+        <v>0.04968857049424655</v>
       </c>
       <c r="D233" t="n">
-        <v>1.172725275829332</v>
+        <v>-0.05434514443345093</v>
       </c>
       <c r="E233" t="n">
-        <v>1.308233986022669</v>
+        <v>0.02228958110177498</v>
       </c>
       <c r="F233" t="n">
-        <v>0.3226651658850571</v>
+        <v>0.0006854669013116186</v>
       </c>
     </row>
     <row r="234">
@@ -5097,19 +5097,19 @@
         <v>45968</v>
       </c>
       <c r="B234" t="n">
-        <v>2.416840025287019</v>
+        <v>-0.1872841219627767</v>
       </c>
       <c r="C234" t="n">
-        <v>0.04360283912595149</v>
+        <v>0.005729677845787014</v>
       </c>
       <c r="D234" t="n">
-        <v>1.492433387685008</v>
+        <v>-0.06229911787582421</v>
       </c>
       <c r="E234" t="n">
-        <v>0.2284369327664718</v>
+        <v>-0.005452074335971241</v>
       </c>
       <c r="F234" t="n">
-        <v>0.1044487573897326</v>
+        <v>-0.03378166593243848</v>
       </c>
     </row>
     <row r="235">
@@ -5117,19 +5117,19 @@
         <v>45971</v>
       </c>
       <c r="B235" t="n">
-        <v>1.948384557771417</v>
+        <v>-0.1487595383565499</v>
       </c>
       <c r="C235" t="n">
-        <v>-2.213887046739577</v>
+        <v>0.0373363850488529</v>
       </c>
       <c r="D235" t="n">
-        <v>0.3329740953539406</v>
+        <v>-0.02793009691422082</v>
       </c>
       <c r="E235" t="n">
-        <v>0.9013172518582622</v>
+        <v>-0.01083881180592373</v>
       </c>
       <c r="F235" t="n">
-        <v>1.317830021023187</v>
+        <v>0.006655041955312463</v>
       </c>
     </row>
     <row r="236">
@@ -5137,19 +5137,19 @@
         <v>45972</v>
       </c>
       <c r="B236" t="n">
-        <v>-1.709864556998218</v>
+        <v>-0.04047761743818878</v>
       </c>
       <c r="C236" t="n">
-        <v>-2.601108626565366</v>
+        <v>0.02459731587774883</v>
       </c>
       <c r="D236" t="n">
-        <v>-0.2197011639706711</v>
+        <v>-0.09693909015129096</v>
       </c>
       <c r="E236" t="n">
-        <v>0.002438073825550724</v>
+        <v>0.004853216250386336</v>
       </c>
       <c r="F236" t="n">
-        <v>-0.421292782056794</v>
+        <v>0.01025404121639807</v>
       </c>
     </row>
     <row r="237">
@@ -5157,19 +5157,19 @@
         <v>45973</v>
       </c>
       <c r="B237" t="n">
-        <v>3.265378975845286</v>
+        <v>-0.1635495720455494</v>
       </c>
       <c r="C237" t="n">
-        <v>0.8725816899818639</v>
+        <v>0.04132331548930178</v>
       </c>
       <c r="D237" t="n">
-        <v>1.415146820495347</v>
+        <v>-0.07280611177357453</v>
       </c>
       <c r="E237" t="n">
-        <v>-1.149717324916672</v>
+        <v>-0.01253972701334316</v>
       </c>
       <c r="F237" t="n">
-        <v>-0.7860078962725336</v>
+        <v>-0.01722705236551956</v>
       </c>
     </row>
     <row r="238">
@@ -5177,19 +5177,19 @@
         <v>45974</v>
       </c>
       <c r="B238" t="n">
-        <v>-2.443912347038425</v>
+        <v>0.07298764712649584</v>
       </c>
       <c r="C238" t="n">
-        <v>-0.03971241476376837</v>
+        <v>0.03103195569106388</v>
       </c>
       <c r="D238" t="n">
-        <v>-0.1072570755382389</v>
+        <v>-0.004022435434532981</v>
       </c>
       <c r="E238" t="n">
-        <v>0.06917868759142985</v>
+        <v>-0.01909805822926478</v>
       </c>
       <c r="F238" t="n">
-        <v>-0.04615885049669124</v>
+        <v>0.007762743578161553</v>
       </c>
     </row>
     <row r="239">
@@ -5197,19 +5197,19 @@
         <v>45975</v>
       </c>
       <c r="B239" t="n">
-        <v>-1.563809605014748</v>
+        <v>0.07680676590881344</v>
       </c>
       <c r="C239" t="n">
-        <v>0.9309495850062272</v>
+        <v>-0.01654074736450022</v>
       </c>
       <c r="D239" t="n">
-        <v>1.101304783555278</v>
+        <v>-0.02482770392966888</v>
       </c>
       <c r="E239" t="n">
-        <v>0.2460724283920808</v>
+        <v>-0.003468677387670745</v>
       </c>
       <c r="F239" t="n">
-        <v>0.07688777573851716</v>
+        <v>-0.03185463225690607</v>
       </c>
     </row>
     <row r="240">
@@ -5217,19 +5217,19 @@
         <v>45978</v>
       </c>
       <c r="B240" t="n">
-        <v>1.843483591206507</v>
+        <v>-0.04170936343949316</v>
       </c>
       <c r="C240" t="n">
-        <v>1.56364249687566</v>
+        <v>-0.02852427860706288</v>
       </c>
       <c r="D240" t="n">
-        <v>1.075238812403748</v>
+        <v>-0.02499586258688722</v>
       </c>
       <c r="E240" t="n">
-        <v>-0.7033328407315363</v>
+        <v>-0.05529199555367367</v>
       </c>
       <c r="F240" t="n">
-        <v>-0.202357892973145</v>
+        <v>-0.02437889361112707</v>
       </c>
     </row>
     <row r="241">
@@ -5237,19 +5237,19 @@
         <v>45979</v>
       </c>
       <c r="B241" t="n">
-        <v>3.027538313652547</v>
+        <v>-0.143430327010257</v>
       </c>
       <c r="C241" t="n">
-        <v>0.02819482373023596</v>
+        <v>-0.07131046560976689</v>
       </c>
       <c r="D241" t="n">
-        <v>-0.5645669262965926</v>
+        <v>-0.02421641203505261</v>
       </c>
       <c r="E241" t="n">
-        <v>1.155546540602589</v>
+        <v>0.002534751905343849</v>
       </c>
       <c r="F241" t="n">
-        <v>-0.2345270345941302</v>
+        <v>-0.03219884400088292</v>
       </c>
     </row>
     <row r="242">
@@ -5257,19 +5257,19 @@
         <v>45980</v>
       </c>
       <c r="B242" t="n">
-        <v>6.872611515165445</v>
+        <v>-0.2287794128571413</v>
       </c>
       <c r="C242" t="n">
-        <v>-0.0001773687675752811</v>
+        <v>0.07724438493512532</v>
       </c>
       <c r="D242" t="n">
-        <v>1.769140859890703</v>
+        <v>0.0326151509098222</v>
       </c>
       <c r="E242" t="n">
-        <v>0.5974327770504231</v>
+        <v>-0.02695944301325968</v>
       </c>
       <c r="F242" t="n">
-        <v>0.7207041990984541</v>
+        <v>-0.02706368314483439</v>
       </c>
     </row>
     <row r="243">
@@ -5277,19 +5277,19 @@
         <v>45982</v>
       </c>
       <c r="B243" t="n">
-        <v>-2.117608017228803</v>
+        <v>-0.0133135174521691</v>
       </c>
       <c r="C243" t="n">
-        <v>0.8437594739726054</v>
+        <v>-0.08082427157183082</v>
       </c>
       <c r="D243" t="n">
-        <v>-0.06076207656771276</v>
+        <v>-0.003768929622338671</v>
       </c>
       <c r="E243" t="n">
-        <v>-0.7030597760141953</v>
+        <v>-0.03865776012284364</v>
       </c>
       <c r="F243" t="n">
-        <v>-0.3854477602073757</v>
+        <v>-0.05692959813796977</v>
       </c>
     </row>
     <row r="244">
@@ -5297,19 +5297,19 @@
         <v>45985</v>
       </c>
       <c r="B244" t="n">
-        <v>4.288994296934245</v>
+        <v>-0.2606018007689596</v>
       </c>
       <c r="C244" t="n">
-        <v>-1.691477309986898</v>
+        <v>0.01743081179671138</v>
       </c>
       <c r="D244" t="n">
-        <v>-0.05876364092194484</v>
+        <v>-0.02962228099340954</v>
       </c>
       <c r="E244" t="n">
-        <v>-0.7766970082436506</v>
+        <v>-0.02811695998144554</v>
       </c>
       <c r="F244" t="n">
-        <v>0.3171627697469253</v>
+        <v>-0.005380671976788909</v>
       </c>
     </row>
     <row r="245">
@@ -5317,19 +5317,19 @@
         <v>45986</v>
       </c>
       <c r="B245" t="n">
-        <v>-1.141839571348519</v>
+        <v>-0.1045848674549458</v>
       </c>
       <c r="C245" t="n">
-        <v>0.5030801908633208</v>
+        <v>-0.05441782872951892</v>
       </c>
       <c r="D245" t="n">
-        <v>-0.9602063157552583</v>
+        <v>-0.004863804139306656</v>
       </c>
       <c r="E245" t="n">
-        <v>-0.6569156728683503</v>
+        <v>-0.02631921343693312</v>
       </c>
       <c r="F245" t="n">
-        <v>-1.145806923188427</v>
+        <v>-0.03975613488420423</v>
       </c>
     </row>
     <row r="246">
@@ -5337,19 +5337,19 @@
         <v>45987</v>
       </c>
       <c r="B246" t="n">
-        <v>3.433741458292041</v>
+        <v>-0.1682912588440969</v>
       </c>
       <c r="C246" t="n">
-        <v>0.4509597245219032</v>
+        <v>-0.001804982847088023</v>
       </c>
       <c r="D246" t="n">
-        <v>0.4685240418669199</v>
+        <v>0.0430175652354156</v>
       </c>
       <c r="E246" t="n">
-        <v>-0.3694632449001294</v>
+        <v>-0.07922700130523899</v>
       </c>
       <c r="F246" t="n">
-        <v>0.8389870908978999</v>
+        <v>-0.01169565593501704</v>
       </c>
     </row>
     <row r="247">
@@ -5357,19 +5357,19 @@
         <v>45988</v>
       </c>
       <c r="B247" t="n">
-        <v>11.78332167847231</v>
+        <v>-0.5578121145619934</v>
       </c>
       <c r="C247" t="n">
-        <v>2.773310329990914</v>
+        <v>-0.06291710449587014</v>
       </c>
       <c r="D247" t="n">
-        <v>-0.6374017990218658</v>
+        <v>0.02767189174769957</v>
       </c>
       <c r="E247" t="n">
-        <v>0.6200927027004166</v>
+        <v>0.02833959874950652</v>
       </c>
       <c r="F247" t="n">
-        <v>-0.9239767973087158</v>
+        <v>-0.01697018617061786</v>
       </c>
     </row>
     <row r="248">
@@ -5377,19 +5377,19 @@
         <v>45989</v>
       </c>
       <c r="B248" t="n">
-        <v>2.425987369426313</v>
+        <v>-0.2557828600675879</v>
       </c>
       <c r="C248" t="n">
-        <v>-0.8036811466993671</v>
+        <v>-0.002252027378014043</v>
       </c>
       <c r="D248" t="n">
-        <v>0.2532200936832126</v>
+        <v>-0.07710278005793041</v>
       </c>
       <c r="E248" t="n">
-        <v>0.05186050069462349</v>
+        <v>0.003514415917503098</v>
       </c>
       <c r="F248" t="n">
-        <v>-0.8167994916655976</v>
+        <v>-0.004975906100685956</v>
       </c>
     </row>
   </sheetData>
